--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -1326,7 +1326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="7" min="1" max="1"/>
@@ -4414,6 +4414,86 @@
       <c r="J66" s="16" t="inlineStr">
         <is>
           <t>[Auto-added from Paperclip 04/15]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>T-315</t>
+        </is>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>Paperclip</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>CEO: Document session progress and update Excel tracker</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E67" s="16" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G67" s="16" t="n"/>
+      <c r="H67" s="16" t="n"/>
+      <c r="I67" s="16" t="n"/>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>[Auto-added from Paperclip 04/15]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>T-316</t>
+        </is>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>Paperclip</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="inlineStr">
+        <is>
+          <t>CEO: Morning check-in 2026-04-16 — catch-up sprint begins</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E68" s="16" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="F68" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G68" s="16" t="n"/>
+      <c r="H68" s="16" t="n"/>
+      <c r="I68" s="16" t="n"/>
+      <c r="J68" s="16" t="inlineStr">
+        <is>
+          <t>[Auto-added from Paperclip 04/16]</t>
         </is>
       </c>
     </row>
@@ -4936,7 +5016,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>PAPERCLIP STATUS — 2026-04-15 17:24</t>
+          <t>PAPERCLIP STATUS — 2026-04-16 16:48</t>
         </is>
       </c>
     </row>
@@ -4985,7 +5065,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>idle</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
@@ -5391,7 +5471,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -5428,7 +5508,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26">
@@ -5456,7 +5536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="7" min="1" max="1"/>
@@ -5470,7 +5550,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>RUN HISTORY (Last 24h) — 2026-04-15 17:24</t>
+          <t>RUN HISTORY (Last 24h) — 2026-04-16 16:48</t>
         </is>
       </c>
     </row>
@@ -5507,610 +5587,534 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
-        <is>
-          <t>Quota exceeded. Check your plan and billing details.</t>
-        </is>
-      </c>
-      <c r="E4" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:20:39</t>
-        </is>
-      </c>
-      <c r="F4" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:20:46</t>
+      <c r="D4" s="24" t="inlineStr"/>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:43:47</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:43:58</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t>Quota exceeded. Check your plan and billing details.</t>
-        </is>
-      </c>
-      <c r="E5" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:15:24</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:15:32</t>
+      <c r="D5" s="24" t="inlineStr"/>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:38:17</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:38:36</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>unknown variant `api-key`, expected one of `apikey`, `chatgpt`, `chatgptAuthTokens` at line 2 column 24</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:10:09</t>
-        </is>
-      </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:10:09</t>
+      <c r="D6" s="24" t="inlineStr"/>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:32:47</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:32:58</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>{"type":"error","status":400,"error":{"type":"invalid_request_error","message":"The 'gpt-4o-mini' model is not supported when using Codex with a ChatGPT account."}}</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:04:54</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:04:57</t>
+      <c r="D7" s="24" t="inlineStr"/>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:27:17</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:27:25</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>{"type":"error","status":400,"error":{"type":"invalid_request_error","message":"The 'gpt-4o-mini' model is not supported when using Codex with a ChatGPT account."}}</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:59:39</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:59:41</t>
+      <c r="D8" s="24" t="inlineStr"/>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:21:47</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:22:05</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>{"type":"error","status":400,"error":{"type":"invalid_request_error","message":"The 'gpt-oss:20b' model is not supported when using Codex with a ChatGPT account."}}</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:54:24</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:54:30</t>
+      <c r="D9" s="24" t="inlineStr"/>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:16:17</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:16:42</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>{"type":"error","status":400,"error":{"type":"invalid_request_error","message":"The 'gpt-oss:20b' model is not supported when using Codex with a ChatGPT account."}}</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:49:09</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:49:13</t>
+      <c r="D10" s="24" t="inlineStr"/>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:10:47</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:10:58</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>{"type":"error","status":400,"error":{"type":"invalid_request_error","message":"The 'gpt-oss:20b' model is not supported when using Codex with a ChatGPT account."}}</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:43:54</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:43:58</t>
+      <c r="D11" s="24" t="inlineStr"/>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:05:17</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:05:45</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>{"type":"error","status":400,"error":{"type":"invalid_request_error","message":"The 'gpt-oss:20b' model is not supported when using Codex with a ChatGPT account."}}</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:38:39</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:38:45</t>
+      <c r="D12" s="24" t="inlineStr"/>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:59:47</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:59:56</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>Not inside a trusted directory and --skip-git-repo-check was not specified.</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:33:24</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:33:24</t>
+      <c r="D13" s="24" t="inlineStr"/>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:54:17</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:54:38</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>Not inside a trusted directory and --skip-git-repo-check was not specified.</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:28:09</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:28:09</t>
+      <c r="D14" s="24" t="inlineStr"/>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:48:47</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:48:52</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>Not inside a trusted directory and --skip-git-repo-check was not specified.</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:22:54</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:22:54</t>
+      <c r="D15" s="24" t="inlineStr"/>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:43:17</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:43:41</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>Not inside a trusted directory and --skip-git-repo-check was not specified.</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:17:39</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:17:39</t>
+      <c r="D16" s="24" t="inlineStr"/>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:37:47</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:38:01</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>Not inside a trusted directory and --skip-git-repo-check was not specified.</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:12:24</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:12:24</t>
+      <c r="D17" s="24" t="inlineStr"/>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:32:17</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:32:41</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>Not inside a trusted directory and --skip-git-repo-check was not specified.</t>
-        </is>
-      </c>
-      <c r="E18" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:07:09</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:07:09</t>
+      <c r="D18" s="24" t="inlineStr"/>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:26:47</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:27:04</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
-        <is>
-          <t>Not inside a trusted directory and --skip-git-repo-check was not specified.</t>
-        </is>
-      </c>
-      <c r="E19" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:02:00</t>
-        </is>
-      </c>
-      <c r="F19" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:02:00</t>
+      <c r="D19" s="24" t="inlineStr"/>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:21:17</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:21:40</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>Not inside a trusted directory and --skip-git-repo-check was not specified.</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:00:09</t>
-        </is>
-      </c>
-      <c r="F20" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:00:09</t>
+      <c r="D20" s="24" t="inlineStr"/>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:15:47</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:16:00</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
-        <is>
-          <t>Not inside a trusted directory and --skip-git-repo-check was not specified.</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 15:54:54</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 15:54:55</t>
+      <c r="D21" s="24" t="inlineStr"/>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:10:17</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:10:37</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
-        <is>
-          <t>Not inside a trusted directory and --skip-git-repo-check was not specified.</t>
-        </is>
-      </c>
-      <c r="E22" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 15:48:24</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 15:48:24</t>
+      <c r="D22" s="24" t="inlineStr"/>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:04:47</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:05:01</t>
         </is>
       </c>
     </row>
@@ -6127,18 +6131,18 @@
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr"/>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 15:47:09</t>
+          <t>2026-04-16 14:58:17</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 15:49:45</t>
+          <t>2026-04-16 14:59:20</t>
         </is>
       </c>
     </row>
@@ -6155,18 +6159,18 @@
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr"/>
       <c r="E24" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 15:39:24</t>
+          <t>2026-04-16 14:52:47</t>
         </is>
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 15:41:58</t>
+          <t>2026-04-16 14:53:05</t>
         </is>
       </c>
     </row>
@@ -6183,18 +6187,18 @@
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr"/>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 15:31:38</t>
+          <t>2026-04-16 14:47:17</t>
         </is>
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 15:34:12</t>
+          <t>2026-04-16 14:47:33</t>
         </is>
       </c>
     </row>
@@ -6211,18 +6215,18 @@
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>3m</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr"/>
       <c r="E26" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 15:22:54</t>
+          <t>2026-04-16 14:40:47</t>
         </is>
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 15:26:31</t>
+          <t>2026-04-16 14:42:02</t>
         </is>
       </c>
     </row>
@@ -6239,50 +6243,46 @@
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>3m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr"/>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 15:14:38</t>
+          <t>2026-04-16 14:35:17</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 15:17:49</t>
+          <t>2026-04-16 14:35:28</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C28" s="23" t="inlineStr">
-        <is>
-          <t>3m</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=error_max_turns: Reached maximum number of turns (30)</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 15:09:42</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 15:13:31</t>
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr"/>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:29:47</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:30:04</t>
         </is>
       </c>
     </row>
@@ -6299,114 +6299,102 @@
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr"/>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 15:07:08</t>
+          <t>2026-04-16 14:24:17</t>
         </is>
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 15:09:34</t>
+          <t>2026-04-16 14:24:38</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B30" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="inlineStr">
-        <is>
-          <t>4m</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=error_max_turns: Reached maximum number of turns (30)</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 15:05:04</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 15:09:42</t>
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr"/>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:18:47</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:18:52</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B31" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
-      <c r="D31" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=error_max_turns: Reached maximum number of turns (30)</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 15:03:11</t>
-        </is>
-      </c>
-      <c r="F31" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 15:05:04</t>
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr"/>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:13:17</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:13:39</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B32" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C32" s="23" t="inlineStr">
-        <is>
-          <t>2m</t>
-        </is>
-      </c>
-      <c r="D32" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=error_max_turns: Reached maximum number of turns (30)</t>
-        </is>
-      </c>
-      <c r="E32" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 15:00:19</t>
-        </is>
-      </c>
-      <c r="F32" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 15:03:11</t>
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr"/>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:07:47</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:07:59</t>
         </is>
       </c>
     </row>
@@ -6423,89 +6411,81 @@
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>5m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr"/>
       <c r="E33" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 14:56:54</t>
+          <t>2026-04-16 14:02:17</t>
         </is>
       </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 15:02:02</t>
+          <t>2026-04-16 14:02:42</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="23" t="inlineStr">
-        <is>
-          <t>Senior iOS Developer</t>
-        </is>
-      </c>
-      <c r="B34" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D34" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E34" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 14:44:30</t>
-        </is>
-      </c>
-      <c r="F34" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 14:54:30</t>
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr"/>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:56:47</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:56:57</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>Senior Android Developer</t>
-        </is>
-      </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C35" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D35" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 14:44:22</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 14:54:22</t>
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr"/>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:51:16</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:51:39</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>Senior Web Developer</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
@@ -6515,25 +6495,25 @@
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>8m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D36" s="24" t="inlineStr"/>
       <c r="E36" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 14:12:04</t>
+          <t>2026-04-16 13:45:46</t>
         </is>
       </c>
       <c r="F36" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 14:21:02</t>
+          <t>2026-04-16 13:46:06</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>Senior Web Developer</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
@@ -6543,25 +6523,25 @@
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>8m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D37" s="24" t="inlineStr"/>
       <c r="E37" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 14:03:45</t>
+          <t>2026-04-16 13:40:16</t>
         </is>
       </c>
       <c r="F37" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 14:12:04</t>
+          <t>2026-04-16 13:40:46</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>Head of Product</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B38" s="24" t="inlineStr">
@@ -6571,57 +6551,53 @@
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>8m</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="D38" s="24" t="inlineStr"/>
       <c r="E38" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 13:54:07</t>
+          <t>2026-04-16 13:33:16</t>
         </is>
       </c>
       <c r="F38" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 14:03:03</t>
+          <t>2026-04-16 13:35:08</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="23" t="inlineStr">
-        <is>
-          <t>Senior Web Developer</t>
-        </is>
-      </c>
-      <c r="B39" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C39" s="23" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
-      <c r="D39" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:53:47</t>
-        </is>
-      </c>
-      <c r="F39" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 14:03:45</t>
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr"/>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:27:46</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:28:11</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>Senior Web Developer</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B40" s="24" t="inlineStr">
@@ -6631,25 +6607,25 @@
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>6m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D40" s="24" t="inlineStr"/>
       <c r="E40" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 13:47:34</t>
+          <t>2026-04-16 13:22:16</t>
         </is>
       </c>
       <c r="F40" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 13:53:47</t>
+          <t>2026-04-16 13:22:35</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>Senior Web Developer</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
@@ -6665,83 +6641,75 @@
       <c r="D41" s="24" t="inlineStr"/>
       <c r="E41" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 13:46:54</t>
+          <t>2026-04-16 13:16:46</t>
         </is>
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 13:47:34</t>
+          <t>2026-04-16 13:17:00</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="23" t="inlineStr">
-        <is>
-          <t>Senior Web Developer</t>
-        </is>
-      </c>
-      <c r="B42" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C42" s="23" t="inlineStr">
-        <is>
-          <t>6m</t>
-        </is>
-      </c>
-      <c r="D42" s="23" t="inlineStr">
-        <is>
-          <t>Process lost -- child pid 286 is no longer running; retrying once</t>
-        </is>
-      </c>
-      <c r="E42" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:40:05</t>
-        </is>
-      </c>
-      <c r="F42" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:46:54</t>
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr"/>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:11:16</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:11:36</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="23" t="inlineStr">
-        <is>
-          <t>Senior Android Developer</t>
-        </is>
-      </c>
-      <c r="B43" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C43" s="23" t="inlineStr">
-        <is>
-          <t>6m</t>
-        </is>
-      </c>
-      <c r="D43" s="23" t="inlineStr">
-        <is>
-          <t>Process lost -- child pid 99123 is no longer running</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:35:55</t>
-        </is>
-      </c>
-      <c r="F43" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:42:54</t>
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr"/>
+      <c r="E43" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:05:46</t>
+        </is>
+      </c>
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:05:55</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>Senior Web Developer</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B44" s="24" t="inlineStr">
@@ -6751,281 +6719,249 @@
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>4m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D44" s="24" t="inlineStr"/>
       <c r="E44" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 13:35:55</t>
+          <t>2026-04-16 13:00:16</t>
         </is>
       </c>
       <c r="F44" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 13:40:04</t>
+          <t>2026-04-16 13:00:34</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="23" t="inlineStr">
-        <is>
-          <t>Senior iOS Developer</t>
-        </is>
-      </c>
-      <c r="B45" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C45" s="23" t="inlineStr">
-        <is>
-          <t>6m</t>
-        </is>
-      </c>
-      <c r="D45" s="23" t="inlineStr">
-        <is>
-          <t>Process lost -- child pid 99122 is no longer running</t>
-        </is>
-      </c>
-      <c r="E45" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:35:55</t>
-        </is>
-      </c>
-      <c r="F45" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:42:54</t>
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr"/>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:54:46</t>
+        </is>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:54:55</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B46" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C46" s="23" t="inlineStr">
-        <is>
-          <t>3m</t>
-        </is>
-      </c>
-      <c r="D46" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=error_max_turns: Reached maximum number of turns (30)</t>
-        </is>
-      </c>
-      <c r="E46" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:30:50</t>
-        </is>
-      </c>
-      <c r="F46" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:34:32</t>
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr"/>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:49:16</t>
+        </is>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:49:42</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="23" t="inlineStr">
-        <is>
-          <t>Senior Android Developer</t>
-        </is>
-      </c>
-      <c r="B47" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C47" s="23" t="inlineStr">
-        <is>
-          <t>7m</t>
-        </is>
-      </c>
-      <c r="D47" s="23" t="inlineStr">
-        <is>
-          <t>Process lost -- child pid 97556 is no longer running; retrying once</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:28:46</t>
-        </is>
-      </c>
-      <c r="F47" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:35:55</t>
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr"/>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:43:46</t>
+        </is>
+      </c>
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:43:56</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="23" t="inlineStr">
-        <is>
-          <t>Senior iOS Developer</t>
-        </is>
-      </c>
-      <c r="B48" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C48" s="23" t="inlineStr">
-        <is>
-          <t>7m</t>
-        </is>
-      </c>
-      <c r="D48" s="23" t="inlineStr">
-        <is>
-          <t>Process lost -- child pid 97406 is no longer running; retrying once</t>
-        </is>
-      </c>
-      <c r="E48" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:28:41</t>
-        </is>
-      </c>
-      <c r="F48" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:35:55</t>
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr"/>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:38:16</t>
+        </is>
+      </c>
+      <c r="F48" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:38:26</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="23" t="inlineStr">
-        <is>
-          <t>Senior Web Developer</t>
-        </is>
-      </c>
-      <c r="B49" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C49" s="23" t="inlineStr">
-        <is>
-          <t>8m</t>
-        </is>
-      </c>
-      <c r="D49" s="23" t="inlineStr">
-        <is>
-          <t>Process lost -- child pid 97134 is no longer running; retrying once</t>
-        </is>
-      </c>
-      <c r="E49" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:27:53</t>
-        </is>
-      </c>
-      <c r="F49" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:35:55</t>
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr"/>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:32:46</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:33:11</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B50" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C50" s="23" t="inlineStr">
-        <is>
-          <t>4m</t>
-        </is>
-      </c>
-      <c r="D50" s="23" t="inlineStr">
-        <is>
-          <t>Process lost -- child pid 96333 is no longer running</t>
-        </is>
-      </c>
-      <c r="E50" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:25:54</t>
-        </is>
-      </c>
-      <c r="F50" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:30:25</t>
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr"/>
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:27:16</t>
+        </is>
+      </c>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:27:25</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B51" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C51" s="23" t="inlineStr">
-        <is>
-          <t>4m</t>
-        </is>
-      </c>
-      <c r="D51" s="23" t="inlineStr">
-        <is>
-          <t>Process lost -- child pid 93943 is no longer running; retrying once</t>
-        </is>
-      </c>
-      <c r="E51" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:21:14</t>
-        </is>
-      </c>
-      <c r="F51" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:25:54</t>
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr"/>
+      <c r="E51" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:21:46</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:21:56</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B52" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C52" s="23" t="inlineStr">
-        <is>
-          <t>5m</t>
-        </is>
-      </c>
-      <c r="D52" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=error_max_turns: Reached maximum number of turns (30)</t>
-        </is>
-      </c>
-      <c r="E52" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:12:19</t>
-        </is>
-      </c>
-      <c r="F52" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:17:41</t>
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr"/>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:16:16</t>
+        </is>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:16:30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B53" s="24" t="inlineStr">
@@ -7035,57 +6971,53 @@
       </c>
       <c r="C53" s="24" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D53" s="24" t="inlineStr"/>
       <c r="E53" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 13:05:59</t>
+          <t>2026-04-16 12:10:46</t>
         </is>
       </c>
       <c r="F53" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 13:07:15</t>
+          <t>2026-04-16 12:10:54</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B54" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C54" s="23" t="inlineStr">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
         <is>
           <t>1m</t>
         </is>
       </c>
-      <c r="D54" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=error_max_turns: Reached maximum number of turns (15)</t>
-        </is>
-      </c>
-      <c r="E54" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:03:20</t>
-        </is>
-      </c>
-      <c r="F54" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 13:05:03</t>
+      <c r="D54" s="24" t="inlineStr"/>
+      <c r="E54" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:03:46</t>
+        </is>
+      </c>
+      <c r="F54" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:05:18</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="24" t="inlineStr">
         <is>
-          <t>Head of Product</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
@@ -7095,25 +7027,25 @@
       </c>
       <c r="C55" s="24" t="inlineStr">
         <is>
-          <t>5m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D55" s="24" t="inlineStr"/>
       <c r="E55" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 12:54:57</t>
+          <t>2026-04-16 11:58:16</t>
         </is>
       </c>
       <c r="F55" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 13:00:06</t>
+          <t>2026-04-16 11:58:21</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B56" s="24" t="inlineStr">
@@ -7123,25 +7055,25 @@
       </c>
       <c r="C56" s="24" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D56" s="24" t="inlineStr"/>
       <c r="E56" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 12:48:08</t>
+          <t>2026-04-16 11:52:46</t>
         </is>
       </c>
       <c r="F56" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 12:50:20</t>
+          <t>2026-04-16 11:52:56</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
@@ -7151,25 +7083,25 @@
       </c>
       <c r="C57" s="24" t="inlineStr">
         <is>
-          <t>5m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D57" s="24" t="inlineStr"/>
       <c r="E57" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 12:40:39</t>
+          <t>2026-04-16 11:47:16</t>
         </is>
       </c>
       <c r="F57" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 12:46:36</t>
+          <t>2026-04-16 11:47:21</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>Head of Product</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B58" s="24" t="inlineStr">
@@ -7179,25 +7111,25 @@
       </c>
       <c r="C58" s="24" t="inlineStr">
         <is>
-          <t>6m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D58" s="24" t="inlineStr"/>
       <c r="E58" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 11:50:36</t>
+          <t>2026-04-16 11:41:46</t>
         </is>
       </c>
       <c r="F58" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 11:57:05</t>
+          <t>2026-04-16 11:41:54</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
@@ -7207,2646 +7139,466 @@
       </c>
       <c r="C59" s="24" t="inlineStr">
         <is>
-          <t>5m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D59" s="24" t="inlineStr"/>
       <c r="E59" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 11:40:15</t>
+          <t>2026-04-16 11:36:16</t>
         </is>
       </c>
       <c r="F59" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 11:45:30</t>
+          <t>2026-04-16 11:36:27</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="25" t="inlineStr">
-        <is>
-          <t>Senior Android Developer</t>
-        </is>
-      </c>
-      <c r="B60" s="25" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="C60" s="25" t="inlineStr">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C60" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D60" s="24" t="inlineStr"/>
+      <c r="E60" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 18:04:54</t>
+        </is>
+      </c>
+      <c r="F60" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 18:04:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B61" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C61" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D61" s="24" t="inlineStr"/>
+      <c r="E61" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:59:39</t>
+        </is>
+      </c>
+      <c r="F61" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:59:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B62" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C62" s="24" t="inlineStr">
         <is>
           <t>1m</t>
         </is>
       </c>
-      <c r="D60" s="25" t="inlineStr">
-        <is>
-          <t>Adapter failed</t>
-        </is>
-      </c>
-      <c r="E60" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-15 07:19:37</t>
-        </is>
-      </c>
-      <c r="F60" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-15 07:20:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="25" t="inlineStr">
-        <is>
-          <t>Senior iOS Developer</t>
-        </is>
-      </c>
-      <c r="B61" s="25" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="C61" s="25" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
-      <c r="D61" s="25" t="inlineStr">
-        <is>
-          <t>Adapter failed</t>
-        </is>
-      </c>
-      <c r="E61" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-15 07:19:36</t>
-        </is>
-      </c>
-      <c r="F61" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-15 07:20:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="25" t="inlineStr">
-        <is>
-          <t>Senior Web Developer</t>
-        </is>
-      </c>
-      <c r="B62" s="25" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="C62" s="25" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
-      <c r="D62" s="25" t="inlineStr">
-        <is>
-          <t>Adapter failed</t>
-        </is>
-      </c>
-      <c r="E62" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-15 07:19:36</t>
-        </is>
-      </c>
-      <c r="F62" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-15 07:20:48</t>
+      <c r="D62" s="24" t="inlineStr"/>
+      <c r="E62" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:53:24</t>
+        </is>
+      </c>
+      <c r="F62" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:54:26</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="25" t="inlineStr">
-        <is>
-          <t>Head of Product</t>
-        </is>
-      </c>
-      <c r="B63" s="25" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="C63" s="25" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
-      <c r="D63" s="25" t="inlineStr">
-        <is>
-          <t>Adapter failed</t>
-        </is>
-      </c>
-      <c r="E63" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-15 07:19:36</t>
-        </is>
-      </c>
-      <c r="F63" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-15 07:20:48</t>
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B63" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C63" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D63" s="24" t="inlineStr"/>
+      <c r="E63" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:48:09</t>
+        </is>
+      </c>
+      <c r="F63" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:48:14</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="25" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B64" s="25" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="C64" s="25" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
-      <c r="D64" s="25" t="inlineStr">
-        <is>
-          <t>Adapter failed</t>
-        </is>
-      </c>
-      <c r="E64" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-15 07:19:36</t>
-        </is>
-      </c>
-      <c r="F64" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-15 07:20:46</t>
+      <c r="A64" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B64" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C64" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D64" s="24" t="inlineStr"/>
+      <c r="E64" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:42:54</t>
+        </is>
+      </c>
+      <c r="F64" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:43:03</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="23" t="inlineStr">
-        <is>
-          <t>Senior Android Developer</t>
-        </is>
-      </c>
-      <c r="B65" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C65" s="23" t="inlineStr">
-        <is>
-          <t>30m</t>
-        </is>
-      </c>
-      <c r="D65" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 1800s</t>
-        </is>
-      </c>
-      <c r="E65" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 23:25:23</t>
-        </is>
-      </c>
-      <c r="F65" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 23:55:24</t>
+      <c r="A65" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B65" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C65" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D65" s="24" t="inlineStr"/>
+      <c r="E65" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:37:09</t>
+        </is>
+      </c>
+      <c r="F65" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:37:42</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="23" t="inlineStr">
-        <is>
-          <t>Senior iOS Developer</t>
-        </is>
-      </c>
-      <c r="B66" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C66" s="23" t="inlineStr">
-        <is>
-          <t>30m</t>
-        </is>
-      </c>
-      <c r="D66" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 1800s</t>
-        </is>
-      </c>
-      <c r="E66" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 23:25:22</t>
-        </is>
-      </c>
-      <c r="F66" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 23:55:24</t>
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B66" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C66" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D66" s="24" t="inlineStr"/>
+      <c r="E66" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:31:54</t>
+        </is>
+      </c>
+      <c r="F66" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:32:07</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="23" t="inlineStr">
-        <is>
-          <t>Senior Web Developer</t>
-        </is>
-      </c>
-      <c r="B67" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C67" s="23" t="inlineStr">
-        <is>
-          <t>30m</t>
-        </is>
-      </c>
-      <c r="D67" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 1800s</t>
-        </is>
-      </c>
-      <c r="E67" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 23:25:10</t>
-        </is>
-      </c>
-      <c r="F67" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 23:55:11</t>
+      <c r="A67" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B67" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C67" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D67" s="24" t="inlineStr"/>
+      <c r="E67" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:25:54</t>
+        </is>
+      </c>
+      <c r="F67" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:26:46</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="23" t="inlineStr">
         <is>
-          <t>Head of Product</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B68" s="23" t="inlineStr">
         <is>
-          <t>timed_out</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C68" s="23" t="inlineStr">
         <is>
-          <t>30m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D68" s="23" t="inlineStr">
         <is>
-          <t>Timed out after 1800s</t>
+          <t>Quota exceeded. Check your plan and billing details.</t>
         </is>
       </c>
       <c r="E68" s="23" t="inlineStr">
         <is>
-          <t>2026-04-14 23:13:24</t>
+          <t>2026-04-15 17:20:39</t>
         </is>
       </c>
       <c r="F68" s="23" t="inlineStr">
         <is>
-          <t>2026-04-14 23:43:25</t>
+          <t>2026-04-15 17:20:46</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="23" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B69" s="23" t="inlineStr">
         <is>
-          <t>timed_out</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C69" s="23" t="inlineStr">
         <is>
-          <t>30m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D69" s="23" t="inlineStr">
         <is>
-          <t>Timed out after 1800s</t>
+          <t>Quota exceeded. Check your plan and billing details.</t>
         </is>
       </c>
       <c r="E69" s="23" t="inlineStr">
         <is>
-          <t>2026-04-14 23:08:29</t>
+          <t>2026-04-15 17:15:24</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t>2026-04-14 23:38:31</t>
+          <t>2026-04-15 17:15:32</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="23" t="inlineStr">
         <is>
-          <t>Senior Web Developer</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B70" s="23" t="inlineStr">
         <is>
-          <t>timed_out</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C70" s="23" t="inlineStr">
         <is>
-          <t>30m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D70" s="23" t="inlineStr">
         <is>
-          <t>Timed out after 1800s</t>
+          <t>unknown variant `api-key`, expected one of `apikey`, `chatgpt`, `chatgptAuthTokens` at line 2 column 24</t>
         </is>
       </c>
       <c r="E70" s="23" t="inlineStr">
         <is>
-          <t>2026-04-14 22:54:10</t>
+          <t>2026-04-15 17:10:09</t>
         </is>
       </c>
       <c r="F70" s="23" t="inlineStr">
         <is>
-          <t>2026-04-14 23:24:12</t>
+          <t>2026-04-15 17:10:09</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="25" t="inlineStr">
-        <is>
-          <t>Head of Finance</t>
-        </is>
-      </c>
-      <c r="B71" s="25" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="C71" s="25" t="inlineStr">
-        <is>
-          <t>13m</t>
-        </is>
-      </c>
-      <c r="D71" s="25" t="inlineStr">
-        <is>
-          <t>Adapter failed</t>
-        </is>
-      </c>
-      <c r="E71" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:42:42</t>
-        </is>
-      </c>
-      <c r="F71" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:56:14</t>
+      <c r="A71" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B71" s="23" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="C71" s="23" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D71" s="23" t="inlineStr">
+        <is>
+          <t>{"type":"error","status":400,"error":{"type":"invalid_request_error","message":"The 'gpt-4o-mini' model is not supported when using Codex with a ChatGPT account."}}</t>
+        </is>
+      </c>
+      <c r="E71" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:04:54</t>
+        </is>
+      </c>
+      <c r="F71" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:04:57</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="23" t="inlineStr">
         <is>
-          <t>Head of Product</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B72" s="23" t="inlineStr">
         <is>
-          <t>timed_out</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C72" s="23" t="inlineStr">
         <is>
-          <t>30m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D72" s="23" t="inlineStr">
         <is>
-          <t>Timed out after 1800s</t>
+          <t>{"type":"error","status":400,"error":{"type":"invalid_request_error","message":"The 'gpt-4o-mini' model is not supported when using Codex with a ChatGPT account."}}</t>
         </is>
       </c>
       <c r="E72" s="23" t="inlineStr">
         <is>
-          <t>2026-04-14 22:42:42</t>
+          <t>2026-04-15 16:59:39</t>
         </is>
       </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
-          <t>2026-04-14 23:12:44</t>
+          <t>2026-04-15 16:59:41</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="25" t="inlineStr">
-        <is>
-          <t>Head of Marketing</t>
-        </is>
-      </c>
-      <c r="B73" s="25" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="C73" s="25" t="inlineStr">
-        <is>
-          <t>13m</t>
-        </is>
-      </c>
-      <c r="D73" s="25" t="inlineStr">
-        <is>
-          <t>Adapter failed</t>
-        </is>
-      </c>
-      <c r="E73" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:42:42</t>
-        </is>
-      </c>
-      <c r="F73" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:56:16</t>
+      <c r="A73" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B73" s="23" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="C73" s="23" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D73" s="23" t="inlineStr">
+        <is>
+          <t>{"type":"error","status":400,"error":{"type":"invalid_request_error","message":"The 'gpt-oss:20b' model is not supported when using Codex with a ChatGPT account."}}</t>
+        </is>
+      </c>
+      <c r="E73" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-15 16:54:24</t>
+        </is>
+      </c>
+      <c r="F73" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-15 16:54:30</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="25" t="inlineStr">
-        <is>
-          <t>Head of HR</t>
-        </is>
-      </c>
-      <c r="B74" s="25" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="C74" s="25" t="inlineStr">
-        <is>
-          <t>13m</t>
-        </is>
-      </c>
-      <c r="D74" s="25" t="inlineStr">
-        <is>
-          <t>Adapter failed</t>
-        </is>
-      </c>
-      <c r="E74" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:42:41</t>
-        </is>
-      </c>
-      <c r="F74" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:56:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="25" t="inlineStr">
-        <is>
-          <t>Head of Governance</t>
-        </is>
-      </c>
-      <c r="B75" s="25" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="C75" s="25" t="inlineStr">
-        <is>
-          <t>13m</t>
-        </is>
-      </c>
-      <c r="D75" s="25" t="inlineStr">
-        <is>
-          <t>Adapter failed</t>
-        </is>
-      </c>
-      <c r="E75" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:42:40</t>
-        </is>
-      </c>
-      <c r="F75" s="25" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:56:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B76" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C76" s="23" t="inlineStr">
-        <is>
-          <t>30m</t>
-        </is>
-      </c>
-      <c r="D76" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 1800s</t>
-        </is>
-      </c>
-      <c r="E76" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:37:42</t>
-        </is>
-      </c>
-      <c r="F76" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 23:07:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="23" t="inlineStr">
-        <is>
-          <t>Head of HR</t>
-        </is>
-      </c>
-      <c r="B77" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C77" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D77" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E77" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:27:10</t>
-        </is>
-      </c>
-      <c r="F77" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:37:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B78" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C78" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D78" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E78" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:24:27</t>
-        </is>
-      </c>
-      <c r="F78" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:34:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B79" s="23" t="inlineStr">
+      <c r="A74" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B74" s="23" t="inlineStr">
         <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="C79" s="23" t="inlineStr">
+      <c r="C74" s="23" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D79" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E79" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:22:53</t>
-        </is>
-      </c>
-      <c r="F79" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:22:58</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B80" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C80" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D80" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E80" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:21:48</t>
-        </is>
-      </c>
-      <c r="F80" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:21:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B81" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C81" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D81" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E81" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:20:09</t>
-        </is>
-      </c>
-      <c r="F81" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:20:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B82" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C82" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D82" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E82" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:19:55</t>
-        </is>
-      </c>
-      <c r="F82" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:19:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B83" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C83" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D83" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E83" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:19:40</t>
-        </is>
-      </c>
-      <c r="F83" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:19:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B84" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C84" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D84" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E84" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:19:34</t>
-        </is>
-      </c>
-      <c r="F84" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:19:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B85" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C85" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D85" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E85" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:16:22</t>
-        </is>
-      </c>
-      <c r="F85" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:16:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B86" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C86" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D86" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E86" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:09:59</t>
-        </is>
-      </c>
-      <c r="F86" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:10:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B87" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C87" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D87" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E87" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:09:07</t>
-        </is>
-      </c>
-      <c r="F87" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:09:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B88" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C88" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D88" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E88" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:09:03</t>
-        </is>
-      </c>
-      <c r="F88" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:09:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B89" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C89" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D89" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E89" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:08:58</t>
-        </is>
-      </c>
-      <c r="F89" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:09:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B90" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C90" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D90" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E90" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:08:53</t>
-        </is>
-      </c>
-      <c r="F90" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:08:58</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="23" t="inlineStr">
-        <is>
-          <t>Head of HR</t>
-        </is>
-      </c>
-      <c r="B91" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C91" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D91" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E91" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:49:11</t>
-        </is>
-      </c>
-      <c r="F91" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:59:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="23" t="inlineStr">
-        <is>
-          <t>Head of HR</t>
-        </is>
-      </c>
-      <c r="B92" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C92" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D92" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E92" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:39:09</t>
-        </is>
-      </c>
-      <c r="F92" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:49:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="23" t="inlineStr">
-        <is>
-          <t>Head of Finance</t>
-        </is>
-      </c>
-      <c r="B93" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C93" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D93" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E93" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:29:05</t>
-        </is>
-      </c>
-      <c r="F93" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:39:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="23" t="inlineStr">
-        <is>
-          <t>Head of HR</t>
-        </is>
-      </c>
-      <c r="B94" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C94" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D94" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E94" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:29:05</t>
-        </is>
-      </c>
-      <c r="F94" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:39:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="23" t="inlineStr">
-        <is>
-          <t>Head of Governance</t>
-        </is>
-      </c>
-      <c r="B95" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C95" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D95" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E95" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:29:05</t>
-        </is>
-      </c>
-      <c r="F95" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:39:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="23" t="inlineStr">
-        <is>
-          <t>Head of Product</t>
-        </is>
-      </c>
-      <c r="B96" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C96" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D96" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E96" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:29:02</t>
-        </is>
-      </c>
-      <c r="F96" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:39:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="23" t="inlineStr">
-        <is>
-          <t>Head of Marketing</t>
-        </is>
-      </c>
-      <c r="B97" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C97" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D97" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E97" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:27:54</t>
-        </is>
-      </c>
-      <c r="F97" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:37:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="23" t="inlineStr">
-        <is>
-          <t>Head of HR</t>
-        </is>
-      </c>
-      <c r="B98" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C98" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D98" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E98" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:19:02</t>
-        </is>
-      </c>
-      <c r="F98" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:29:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="23" t="inlineStr">
-        <is>
-          <t>Head of Finance</t>
-        </is>
-      </c>
-      <c r="B99" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C99" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D99" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E99" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:19:02</t>
-        </is>
-      </c>
-      <c r="F99" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:29:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="23" t="inlineStr">
-        <is>
-          <t>Head of Governance</t>
-        </is>
-      </c>
-      <c r="B100" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C100" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D100" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E100" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:19:02</t>
-        </is>
-      </c>
-      <c r="F100" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:29:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="23" t="inlineStr">
-        <is>
-          <t>Head of Product</t>
-        </is>
-      </c>
-      <c r="B101" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C101" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D101" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E101" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:19:00</t>
-        </is>
-      </c>
-      <c r="F101" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:29:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="23" t="inlineStr">
-        <is>
-          <t>Head of Marketing</t>
-        </is>
-      </c>
-      <c r="B102" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C102" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D102" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E102" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:17:50</t>
-        </is>
-      </c>
-      <c r="F102" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:27:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B103" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C103" s="24" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
-      <c r="D103" s="24" t="inlineStr"/>
-      <c r="E103" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:13:13</t>
-        </is>
-      </c>
-      <c r="F103" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:14:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="23" t="inlineStr">
-        <is>
-          <t>Head of Governance</t>
-        </is>
-      </c>
-      <c r="B104" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C104" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D104" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E104" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:09:00</t>
-        </is>
-      </c>
-      <c r="F104" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:19:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="23" t="inlineStr">
-        <is>
-          <t>Head of Finance</t>
-        </is>
-      </c>
-      <c r="B105" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C105" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D105" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E105" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:08:59</t>
-        </is>
-      </c>
-      <c r="F105" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:19:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="23" t="inlineStr">
-        <is>
-          <t>Head of HR</t>
-        </is>
-      </c>
-      <c r="B106" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C106" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D106" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E106" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:08:59</t>
-        </is>
-      </c>
-      <c r="F106" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:19:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="23" t="inlineStr">
-        <is>
-          <t>Head of Product</t>
-        </is>
-      </c>
-      <c r="B107" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C107" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D107" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E107" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:08:58</t>
-        </is>
-      </c>
-      <c r="F107" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:18:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B108" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C108" s="23" t="inlineStr">
-        <is>
-          <t>59m</t>
-        </is>
-      </c>
-      <c r="D108" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E108" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:08:57</t>
-        </is>
-      </c>
-      <c r="F108" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 22:08:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B109" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C109" s="24" t="inlineStr">
-        <is>
-          <t>4m</t>
-        </is>
-      </c>
-      <c r="D109" s="24" t="inlineStr"/>
-      <c r="E109" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:08:40</t>
-        </is>
-      </c>
-      <c r="F109" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:13:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="23" t="inlineStr">
-        <is>
-          <t>Head of Marketing</t>
-        </is>
-      </c>
-      <c r="B110" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C110" s="23" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="D110" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 600s</t>
-        </is>
-      </c>
-      <c r="E110" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:07:49</t>
-        </is>
-      </c>
-      <c r="F110" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:17:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="23" t="inlineStr">
-        <is>
-          <t>Head of Marketing</t>
-        </is>
-      </c>
-      <c r="B111" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C111" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D111" s="23" t="inlineStr">
-        <is>
-          <t>{"type":"error","status":400,"error":{"type":"invalid_request_error","message":"The 'gemma4:31b' model is not supported when using Codex with a ChatGPT account."}}</t>
-        </is>
-      </c>
-      <c r="E111" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:07:02</t>
-        </is>
-      </c>
-      <c r="F111" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:07:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="23" t="inlineStr">
-        <is>
-          <t>Head of Marketing</t>
-        </is>
-      </c>
-      <c r="B112" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C112" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D112" s="23" t="inlineStr">
-        <is>
-          <t>error: unexpected argument '--provider' found</t>
-        </is>
-      </c>
-      <c r="E112" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:06:23</t>
-        </is>
-      </c>
-      <c r="F112" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:06:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="23" t="inlineStr">
-        <is>
-          <t>Head of Marketing</t>
-        </is>
-      </c>
-      <c r="B113" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C113" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D113" s="23" t="inlineStr">
-        <is>
-          <t>{"type":"error","status":400,"error":{"type":"invalid_request_error","message":"The 'gemma4:31b' model is not supported when using Codex with a ChatGPT account."}}</t>
-        </is>
-      </c>
-      <c r="E113" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:05:38</t>
-        </is>
-      </c>
-      <c r="F113" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:05:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="23" t="inlineStr">
-        <is>
-          <t>Head of Marketing</t>
-        </is>
-      </c>
-      <c r="B114" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C114" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D114" s="23" t="inlineStr">
-        <is>
-          <t>Command not found in PATH: "codex"</t>
-        </is>
-      </c>
-      <c r="E114" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:04:33</t>
-        </is>
-      </c>
-      <c r="F114" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 21:04:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B115" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C115" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D115" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E115" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:39:20</t>
-        </is>
-      </c>
-      <c r="F115" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:39:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B116" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C116" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D116" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E116" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:37:27</t>
-        </is>
-      </c>
-      <c r="F116" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:37:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B117" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C117" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D117" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E117" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:31:15</t>
-        </is>
-      </c>
-      <c r="F117" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:31:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B118" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C118" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D118" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E118" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:31:08</t>
-        </is>
-      </c>
-      <c r="F118" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:31:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B119" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C119" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D119" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Credit balance is too low</t>
-        </is>
-      </c>
-      <c r="E119" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:30:12</t>
-        </is>
-      </c>
-      <c r="F119" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:30:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B120" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C120" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D120" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E120" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:25:38</t>
-        </is>
-      </c>
-      <c r="F120" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:25:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B121" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C121" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D121" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E121" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:25:34</t>
-        </is>
-      </c>
-      <c r="F121" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:25:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B122" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C122" s="24" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
-      <c r="D122" s="24" t="inlineStr"/>
-      <c r="E122" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:21:55</t>
-        </is>
-      </c>
-      <c r="F122" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:31:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B123" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C123" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D123" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E123" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:05:38</t>
-        </is>
-      </c>
-      <c r="F123" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:05:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B124" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C124" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D124" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E124" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:05:33</t>
-        </is>
-      </c>
-      <c r="F124" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:05:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B125" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C125" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D125" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E125" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:03:34</t>
-        </is>
-      </c>
-      <c r="F125" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:03:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B126" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C126" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D126" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E126" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:03:30</t>
-        </is>
-      </c>
-      <c r="F126" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:03:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B127" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C127" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D127" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E127" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:01:30</t>
-        </is>
-      </c>
-      <c r="F127" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:01:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B128" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C128" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D128" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E128" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:01:26</t>
-        </is>
-      </c>
-      <c r="F128" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 19:01:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B129" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C129" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D129" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E129" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:59:29</t>
-        </is>
-      </c>
-      <c r="F129" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:59:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B130" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C130" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D130" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E130" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:59:25</t>
-        </is>
-      </c>
-      <c r="F130" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:59:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B131" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C131" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D131" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E131" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:57:28</t>
-        </is>
-      </c>
-      <c r="F131" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:57:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B132" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C132" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D132" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E132" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:57:24</t>
-        </is>
-      </c>
-      <c r="F132" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:57:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B133" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C133" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D133" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E133" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:55:53</t>
-        </is>
-      </c>
-      <c r="F133" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:55:57</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B134" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C134" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D134" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E134" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:55:48</t>
-        </is>
-      </c>
-      <c r="F134" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:55:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B135" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C135" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D135" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E135" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:54:04</t>
-        </is>
-      </c>
-      <c r="F135" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:54:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B136" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C136" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D136" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E136" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:54:00</t>
-        </is>
-      </c>
-      <c r="F136" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:54:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B137" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C137" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D137" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E137" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:52:16</t>
-        </is>
-      </c>
-      <c r="F137" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:52:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="23" t="inlineStr">
-        <is>
-          <t>CTO</t>
-        </is>
-      </c>
-      <c r="B138" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C138" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D138" s="23" t="inlineStr">
-        <is>
-          <t>Claude run failed: subtype=success: Invalid API key · Fix external API key</t>
-        </is>
-      </c>
-      <c r="E138" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:52:12</t>
-        </is>
-      </c>
-      <c r="F138" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:52:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B139" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C139" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D139" s="24" t="inlineStr"/>
-      <c r="E139" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:37:09</t>
-        </is>
-      </c>
-      <c r="F139" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:37:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B140" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C140" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D140" s="24" t="inlineStr"/>
-      <c r="E140" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:36:51</t>
-        </is>
-      </c>
-      <c r="F140" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:37:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B141" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C141" s="24" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
-      <c r="D141" s="24" t="inlineStr"/>
-      <c r="E141" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:34:58</t>
-        </is>
-      </c>
-      <c r="F141" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:35:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B142" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C142" s="24" t="inlineStr">
-        <is>
-          <t>2m</t>
-        </is>
-      </c>
-      <c r="D142" s="24" t="inlineStr"/>
-      <c r="E142" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:32:34</t>
-        </is>
-      </c>
-      <c r="F142" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-14 18:34:58</t>
+      <c r="D74" s="23" t="inlineStr">
+        <is>
+          <t>{"type":"error","status":400,"error":{"type":"invalid_request_error","message":"The 'gpt-oss:20b' model is not supported when using Codex with a ChatGPT account."}}</t>
+        </is>
+      </c>
+      <c r="E74" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-15 16:49:09</t>
+        </is>
+      </c>
+      <c r="F74" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-15 16:49:13</t>
         </is>
       </c>
     </row>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -1326,7 +1326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="7" min="1" max="1"/>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="J2" s="14" t="inlineStr">
         <is>
-          <t>[Sync 04/15 15:54] Paperclip: done</t>
+          <t>[Session 8 04/16] Migrations 001+002 both run in Supabase</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>CORS config for API domain</t>
+          <t>[Session 7] R2 bucket created, keys in .env.local</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Use test mode first</t>
+          <t>[Session 7-8] Stripe test keys configured, dynamic pricing (no fixed products), webhook endpoint set</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Point Namecheap NS to Vercel</t>
+          <t>[Session 6] Vercel deployed, tenu.world live, DNS configured</t>
         </is>
       </c>
     </row>
@@ -4494,6 +4494,392 @@
       <c r="J68" s="16" t="inlineStr">
         <is>
           <t>[Auto-added from Paperclip 04/16]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>T-090</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Rewrite inspection/new form: owner, tenants, contract, property, zone tendue, French UI</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Claude Cowork</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>src/app/inspection/new/page.tsx</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>[Session 8 04/16] Full form with 6 sections, zone tendue auto-detect from postal code</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>T-091</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Build element rating UI (TB/B/M/MV per element, auto-save, progress bar)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Claude Cowork</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>src/components/inspection/ElementRatingPanel.tsx</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>[Session 8 04/16] Integrated in capture flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>T-092</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Build /api/inspection/create route (owner, tenants, contract, zone tendue, rooms)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Claude Cowork</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>src/app/api/inspection/create/route.ts</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>[Session 8 04/16] Server-side zone tendue detection</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>T-094</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Build /api/inspection/ratings route (GET + POST upsert per element)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Claude Cowork</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>src/app/api/inspection/ratings/route.ts</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>[Session 8 04/16] Ownership verification via room-&gt;inspection-&gt;user</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>T-095</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Build zone tendue postal code lookup utility (1100+ postal codes from Décret 2013-392)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Claude Cowork</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>src/lib/geo/zone-tendue.ts</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>[Session 8 04/16] Notice period auto-calc</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>T-096</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Build element checklist definitions per room type (10 standard + kitchen/bathroom extras)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Claude Cowork</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>src/lib/inspection/elements.ts</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>[Session 8 04/16] Matches official état des lieux templates</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>T-097</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Run migration 002: tenants table, element_ratings table, owner/contract/property columns on inspections</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Dr Mubashir</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>T-001</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>supabase/migrations/002_owner_contract_tenants.sql</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>[Session 8 04/16] Both 001+002 run in SQL Editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>T-099</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Configure Stripe webhook endpoint (checkout.session.completed) + signing secret</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Dr Mubashir</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>T-003</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>STRIPE_WEBHOOK_SECRET in .env.local + Vercel</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>[Session 8 04/16] whsec_ key configured</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5402,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>PAPERCLIP STATUS — 2026-04-16 16:48</t>
+          <t>PAPERCLIP STATUS — 2026-04-16 17:18</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5894,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26">
@@ -5550,7 +5936,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>RUN HISTORY (Last 24h) — 2026-04-16 16:48</t>
+          <t>RUN HISTORY (Last 24h) — 2026-04-16 17:18</t>
         </is>
       </c>
     </row>
@@ -5605,12 +5991,12 @@
       <c r="D4" s="24" t="inlineStr"/>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:43:47</t>
+          <t>2026-04-16 17:17:17</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:43:58</t>
+          <t>2026-04-16 17:17:31</t>
         </is>
       </c>
     </row>
@@ -5633,12 +6019,12 @@
       <c r="D5" s="24" t="inlineStr"/>
       <c r="E5" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:38:17</t>
+          <t>2026-04-16 17:11:47</t>
         </is>
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:38:36</t>
+          <t>2026-04-16 17:12:05</t>
         </is>
       </c>
     </row>
@@ -5661,12 +6047,12 @@
       <c r="D6" s="24" t="inlineStr"/>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:32:47</t>
+          <t>2026-04-16 17:06:17</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:32:58</t>
+          <t>2026-04-16 17:06:29</t>
         </is>
       </c>
     </row>
@@ -5689,12 +6075,12 @@
       <c r="D7" s="24" t="inlineStr"/>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:27:17</t>
+          <t>2026-04-16 17:00:47</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:27:25</t>
+          <t>2026-04-16 17:01:13</t>
         </is>
       </c>
     </row>
@@ -5717,12 +6103,12 @@
       <c r="D8" s="24" t="inlineStr"/>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:21:47</t>
+          <t>2026-04-16 16:55:17</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:22:05</t>
+          <t>2026-04-16 16:55:39</t>
         </is>
       </c>
     </row>
@@ -5745,12 +6131,12 @@
       <c r="D9" s="24" t="inlineStr"/>
       <c r="E9" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:16:17</t>
+          <t>2026-04-16 16:49:17</t>
         </is>
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:16:42</t>
+          <t>2026-04-16 16:49:55</t>
         </is>
       </c>
     </row>
@@ -5773,12 +6159,12 @@
       <c r="D10" s="24" t="inlineStr"/>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:10:47</t>
+          <t>2026-04-16 16:43:47</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:10:58</t>
+          <t>2026-04-16 16:43:58</t>
         </is>
       </c>
     </row>
@@ -5801,12 +6187,12 @@
       <c r="D11" s="24" t="inlineStr"/>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:05:17</t>
+          <t>2026-04-16 16:38:17</t>
         </is>
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:05:45</t>
+          <t>2026-04-16 16:38:36</t>
         </is>
       </c>
     </row>
@@ -5829,12 +6215,12 @@
       <c r="D12" s="24" t="inlineStr"/>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:59:47</t>
+          <t>2026-04-16 16:32:47</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:59:56</t>
+          <t>2026-04-16 16:32:58</t>
         </is>
       </c>
     </row>
@@ -5857,12 +6243,12 @@
       <c r="D13" s="24" t="inlineStr"/>
       <c r="E13" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:54:17</t>
+          <t>2026-04-16 16:27:17</t>
         </is>
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:54:38</t>
+          <t>2026-04-16 16:27:25</t>
         </is>
       </c>
     </row>
@@ -5885,12 +6271,12 @@
       <c r="D14" s="24" t="inlineStr"/>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:48:47</t>
+          <t>2026-04-16 16:21:47</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:48:52</t>
+          <t>2026-04-16 16:22:05</t>
         </is>
       </c>
     </row>
@@ -5913,12 +6299,12 @@
       <c r="D15" s="24" t="inlineStr"/>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:43:17</t>
+          <t>2026-04-16 16:16:17</t>
         </is>
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:43:41</t>
+          <t>2026-04-16 16:16:42</t>
         </is>
       </c>
     </row>
@@ -5941,12 +6327,12 @@
       <c r="D16" s="24" t="inlineStr"/>
       <c r="E16" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:37:47</t>
+          <t>2026-04-16 16:10:47</t>
         </is>
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:38:01</t>
+          <t>2026-04-16 16:10:58</t>
         </is>
       </c>
     </row>
@@ -5969,12 +6355,12 @@
       <c r="D17" s="24" t="inlineStr"/>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:32:17</t>
+          <t>2026-04-16 16:05:17</t>
         </is>
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:32:41</t>
+          <t>2026-04-16 16:05:45</t>
         </is>
       </c>
     </row>
@@ -5997,12 +6383,12 @@
       <c r="D18" s="24" t="inlineStr"/>
       <c r="E18" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:26:47</t>
+          <t>2026-04-16 15:59:47</t>
         </is>
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:27:04</t>
+          <t>2026-04-16 15:59:56</t>
         </is>
       </c>
     </row>
@@ -6025,12 +6411,12 @@
       <c r="D19" s="24" t="inlineStr"/>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:21:17</t>
+          <t>2026-04-16 15:54:17</t>
         </is>
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:21:40</t>
+          <t>2026-04-16 15:54:38</t>
         </is>
       </c>
     </row>
@@ -6053,12 +6439,12 @@
       <c r="D20" s="24" t="inlineStr"/>
       <c r="E20" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:15:47</t>
+          <t>2026-04-16 15:48:47</t>
         </is>
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:16:00</t>
+          <t>2026-04-16 15:48:52</t>
         </is>
       </c>
     </row>
@@ -6081,12 +6467,12 @@
       <c r="D21" s="24" t="inlineStr"/>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:10:17</t>
+          <t>2026-04-16 15:43:17</t>
         </is>
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:10:37</t>
+          <t>2026-04-16 15:43:41</t>
         </is>
       </c>
     </row>
@@ -6109,12 +6495,12 @@
       <c r="D22" s="24" t="inlineStr"/>
       <c r="E22" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:04:47</t>
+          <t>2026-04-16 15:37:47</t>
         </is>
       </c>
       <c r="F22" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:05:01</t>
+          <t>2026-04-16 15:38:01</t>
         </is>
       </c>
     </row>
@@ -6131,18 +6517,18 @@
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr"/>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:58:17</t>
+          <t>2026-04-16 15:32:17</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:59:20</t>
+          <t>2026-04-16 15:32:41</t>
         </is>
       </c>
     </row>
@@ -6165,12 +6551,12 @@
       <c r="D24" s="24" t="inlineStr"/>
       <c r="E24" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:52:47</t>
+          <t>2026-04-16 15:26:47</t>
         </is>
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:53:05</t>
+          <t>2026-04-16 15:27:04</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6579,12 @@
       <c r="D25" s="24" t="inlineStr"/>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:47:17</t>
+          <t>2026-04-16 15:21:17</t>
         </is>
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:47:33</t>
+          <t>2026-04-16 15:21:40</t>
         </is>
       </c>
     </row>
@@ -6215,18 +6601,18 @@
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr"/>
       <c r="E26" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:40:47</t>
+          <t>2026-04-16 15:15:47</t>
         </is>
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:42:02</t>
+          <t>2026-04-16 15:16:00</t>
         </is>
       </c>
     </row>
@@ -6249,12 +6635,12 @@
       <c r="D27" s="24" t="inlineStr"/>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:35:17</t>
+          <t>2026-04-16 15:10:17</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:35:28</t>
+          <t>2026-04-16 15:10:37</t>
         </is>
       </c>
     </row>
@@ -6277,12 +6663,12 @@
       <c r="D28" s="24" t="inlineStr"/>
       <c r="E28" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:29:47</t>
+          <t>2026-04-16 15:04:47</t>
         </is>
       </c>
       <c r="F28" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:30:04</t>
+          <t>2026-04-16 15:05:01</t>
         </is>
       </c>
     </row>
@@ -6299,18 +6685,18 @@
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr"/>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:24:17</t>
+          <t>2026-04-16 14:58:17</t>
         </is>
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:24:38</t>
+          <t>2026-04-16 14:59:20</t>
         </is>
       </c>
     </row>
@@ -6333,12 +6719,12 @@
       <c r="D30" s="24" t="inlineStr"/>
       <c r="E30" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:18:47</t>
+          <t>2026-04-16 14:52:47</t>
         </is>
       </c>
       <c r="F30" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:18:52</t>
+          <t>2026-04-16 14:53:05</t>
         </is>
       </c>
     </row>
@@ -6361,12 +6747,12 @@
       <c r="D31" s="24" t="inlineStr"/>
       <c r="E31" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:13:17</t>
+          <t>2026-04-16 14:47:17</t>
         </is>
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:13:39</t>
+          <t>2026-04-16 14:47:33</t>
         </is>
       </c>
     </row>
@@ -6383,18 +6769,18 @@
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr"/>
       <c r="E32" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:07:47</t>
+          <t>2026-04-16 14:40:47</t>
         </is>
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:07:59</t>
+          <t>2026-04-16 14:42:02</t>
         </is>
       </c>
     </row>
@@ -6417,12 +6803,12 @@
       <c r="D33" s="24" t="inlineStr"/>
       <c r="E33" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:02:17</t>
+          <t>2026-04-16 14:35:17</t>
         </is>
       </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:02:42</t>
+          <t>2026-04-16 14:35:28</t>
         </is>
       </c>
     </row>
@@ -6445,12 +6831,12 @@
       <c r="D34" s="24" t="inlineStr"/>
       <c r="E34" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:56:47</t>
+          <t>2026-04-16 14:29:47</t>
         </is>
       </c>
       <c r="F34" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:56:57</t>
+          <t>2026-04-16 14:30:04</t>
         </is>
       </c>
     </row>
@@ -6473,12 +6859,12 @@
       <c r="D35" s="24" t="inlineStr"/>
       <c r="E35" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:51:16</t>
+          <t>2026-04-16 14:24:17</t>
         </is>
       </c>
       <c r="F35" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:51:39</t>
+          <t>2026-04-16 14:24:38</t>
         </is>
       </c>
     </row>
@@ -6501,12 +6887,12 @@
       <c r="D36" s="24" t="inlineStr"/>
       <c r="E36" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:45:46</t>
+          <t>2026-04-16 14:18:47</t>
         </is>
       </c>
       <c r="F36" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:46:06</t>
+          <t>2026-04-16 14:18:52</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6915,12 @@
       <c r="D37" s="24" t="inlineStr"/>
       <c r="E37" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:40:16</t>
+          <t>2026-04-16 14:13:17</t>
         </is>
       </c>
       <c r="F37" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:40:46</t>
+          <t>2026-04-16 14:13:39</t>
         </is>
       </c>
     </row>
@@ -6551,18 +6937,18 @@
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D38" s="24" t="inlineStr"/>
       <c r="E38" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:33:16</t>
+          <t>2026-04-16 14:07:47</t>
         </is>
       </c>
       <c r="F38" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:35:08</t>
+          <t>2026-04-16 14:07:59</t>
         </is>
       </c>
     </row>
@@ -6585,12 +6971,12 @@
       <c r="D39" s="24" t="inlineStr"/>
       <c r="E39" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:27:46</t>
+          <t>2026-04-16 14:02:17</t>
         </is>
       </c>
       <c r="F39" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:28:11</t>
+          <t>2026-04-16 14:02:42</t>
         </is>
       </c>
     </row>
@@ -6613,12 +6999,12 @@
       <c r="D40" s="24" t="inlineStr"/>
       <c r="E40" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:22:16</t>
+          <t>2026-04-16 13:56:47</t>
         </is>
       </c>
       <c r="F40" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:22:35</t>
+          <t>2026-04-16 13:56:57</t>
         </is>
       </c>
     </row>
@@ -6641,12 +7027,12 @@
       <c r="D41" s="24" t="inlineStr"/>
       <c r="E41" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:16:46</t>
+          <t>2026-04-16 13:51:16</t>
         </is>
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:17:00</t>
+          <t>2026-04-16 13:51:39</t>
         </is>
       </c>
     </row>
@@ -6669,12 +7055,12 @@
       <c r="D42" s="24" t="inlineStr"/>
       <c r="E42" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:11:16</t>
+          <t>2026-04-16 13:45:46</t>
         </is>
       </c>
       <c r="F42" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:11:36</t>
+          <t>2026-04-16 13:46:06</t>
         </is>
       </c>
     </row>
@@ -6697,12 +7083,12 @@
       <c r="D43" s="24" t="inlineStr"/>
       <c r="E43" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:05:46</t>
+          <t>2026-04-16 13:40:16</t>
         </is>
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:05:55</t>
+          <t>2026-04-16 13:40:46</t>
         </is>
       </c>
     </row>
@@ -6719,18 +7105,18 @@
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="D44" s="24" t="inlineStr"/>
       <c r="E44" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:00:16</t>
+          <t>2026-04-16 13:33:16</t>
         </is>
       </c>
       <c r="F44" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:00:34</t>
+          <t>2026-04-16 13:35:08</t>
         </is>
       </c>
     </row>
@@ -6753,12 +7139,12 @@
       <c r="D45" s="24" t="inlineStr"/>
       <c r="E45" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:54:46</t>
+          <t>2026-04-16 13:27:46</t>
         </is>
       </c>
       <c r="F45" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:54:55</t>
+          <t>2026-04-16 13:28:11</t>
         </is>
       </c>
     </row>
@@ -6781,12 +7167,12 @@
       <c r="D46" s="24" t="inlineStr"/>
       <c r="E46" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:49:16</t>
+          <t>2026-04-16 13:22:16</t>
         </is>
       </c>
       <c r="F46" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:49:42</t>
+          <t>2026-04-16 13:22:35</t>
         </is>
       </c>
     </row>
@@ -6809,12 +7195,12 @@
       <c r="D47" s="24" t="inlineStr"/>
       <c r="E47" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:43:46</t>
+          <t>2026-04-16 13:16:46</t>
         </is>
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:43:56</t>
+          <t>2026-04-16 13:17:00</t>
         </is>
       </c>
     </row>
@@ -6837,12 +7223,12 @@
       <c r="D48" s="24" t="inlineStr"/>
       <c r="E48" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:38:16</t>
+          <t>2026-04-16 13:11:16</t>
         </is>
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:38:26</t>
+          <t>2026-04-16 13:11:36</t>
         </is>
       </c>
     </row>
@@ -6865,12 +7251,12 @@
       <c r="D49" s="24" t="inlineStr"/>
       <c r="E49" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:32:46</t>
+          <t>2026-04-16 13:05:46</t>
         </is>
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:33:11</t>
+          <t>2026-04-16 13:05:55</t>
         </is>
       </c>
     </row>
@@ -6893,12 +7279,12 @@
       <c r="D50" s="24" t="inlineStr"/>
       <c r="E50" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:27:16</t>
+          <t>2026-04-16 13:00:16</t>
         </is>
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:27:25</t>
+          <t>2026-04-16 13:00:34</t>
         </is>
       </c>
     </row>
@@ -6921,12 +7307,12 @@
       <c r="D51" s="24" t="inlineStr"/>
       <c r="E51" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:21:46</t>
+          <t>2026-04-16 12:54:46</t>
         </is>
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:21:56</t>
+          <t>2026-04-16 12:54:55</t>
         </is>
       </c>
     </row>
@@ -6949,12 +7335,12 @@
       <c r="D52" s="24" t="inlineStr"/>
       <c r="E52" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:16:16</t>
+          <t>2026-04-16 12:49:16</t>
         </is>
       </c>
       <c r="F52" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:16:30</t>
+          <t>2026-04-16 12:49:42</t>
         </is>
       </c>
     </row>
@@ -6977,12 +7363,12 @@
       <c r="D53" s="24" t="inlineStr"/>
       <c r="E53" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:10:46</t>
+          <t>2026-04-16 12:43:46</t>
         </is>
       </c>
       <c r="F53" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:10:54</t>
+          <t>2026-04-16 12:43:56</t>
         </is>
       </c>
     </row>
@@ -6999,18 +7385,18 @@
       </c>
       <c r="C54" s="24" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D54" s="24" t="inlineStr"/>
       <c r="E54" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:03:46</t>
+          <t>2026-04-16 12:38:16</t>
         </is>
       </c>
       <c r="F54" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:05:18</t>
+          <t>2026-04-16 12:38:26</t>
         </is>
       </c>
     </row>
@@ -7033,12 +7419,12 @@
       <c r="D55" s="24" t="inlineStr"/>
       <c r="E55" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:58:16</t>
+          <t>2026-04-16 12:32:46</t>
         </is>
       </c>
       <c r="F55" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:58:21</t>
+          <t>2026-04-16 12:33:11</t>
         </is>
       </c>
     </row>
@@ -7061,12 +7447,12 @@
       <c r="D56" s="24" t="inlineStr"/>
       <c r="E56" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:52:46</t>
+          <t>2026-04-16 12:27:16</t>
         </is>
       </c>
       <c r="F56" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:52:56</t>
+          <t>2026-04-16 12:27:25</t>
         </is>
       </c>
     </row>
@@ -7089,12 +7475,12 @@
       <c r="D57" s="24" t="inlineStr"/>
       <c r="E57" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:47:16</t>
+          <t>2026-04-16 12:21:46</t>
         </is>
       </c>
       <c r="F57" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:47:21</t>
+          <t>2026-04-16 12:21:56</t>
         </is>
       </c>
     </row>
@@ -7117,12 +7503,12 @@
       <c r="D58" s="24" t="inlineStr"/>
       <c r="E58" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:41:46</t>
+          <t>2026-04-16 12:16:16</t>
         </is>
       </c>
       <c r="F58" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:41:54</t>
+          <t>2026-04-16 12:16:30</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7531,12 @@
       <c r="D59" s="24" t="inlineStr"/>
       <c r="E59" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:36:16</t>
+          <t>2026-04-16 12:10:46</t>
         </is>
       </c>
       <c r="F59" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:36:27</t>
+          <t>2026-04-16 12:10:54</t>
         </is>
       </c>
     </row>
@@ -7167,18 +7553,18 @@
       </c>
       <c r="C60" s="24" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="D60" s="24" t="inlineStr"/>
       <c r="E60" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 18:04:54</t>
+          <t>2026-04-16 12:03:46</t>
         </is>
       </c>
       <c r="F60" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 18:04:59</t>
+          <t>2026-04-16 12:05:18</t>
         </is>
       </c>
     </row>
@@ -7201,12 +7587,12 @@
       <c r="D61" s="24" t="inlineStr"/>
       <c r="E61" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:59:39</t>
+          <t>2026-04-16 11:58:16</t>
         </is>
       </c>
       <c r="F61" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:59:51</t>
+          <t>2026-04-16 11:58:21</t>
         </is>
       </c>
     </row>
@@ -7223,18 +7609,18 @@
       </c>
       <c r="C62" s="24" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D62" s="24" t="inlineStr"/>
       <c r="E62" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:53:24</t>
+          <t>2026-04-16 11:52:46</t>
         </is>
       </c>
       <c r="F62" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:54:26</t>
+          <t>2026-04-16 11:52:56</t>
         </is>
       </c>
     </row>
@@ -7257,12 +7643,12 @@
       <c r="D63" s="24" t="inlineStr"/>
       <c r="E63" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:48:09</t>
+          <t>2026-04-16 11:47:16</t>
         </is>
       </c>
       <c r="F63" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:48:14</t>
+          <t>2026-04-16 11:47:21</t>
         </is>
       </c>
     </row>
@@ -7285,12 +7671,12 @@
       <c r="D64" s="24" t="inlineStr"/>
       <c r="E64" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:42:54</t>
+          <t>2026-04-16 11:41:46</t>
         </is>
       </c>
       <c r="F64" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:43:03</t>
+          <t>2026-04-16 11:41:54</t>
         </is>
       </c>
     </row>
@@ -7313,12 +7699,12 @@
       <c r="D65" s="24" t="inlineStr"/>
       <c r="E65" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:37:09</t>
+          <t>2026-04-16 11:36:16</t>
         </is>
       </c>
       <c r="F65" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:37:42</t>
+          <t>2026-04-16 11:36:27</t>
         </is>
       </c>
     </row>
@@ -7341,12 +7727,12 @@
       <c r="D66" s="24" t="inlineStr"/>
       <c r="E66" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:31:54</t>
+          <t>2026-04-15 18:04:54</t>
         </is>
       </c>
       <c r="F66" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:32:07</t>
+          <t>2026-04-15 18:04:59</t>
         </is>
       </c>
     </row>
@@ -7369,204 +7755,180 @@
       <c r="D67" s="24" t="inlineStr"/>
       <c r="E67" s="24" t="inlineStr">
         <is>
+          <t>2026-04-15 17:59:39</t>
+        </is>
+      </c>
+      <c r="F67" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:59:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="D68" s="24" t="inlineStr"/>
+      <c r="E68" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:53:24</t>
+        </is>
+      </c>
+      <c r="F68" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:54:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B69" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C69" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D69" s="24" t="inlineStr"/>
+      <c r="E69" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:48:09</t>
+        </is>
+      </c>
+      <c r="F69" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:48:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B70" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C70" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D70" s="24" t="inlineStr"/>
+      <c r="E70" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:42:54</t>
+        </is>
+      </c>
+      <c r="F70" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:43:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C71" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D71" s="24" t="inlineStr"/>
+      <c r="E71" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:37:09</t>
+        </is>
+      </c>
+      <c r="F71" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:37:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B72" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C72" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D72" s="24" t="inlineStr"/>
+      <c r="E72" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:31:54</t>
+        </is>
+      </c>
+      <c r="F72" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-15 17:32:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B73" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C73" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D73" s="24" t="inlineStr"/>
+      <c r="E73" s="24" t="inlineStr">
+        <is>
           <t>2026-04-15 17:25:54</t>
         </is>
       </c>
-      <c r="F67" s="24" t="inlineStr">
+      <c r="F73" s="24" t="inlineStr">
         <is>
           <t>2026-04-15 17:26:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B68" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C68" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D68" s="23" t="inlineStr">
-        <is>
-          <t>Quota exceeded. Check your plan and billing details.</t>
-        </is>
-      </c>
-      <c r="E68" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:20:39</t>
-        </is>
-      </c>
-      <c r="F68" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:20:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B69" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C69" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D69" s="23" t="inlineStr">
-        <is>
-          <t>Quota exceeded. Check your plan and billing details.</t>
-        </is>
-      </c>
-      <c r="E69" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:15:24</t>
-        </is>
-      </c>
-      <c r="F69" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:15:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B70" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C70" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D70" s="23" t="inlineStr">
-        <is>
-          <t>unknown variant `api-key`, expected one of `apikey`, `chatgpt`, `chatgptAuthTokens` at line 2 column 24</t>
-        </is>
-      </c>
-      <c r="E70" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:10:09</t>
-        </is>
-      </c>
-      <c r="F70" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:10:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B71" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C71" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D71" s="23" t="inlineStr">
-        <is>
-          <t>{"type":"error","status":400,"error":{"type":"invalid_request_error","message":"The 'gpt-4o-mini' model is not supported when using Codex with a ChatGPT account."}}</t>
-        </is>
-      </c>
-      <c r="E71" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:04:54</t>
-        </is>
-      </c>
-      <c r="F71" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:04:57</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B72" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C72" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D72" s="23" t="inlineStr">
-        <is>
-          <t>{"type":"error","status":400,"error":{"type":"invalid_request_error","message":"The 'gpt-4o-mini' model is not supported when using Codex with a ChatGPT account."}}</t>
-        </is>
-      </c>
-      <c r="E72" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:59:39</t>
-        </is>
-      </c>
-      <c r="F72" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:59:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B73" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C73" s="23" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D73" s="23" t="inlineStr">
-        <is>
-          <t>{"type":"error","status":400,"error":{"type":"invalid_request_error","message":"The 'gpt-oss:20b' model is not supported when using Codex with a ChatGPT account."}}</t>
-        </is>
-      </c>
-      <c r="E73" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:54:24</t>
-        </is>
-      </c>
-      <c r="F73" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 16:54:30</t>
         </is>
       </c>
     </row>
@@ -7588,17 +7950,17 @@
       </c>
       <c r="D74" s="23" t="inlineStr">
         <is>
-          <t>{"type":"error","status":400,"error":{"type":"invalid_request_error","message":"The 'gpt-oss:20b' model is not supported when using Codex with a ChatGPT account."}}</t>
+          <t>Quota exceeded. Check your plan and billing details.</t>
         </is>
       </c>
       <c r="E74" s="23" t="inlineStr">
         <is>
-          <t>2026-04-15 16:49:09</t>
+          <t>2026-04-15 17:20:39</t>
         </is>
       </c>
       <c r="F74" s="23" t="inlineStr">
         <is>
-          <t>2026-04-15 16:49:13</t>
+          <t>2026-04-15 17:20:46</t>
         </is>
       </c>
     </row>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -1326,7 +1326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="7" min="1" max="1"/>
@@ -4880,6 +4880,486 @@
       <c r="J76" t="inlineStr">
         <is>
           <t>[Session 8 04/16] whsec_ key configured</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t>T-100</t>
+        </is>
+      </c>
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>Paperclip</t>
+        </is>
+      </c>
+      <c r="C77" s="17" t="inlineStr">
+        <is>
+          <t>CTO-01 Grille de vetuste data file (JSON)</t>
+        </is>
+      </c>
+      <c r="D77" s="17" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="E77" s="17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F77" s="17" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G77" s="17" t="n"/>
+      <c r="H77" s="17" t="n"/>
+      <c r="I77" s="17" t="n"/>
+      <c r="J77" s="17" t="inlineStr">
+        <is>
+          <t>[Auto-added from Paperclip 04/17]</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>T-102</t>
+        </is>
+      </c>
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>Paperclip</t>
+        </is>
+      </c>
+      <c r="C78" s="16" t="inlineStr">
+        <is>
+          <t>CEO-02 Cold outreach DM template FR (400 chars max)</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E78" s="16" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="F78" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G78" s="16" t="n"/>
+      <c r="H78" s="16" t="n"/>
+      <c r="I78" s="16" t="n"/>
+      <c r="J78" s="16" t="inlineStr">
+        <is>
+          <t>[Auto-added from Paperclip 04/17]</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>T-105</t>
+        </is>
+      </c>
+      <c r="B79" s="16" t="inlineStr">
+        <is>
+          <t>Paperclip</t>
+        </is>
+      </c>
+      <c r="C79" s="16" t="inlineStr">
+        <is>
+          <t>CEO-03 Politique de confidentialite FR</t>
+        </is>
+      </c>
+      <c r="D79" s="16" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E79" s="16" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="F79" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G79" s="16" t="n"/>
+      <c r="H79" s="16" t="n"/>
+      <c r="I79" s="16" t="n"/>
+      <c r="J79" s="16" t="inlineStr">
+        <is>
+          <t>[Auto-added from Paperclip 04/17]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t>T-109</t>
+        </is>
+      </c>
+      <c r="B80" s="16" t="inlineStr">
+        <is>
+          <t>Paperclip</t>
+        </is>
+      </c>
+      <c r="C80" s="16" t="inlineStr">
+        <is>
+          <t>CTO-05 Security checklist for API routes</t>
+        </is>
+      </c>
+      <c r="D80" s="16" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="E80" s="16" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="F80" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G80" s="16" t="n"/>
+      <c r="H80" s="16" t="n"/>
+      <c r="I80" s="16" t="n"/>
+      <c r="J80" s="16" t="inlineStr">
+        <is>
+          <t>[Auto-added from Paperclip 04/17]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="16" t="inlineStr">
+        <is>
+          <t>T-114</t>
+        </is>
+      </c>
+      <c r="B81" s="16" t="inlineStr">
+        <is>
+          <t>Paperclip</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="inlineStr">
+        <is>
+          <t>CEO-05 CGU FR</t>
+        </is>
+      </c>
+      <c r="D81" s="16" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E81" s="16" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="F81" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G81" s="16" t="n"/>
+      <c r="H81" s="16" t="n"/>
+      <c r="I81" s="16" t="n"/>
+      <c r="J81" s="16" t="inlineStr">
+        <is>
+          <t>[Auto-added from Paperclip 04/17]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="16" t="inlineStr">
+        <is>
+          <t>T-120</t>
+        </is>
+      </c>
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>Paperclip</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>CEO-07 Politique de remboursement FR</t>
+        </is>
+      </c>
+      <c r="D82" s="16" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E82" s="16" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="F82" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G82" s="16" t="n"/>
+      <c r="H82" s="16" t="n"/>
+      <c r="I82" s="16" t="n"/>
+      <c r="J82" s="16" t="inlineStr">
+        <is>
+          <t>[Auto-added from Paperclip 04/17]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="16" t="inlineStr">
+        <is>
+          <t>T-127</t>
+        </is>
+      </c>
+      <c r="B83" s="16" t="inlineStr">
+        <is>
+          <t>Paperclip</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="inlineStr">
+        <is>
+          <t>CEO-08 Refund Policy EN (translate FR)</t>
+        </is>
+      </c>
+      <c r="D83" s="16" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E83" s="16" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="F83" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G83" s="16" t="n"/>
+      <c r="H83" s="16" t="n"/>
+      <c r="I83" s="16" t="n"/>
+      <c r="J83" s="16" t="inlineStr">
+        <is>
+          <t>[Auto-added from Paperclip 04/17]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="16" t="inlineStr">
+        <is>
+          <t>T-135</t>
+        </is>
+      </c>
+      <c r="B84" s="16" t="inlineStr">
+        <is>
+          <t>Paperclip</t>
+        </is>
+      </c>
+      <c r="C84" s="16" t="inlineStr">
+        <is>
+          <t>CTO-02 ADR-001 Grille de vetuste integration</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="E84" s="16" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="F84" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G84" s="16" t="n"/>
+      <c r="H84" s="16" t="n"/>
+      <c r="I84" s="16" t="n"/>
+      <c r="J84" s="16" t="inlineStr">
+        <is>
+          <t>[Auto-added from Paperclip 04/17]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>T-144</t>
+        </is>
+      </c>
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>Paperclip</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="inlineStr">
+        <is>
+          <t>CTO-03 Prompt spec for /api/ai/scan v2 (Haiku)</t>
+        </is>
+      </c>
+      <c r="D85" s="16" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="E85" s="16" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="F85" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G85" s="16" t="n"/>
+      <c r="H85" s="16" t="n"/>
+      <c r="I85" s="16" t="n"/>
+      <c r="J85" s="16" t="inlineStr">
+        <is>
+          <t>[Auto-added from Paperclip 04/17]</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>T-154</t>
+        </is>
+      </c>
+      <c r="B86" s="16" t="inlineStr">
+        <is>
+          <t>Paperclip</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="inlineStr">
+        <is>
+          <t>CTO-04 Prompt spec for /api/ai/dispute v2 (Sonnet)</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="E86" s="16" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="F86" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G86" s="16" t="n"/>
+      <c r="H86" s="16" t="n"/>
+      <c r="I86" s="16" t="n"/>
+      <c r="J86" s="16" t="inlineStr">
+        <is>
+          <t>[Auto-added from Paperclip 04/17]</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>T-165</t>
+        </is>
+      </c>
+      <c r="B87" s="16" t="inlineStr">
+        <is>
+          <t>Paperclip</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="inlineStr">
+        <is>
+          <t>CTO-06 T-103 end-to-end smoke test plan</t>
+        </is>
+      </c>
+      <c r="D87" s="16" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="E87" s="16" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="F87" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G87" s="16" t="n"/>
+      <c r="H87" s="16" t="n"/>
+      <c r="I87" s="16" t="n"/>
+      <c r="J87" s="16" t="inlineStr">
+        <is>
+          <t>[Auto-added from Paperclip 04/17]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="17" t="inlineStr">
+        <is>
+          <t>T-177</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>Paperclip</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>CEO-01 PDF disclaimer footer (FR+EN, 25 words each)</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="n"/>
+      <c r="H88" s="17" t="n"/>
+      <c r="I88" s="17" t="n"/>
+      <c r="J88" s="17" t="inlineStr">
+        <is>
+          <t>[Auto-added from Paperclip 04/17]</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5882,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>PAPERCLIP STATUS — 2026-04-16 17:18</t>
+          <t>PAPERCLIP STATUS — 2026-04-17 11:18</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5968,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>idle</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -5513,7 +5993,7 @@
       </c>
       <c r="G5" s="20" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$13.78</t>
         </is>
       </c>
     </row>
@@ -5827,7 +6307,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -5847,7 +6327,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -5894,7 +6374,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>96</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26">
@@ -5904,7 +6384,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -5922,7 +6402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="7" min="1" max="1"/>
@@ -5936,7 +6416,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>RUN HISTORY (Last 24h) — 2026-04-16 17:18</t>
+          <t>RUN HISTORY (Last 24h) — 2026-04-17 11:18</t>
         </is>
       </c>
     </row>
@@ -5991,12 +6471,12 @@
       <c r="D4" s="24" t="inlineStr"/>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 17:17:17</t>
+          <t>2026-04-17 11:17:52</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 17:17:31</t>
+          <t>2026-04-17 11:18:03</t>
         </is>
       </c>
     </row>
@@ -6019,12 +6499,12 @@
       <c r="D5" s="24" t="inlineStr"/>
       <c r="E5" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 17:11:47</t>
+          <t>2026-04-17 11:12:14</t>
         </is>
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 17:12:05</t>
+          <t>2026-04-17 11:12:43</t>
         </is>
       </c>
     </row>
@@ -6047,19 +6527,19 @@
       <c r="D6" s="24" t="inlineStr"/>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 17:06:17</t>
+          <t>2026-04-17 11:08:52</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 17:06:29</t>
+          <t>2026-04-17 11:08:58</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
@@ -6075,12 +6555,12 @@
       <c r="D7" s="24" t="inlineStr"/>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 17:00:47</t>
+          <t>2026-04-17 11:03:30</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 17:01:13</t>
+          <t>2026-04-17 11:03:37</t>
         </is>
       </c>
     </row>
@@ -6103,12 +6583,12 @@
       <c r="D8" s="24" t="inlineStr"/>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:55:17</t>
+          <t>2026-04-17 11:03:24</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:55:39</t>
+          <t>2026-04-17 11:03:35</t>
         </is>
       </c>
     </row>
@@ -6131,19 +6611,19 @@
       <c r="D9" s="24" t="inlineStr"/>
       <c r="E9" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:49:17</t>
+          <t>2026-04-17 11:01:52</t>
         </is>
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:49:55</t>
+          <t>2026-04-17 11:02:02</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
@@ -6159,12 +6639,12 @@
       <c r="D10" s="24" t="inlineStr"/>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:43:47</t>
+          <t>2026-04-17 10:56:27</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:43:58</t>
+          <t>2026-04-17 10:56:35</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6667,12 @@
       <c r="D11" s="24" t="inlineStr"/>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:38:17</t>
+          <t>2026-04-17 10:56:27</t>
         </is>
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:38:36</t>
+          <t>2026-04-17 10:56:35</t>
         </is>
       </c>
     </row>
@@ -6215,12 +6695,12 @@
       <c r="D12" s="24" t="inlineStr"/>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:32:47</t>
+          <t>2026-04-17 10:53:52</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:32:58</t>
+          <t>2026-04-17 10:54:01</t>
         </is>
       </c>
     </row>
@@ -6243,12 +6723,12 @@
       <c r="D13" s="24" t="inlineStr"/>
       <c r="E13" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:27:17</t>
+          <t>2026-04-17 10:48:22</t>
         </is>
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:27:25</t>
+          <t>2026-04-17 10:48:37</t>
         </is>
       </c>
     </row>
@@ -6271,12 +6751,12 @@
       <c r="D14" s="24" t="inlineStr"/>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:21:47</t>
+          <t>2026-04-17 10:42:52</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:22:05</t>
+          <t>2026-04-17 10:43:02</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6779,12 @@
       <c r="D15" s="24" t="inlineStr"/>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:16:17</t>
+          <t>2026-04-17 10:37:22</t>
         </is>
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:16:42</t>
+          <t>2026-04-17 10:37:29</t>
         </is>
       </c>
     </row>
@@ -6327,12 +6807,12 @@
       <c r="D16" s="24" t="inlineStr"/>
       <c r="E16" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:10:47</t>
+          <t>2026-04-17 10:31:52</t>
         </is>
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:10:58</t>
+          <t>2026-04-17 10:32:02</t>
         </is>
       </c>
     </row>
@@ -6355,12 +6835,12 @@
       <c r="D17" s="24" t="inlineStr"/>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:05:17</t>
+          <t>2026-04-17 10:26:22</t>
         </is>
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:05:45</t>
+          <t>2026-04-17 10:26:28</t>
         </is>
       </c>
     </row>
@@ -6383,12 +6863,12 @@
       <c r="D18" s="24" t="inlineStr"/>
       <c r="E18" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:59:47</t>
+          <t>2026-04-17 10:20:52</t>
         </is>
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:59:56</t>
+          <t>2026-04-17 10:21:17</t>
         </is>
       </c>
     </row>
@@ -6411,12 +6891,12 @@
       <c r="D19" s="24" t="inlineStr"/>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:54:17</t>
+          <t>2026-04-17 10:15:22</t>
         </is>
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:54:38</t>
+          <t>2026-04-17 10:15:29</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6919,12 @@
       <c r="D20" s="24" t="inlineStr"/>
       <c r="E20" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:48:47</t>
+          <t>2026-04-17 10:09:52</t>
         </is>
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:48:52</t>
+          <t>2026-04-17 10:10:05</t>
         </is>
       </c>
     </row>
@@ -6467,12 +6947,12 @@
       <c r="D21" s="24" t="inlineStr"/>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:43:17</t>
+          <t>2026-04-17 10:04:22</t>
         </is>
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:43:41</t>
+          <t>2026-04-17 10:04:38</t>
         </is>
       </c>
     </row>
@@ -6495,12 +6975,12 @@
       <c r="D22" s="24" t="inlineStr"/>
       <c r="E22" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:37:47</t>
+          <t>2026-04-17 09:58:52</t>
         </is>
       </c>
       <c r="F22" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:38:01</t>
+          <t>2026-04-17 09:59:08</t>
         </is>
       </c>
     </row>
@@ -6523,12 +7003,12 @@
       <c r="D23" s="24" t="inlineStr"/>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:32:17</t>
+          <t>2026-04-17 09:53:22</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:32:41</t>
+          <t>2026-04-17 09:53:29</t>
         </is>
       </c>
     </row>
@@ -6551,12 +7031,12 @@
       <c r="D24" s="24" t="inlineStr"/>
       <c r="E24" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:26:47</t>
+          <t>2026-04-17 09:47:52</t>
         </is>
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:27:04</t>
+          <t>2026-04-17 09:47:58</t>
         </is>
       </c>
     </row>
@@ -6579,12 +7059,12 @@
       <c r="D25" s="24" t="inlineStr"/>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:21:17</t>
+          <t>2026-04-17 09:42:22</t>
         </is>
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:21:40</t>
+          <t>2026-04-17 09:42:27</t>
         </is>
       </c>
     </row>
@@ -6607,12 +7087,12 @@
       <c r="D26" s="24" t="inlineStr"/>
       <c r="E26" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:15:47</t>
+          <t>2026-04-17 09:36:52</t>
         </is>
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:16:00</t>
+          <t>2026-04-17 09:37:00</t>
         </is>
       </c>
     </row>
@@ -6629,74 +7109,82 @@
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>8m</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr"/>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:10:17</t>
+          <t>2026-04-17 09:23:27</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:10:37</t>
+          <t>2026-04-17 09:31:27</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D28" s="24" t="inlineStr"/>
-      <c r="E28" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:04:47</t>
-        </is>
-      </c>
-      <c r="F28" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:05:01</t>
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>17m</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:49:10</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 09:06:32</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B29" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
-      <c r="D29" s="24" t="inlineStr"/>
-      <c r="E29" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:58:17</t>
-        </is>
-      </c>
-      <c r="F29" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:59:20</t>
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>16m</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:16:50</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:33:02</t>
         </is>
       </c>
     </row>
@@ -6719,12 +7207,12 @@
       <c r="D30" s="24" t="inlineStr"/>
       <c r="E30" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:52:47</t>
+          <t>2026-04-17 08:11:20</t>
         </is>
       </c>
       <c r="F30" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:53:05</t>
+          <t>2026-04-17 08:11:28</t>
         </is>
       </c>
     </row>
@@ -6747,12 +7235,12 @@
       <c r="D31" s="24" t="inlineStr"/>
       <c r="E31" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:47:17</t>
+          <t>2026-04-17 08:05:50</t>
         </is>
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:47:33</t>
+          <t>2026-04-17 08:06:12</t>
         </is>
       </c>
     </row>
@@ -6769,18 +7257,18 @@
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr"/>
       <c r="E32" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:40:47</t>
+          <t>2026-04-17 07:59:50</t>
         </is>
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:42:02</t>
+          <t>2026-04-17 08:00:20</t>
         </is>
       </c>
     </row>
@@ -6803,712 +7291,812 @@
       <c r="D33" s="24" t="inlineStr"/>
       <c r="E33" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:35:17</t>
+          <t>2026-04-17 07:54:20</t>
         </is>
       </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:35:28</t>
+          <t>2026-04-17 07:54:45</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B34" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D34" s="24" t="inlineStr"/>
-      <c r="E34" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:29:47</t>
-        </is>
-      </c>
-      <c r="F34" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:30:04</t>
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>20m</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 07:33:28</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 07:54:20</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B35" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D35" s="24" t="inlineStr"/>
-      <c r="E35" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:24:17</t>
-        </is>
-      </c>
-      <c r="F35" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:24:38</t>
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>16m</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 07:16:37</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 07:33:28</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D36" s="24" t="inlineStr"/>
-      <c r="E36" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:18:47</t>
-        </is>
-      </c>
-      <c r="F36" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:18:52</t>
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>17m</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E36" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 06:58:44</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 07:16:37</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D37" s="24" t="inlineStr"/>
-      <c r="E37" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:13:17</t>
-        </is>
-      </c>
-      <c r="F37" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:13:39</t>
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>28m</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 06:30:30</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 06:58:44</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B38" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="inlineStr"/>
-      <c r="E38" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:07:47</t>
-        </is>
-      </c>
-      <c r="F38" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:07:59</t>
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>16m</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 06:13:51</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 06:30:30</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D39" s="24" t="inlineStr"/>
-      <c r="E39" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:02:17</t>
-        </is>
-      </c>
-      <c r="F39" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:02:42</t>
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>17m</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 05:40:44</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 05:57:55</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B40" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D40" s="24" t="inlineStr"/>
-      <c r="E40" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:56:47</t>
-        </is>
-      </c>
-      <c r="F40" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:56:57</t>
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>15m</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 05:13:44</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 05:28:51</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D41" s="24" t="inlineStr"/>
-      <c r="E41" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:51:16</t>
-        </is>
-      </c>
-      <c r="F41" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:51:39</t>
+      <c r="A41" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>30m</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 04:26:04</t>
+        </is>
+      </c>
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 04:56:33</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B42" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D42" s="24" t="inlineStr"/>
-      <c r="E42" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:45:46</t>
-        </is>
-      </c>
-      <c r="F42" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:46:06</t>
+      <c r="A42" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>16m</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:53:51</t>
+        </is>
+      </c>
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 04:10:45</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B43" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C43" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D43" s="24" t="inlineStr"/>
-      <c r="E43" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:40:16</t>
-        </is>
-      </c>
-      <c r="F43" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:40:46</t>
+      <c r="A43" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>15m</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:38:43</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:53:51</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B44" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
-      <c r="D44" s="24" t="inlineStr"/>
-      <c r="E44" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:33:16</t>
-        </is>
-      </c>
-      <c r="F44" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:35:08</t>
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>19m</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:11:18</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:30:37</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D45" s="24" t="inlineStr"/>
-      <c r="E45" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:27:46</t>
-        </is>
-      </c>
-      <c r="F45" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:28:11</t>
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>16m</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:37:43</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:54:24</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B46" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C46" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D46" s="24" t="inlineStr"/>
-      <c r="E46" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:22:16</t>
-        </is>
-      </c>
-      <c r="F46" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:22:35</t>
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>17m</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:10:00</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:27:59</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B47" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D47" s="24" t="inlineStr"/>
-      <c r="E47" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:16:46</t>
-        </is>
-      </c>
-      <c r="F47" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:17:00</t>
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>29m</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 01:25:01</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 01:54:16</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B48" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="inlineStr"/>
-      <c r="E48" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:11:16</t>
-        </is>
-      </c>
-      <c r="F48" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:11:36</t>
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C48" s="23" t="inlineStr">
+        <is>
+          <t>15m</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E48" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 01:09:55</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 01:25:01</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B49" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C49" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="inlineStr"/>
-      <c r="E49" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:05:46</t>
-        </is>
-      </c>
-      <c r="F49" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:05:55</t>
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C49" s="23" t="inlineStr">
+        <is>
+          <t>20m</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 00:33:15</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 00:53:19</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C50" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D50" s="24" t="inlineStr"/>
-      <c r="E50" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:00:16</t>
-        </is>
-      </c>
-      <c r="F50" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:00:34</t>
+      <c r="A50" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C50" s="23" t="inlineStr">
+        <is>
+          <t>24m</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E50" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:51:44</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 00:16:23</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B51" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C51" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D51" s="24" t="inlineStr"/>
-      <c r="E51" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:54:46</t>
-        </is>
-      </c>
-      <c r="F51" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:54:55</t>
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="inlineStr">
+        <is>
+          <t>28m</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:23:05</t>
+        </is>
+      </c>
+      <c r="F51" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:51:44</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B52" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C52" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D52" s="24" t="inlineStr"/>
-      <c r="E52" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:49:16</t>
-        </is>
-      </c>
-      <c r="F52" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:49:42</t>
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="inlineStr">
+        <is>
+          <t>16m</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E52" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:06:41</t>
+        </is>
+      </c>
+      <c r="F52" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:23:05</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B53" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C53" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D53" s="24" t="inlineStr"/>
-      <c r="E53" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:43:46</t>
-        </is>
-      </c>
-      <c r="F53" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:43:56</t>
+      <c r="A53" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="inlineStr">
+        <is>
+          <t>26m</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E53" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:24:28</t>
+        </is>
+      </c>
+      <c r="F53" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:50:39</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B54" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C54" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D54" s="24" t="inlineStr"/>
-      <c r="E54" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:38:16</t>
-        </is>
-      </c>
-      <c r="F54" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:38:26</t>
+      <c r="A54" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="inlineStr">
+        <is>
+          <t>18m</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E54" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:06:27</t>
+        </is>
+      </c>
+      <c r="F54" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:24:28</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B55" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C55" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D55" s="24" t="inlineStr"/>
-      <c r="E55" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:32:46</t>
-        </is>
-      </c>
-      <c r="F55" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:33:11</t>
+      <c r="A55" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>31m</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:18:50</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:50:20</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B56" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C56" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D56" s="24" t="inlineStr"/>
-      <c r="E56" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:27:16</t>
-        </is>
-      </c>
-      <c r="F56" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:27:25</t>
+      <c r="A56" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B56" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C56" s="23" t="inlineStr">
+        <is>
+          <t>16m</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E56" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:02:10</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:18:50</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B57" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C57" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D57" s="24" t="inlineStr"/>
-      <c r="E57" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:21:46</t>
-        </is>
-      </c>
-      <c r="F57" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:21:56</t>
+      <c r="A57" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B57" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C57" s="23" t="inlineStr">
+        <is>
+          <t>27m</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E57" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:19:12</t>
+        </is>
+      </c>
+      <c r="F57" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:46:53</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B58" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C58" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D58" s="24" t="inlineStr"/>
-      <c r="E58" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:16:16</t>
-        </is>
-      </c>
-      <c r="F58" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:16:30</t>
+      <c r="A58" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B58" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C58" s="23" t="inlineStr">
+        <is>
+          <t>15m</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E58" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 19:47:03</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:02:06</t>
         </is>
       </c>
     </row>
@@ -7531,152 +8119,172 @@
       <c r="D59" s="24" t="inlineStr"/>
       <c r="E59" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:10:46</t>
+          <t>2026-04-16 19:30:43</t>
         </is>
       </c>
       <c r="F59" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:10:54</t>
+          <t>2026-04-16 19:30:51</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B60" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C60" s="24" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
-      <c r="D60" s="24" t="inlineStr"/>
-      <c r="E60" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:03:46</t>
-        </is>
-      </c>
-      <c r="F60" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:05:18</t>
+      <c r="A60" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B60" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C60" s="23" t="inlineStr">
+        <is>
+          <t>21m</t>
+        </is>
+      </c>
+      <c r="D60" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E60" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 19:01:04</t>
+        </is>
+      </c>
+      <c r="F60" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 19:22:22</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B61" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C61" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D61" s="24" t="inlineStr"/>
-      <c r="E61" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 11:58:16</t>
-        </is>
-      </c>
-      <c r="F61" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 11:58:21</t>
+      <c r="A61" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B61" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C61" s="23" t="inlineStr">
+        <is>
+          <t>15m</t>
+        </is>
+      </c>
+      <c r="D61" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E61" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 18:40:38</t>
+        </is>
+      </c>
+      <c r="F61" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 18:55:55</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B62" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C62" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D62" s="24" t="inlineStr"/>
-      <c r="E62" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 11:52:46</t>
-        </is>
-      </c>
-      <c r="F62" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 11:52:56</t>
+      <c r="A62" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B62" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C62" s="23" t="inlineStr">
+        <is>
+          <t>17m</t>
+        </is>
+      </c>
+      <c r="D62" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E62" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 18:06:53</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 18:24:23</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B63" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C63" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D63" s="24" t="inlineStr"/>
-      <c r="E63" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 11:47:16</t>
-        </is>
-      </c>
-      <c r="F63" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 11:47:21</t>
+      <c r="A63" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B63" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C63" s="23" t="inlineStr">
+        <is>
+          <t>15m</t>
+        </is>
+      </c>
+      <c r="D63" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E63" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 17:51:34</t>
+        </is>
+      </c>
+      <c r="F63" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 18:06:53</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B64" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C64" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D64" s="24" t="inlineStr"/>
-      <c r="E64" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 11:41:46</t>
-        </is>
-      </c>
-      <c r="F64" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 11:41:54</t>
+      <c r="A64" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B64" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C64" s="23" t="inlineStr">
+        <is>
+          <t>17m</t>
+        </is>
+      </c>
+      <c r="D64" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E64" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 17:33:50</t>
+        </is>
+      </c>
+      <c r="F64" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 17:51:34</t>
         </is>
       </c>
     </row>
@@ -7699,12 +8307,12 @@
       <c r="D65" s="24" t="inlineStr"/>
       <c r="E65" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:36:16</t>
+          <t>2026-04-16 17:28:17</t>
         </is>
       </c>
       <c r="F65" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:36:27</t>
+          <t>2026-04-16 17:28:32</t>
         </is>
       </c>
     </row>
@@ -7727,12 +8335,12 @@
       <c r="D66" s="24" t="inlineStr"/>
       <c r="E66" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 18:04:54</t>
+          <t>2026-04-16 17:22:47</t>
         </is>
       </c>
       <c r="F66" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 18:04:59</t>
+          <t>2026-04-16 17:22:58</t>
         </is>
       </c>
     </row>
@@ -7755,12 +8363,12 @@
       <c r="D67" s="24" t="inlineStr"/>
       <c r="E67" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:59:39</t>
+          <t>2026-04-16 17:17:17</t>
         </is>
       </c>
       <c r="F67" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:59:51</t>
+          <t>2026-04-16 17:17:31</t>
         </is>
       </c>
     </row>
@@ -7777,18 +8385,18 @@
       </c>
       <c r="C68" s="24" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D68" s="24" t="inlineStr"/>
       <c r="E68" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:53:24</t>
+          <t>2026-04-16 17:11:47</t>
         </is>
       </c>
       <c r="F68" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:54:26</t>
+          <t>2026-04-16 17:12:05</t>
         </is>
       </c>
     </row>
@@ -7811,12 +8419,12 @@
       <c r="D69" s="24" t="inlineStr"/>
       <c r="E69" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:48:09</t>
+          <t>2026-04-16 17:06:17</t>
         </is>
       </c>
       <c r="F69" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:48:14</t>
+          <t>2026-04-16 17:06:29</t>
         </is>
       </c>
     </row>
@@ -7839,12 +8447,12 @@
       <c r="D70" s="24" t="inlineStr"/>
       <c r="E70" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:42:54</t>
+          <t>2026-04-16 17:00:47</t>
         </is>
       </c>
       <c r="F70" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:43:03</t>
+          <t>2026-04-16 17:01:13</t>
         </is>
       </c>
     </row>
@@ -7867,12 +8475,12 @@
       <c r="D71" s="24" t="inlineStr"/>
       <c r="E71" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:37:09</t>
+          <t>2026-04-16 16:55:17</t>
         </is>
       </c>
       <c r="F71" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:37:42</t>
+          <t>2026-04-16 16:55:39</t>
         </is>
       </c>
     </row>
@@ -7895,12 +8503,12 @@
       <c r="D72" s="24" t="inlineStr"/>
       <c r="E72" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:31:54</t>
+          <t>2026-04-16 16:49:17</t>
         </is>
       </c>
       <c r="F72" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:32:07</t>
+          <t>2026-04-16 16:49:55</t>
         </is>
       </c>
     </row>
@@ -7923,44 +8531,1552 @@
       <c r="D73" s="24" t="inlineStr"/>
       <c r="E73" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:25:54</t>
+          <t>2026-04-16 16:43:47</t>
         </is>
       </c>
       <c r="F73" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 17:26:46</t>
+          <t>2026-04-16 16:43:58</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B74" s="23" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="C74" s="23" t="inlineStr">
+      <c r="A74" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B74" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C74" s="24" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="D74" s="23" t="inlineStr">
-        <is>
-          <t>Quota exceeded. Check your plan and billing details.</t>
-        </is>
-      </c>
-      <c r="E74" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:20:39</t>
-        </is>
-      </c>
-      <c r="F74" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:20:46</t>
+      <c r="D74" s="24" t="inlineStr"/>
+      <c r="E74" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:38:17</t>
+        </is>
+      </c>
+      <c r="F74" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:38:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B75" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C75" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D75" s="24" t="inlineStr"/>
+      <c r="E75" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:32:47</t>
+        </is>
+      </c>
+      <c r="F75" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:32:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B76" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C76" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D76" s="24" t="inlineStr"/>
+      <c r="E76" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:27:17</t>
+        </is>
+      </c>
+      <c r="F76" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:27:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B77" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C77" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr"/>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:21:47</t>
+        </is>
+      </c>
+      <c r="F77" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:22:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B78" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C78" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D78" s="24" t="inlineStr"/>
+      <c r="E78" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:16:17</t>
+        </is>
+      </c>
+      <c r="F78" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:16:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B79" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C79" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D79" s="24" t="inlineStr"/>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:10:47</t>
+        </is>
+      </c>
+      <c r="F79" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:10:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B80" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C80" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D80" s="24" t="inlineStr"/>
+      <c r="E80" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:05:17</t>
+        </is>
+      </c>
+      <c r="F80" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:05:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C81" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="inlineStr"/>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:59:47</t>
+        </is>
+      </c>
+      <c r="F81" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:59:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B82" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C82" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D82" s="24" t="inlineStr"/>
+      <c r="E82" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:54:17</t>
+        </is>
+      </c>
+      <c r="F82" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:54:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C83" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr"/>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:48:47</t>
+        </is>
+      </c>
+      <c r="F83" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:48:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B84" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C84" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D84" s="24" t="inlineStr"/>
+      <c r="E84" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:43:17</t>
+        </is>
+      </c>
+      <c r="F84" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:43:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B85" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C85" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr"/>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:37:47</t>
+        </is>
+      </c>
+      <c r="F85" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:38:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B86" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C86" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D86" s="24" t="inlineStr"/>
+      <c r="E86" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:32:17</t>
+        </is>
+      </c>
+      <c r="F86" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:32:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B87" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C87" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="inlineStr"/>
+      <c r="E87" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:26:47</t>
+        </is>
+      </c>
+      <c r="F87" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:27:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B88" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C88" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D88" s="24" t="inlineStr"/>
+      <c r="E88" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:21:17</t>
+        </is>
+      </c>
+      <c r="F88" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:21:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C89" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="inlineStr"/>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:15:47</t>
+        </is>
+      </c>
+      <c r="F89" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B90" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C90" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D90" s="24" t="inlineStr"/>
+      <c r="E90" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:10:17</t>
+        </is>
+      </c>
+      <c r="F90" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:10:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B91" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C91" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="inlineStr"/>
+      <c r="E91" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:04:47</t>
+        </is>
+      </c>
+      <c r="F91" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:05:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B92" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C92" s="24" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="D92" s="24" t="inlineStr"/>
+      <c r="E92" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:58:17</t>
+        </is>
+      </c>
+      <c r="F92" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:59:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B93" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C93" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D93" s="24" t="inlineStr"/>
+      <c r="E93" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:52:47</t>
+        </is>
+      </c>
+      <c r="F93" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:53:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B94" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C94" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D94" s="24" t="inlineStr"/>
+      <c r="E94" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:47:17</t>
+        </is>
+      </c>
+      <c r="F94" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:47:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B95" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C95" s="24" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="D95" s="24" t="inlineStr"/>
+      <c r="E95" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:40:47</t>
+        </is>
+      </c>
+      <c r="F95" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:42:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B96" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C96" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D96" s="24" t="inlineStr"/>
+      <c r="E96" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:35:17</t>
+        </is>
+      </c>
+      <c r="F96" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:35:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B97" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C97" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D97" s="24" t="inlineStr"/>
+      <c r="E97" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:29:47</t>
+        </is>
+      </c>
+      <c r="F97" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:30:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B98" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C98" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D98" s="24" t="inlineStr"/>
+      <c r="E98" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:24:17</t>
+        </is>
+      </c>
+      <c r="F98" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:24:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B99" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C99" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D99" s="24" t="inlineStr"/>
+      <c r="E99" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:18:47</t>
+        </is>
+      </c>
+      <c r="F99" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:18:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B100" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C100" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D100" s="24" t="inlineStr"/>
+      <c r="E100" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:13:17</t>
+        </is>
+      </c>
+      <c r="F100" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B101" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C101" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D101" s="24" t="inlineStr"/>
+      <c r="E101" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:07:47</t>
+        </is>
+      </c>
+      <c r="F101" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:07:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B102" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C102" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D102" s="24" t="inlineStr"/>
+      <c r="E102" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:02:17</t>
+        </is>
+      </c>
+      <c r="F102" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B103" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C103" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D103" s="24" t="inlineStr"/>
+      <c r="E103" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:56:47</t>
+        </is>
+      </c>
+      <c r="F103" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:56:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B104" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C104" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D104" s="24" t="inlineStr"/>
+      <c r="E104" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:51:16</t>
+        </is>
+      </c>
+      <c r="F104" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:51:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B105" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C105" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D105" s="24" t="inlineStr"/>
+      <c r="E105" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:45:46</t>
+        </is>
+      </c>
+      <c r="F105" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:46:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B106" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C106" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D106" s="24" t="inlineStr"/>
+      <c r="E106" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:40:16</t>
+        </is>
+      </c>
+      <c r="F106" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:40:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B107" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C107" s="24" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="D107" s="24" t="inlineStr"/>
+      <c r="E107" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:33:16</t>
+        </is>
+      </c>
+      <c r="F107" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:35:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B108" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C108" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D108" s="24" t="inlineStr"/>
+      <c r="E108" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:27:46</t>
+        </is>
+      </c>
+      <c r="F108" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:28:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B109" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C109" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D109" s="24" t="inlineStr"/>
+      <c r="E109" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:22:16</t>
+        </is>
+      </c>
+      <c r="F109" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:22:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B110" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C110" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D110" s="24" t="inlineStr"/>
+      <c r="E110" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:16:46</t>
+        </is>
+      </c>
+      <c r="F110" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:17:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B111" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C111" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D111" s="24" t="inlineStr"/>
+      <c r="E111" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:11:16</t>
+        </is>
+      </c>
+      <c r="F111" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:11:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B112" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C112" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D112" s="24" t="inlineStr"/>
+      <c r="E112" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:05:46</t>
+        </is>
+      </c>
+      <c r="F112" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:05:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B113" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C113" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D113" s="24" t="inlineStr"/>
+      <c r="E113" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:00:16</t>
+        </is>
+      </c>
+      <c r="F113" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:00:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B114" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C114" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D114" s="24" t="inlineStr"/>
+      <c r="E114" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:54:46</t>
+        </is>
+      </c>
+      <c r="F114" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:54:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B115" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C115" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D115" s="24" t="inlineStr"/>
+      <c r="E115" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:49:16</t>
+        </is>
+      </c>
+      <c r="F115" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:49:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B116" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C116" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D116" s="24" t="inlineStr"/>
+      <c r="E116" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:43:46</t>
+        </is>
+      </c>
+      <c r="F116" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:43:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B117" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C117" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D117" s="24" t="inlineStr"/>
+      <c r="E117" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:38:16</t>
+        </is>
+      </c>
+      <c r="F117" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:38:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B118" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C118" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D118" s="24" t="inlineStr"/>
+      <c r="E118" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:32:46</t>
+        </is>
+      </c>
+      <c r="F118" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:33:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B119" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C119" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D119" s="24" t="inlineStr"/>
+      <c r="E119" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:27:16</t>
+        </is>
+      </c>
+      <c r="F119" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:27:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B120" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C120" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D120" s="24" t="inlineStr"/>
+      <c r="E120" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:21:46</t>
+        </is>
+      </c>
+      <c r="F120" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:21:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B121" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C121" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D121" s="24" t="inlineStr"/>
+      <c r="E121" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:16:16</t>
+        </is>
+      </c>
+      <c r="F121" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B122" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C122" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D122" s="24" t="inlineStr"/>
+      <c r="E122" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:10:46</t>
+        </is>
+      </c>
+      <c r="F122" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:10:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B123" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C123" s="24" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="D123" s="24" t="inlineStr"/>
+      <c r="E123" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:03:46</t>
+        </is>
+      </c>
+      <c r="F123" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:05:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B124" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C124" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D124" s="24" t="inlineStr"/>
+      <c r="E124" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:58:16</t>
+        </is>
+      </c>
+      <c r="F124" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:58:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B125" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C125" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D125" s="24" t="inlineStr"/>
+      <c r="E125" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:52:46</t>
+        </is>
+      </c>
+      <c r="F125" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:52:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B126" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C126" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D126" s="24" t="inlineStr"/>
+      <c r="E126" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:47:16</t>
+        </is>
+      </c>
+      <c r="F126" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:47:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B127" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C127" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D127" s="24" t="inlineStr"/>
+      <c r="E127" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:41:46</t>
+        </is>
+      </c>
+      <c r="F127" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:41:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B128" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C128" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D128" s="24" t="inlineStr"/>
+      <c r="E128" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:36:16</t>
+        </is>
+      </c>
+      <c r="F128" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:36:27</t>
         </is>
       </c>
     </row>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -2232,102 +2232,102 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>T-032</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>Create privacy policy page (/privacy) — FR + EN</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>Claude Cowork</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="G19" s="15" t="n">
         <v>46133</v>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
         <is>
           <t>src/app/privacy/page.tsx</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Must be live before first payment</t>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>[Sync 04/17 12:18] Paperclip: done</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>T-033</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>Create terms of service page (/terms) — FR + EN</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>Claude Cowork</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="G20" s="15" t="n">
         <v>46133</v>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
         <is>
           <t>src/app/terms/page.tsx</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>Include 'not legal advice' disclaimer</t>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>[Sync 04/17 12:18] Paperclip: done</t>
         </is>
       </c>
     </row>
@@ -4884,482 +4884,482 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="17" t="inlineStr">
+      <c r="A77" s="26" t="inlineStr">
         <is>
           <t>T-100</t>
         </is>
       </c>
-      <c r="B77" s="17" t="inlineStr">
+      <c r="B77" s="26" t="inlineStr">
         <is>
           <t>Paperclip</t>
         </is>
       </c>
-      <c r="C77" s="17" t="inlineStr">
+      <c r="C77" s="26" t="inlineStr">
         <is>
           <t>CTO-01 Grille de vetuste data file (JSON)</t>
         </is>
       </c>
-      <c r="D77" s="17" t="inlineStr">
+      <c r="D77" s="26" t="inlineStr">
         <is>
           <t>CTO</t>
         </is>
       </c>
-      <c r="E77" s="17" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F77" s="17" t="inlineStr">
+      <c r="E77" s="26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F77" s="26" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G77" s="17" t="n"/>
-      <c r="H77" s="17" t="n"/>
-      <c r="I77" s="17" t="n"/>
-      <c r="J77" s="17" t="inlineStr">
-        <is>
-          <t>[Auto-added from Paperclip 04/17]</t>
+      <c r="G77" s="26" t="n"/>
+      <c r="H77" s="26" t="n"/>
+      <c r="I77" s="26" t="n"/>
+      <c r="J77" s="26" t="inlineStr">
+        <is>
+          <t>[Sync 04/17 12:18] Paperclip: done</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="inlineStr">
+      <c r="A78" s="26" t="inlineStr">
         <is>
           <t>T-102</t>
         </is>
       </c>
-      <c r="B78" s="16" t="inlineStr">
+      <c r="B78" s="26" t="inlineStr">
         <is>
           <t>Paperclip</t>
         </is>
       </c>
-      <c r="C78" s="16" t="inlineStr">
+      <c r="C78" s="26" t="inlineStr">
         <is>
           <t>CEO-02 Cold outreach DM template FR (400 chars max)</t>
         </is>
       </c>
-      <c r="D78" s="16" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E78" s="16" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="F78" s="16" t="inlineStr">
+      <c r="D78" s="26" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E78" s="26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F78" s="26" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G78" s="16" t="n"/>
-      <c r="H78" s="16" t="n"/>
-      <c r="I78" s="16" t="n"/>
-      <c r="J78" s="16" t="inlineStr">
-        <is>
-          <t>[Auto-added from Paperclip 04/17]</t>
+      <c r="G78" s="26" t="n"/>
+      <c r="H78" s="26" t="n"/>
+      <c r="I78" s="26" t="n"/>
+      <c r="J78" s="26" t="inlineStr">
+        <is>
+          <t>[Sync 04/17 12:18] Paperclip: done</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="inlineStr">
+      <c r="A79" s="26" t="inlineStr">
         <is>
           <t>T-105</t>
         </is>
       </c>
-      <c r="B79" s="16" t="inlineStr">
+      <c r="B79" s="26" t="inlineStr">
         <is>
           <t>Paperclip</t>
         </is>
       </c>
-      <c r="C79" s="16" t="inlineStr">
+      <c r="C79" s="26" t="inlineStr">
         <is>
           <t>CEO-03 Politique de confidentialite FR</t>
         </is>
       </c>
-      <c r="D79" s="16" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E79" s="16" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="F79" s="16" t="inlineStr">
+      <c r="D79" s="26" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E79" s="26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F79" s="26" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G79" s="16" t="n"/>
-      <c r="H79" s="16" t="n"/>
-      <c r="I79" s="16" t="n"/>
-      <c r="J79" s="16" t="inlineStr">
-        <is>
-          <t>[Auto-added from Paperclip 04/17]</t>
+      <c r="G79" s="26" t="n"/>
+      <c r="H79" s="26" t="n"/>
+      <c r="I79" s="26" t="n"/>
+      <c r="J79" s="26" t="inlineStr">
+        <is>
+          <t>[Sync 04/17 12:18] Paperclip: done</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="inlineStr">
+      <c r="A80" s="26" t="inlineStr">
         <is>
           <t>T-109</t>
         </is>
       </c>
-      <c r="B80" s="16" t="inlineStr">
+      <c r="B80" s="26" t="inlineStr">
         <is>
           <t>Paperclip</t>
         </is>
       </c>
-      <c r="C80" s="16" t="inlineStr">
+      <c r="C80" s="26" t="inlineStr">
         <is>
           <t>CTO-05 Security checklist for API routes</t>
         </is>
       </c>
-      <c r="D80" s="16" t="inlineStr">
+      <c r="D80" s="26" t="inlineStr">
         <is>
           <t>CTO</t>
         </is>
       </c>
-      <c r="E80" s="16" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="F80" s="16" t="inlineStr">
+      <c r="E80" s="26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F80" s="26" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G80" s="16" t="n"/>
-      <c r="H80" s="16" t="n"/>
-      <c r="I80" s="16" t="n"/>
-      <c r="J80" s="16" t="inlineStr">
-        <is>
-          <t>[Auto-added from Paperclip 04/17]</t>
+      <c r="G80" s="26" t="n"/>
+      <c r="H80" s="26" t="n"/>
+      <c r="I80" s="26" t="n"/>
+      <c r="J80" s="26" t="inlineStr">
+        <is>
+          <t>[Sync 04/17 12:18] Paperclip: done</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="inlineStr">
+      <c r="A81" s="26" t="inlineStr">
         <is>
           <t>T-114</t>
         </is>
       </c>
-      <c r="B81" s="16" t="inlineStr">
+      <c r="B81" s="26" t="inlineStr">
         <is>
           <t>Paperclip</t>
         </is>
       </c>
-      <c r="C81" s="16" t="inlineStr">
+      <c r="C81" s="26" t="inlineStr">
         <is>
           <t>CEO-05 CGU FR</t>
         </is>
       </c>
-      <c r="D81" s="16" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E81" s="16" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="F81" s="16" t="inlineStr">
+      <c r="D81" s="26" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E81" s="26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F81" s="26" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G81" s="16" t="n"/>
-      <c r="H81" s="16" t="n"/>
-      <c r="I81" s="16" t="n"/>
-      <c r="J81" s="16" t="inlineStr">
-        <is>
-          <t>[Auto-added from Paperclip 04/17]</t>
+      <c r="G81" s="26" t="n"/>
+      <c r="H81" s="26" t="n"/>
+      <c r="I81" s="26" t="n"/>
+      <c r="J81" s="26" t="inlineStr">
+        <is>
+          <t>[Sync 04/17 12:18] Paperclip: done</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="16" t="inlineStr">
+      <c r="A82" s="26" t="inlineStr">
         <is>
           <t>T-120</t>
         </is>
       </c>
-      <c r="B82" s="16" t="inlineStr">
+      <c r="B82" s="26" t="inlineStr">
         <is>
           <t>Paperclip</t>
         </is>
       </c>
-      <c r="C82" s="16" t="inlineStr">
+      <c r="C82" s="26" t="inlineStr">
         <is>
           <t>CEO-07 Politique de remboursement FR</t>
         </is>
       </c>
-      <c r="D82" s="16" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E82" s="16" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="F82" s="16" t="inlineStr">
+      <c r="D82" s="26" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E82" s="26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F82" s="26" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G82" s="16" t="n"/>
-      <c r="H82" s="16" t="n"/>
-      <c r="I82" s="16" t="n"/>
-      <c r="J82" s="16" t="inlineStr">
-        <is>
-          <t>[Auto-added from Paperclip 04/17]</t>
+      <c r="G82" s="26" t="n"/>
+      <c r="H82" s="26" t="n"/>
+      <c r="I82" s="26" t="n"/>
+      <c r="J82" s="26" t="inlineStr">
+        <is>
+          <t>[Sync 04/17 12:18] Paperclip: done</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="16" t="inlineStr">
+      <c r="A83" s="26" t="inlineStr">
         <is>
           <t>T-127</t>
         </is>
       </c>
-      <c r="B83" s="16" t="inlineStr">
+      <c r="B83" s="26" t="inlineStr">
         <is>
           <t>Paperclip</t>
         </is>
       </c>
-      <c r="C83" s="16" t="inlineStr">
+      <c r="C83" s="26" t="inlineStr">
         <is>
           <t>CEO-08 Refund Policy EN (translate FR)</t>
         </is>
       </c>
-      <c r="D83" s="16" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E83" s="16" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="F83" s="16" t="inlineStr">
+      <c r="D83" s="26" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E83" s="26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F83" s="26" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G83" s="16" t="n"/>
-      <c r="H83" s="16" t="n"/>
-      <c r="I83" s="16" t="n"/>
-      <c r="J83" s="16" t="inlineStr">
-        <is>
-          <t>[Auto-added from Paperclip 04/17]</t>
+      <c r="G83" s="26" t="n"/>
+      <c r="H83" s="26" t="n"/>
+      <c r="I83" s="26" t="n"/>
+      <c r="J83" s="26" t="inlineStr">
+        <is>
+          <t>[Sync 04/17 12:18] Paperclip: done</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="16" t="inlineStr">
+      <c r="A84" s="26" t="inlineStr">
         <is>
           <t>T-135</t>
         </is>
       </c>
-      <c r="B84" s="16" t="inlineStr">
+      <c r="B84" s="26" t="inlineStr">
         <is>
           <t>Paperclip</t>
         </is>
       </c>
-      <c r="C84" s="16" t="inlineStr">
+      <c r="C84" s="26" t="inlineStr">
         <is>
           <t>CTO-02 ADR-001 Grille de vetuste integration</t>
         </is>
       </c>
-      <c r="D84" s="16" t="inlineStr">
+      <c r="D84" s="26" t="inlineStr">
         <is>
           <t>CTO</t>
         </is>
       </c>
-      <c r="E84" s="16" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="F84" s="16" t="inlineStr">
+      <c r="E84" s="26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F84" s="26" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G84" s="16" t="n"/>
-      <c r="H84" s="16" t="n"/>
-      <c r="I84" s="16" t="n"/>
-      <c r="J84" s="16" t="inlineStr">
-        <is>
-          <t>[Auto-added from Paperclip 04/17]</t>
+      <c r="G84" s="26" t="n"/>
+      <c r="H84" s="26" t="n"/>
+      <c r="I84" s="26" t="n"/>
+      <c r="J84" s="26" t="inlineStr">
+        <is>
+          <t>[Sync 04/17 12:18] Paperclip: done</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="inlineStr">
+      <c r="A85" s="26" t="inlineStr">
         <is>
           <t>T-144</t>
         </is>
       </c>
-      <c r="B85" s="16" t="inlineStr">
+      <c r="B85" s="26" t="inlineStr">
         <is>
           <t>Paperclip</t>
         </is>
       </c>
-      <c r="C85" s="16" t="inlineStr">
+      <c r="C85" s="26" t="inlineStr">
         <is>
           <t>CTO-03 Prompt spec for /api/ai/scan v2 (Haiku)</t>
         </is>
       </c>
-      <c r="D85" s="16" t="inlineStr">
+      <c r="D85" s="26" t="inlineStr">
         <is>
           <t>CTO</t>
         </is>
       </c>
-      <c r="E85" s="16" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="F85" s="16" t="inlineStr">
+      <c r="E85" s="26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F85" s="26" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G85" s="16" t="n"/>
-      <c r="H85" s="16" t="n"/>
-      <c r="I85" s="16" t="n"/>
-      <c r="J85" s="16" t="inlineStr">
-        <is>
-          <t>[Auto-added from Paperclip 04/17]</t>
+      <c r="G85" s="26" t="n"/>
+      <c r="H85" s="26" t="n"/>
+      <c r="I85" s="26" t="n"/>
+      <c r="J85" s="26" t="inlineStr">
+        <is>
+          <t>[Sync 04/17 12:18] Paperclip: done</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="16" t="inlineStr">
+      <c r="A86" s="26" t="inlineStr">
         <is>
           <t>T-154</t>
         </is>
       </c>
-      <c r="B86" s="16" t="inlineStr">
+      <c r="B86" s="26" t="inlineStr">
         <is>
           <t>Paperclip</t>
         </is>
       </c>
-      <c r="C86" s="16" t="inlineStr">
+      <c r="C86" s="26" t="inlineStr">
         <is>
           <t>CTO-04 Prompt spec for /api/ai/dispute v2 (Sonnet)</t>
         </is>
       </c>
-      <c r="D86" s="16" t="inlineStr">
+      <c r="D86" s="26" t="inlineStr">
         <is>
           <t>CTO</t>
         </is>
       </c>
-      <c r="E86" s="16" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="F86" s="16" t="inlineStr">
+      <c r="E86" s="26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F86" s="26" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G86" s="16" t="n"/>
-      <c r="H86" s="16" t="n"/>
-      <c r="I86" s="16" t="n"/>
-      <c r="J86" s="16" t="inlineStr">
-        <is>
-          <t>[Auto-added from Paperclip 04/17]</t>
+      <c r="G86" s="26" t="n"/>
+      <c r="H86" s="26" t="n"/>
+      <c r="I86" s="26" t="n"/>
+      <c r="J86" s="26" t="inlineStr">
+        <is>
+          <t>[Sync 04/17 12:18] Paperclip: done</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="16" t="inlineStr">
+      <c r="A87" s="26" t="inlineStr">
         <is>
           <t>T-165</t>
         </is>
       </c>
-      <c r="B87" s="16" t="inlineStr">
+      <c r="B87" s="26" t="inlineStr">
         <is>
           <t>Paperclip</t>
         </is>
       </c>
-      <c r="C87" s="16" t="inlineStr">
+      <c r="C87" s="26" t="inlineStr">
         <is>
           <t>CTO-06 T-103 end-to-end smoke test plan</t>
         </is>
       </c>
-      <c r="D87" s="16" t="inlineStr">
+      <c r="D87" s="26" t="inlineStr">
         <is>
           <t>CTO</t>
         </is>
       </c>
-      <c r="E87" s="16" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="F87" s="16" t="inlineStr">
+      <c r="E87" s="26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F87" s="26" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G87" s="16" t="n"/>
-      <c r="H87" s="16" t="n"/>
-      <c r="I87" s="16" t="n"/>
-      <c r="J87" s="16" t="inlineStr">
-        <is>
-          <t>[Auto-added from Paperclip 04/17]</t>
+      <c r="G87" s="26" t="n"/>
+      <c r="H87" s="26" t="n"/>
+      <c r="I87" s="26" t="n"/>
+      <c r="J87" s="26" t="inlineStr">
+        <is>
+          <t>[Sync 04/17 12:18] Paperclip: done</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="17" t="inlineStr">
+      <c r="A88" s="26" t="inlineStr">
         <is>
           <t>T-177</t>
         </is>
       </c>
-      <c r="B88" s="17" t="inlineStr">
+      <c r="B88" s="26" t="inlineStr">
         <is>
           <t>Paperclip</t>
         </is>
       </c>
-      <c r="C88" s="17" t="inlineStr">
+      <c r="C88" s="26" t="inlineStr">
         <is>
           <t>CEO-01 PDF disclaimer footer (FR+EN, 25 words each)</t>
         </is>
       </c>
-      <c r="D88" s="17" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="E88" s="17" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F88" s="17" t="inlineStr">
+      <c r="D88" s="26" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E88" s="26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F88" s="26" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G88" s="17" t="n"/>
-      <c r="H88" s="17" t="n"/>
-      <c r="I88" s="17" t="n"/>
-      <c r="J88" s="17" t="inlineStr">
-        <is>
-          <t>[Auto-added from Paperclip 04/17]</t>
+      <c r="G88" s="26" t="n"/>
+      <c r="H88" s="26" t="n"/>
+      <c r="I88" s="26" t="n"/>
+      <c r="J88" s="26" t="inlineStr">
+        <is>
+          <t>[Sync 04/17 12:18] Paperclip: done</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>PAPERCLIP STATUS — 2026-04-17 11:18</t>
+          <t>PAPERCLIP STATUS — 2026-04-17 12:18</t>
         </is>
       </c>
     </row>
@@ -5924,74 +5924,74 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>idle</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>paused</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>codex_local</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>PAUSED</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t>$15</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr">
+      <c r="G4" s="21" t="inlineStr">
         <is>
           <t>$4.06</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>CTO</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>idle</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>paused</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>codex_local</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>PAUSED</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>$20</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>$13.78</t>
         </is>
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26">
@@ -6402,7 +6402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="7" min="1" max="1"/>
@@ -6416,7 +6416,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>RUN HISTORY (Last 24h) — 2026-04-17 11:18</t>
+          <t>RUN HISTORY (Last 24h) — 2026-04-17 12:18</t>
         </is>
       </c>
     </row>
@@ -6471,12 +6471,12 @@
       <c r="D4" s="24" t="inlineStr"/>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 11:17:52</t>
+          <t>2026-04-17 12:12:52</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 11:18:03</t>
+          <t>2026-04-17 12:13:12</t>
         </is>
       </c>
     </row>
@@ -6499,12 +6499,12 @@
       <c r="D5" s="24" t="inlineStr"/>
       <c r="E5" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 11:12:14</t>
+          <t>2026-04-17 12:07:22</t>
         </is>
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 11:12:43</t>
+          <t>2026-04-17 12:07:30</t>
         </is>
       </c>
     </row>
@@ -6527,19 +6527,19 @@
       <c r="D6" s="24" t="inlineStr"/>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 11:08:52</t>
+          <t>2026-04-17 12:01:52</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 11:08:58</t>
+          <t>2026-04-17 12:02:05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
@@ -6555,12 +6555,12 @@
       <c r="D7" s="24" t="inlineStr"/>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 11:03:30</t>
+          <t>2026-04-17 11:56:22</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 11:03:37</t>
+          <t>2026-04-17 11:56:37</t>
         </is>
       </c>
     </row>
@@ -6583,12 +6583,12 @@
       <c r="D8" s="24" t="inlineStr"/>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 11:03:24</t>
+          <t>2026-04-17 11:50:52</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 11:03:35</t>
+          <t>2026-04-17 11:51:19</t>
         </is>
       </c>
     </row>
@@ -6611,19 +6611,19 @@
       <c r="D9" s="24" t="inlineStr"/>
       <c r="E9" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 11:01:52</t>
+          <t>2026-04-17 11:45:22</t>
         </is>
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 11:02:02</t>
+          <t>2026-04-17 11:45:29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
@@ -6639,12 +6639,12 @@
       <c r="D10" s="24" t="inlineStr"/>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:56:27</t>
+          <t>2026-04-17 11:39:52</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:56:35</t>
+          <t>2026-04-17 11:40:04</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       <c r="D11" s="24" t="inlineStr"/>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:56:27</t>
+          <t>2026-04-17 11:34:22</t>
         </is>
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:56:35</t>
+          <t>2026-04-17 11:34:41</t>
         </is>
       </c>
     </row>
@@ -6695,12 +6695,12 @@
       <c r="D12" s="24" t="inlineStr"/>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:53:52</t>
+          <t>2026-04-17 11:28:52</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:54:01</t>
+          <t>2026-04-17 11:29:02</t>
         </is>
       </c>
     </row>
@@ -6723,12 +6723,12 @@
       <c r="D13" s="24" t="inlineStr"/>
       <c r="E13" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:48:22</t>
+          <t>2026-04-17 11:23:22</t>
         </is>
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:48:37</t>
+          <t>2026-04-17 11:23:28</t>
         </is>
       </c>
     </row>
@@ -6751,12 +6751,12 @@
       <c r="D14" s="24" t="inlineStr"/>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:42:52</t>
+          <t>2026-04-17 11:17:52</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:43:02</t>
+          <t>2026-04-17 11:18:03</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6779,12 @@
       <c r="D15" s="24" t="inlineStr"/>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:37:22</t>
+          <t>2026-04-17 11:12:14</t>
         </is>
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:37:29</t>
+          <t>2026-04-17 11:12:43</t>
         </is>
       </c>
     </row>
@@ -6807,19 +6807,19 @@
       <c r="D16" s="24" t="inlineStr"/>
       <c r="E16" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:31:52</t>
+          <t>2026-04-17 11:08:52</t>
         </is>
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:32:02</t>
+          <t>2026-04-17 11:08:58</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
@@ -6835,12 +6835,12 @@
       <c r="D17" s="24" t="inlineStr"/>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:26:22</t>
+          <t>2026-04-17 11:03:30</t>
         </is>
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:26:28</t>
+          <t>2026-04-17 11:03:37</t>
         </is>
       </c>
     </row>
@@ -6863,12 +6863,12 @@
       <c r="D18" s="24" t="inlineStr"/>
       <c r="E18" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:20:52</t>
+          <t>2026-04-17 11:03:24</t>
         </is>
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:21:17</t>
+          <t>2026-04-17 11:03:35</t>
         </is>
       </c>
     </row>
@@ -6891,19 +6891,19 @@
       <c r="D19" s="24" t="inlineStr"/>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:15:22</t>
+          <t>2026-04-17 11:01:52</t>
         </is>
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:15:29</t>
+          <t>2026-04-17 11:02:02</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
@@ -6919,12 +6919,12 @@
       <c r="D20" s="24" t="inlineStr"/>
       <c r="E20" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:09:52</t>
+          <t>2026-04-17 10:56:27</t>
         </is>
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:10:05</t>
+          <t>2026-04-17 10:56:35</t>
         </is>
       </c>
     </row>
@@ -6947,12 +6947,12 @@
       <c r="D21" s="24" t="inlineStr"/>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:04:22</t>
+          <t>2026-04-17 10:56:27</t>
         </is>
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 10:04:38</t>
+          <t>2026-04-17 10:56:35</t>
         </is>
       </c>
     </row>
@@ -6975,12 +6975,12 @@
       <c r="D22" s="24" t="inlineStr"/>
       <c r="E22" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 09:58:52</t>
+          <t>2026-04-17 10:53:52</t>
         </is>
       </c>
       <c r="F22" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 09:59:08</t>
+          <t>2026-04-17 10:54:01</t>
         </is>
       </c>
     </row>
@@ -7003,12 +7003,12 @@
       <c r="D23" s="24" t="inlineStr"/>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 09:53:22</t>
+          <t>2026-04-17 10:48:22</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 09:53:29</t>
+          <t>2026-04-17 10:48:37</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       <c r="D24" s="24" t="inlineStr"/>
       <c r="E24" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 09:47:52</t>
+          <t>2026-04-17 10:42:52</t>
         </is>
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 09:47:58</t>
+          <t>2026-04-17 10:43:02</t>
         </is>
       </c>
     </row>
@@ -7059,12 +7059,12 @@
       <c r="D25" s="24" t="inlineStr"/>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 09:42:22</t>
+          <t>2026-04-17 10:37:22</t>
         </is>
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 09:42:27</t>
+          <t>2026-04-17 10:37:29</t>
         </is>
       </c>
     </row>
@@ -7087,12 +7087,12 @@
       <c r="D26" s="24" t="inlineStr"/>
       <c r="E26" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 09:36:52</t>
+          <t>2026-04-17 10:31:52</t>
         </is>
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 09:37:00</t>
+          <t>2026-04-17 10:32:02</t>
         </is>
       </c>
     </row>
@@ -7109,82 +7109,74 @@
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>8m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr"/>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 09:23:27</t>
+          <t>2026-04-17 10:26:22</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 09:31:27</t>
+          <t>2026-04-17 10:26:28</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C28" s="23" t="inlineStr">
-        <is>
-          <t>17m</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 900s</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 08:49:10</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 09:06:32</t>
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr"/>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 10:20:52</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 10:21:17</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="inlineStr">
-        <is>
-          <t>16m</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 900s</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 08:16:50</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 08:33:02</t>
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr"/>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 10:15:22</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 10:15:29</t>
         </is>
       </c>
     </row>
@@ -7207,12 +7199,12 @@
       <c r="D30" s="24" t="inlineStr"/>
       <c r="E30" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 08:11:20</t>
+          <t>2026-04-17 10:09:52</t>
         </is>
       </c>
       <c r="F30" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 08:11:28</t>
+          <t>2026-04-17 10:10:05</t>
         </is>
       </c>
     </row>
@@ -7235,12 +7227,12 @@
       <c r="D31" s="24" t="inlineStr"/>
       <c r="E31" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 08:05:50</t>
+          <t>2026-04-17 10:04:22</t>
         </is>
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 08:06:12</t>
+          <t>2026-04-17 10:04:38</t>
         </is>
       </c>
     </row>
@@ -7263,12 +7255,12 @@
       <c r="D32" s="24" t="inlineStr"/>
       <c r="E32" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 07:59:50</t>
+          <t>2026-04-17 09:58:52</t>
         </is>
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 08:00:20</t>
+          <t>2026-04-17 09:59:08</t>
         </is>
       </c>
     </row>
@@ -7291,140 +7283,124 @@
       <c r="D33" s="24" t="inlineStr"/>
       <c r="E33" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 07:54:20</t>
+          <t>2026-04-17 09:53:22</t>
         </is>
       </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
-          <t>2026-04-17 07:54:45</t>
+          <t>2026-04-17 09:53:29</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B34" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="inlineStr">
-        <is>
-          <t>20m</t>
-        </is>
-      </c>
-      <c r="D34" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 900s</t>
-        </is>
-      </c>
-      <c r="E34" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 07:33:28</t>
-        </is>
-      </c>
-      <c r="F34" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 07:54:20</t>
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr"/>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 09:47:52</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 09:47:58</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C35" s="23" t="inlineStr">
-        <is>
-          <t>16m</t>
-        </is>
-      </c>
-      <c r="D35" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 900s</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 07:16:37</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 07:33:28</t>
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr"/>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 09:42:22</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 09:42:27</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B36" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C36" s="23" t="inlineStr">
-        <is>
-          <t>17m</t>
-        </is>
-      </c>
-      <c r="D36" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 900s</t>
-        </is>
-      </c>
-      <c r="E36" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 06:58:44</t>
-        </is>
-      </c>
-      <c r="F36" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 07:16:37</t>
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr"/>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 09:36:52</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 09:37:00</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B37" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C37" s="23" t="inlineStr">
-        <is>
-          <t>28m</t>
-        </is>
-      </c>
-      <c r="D37" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 900s</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 06:30:30</t>
-        </is>
-      </c>
-      <c r="F37" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 06:58:44</t>
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>8m</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr"/>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 09:23:27</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 09:31:27</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7417,7 @@
       </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
-          <t>16m</t>
+          <t>17m</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
@@ -7451,12 +7427,12 @@
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 06:13:51</t>
+          <t>2026-04-17 08:49:10</t>
         </is>
       </c>
       <c r="F38" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 06:30:30</t>
+          <t>2026-04-17 09:06:32</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7449,7 @@
       </c>
       <c r="C39" s="23" t="inlineStr">
         <is>
-          <t>17m</t>
+          <t>16m</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
@@ -7483,140 +7459,124 @@
       </c>
       <c r="E39" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 05:40:44</t>
+          <t>2026-04-17 08:16:50</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 05:57:55</t>
+          <t>2026-04-17 08:33:02</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B40" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C40" s="23" t="inlineStr">
-        <is>
-          <t>15m</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 900s</t>
-        </is>
-      </c>
-      <c r="E40" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 05:13:44</t>
-        </is>
-      </c>
-      <c r="F40" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 05:28:51</t>
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr"/>
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:11:20</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:11:28</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B41" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C41" s="23" t="inlineStr">
-        <is>
-          <t>30m</t>
-        </is>
-      </c>
-      <c r="D41" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 900s</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 04:26:04</t>
-        </is>
-      </c>
-      <c r="F41" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 04:56:33</t>
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr"/>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:05:50</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:06:12</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B42" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C42" s="23" t="inlineStr">
-        <is>
-          <t>16m</t>
-        </is>
-      </c>
-      <c r="D42" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 900s</t>
-        </is>
-      </c>
-      <c r="E42" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 03:53:51</t>
-        </is>
-      </c>
-      <c r="F42" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 04:10:45</t>
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr"/>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 07:59:50</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 08:00:20</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B43" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C43" s="23" t="inlineStr">
-        <is>
-          <t>15m</t>
-        </is>
-      </c>
-      <c r="D43" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 900s</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 03:38:43</t>
-        </is>
-      </c>
-      <c r="F43" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-17 03:53:51</t>
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr"/>
+      <c r="E43" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 07:54:20</t>
+        </is>
+      </c>
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-17 07:54:45</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7593,7 @@
       </c>
       <c r="C44" s="23" t="inlineStr">
         <is>
-          <t>19m</t>
+          <t>20m</t>
         </is>
       </c>
       <c r="D44" s="23" t="inlineStr">
@@ -7643,12 +7603,12 @@
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 03:11:18</t>
+          <t>2026-04-17 07:33:28</t>
         </is>
       </c>
       <c r="F44" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 03:30:37</t>
+          <t>2026-04-17 07:54:20</t>
         </is>
       </c>
     </row>
@@ -7675,12 +7635,12 @@
       </c>
       <c r="E45" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 02:37:43</t>
+          <t>2026-04-17 07:16:37</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 02:54:24</t>
+          <t>2026-04-17 07:33:28</t>
         </is>
       </c>
     </row>
@@ -7707,12 +7667,12 @@
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 02:10:00</t>
+          <t>2026-04-17 06:58:44</t>
         </is>
       </c>
       <c r="F46" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 02:27:59</t>
+          <t>2026-04-17 07:16:37</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7689,7 @@
       </c>
       <c r="C47" s="23" t="inlineStr">
         <is>
-          <t>29m</t>
+          <t>28m</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
@@ -7739,12 +7699,12 @@
       </c>
       <c r="E47" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 01:25:01</t>
+          <t>2026-04-17 06:30:30</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 01:54:16</t>
+          <t>2026-04-17 06:58:44</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7721,7 @@
       </c>
       <c r="C48" s="23" t="inlineStr">
         <is>
-          <t>15m</t>
+          <t>16m</t>
         </is>
       </c>
       <c r="D48" s="23" t="inlineStr">
@@ -7771,12 +7731,12 @@
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 01:09:55</t>
+          <t>2026-04-17 06:13:51</t>
         </is>
       </c>
       <c r="F48" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 01:25:01</t>
+          <t>2026-04-17 06:30:30</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7753,7 @@
       </c>
       <c r="C49" s="23" t="inlineStr">
         <is>
-          <t>20m</t>
+          <t>17m</t>
         </is>
       </c>
       <c r="D49" s="23" t="inlineStr">
@@ -7803,12 +7763,12 @@
       </c>
       <c r="E49" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 00:33:15</t>
+          <t>2026-04-17 05:40:44</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 00:53:19</t>
+          <t>2026-04-17 05:57:55</t>
         </is>
       </c>
     </row>
@@ -7825,7 +7785,7 @@
       </c>
       <c r="C50" s="23" t="inlineStr">
         <is>
-          <t>24m</t>
+          <t>15m</t>
         </is>
       </c>
       <c r="D50" s="23" t="inlineStr">
@@ -7835,12 +7795,12 @@
       </c>
       <c r="E50" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 23:51:44</t>
+          <t>2026-04-17 05:13:44</t>
         </is>
       </c>
       <c r="F50" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 00:16:23</t>
+          <t>2026-04-17 05:28:51</t>
         </is>
       </c>
     </row>
@@ -7857,7 +7817,7 @@
       </c>
       <c r="C51" s="23" t="inlineStr">
         <is>
-          <t>28m</t>
+          <t>30m</t>
         </is>
       </c>
       <c r="D51" s="23" t="inlineStr">
@@ -7867,12 +7827,12 @@
       </c>
       <c r="E51" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 23:23:05</t>
+          <t>2026-04-17 04:26:04</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 23:51:44</t>
+          <t>2026-04-17 04:56:33</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7859,12 @@
       </c>
       <c r="E52" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 23:06:41</t>
+          <t>2026-04-17 03:53:51</t>
         </is>
       </c>
       <c r="F52" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 23:23:05</t>
+          <t>2026-04-17 04:10:45</t>
         </is>
       </c>
     </row>
@@ -7921,7 +7881,7 @@
       </c>
       <c r="C53" s="23" t="inlineStr">
         <is>
-          <t>26m</t>
+          <t>15m</t>
         </is>
       </c>
       <c r="D53" s="23" t="inlineStr">
@@ -7931,12 +7891,12 @@
       </c>
       <c r="E53" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 22:24:28</t>
+          <t>2026-04-17 03:38:43</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 22:50:39</t>
+          <t>2026-04-17 03:53:51</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7913,7 @@
       </c>
       <c r="C54" s="23" t="inlineStr">
         <is>
-          <t>18m</t>
+          <t>19m</t>
         </is>
       </c>
       <c r="D54" s="23" t="inlineStr">
@@ -7963,12 +7923,12 @@
       </c>
       <c r="E54" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 22:06:27</t>
+          <t>2026-04-17 03:11:18</t>
         </is>
       </c>
       <c r="F54" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 22:24:28</t>
+          <t>2026-04-17 03:30:37</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7945,7 @@
       </c>
       <c r="C55" s="23" t="inlineStr">
         <is>
-          <t>31m</t>
+          <t>16m</t>
         </is>
       </c>
       <c r="D55" s="23" t="inlineStr">
@@ -7995,12 +7955,12 @@
       </c>
       <c r="E55" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 21:18:50</t>
+          <t>2026-04-17 02:37:43</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 21:50:20</t>
+          <t>2026-04-17 02:54:24</t>
         </is>
       </c>
     </row>
@@ -8017,7 +7977,7 @@
       </c>
       <c r="C56" s="23" t="inlineStr">
         <is>
-          <t>16m</t>
+          <t>17m</t>
         </is>
       </c>
       <c r="D56" s="23" t="inlineStr">
@@ -8027,12 +7987,12 @@
       </c>
       <c r="E56" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 21:02:10</t>
+          <t>2026-04-17 02:10:00</t>
         </is>
       </c>
       <c r="F56" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 21:18:50</t>
+          <t>2026-04-17 02:27:59</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8009,7 @@
       </c>
       <c r="C57" s="23" t="inlineStr">
         <is>
-          <t>27m</t>
+          <t>29m</t>
         </is>
       </c>
       <c r="D57" s="23" t="inlineStr">
@@ -8059,12 +8019,12 @@
       </c>
       <c r="E57" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 20:19:12</t>
+          <t>2026-04-17 01:25:01</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 20:46:53</t>
+          <t>2026-04-17 01:54:16</t>
         </is>
       </c>
     </row>
@@ -8091,40 +8051,44 @@
       </c>
       <c r="E58" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 19:47:03</t>
+          <t>2026-04-17 01:09:55</t>
         </is>
       </c>
       <c r="F58" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 20:02:06</t>
+          <t>2026-04-17 01:25:01</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B59" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C59" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D59" s="24" t="inlineStr"/>
-      <c r="E59" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 19:30:43</t>
-        </is>
-      </c>
-      <c r="F59" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 19:30:51</t>
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B59" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C59" s="23" t="inlineStr">
+        <is>
+          <t>20m</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E59" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 00:33:15</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-17 00:53:19</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8105,7 @@
       </c>
       <c r="C60" s="23" t="inlineStr">
         <is>
-          <t>21m</t>
+          <t>24m</t>
         </is>
       </c>
       <c r="D60" s="23" t="inlineStr">
@@ -8151,12 +8115,12 @@
       </c>
       <c r="E60" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 19:01:04</t>
+          <t>2026-04-16 23:51:44</t>
         </is>
       </c>
       <c r="F60" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 19:22:22</t>
+          <t>2026-04-17 00:16:23</t>
         </is>
       </c>
     </row>
@@ -8173,7 +8137,7 @@
       </c>
       <c r="C61" s="23" t="inlineStr">
         <is>
-          <t>15m</t>
+          <t>28m</t>
         </is>
       </c>
       <c r="D61" s="23" t="inlineStr">
@@ -8183,12 +8147,12 @@
       </c>
       <c r="E61" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 18:40:38</t>
+          <t>2026-04-16 23:23:05</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 18:55:55</t>
+          <t>2026-04-16 23:51:44</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8169,7 @@
       </c>
       <c r="C62" s="23" t="inlineStr">
         <is>
-          <t>17m</t>
+          <t>16m</t>
         </is>
       </c>
       <c r="D62" s="23" t="inlineStr">
@@ -8215,12 +8179,12 @@
       </c>
       <c r="E62" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 18:06:53</t>
+          <t>2026-04-16 23:06:41</t>
         </is>
       </c>
       <c r="F62" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 18:24:23</t>
+          <t>2026-04-16 23:23:05</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8201,7 @@
       </c>
       <c r="C63" s="23" t="inlineStr">
         <is>
-          <t>15m</t>
+          <t>26m</t>
         </is>
       </c>
       <c r="D63" s="23" t="inlineStr">
@@ -8247,12 +8211,12 @@
       </c>
       <c r="E63" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 17:51:34</t>
+          <t>2026-04-16 22:24:28</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 18:06:53</t>
+          <t>2026-04-16 22:50:39</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8233,7 @@
       </c>
       <c r="C64" s="23" t="inlineStr">
         <is>
-          <t>17m</t>
+          <t>18m</t>
         </is>
       </c>
       <c r="D64" s="23" t="inlineStr">
@@ -8279,124 +8243,140 @@
       </c>
       <c r="E64" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 17:33:50</t>
+          <t>2026-04-16 22:06:27</t>
         </is>
       </c>
       <c r="F64" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 17:51:34</t>
+          <t>2026-04-16 22:24:28</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B65" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C65" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D65" s="24" t="inlineStr"/>
-      <c r="E65" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:28:17</t>
-        </is>
-      </c>
-      <c r="F65" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:28:32</t>
+      <c r="A65" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B65" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C65" s="23" t="inlineStr">
+        <is>
+          <t>31m</t>
+        </is>
+      </c>
+      <c r="D65" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E65" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:18:50</t>
+        </is>
+      </c>
+      <c r="F65" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:50:20</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B66" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C66" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D66" s="24" t="inlineStr"/>
-      <c r="E66" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:22:47</t>
-        </is>
-      </c>
-      <c r="F66" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:22:58</t>
+      <c r="A66" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B66" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C66" s="23" t="inlineStr">
+        <is>
+          <t>16m</t>
+        </is>
+      </c>
+      <c r="D66" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E66" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:02:10</t>
+        </is>
+      </c>
+      <c r="F66" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:18:50</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B67" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C67" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D67" s="24" t="inlineStr"/>
-      <c r="E67" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:17:17</t>
-        </is>
-      </c>
-      <c r="F67" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:17:31</t>
+      <c r="A67" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B67" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C67" s="23" t="inlineStr">
+        <is>
+          <t>27m</t>
+        </is>
+      </c>
+      <c r="D67" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E67" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:19:12</t>
+        </is>
+      </c>
+      <c r="F67" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:46:53</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B68" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C68" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D68" s="24" t="inlineStr"/>
-      <c r="E68" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:11:47</t>
-        </is>
-      </c>
-      <c r="F68" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:12:05</t>
+      <c r="A68" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B68" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C68" s="23" t="inlineStr">
+        <is>
+          <t>15m</t>
+        </is>
+      </c>
+      <c r="D68" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E68" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 19:47:03</t>
+        </is>
+      </c>
+      <c r="F68" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 20:02:06</t>
         </is>
       </c>
     </row>
@@ -8419,152 +8399,172 @@
       <c r="D69" s="24" t="inlineStr"/>
       <c r="E69" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 17:06:17</t>
+          <t>2026-04-16 19:30:43</t>
         </is>
       </c>
       <c r="F69" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 17:06:29</t>
+          <t>2026-04-16 19:30:51</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B70" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C70" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D70" s="24" t="inlineStr"/>
-      <c r="E70" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:00:47</t>
-        </is>
-      </c>
-      <c r="F70" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:01:13</t>
+      <c r="A70" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B70" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C70" s="23" t="inlineStr">
+        <is>
+          <t>21m</t>
+        </is>
+      </c>
+      <c r="D70" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E70" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 19:01:04</t>
+        </is>
+      </c>
+      <c r="F70" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 19:22:22</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B71" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C71" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D71" s="24" t="inlineStr"/>
-      <c r="E71" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:55:17</t>
-        </is>
-      </c>
-      <c r="F71" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:55:39</t>
+      <c r="A71" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B71" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C71" s="23" t="inlineStr">
+        <is>
+          <t>15m</t>
+        </is>
+      </c>
+      <c r="D71" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E71" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 18:40:38</t>
+        </is>
+      </c>
+      <c r="F71" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 18:55:55</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B72" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C72" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D72" s="24" t="inlineStr"/>
-      <c r="E72" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:49:17</t>
-        </is>
-      </c>
-      <c r="F72" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:49:55</t>
+      <c r="A72" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B72" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C72" s="23" t="inlineStr">
+        <is>
+          <t>17m</t>
+        </is>
+      </c>
+      <c r="D72" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E72" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 18:06:53</t>
+        </is>
+      </c>
+      <c r="F72" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 18:24:23</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B73" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C73" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D73" s="24" t="inlineStr"/>
-      <c r="E73" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:43:47</t>
-        </is>
-      </c>
-      <c r="F73" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:43:58</t>
+      <c r="A73" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B73" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C73" s="23" t="inlineStr">
+        <is>
+          <t>15m</t>
+        </is>
+      </c>
+      <c r="D73" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E73" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 17:51:34</t>
+        </is>
+      </c>
+      <c r="F73" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 18:06:53</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B74" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C74" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D74" s="24" t="inlineStr"/>
-      <c r="E74" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:38:17</t>
-        </is>
-      </c>
-      <c r="F74" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:38:36</t>
+      <c r="A74" s="23" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B74" s="23" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="C74" s="23" t="inlineStr">
+        <is>
+          <t>17m</t>
+        </is>
+      </c>
+      <c r="D74" s="23" t="inlineStr">
+        <is>
+          <t>Timed out after 900s</t>
+        </is>
+      </c>
+      <c r="E74" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 17:33:50</t>
+        </is>
+      </c>
+      <c r="F74" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 17:51:34</t>
         </is>
       </c>
     </row>
@@ -8587,12 +8587,12 @@
       <c r="D75" s="24" t="inlineStr"/>
       <c r="E75" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:32:47</t>
+          <t>2026-04-16 17:28:17</t>
         </is>
       </c>
       <c r="F75" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:32:58</t>
+          <t>2026-04-16 17:28:32</t>
         </is>
       </c>
     </row>
@@ -8615,12 +8615,12 @@
       <c r="D76" s="24" t="inlineStr"/>
       <c r="E76" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:27:17</t>
+          <t>2026-04-16 17:22:47</t>
         </is>
       </c>
       <c r="F76" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:27:25</t>
+          <t>2026-04-16 17:22:58</t>
         </is>
       </c>
     </row>
@@ -8643,12 +8643,12 @@
       <c r="D77" s="24" t="inlineStr"/>
       <c r="E77" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:21:47</t>
+          <t>2026-04-16 17:17:17</t>
         </is>
       </c>
       <c r="F77" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:22:05</t>
+          <t>2026-04-16 17:17:31</t>
         </is>
       </c>
     </row>
@@ -8671,12 +8671,12 @@
       <c r="D78" s="24" t="inlineStr"/>
       <c r="E78" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:16:17</t>
+          <t>2026-04-16 17:11:47</t>
         </is>
       </c>
       <c r="F78" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:16:42</t>
+          <t>2026-04-16 17:12:05</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       <c r="D79" s="24" t="inlineStr"/>
       <c r="E79" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:10:47</t>
+          <t>2026-04-16 17:06:17</t>
         </is>
       </c>
       <c r="F79" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:10:58</t>
+          <t>2026-04-16 17:06:29</t>
         </is>
       </c>
     </row>
@@ -8727,12 +8727,12 @@
       <c r="D80" s="24" t="inlineStr"/>
       <c r="E80" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:05:17</t>
+          <t>2026-04-16 17:00:47</t>
         </is>
       </c>
       <c r="F80" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 16:05:45</t>
+          <t>2026-04-16 17:01:13</t>
         </is>
       </c>
     </row>
@@ -8755,12 +8755,12 @@
       <c r="D81" s="24" t="inlineStr"/>
       <c r="E81" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:59:47</t>
+          <t>2026-04-16 16:55:17</t>
         </is>
       </c>
       <c r="F81" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:59:56</t>
+          <t>2026-04-16 16:55:39</t>
         </is>
       </c>
     </row>
@@ -8783,12 +8783,12 @@
       <c r="D82" s="24" t="inlineStr"/>
       <c r="E82" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:54:17</t>
+          <t>2026-04-16 16:49:17</t>
         </is>
       </c>
       <c r="F82" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:54:38</t>
+          <t>2026-04-16 16:49:55</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       <c r="D83" s="24" t="inlineStr"/>
       <c r="E83" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:48:47</t>
+          <t>2026-04-16 16:43:47</t>
         </is>
       </c>
       <c r="F83" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:48:52</t>
+          <t>2026-04-16 16:43:58</t>
         </is>
       </c>
     </row>
@@ -8839,12 +8839,12 @@
       <c r="D84" s="24" t="inlineStr"/>
       <c r="E84" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:43:17</t>
+          <t>2026-04-16 16:38:17</t>
         </is>
       </c>
       <c r="F84" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:43:41</t>
+          <t>2026-04-16 16:38:36</t>
         </is>
       </c>
     </row>
@@ -8867,12 +8867,12 @@
       <c r="D85" s="24" t="inlineStr"/>
       <c r="E85" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:37:47</t>
+          <t>2026-04-16 16:32:47</t>
         </is>
       </c>
       <c r="F85" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:38:01</t>
+          <t>2026-04-16 16:32:58</t>
         </is>
       </c>
     </row>
@@ -8895,12 +8895,12 @@
       <c r="D86" s="24" t="inlineStr"/>
       <c r="E86" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:32:17</t>
+          <t>2026-04-16 16:27:17</t>
         </is>
       </c>
       <c r="F86" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:32:41</t>
+          <t>2026-04-16 16:27:25</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       <c r="D87" s="24" t="inlineStr"/>
       <c r="E87" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:26:47</t>
+          <t>2026-04-16 16:21:47</t>
         </is>
       </c>
       <c r="F87" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:27:04</t>
+          <t>2026-04-16 16:22:05</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       <c r="D88" s="24" t="inlineStr"/>
       <c r="E88" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:21:17</t>
+          <t>2026-04-16 16:16:17</t>
         </is>
       </c>
       <c r="F88" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:21:40</t>
+          <t>2026-04-16 16:16:42</t>
         </is>
       </c>
     </row>
@@ -8979,12 +8979,12 @@
       <c r="D89" s="24" t="inlineStr"/>
       <c r="E89" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:15:47</t>
+          <t>2026-04-16 16:10:47</t>
         </is>
       </c>
       <c r="F89" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:16:00</t>
+          <t>2026-04-16 16:10:58</t>
         </is>
       </c>
     </row>
@@ -9007,12 +9007,12 @@
       <c r="D90" s="24" t="inlineStr"/>
       <c r="E90" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:10:17</t>
+          <t>2026-04-16 16:05:17</t>
         </is>
       </c>
       <c r="F90" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:10:37</t>
+          <t>2026-04-16 16:05:45</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       <c r="D91" s="24" t="inlineStr"/>
       <c r="E91" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:04:47</t>
+          <t>2026-04-16 15:59:47</t>
         </is>
       </c>
       <c r="F91" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 15:05:01</t>
+          <t>2026-04-16 15:59:56</t>
         </is>
       </c>
     </row>
@@ -9057,18 +9057,18 @@
       </c>
       <c r="C92" s="24" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D92" s="24" t="inlineStr"/>
       <c r="E92" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:58:17</t>
+          <t>2026-04-16 15:54:17</t>
         </is>
       </c>
       <c r="F92" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:59:20</t>
+          <t>2026-04-16 15:54:38</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       <c r="D93" s="24" t="inlineStr"/>
       <c r="E93" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:52:47</t>
+          <t>2026-04-16 15:48:47</t>
         </is>
       </c>
       <c r="F93" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:53:05</t>
+          <t>2026-04-16 15:48:52</t>
         </is>
       </c>
     </row>
@@ -9119,12 +9119,12 @@
       <c r="D94" s="24" t="inlineStr"/>
       <c r="E94" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:47:17</t>
+          <t>2026-04-16 15:43:17</t>
         </is>
       </c>
       <c r="F94" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:47:33</t>
+          <t>2026-04-16 15:43:41</t>
         </is>
       </c>
     </row>
@@ -9141,18 +9141,18 @@
       </c>
       <c r="C95" s="24" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D95" s="24" t="inlineStr"/>
       <c r="E95" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:40:47</t>
+          <t>2026-04-16 15:37:47</t>
         </is>
       </c>
       <c r="F95" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:42:02</t>
+          <t>2026-04-16 15:38:01</t>
         </is>
       </c>
     </row>
@@ -9175,12 +9175,12 @@
       <c r="D96" s="24" t="inlineStr"/>
       <c r="E96" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:35:17</t>
+          <t>2026-04-16 15:32:17</t>
         </is>
       </c>
       <c r="F96" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:35:28</t>
+          <t>2026-04-16 15:32:41</t>
         </is>
       </c>
     </row>
@@ -9203,12 +9203,12 @@
       <c r="D97" s="24" t="inlineStr"/>
       <c r="E97" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:29:47</t>
+          <t>2026-04-16 15:26:47</t>
         </is>
       </c>
       <c r="F97" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:30:04</t>
+          <t>2026-04-16 15:27:04</t>
         </is>
       </c>
     </row>
@@ -9231,12 +9231,12 @@
       <c r="D98" s="24" t="inlineStr"/>
       <c r="E98" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:24:17</t>
+          <t>2026-04-16 15:21:17</t>
         </is>
       </c>
       <c r="F98" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:24:38</t>
+          <t>2026-04-16 15:21:40</t>
         </is>
       </c>
     </row>
@@ -9259,12 +9259,12 @@
       <c r="D99" s="24" t="inlineStr"/>
       <c r="E99" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:18:47</t>
+          <t>2026-04-16 15:15:47</t>
         </is>
       </c>
       <c r="F99" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:18:52</t>
+          <t>2026-04-16 15:16:00</t>
         </is>
       </c>
     </row>
@@ -9287,12 +9287,12 @@
       <c r="D100" s="24" t="inlineStr"/>
       <c r="E100" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:13:17</t>
+          <t>2026-04-16 15:10:17</t>
         </is>
       </c>
       <c r="F100" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:13:39</t>
+          <t>2026-04-16 15:10:37</t>
         </is>
       </c>
     </row>
@@ -9315,12 +9315,12 @@
       <c r="D101" s="24" t="inlineStr"/>
       <c r="E101" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:07:47</t>
+          <t>2026-04-16 15:04:47</t>
         </is>
       </c>
       <c r="F101" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:07:59</t>
+          <t>2026-04-16 15:05:01</t>
         </is>
       </c>
     </row>
@@ -9337,18 +9337,18 @@
       </c>
       <c r="C102" s="24" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="D102" s="24" t="inlineStr"/>
       <c r="E102" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:02:17</t>
+          <t>2026-04-16 14:58:17</t>
         </is>
       </c>
       <c r="F102" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 14:02:42</t>
+          <t>2026-04-16 14:59:20</t>
         </is>
       </c>
     </row>
@@ -9371,12 +9371,12 @@
       <c r="D103" s="24" t="inlineStr"/>
       <c r="E103" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:56:47</t>
+          <t>2026-04-16 14:52:47</t>
         </is>
       </c>
       <c r="F103" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:56:57</t>
+          <t>2026-04-16 14:53:05</t>
         </is>
       </c>
     </row>
@@ -9399,12 +9399,12 @@
       <c r="D104" s="24" t="inlineStr"/>
       <c r="E104" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:51:16</t>
+          <t>2026-04-16 14:47:17</t>
         </is>
       </c>
       <c r="F104" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:51:39</t>
+          <t>2026-04-16 14:47:33</t>
         </is>
       </c>
     </row>
@@ -9421,18 +9421,18 @@
       </c>
       <c r="C105" s="24" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="D105" s="24" t="inlineStr"/>
       <c r="E105" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:45:46</t>
+          <t>2026-04-16 14:40:47</t>
         </is>
       </c>
       <c r="F105" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:46:06</t>
+          <t>2026-04-16 14:42:02</t>
         </is>
       </c>
     </row>
@@ -9455,12 +9455,12 @@
       <c r="D106" s="24" t="inlineStr"/>
       <c r="E106" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:40:16</t>
+          <t>2026-04-16 14:35:17</t>
         </is>
       </c>
       <c r="F106" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:40:46</t>
+          <t>2026-04-16 14:35:28</t>
         </is>
       </c>
     </row>
@@ -9477,18 +9477,18 @@
       </c>
       <c r="C107" s="24" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D107" s="24" t="inlineStr"/>
       <c r="E107" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:33:16</t>
+          <t>2026-04-16 14:29:47</t>
         </is>
       </c>
       <c r="F107" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:35:08</t>
+          <t>2026-04-16 14:30:04</t>
         </is>
       </c>
     </row>
@@ -9511,12 +9511,12 @@
       <c r="D108" s="24" t="inlineStr"/>
       <c r="E108" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:27:46</t>
+          <t>2026-04-16 14:24:17</t>
         </is>
       </c>
       <c r="F108" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:28:11</t>
+          <t>2026-04-16 14:24:38</t>
         </is>
       </c>
     </row>
@@ -9539,12 +9539,12 @@
       <c r="D109" s="24" t="inlineStr"/>
       <c r="E109" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:22:16</t>
+          <t>2026-04-16 14:18:47</t>
         </is>
       </c>
       <c r="F109" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:22:35</t>
+          <t>2026-04-16 14:18:52</t>
         </is>
       </c>
     </row>
@@ -9567,12 +9567,12 @@
       <c r="D110" s="24" t="inlineStr"/>
       <c r="E110" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:16:46</t>
+          <t>2026-04-16 14:13:17</t>
         </is>
       </c>
       <c r="F110" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:17:00</t>
+          <t>2026-04-16 14:13:39</t>
         </is>
       </c>
     </row>
@@ -9595,12 +9595,12 @@
       <c r="D111" s="24" t="inlineStr"/>
       <c r="E111" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:11:16</t>
+          <t>2026-04-16 14:07:47</t>
         </is>
       </c>
       <c r="F111" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:11:36</t>
+          <t>2026-04-16 14:07:59</t>
         </is>
       </c>
     </row>
@@ -9623,12 +9623,12 @@
       <c r="D112" s="24" t="inlineStr"/>
       <c r="E112" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:05:46</t>
+          <t>2026-04-16 14:02:17</t>
         </is>
       </c>
       <c r="F112" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:05:55</t>
+          <t>2026-04-16 14:02:42</t>
         </is>
       </c>
     </row>
@@ -9651,12 +9651,12 @@
       <c r="D113" s="24" t="inlineStr"/>
       <c r="E113" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:00:16</t>
+          <t>2026-04-16 13:56:47</t>
         </is>
       </c>
       <c r="F113" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 13:00:34</t>
+          <t>2026-04-16 13:56:57</t>
         </is>
       </c>
     </row>
@@ -9679,12 +9679,12 @@
       <c r="D114" s="24" t="inlineStr"/>
       <c r="E114" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:54:46</t>
+          <t>2026-04-16 13:51:16</t>
         </is>
       </c>
       <c r="F114" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:54:55</t>
+          <t>2026-04-16 13:51:39</t>
         </is>
       </c>
     </row>
@@ -9707,12 +9707,12 @@
       <c r="D115" s="24" t="inlineStr"/>
       <c r="E115" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:49:16</t>
+          <t>2026-04-16 13:45:46</t>
         </is>
       </c>
       <c r="F115" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:49:42</t>
+          <t>2026-04-16 13:46:06</t>
         </is>
       </c>
     </row>
@@ -9735,12 +9735,12 @@
       <c r="D116" s="24" t="inlineStr"/>
       <c r="E116" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:43:46</t>
+          <t>2026-04-16 13:40:16</t>
         </is>
       </c>
       <c r="F116" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:43:56</t>
+          <t>2026-04-16 13:40:46</t>
         </is>
       </c>
     </row>
@@ -9757,18 +9757,18 @@
       </c>
       <c r="C117" s="24" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="D117" s="24" t="inlineStr"/>
       <c r="E117" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:38:16</t>
+          <t>2026-04-16 13:33:16</t>
         </is>
       </c>
       <c r="F117" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:38:26</t>
+          <t>2026-04-16 13:35:08</t>
         </is>
       </c>
     </row>
@@ -9791,12 +9791,12 @@
       <c r="D118" s="24" t="inlineStr"/>
       <c r="E118" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:32:46</t>
+          <t>2026-04-16 13:27:46</t>
         </is>
       </c>
       <c r="F118" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:33:11</t>
+          <t>2026-04-16 13:28:11</t>
         </is>
       </c>
     </row>
@@ -9819,12 +9819,12 @@
       <c r="D119" s="24" t="inlineStr"/>
       <c r="E119" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:27:16</t>
+          <t>2026-04-16 13:22:16</t>
         </is>
       </c>
       <c r="F119" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:27:25</t>
+          <t>2026-04-16 13:22:35</t>
         </is>
       </c>
     </row>
@@ -9847,12 +9847,12 @@
       <c r="D120" s="24" t="inlineStr"/>
       <c r="E120" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:21:46</t>
+          <t>2026-04-16 13:16:46</t>
         </is>
       </c>
       <c r="F120" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:21:56</t>
+          <t>2026-04-16 13:17:00</t>
         </is>
       </c>
     </row>
@@ -9875,12 +9875,12 @@
       <c r="D121" s="24" t="inlineStr"/>
       <c r="E121" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:16:16</t>
+          <t>2026-04-16 13:11:16</t>
         </is>
       </c>
       <c r="F121" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:16:30</t>
+          <t>2026-04-16 13:11:36</t>
         </is>
       </c>
     </row>
@@ -9903,12 +9903,12 @@
       <c r="D122" s="24" t="inlineStr"/>
       <c r="E122" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:10:46</t>
+          <t>2026-04-16 13:05:46</t>
         </is>
       </c>
       <c r="F122" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:10:54</t>
+          <t>2026-04-16 13:05:55</t>
         </is>
       </c>
     </row>
@@ -9925,18 +9925,18 @@
       </c>
       <c r="C123" s="24" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D123" s="24" t="inlineStr"/>
       <c r="E123" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:03:46</t>
+          <t>2026-04-16 13:00:16</t>
         </is>
       </c>
       <c r="F123" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 12:05:18</t>
+          <t>2026-04-16 13:00:34</t>
         </is>
       </c>
     </row>
@@ -9959,12 +9959,12 @@
       <c r="D124" s="24" t="inlineStr"/>
       <c r="E124" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:58:16</t>
+          <t>2026-04-16 12:54:46</t>
         </is>
       </c>
       <c r="F124" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:58:21</t>
+          <t>2026-04-16 12:54:55</t>
         </is>
       </c>
     </row>
@@ -9987,12 +9987,12 @@
       <c r="D125" s="24" t="inlineStr"/>
       <c r="E125" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:52:46</t>
+          <t>2026-04-16 12:49:16</t>
         </is>
       </c>
       <c r="F125" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:52:56</t>
+          <t>2026-04-16 12:49:42</t>
         </is>
       </c>
     </row>
@@ -10015,12 +10015,12 @@
       <c r="D126" s="24" t="inlineStr"/>
       <c r="E126" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:47:16</t>
+          <t>2026-04-16 12:43:46</t>
         </is>
       </c>
       <c r="F126" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:47:21</t>
+          <t>2026-04-16 12:43:56</t>
         </is>
       </c>
     </row>
@@ -10043,12 +10043,12 @@
       <c r="D127" s="24" t="inlineStr"/>
       <c r="E127" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:41:46</t>
+          <t>2026-04-16 12:38:16</t>
         </is>
       </c>
       <c r="F127" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:41:54</t>
+          <t>2026-04-16 12:38:26</t>
         </is>
       </c>
     </row>
@@ -10071,12 +10071,68 @@
       <c r="D128" s="24" t="inlineStr"/>
       <c r="E128" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:36:16</t>
+          <t>2026-04-16 12:32:46</t>
         </is>
       </c>
       <c r="F128" s="24" t="inlineStr">
         <is>
-          <t>2026-04-16 11:36:27</t>
+          <t>2026-04-16 12:33:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B129" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C129" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D129" s="24" t="inlineStr"/>
+      <c r="E129" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:27:16</t>
+        </is>
+      </c>
+      <c r="F129" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:27:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="24" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B130" s="24" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C130" s="24" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="D130" s="24" t="inlineStr"/>
+      <c r="E130" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:21:46</t>
+        </is>
+      </c>
+      <c r="F130" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-16 12:21:56</t>
         </is>
       </c>
     </row>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -5882,7 +5882,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>PAPERCLIP STATUS — 2026-04-17 12:18</t>
+          <t>PAPERCLIP STATUS — 2026-04-17 12:48</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F130"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="7" min="1" max="1"/>
@@ -6416,7 +6416,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>RUN HISTORY (Last 24h) — 2026-04-17 12:18</t>
+          <t>RUN HISTORY (Last 24h) — 2026-04-17 12:48</t>
         </is>
       </c>
     </row>
@@ -9993,146 +9993,6 @@
       <c r="F125" s="24" t="inlineStr">
         <is>
           <t>2026-04-16 12:49:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B126" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C126" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D126" s="24" t="inlineStr"/>
-      <c r="E126" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:43:46</t>
-        </is>
-      </c>
-      <c r="F126" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:43:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B127" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C127" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D127" s="24" t="inlineStr"/>
-      <c r="E127" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:38:16</t>
-        </is>
-      </c>
-      <c r="F127" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:38:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B128" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C128" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D128" s="24" t="inlineStr"/>
-      <c r="E128" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:32:46</t>
-        </is>
-      </c>
-      <c r="F128" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:33:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B129" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C129" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D129" s="24" t="inlineStr"/>
-      <c r="E129" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:27:16</t>
-        </is>
-      </c>
-      <c r="F129" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:27:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B130" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C130" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D130" s="24" t="inlineStr"/>
-      <c r="E130" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:21:46</t>
-        </is>
-      </c>
-      <c r="F130" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:21:56</t>
         </is>
       </c>
     </row>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -5882,7 +5882,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>PAPERCLIP STATUS — 2026-04-17 12:48</t>
+          <t>PAPERCLIP STATUS — 2026-04-17 15:48</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="7" min="1" max="1"/>
@@ -6416,7 +6416,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>RUN HISTORY (Last 24h) — 2026-04-17 12:48</t>
+          <t>RUN HISTORY (Last 24h) — 2026-04-17 15:48</t>
         </is>
       </c>
     </row>
@@ -9069,930 +9069,6 @@
       <c r="F92" s="24" t="inlineStr">
         <is>
           <t>2026-04-16 15:54:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B93" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C93" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D93" s="24" t="inlineStr"/>
-      <c r="E93" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:48:47</t>
-        </is>
-      </c>
-      <c r="F93" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:48:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B94" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C94" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D94" s="24" t="inlineStr"/>
-      <c r="E94" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:43:17</t>
-        </is>
-      </c>
-      <c r="F94" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:43:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B95" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C95" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D95" s="24" t="inlineStr"/>
-      <c r="E95" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:37:47</t>
-        </is>
-      </c>
-      <c r="F95" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:38:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B96" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C96" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D96" s="24" t="inlineStr"/>
-      <c r="E96" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:32:17</t>
-        </is>
-      </c>
-      <c r="F96" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:32:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B97" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C97" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D97" s="24" t="inlineStr"/>
-      <c r="E97" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:26:47</t>
-        </is>
-      </c>
-      <c r="F97" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:27:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B98" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C98" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D98" s="24" t="inlineStr"/>
-      <c r="E98" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:21:17</t>
-        </is>
-      </c>
-      <c r="F98" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:21:40</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B99" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C99" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D99" s="24" t="inlineStr"/>
-      <c r="E99" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:15:47</t>
-        </is>
-      </c>
-      <c r="F99" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:16:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B100" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C100" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D100" s="24" t="inlineStr"/>
-      <c r="E100" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:10:17</t>
-        </is>
-      </c>
-      <c r="F100" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:10:37</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B101" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C101" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D101" s="24" t="inlineStr"/>
-      <c r="E101" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:04:47</t>
-        </is>
-      </c>
-      <c r="F101" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:05:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B102" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C102" s="24" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
-      <c r="D102" s="24" t="inlineStr"/>
-      <c r="E102" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:58:17</t>
-        </is>
-      </c>
-      <c r="F102" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:59:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B103" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C103" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D103" s="24" t="inlineStr"/>
-      <c r="E103" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:52:47</t>
-        </is>
-      </c>
-      <c r="F103" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:53:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B104" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C104" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D104" s="24" t="inlineStr"/>
-      <c r="E104" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:47:17</t>
-        </is>
-      </c>
-      <c r="F104" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:47:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B105" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C105" s="24" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
-      <c r="D105" s="24" t="inlineStr"/>
-      <c r="E105" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:40:47</t>
-        </is>
-      </c>
-      <c r="F105" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:42:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B106" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C106" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D106" s="24" t="inlineStr"/>
-      <c r="E106" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:35:17</t>
-        </is>
-      </c>
-      <c r="F106" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:35:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B107" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C107" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D107" s="24" t="inlineStr"/>
-      <c r="E107" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:29:47</t>
-        </is>
-      </c>
-      <c r="F107" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:30:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B108" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C108" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D108" s="24" t="inlineStr"/>
-      <c r="E108" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:24:17</t>
-        </is>
-      </c>
-      <c r="F108" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:24:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B109" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C109" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D109" s="24" t="inlineStr"/>
-      <c r="E109" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:18:47</t>
-        </is>
-      </c>
-      <c r="F109" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:18:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B110" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C110" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D110" s="24" t="inlineStr"/>
-      <c r="E110" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:13:17</t>
-        </is>
-      </c>
-      <c r="F110" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:13:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B111" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C111" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D111" s="24" t="inlineStr"/>
-      <c r="E111" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:07:47</t>
-        </is>
-      </c>
-      <c r="F111" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:07:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B112" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C112" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D112" s="24" t="inlineStr"/>
-      <c r="E112" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:02:17</t>
-        </is>
-      </c>
-      <c r="F112" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 14:02:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B113" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C113" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D113" s="24" t="inlineStr"/>
-      <c r="E113" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:56:47</t>
-        </is>
-      </c>
-      <c r="F113" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:56:57</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B114" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C114" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D114" s="24" t="inlineStr"/>
-      <c r="E114" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:51:16</t>
-        </is>
-      </c>
-      <c r="F114" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:51:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B115" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C115" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D115" s="24" t="inlineStr"/>
-      <c r="E115" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:45:46</t>
-        </is>
-      </c>
-      <c r="F115" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:46:06</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B116" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C116" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D116" s="24" t="inlineStr"/>
-      <c r="E116" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:40:16</t>
-        </is>
-      </c>
-      <c r="F116" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:40:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B117" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C117" s="24" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
-      <c r="D117" s="24" t="inlineStr"/>
-      <c r="E117" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:33:16</t>
-        </is>
-      </c>
-      <c r="F117" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:35:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B118" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C118" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D118" s="24" t="inlineStr"/>
-      <c r="E118" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:27:46</t>
-        </is>
-      </c>
-      <c r="F118" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:28:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B119" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C119" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D119" s="24" t="inlineStr"/>
-      <c r="E119" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:22:16</t>
-        </is>
-      </c>
-      <c r="F119" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:22:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B120" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C120" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D120" s="24" t="inlineStr"/>
-      <c r="E120" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:16:46</t>
-        </is>
-      </c>
-      <c r="F120" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:17:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B121" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C121" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D121" s="24" t="inlineStr"/>
-      <c r="E121" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:11:16</t>
-        </is>
-      </c>
-      <c r="F121" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:11:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B122" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C122" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D122" s="24" t="inlineStr"/>
-      <c r="E122" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:05:46</t>
-        </is>
-      </c>
-      <c r="F122" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:05:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B123" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C123" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D123" s="24" t="inlineStr"/>
-      <c r="E123" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:00:16</t>
-        </is>
-      </c>
-      <c r="F123" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:00:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B124" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C124" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D124" s="24" t="inlineStr"/>
-      <c r="E124" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:54:46</t>
-        </is>
-      </c>
-      <c r="F124" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:54:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B125" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C125" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D125" s="24" t="inlineStr"/>
-      <c r="E125" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:49:16</t>
-        </is>
-      </c>
-      <c r="F125" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:49:42</t>
         </is>
       </c>
     </row>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -5882,7 +5882,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>PAPERCLIP STATUS — 2026-04-17 15:48</t>
+          <t>PAPERCLIP STATUS — 2026-04-17 16:18</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="7" min="1" max="1"/>
@@ -6416,7 +6416,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>RUN HISTORY (Last 24h) — 2026-04-17 15:48</t>
+          <t>RUN HISTORY (Last 24h) — 2026-04-17 16:18</t>
         </is>
       </c>
     </row>
@@ -8929,146 +8929,6 @@
       <c r="F87" s="24" t="inlineStr">
         <is>
           <t>2026-04-16 16:22:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B88" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C88" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D88" s="24" t="inlineStr"/>
-      <c r="E88" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:16:17</t>
-        </is>
-      </c>
-      <c r="F88" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:16:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B89" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C89" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D89" s="24" t="inlineStr"/>
-      <c r="E89" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:10:47</t>
-        </is>
-      </c>
-      <c r="F89" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:10:58</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B90" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C90" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D90" s="24" t="inlineStr"/>
-      <c r="E90" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:05:17</t>
-        </is>
-      </c>
-      <c r="F90" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:05:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B91" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C91" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D91" s="24" t="inlineStr"/>
-      <c r="E91" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:59:47</t>
-        </is>
-      </c>
-      <c r="F91" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:59:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B92" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C92" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D92" s="24" t="inlineStr"/>
-      <c r="E92" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:54:17</t>
-        </is>
-      </c>
-      <c r="F92" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:54:38</t>
         </is>
       </c>
     </row>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -5882,7 +5882,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>PAPERCLIP STATUS — 2026-04-17 16:18</t>
+          <t>PAPERCLIP STATUS — 2026-04-17 19:19</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="7" min="1" max="1"/>
@@ -6416,7 +6416,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>RUN HISTORY (Last 24h) — 2026-04-17 16:18</t>
+          <t>RUN HISTORY (Last 24h) — 2026-04-17 19:19</t>
         </is>
       </c>
     </row>
@@ -8405,530 +8405,6 @@
       <c r="F69" s="24" t="inlineStr">
         <is>
           <t>2026-04-16 19:30:51</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B70" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C70" s="23" t="inlineStr">
-        <is>
-          <t>21m</t>
-        </is>
-      </c>
-      <c r="D70" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 900s</t>
-        </is>
-      </c>
-      <c r="E70" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-16 19:01:04</t>
-        </is>
-      </c>
-      <c r="F70" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-16 19:22:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B71" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C71" s="23" t="inlineStr">
-        <is>
-          <t>15m</t>
-        </is>
-      </c>
-      <c r="D71" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 900s</t>
-        </is>
-      </c>
-      <c r="E71" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-16 18:40:38</t>
-        </is>
-      </c>
-      <c r="F71" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-16 18:55:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B72" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C72" s="23" t="inlineStr">
-        <is>
-          <t>17m</t>
-        </is>
-      </c>
-      <c r="D72" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 900s</t>
-        </is>
-      </c>
-      <c r="E72" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-16 18:06:53</t>
-        </is>
-      </c>
-      <c r="F72" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-16 18:24:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B73" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C73" s="23" t="inlineStr">
-        <is>
-          <t>15m</t>
-        </is>
-      </c>
-      <c r="D73" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 900s</t>
-        </is>
-      </c>
-      <c r="E73" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:51:34</t>
-        </is>
-      </c>
-      <c r="F73" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-16 18:06:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B74" s="23" t="inlineStr">
-        <is>
-          <t>timed_out</t>
-        </is>
-      </c>
-      <c r="C74" s="23" t="inlineStr">
-        <is>
-          <t>17m</t>
-        </is>
-      </c>
-      <c r="D74" s="23" t="inlineStr">
-        <is>
-          <t>Timed out after 900s</t>
-        </is>
-      </c>
-      <c r="E74" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:33:50</t>
-        </is>
-      </c>
-      <c r="F74" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:51:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B75" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C75" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D75" s="24" t="inlineStr"/>
-      <c r="E75" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:28:17</t>
-        </is>
-      </c>
-      <c r="F75" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:28:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B76" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C76" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D76" s="24" t="inlineStr"/>
-      <c r="E76" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:22:47</t>
-        </is>
-      </c>
-      <c r="F76" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:22:58</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B77" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C77" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D77" s="24" t="inlineStr"/>
-      <c r="E77" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:17:17</t>
-        </is>
-      </c>
-      <c r="F77" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:17:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B78" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C78" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D78" s="24" t="inlineStr"/>
-      <c r="E78" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:11:47</t>
-        </is>
-      </c>
-      <c r="F78" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:12:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B79" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C79" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D79" s="24" t="inlineStr"/>
-      <c r="E79" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:06:17</t>
-        </is>
-      </c>
-      <c r="F79" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:06:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B80" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C80" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D80" s="24" t="inlineStr"/>
-      <c r="E80" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:00:47</t>
-        </is>
-      </c>
-      <c r="F80" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 17:01:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B81" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C81" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D81" s="24" t="inlineStr"/>
-      <c r="E81" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:55:17</t>
-        </is>
-      </c>
-      <c r="F81" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:55:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B82" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C82" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D82" s="24" t="inlineStr"/>
-      <c r="E82" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:49:17</t>
-        </is>
-      </c>
-      <c r="F82" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:49:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B83" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C83" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D83" s="24" t="inlineStr"/>
-      <c r="E83" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:43:47</t>
-        </is>
-      </c>
-      <c r="F83" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:43:58</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B84" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C84" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D84" s="24" t="inlineStr"/>
-      <c r="E84" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:38:17</t>
-        </is>
-      </c>
-      <c r="F84" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:38:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B85" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C85" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D85" s="24" t="inlineStr"/>
-      <c r="E85" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:32:47</t>
-        </is>
-      </c>
-      <c r="F85" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:32:58</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B86" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C86" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D86" s="24" t="inlineStr"/>
-      <c r="E86" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:27:17</t>
-        </is>
-      </c>
-      <c r="F86" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:27:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="24" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B87" s="24" t="inlineStr">
-        <is>
-          <t>succeeded</t>
-        </is>
-      </c>
-      <c r="C87" s="24" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="D87" s="24" t="inlineStr"/>
-      <c r="E87" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:21:47</t>
-        </is>
-      </c>
-      <c r="F87" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-16 16:22:05</t>
         </is>
       </c>
     </row>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -2918,7 +2918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2981,42 +2981,126 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
+          <t>THIS WEEKEND (17-20 Apr)</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Fix footer legal routes redirecting to /auth/login</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>expose /legal, /auth/accept-terms, /api/consents as public paths in middleware — done 2026-04-18: middleware allow-list extended, verified on tenu.world production in incognito, all six legal pages render without auth. Commit via PR fix/public-legal-routes merged to main. Pre-contractual disclosure (art. L221-5 Code de la conso) now reachable as required for Stripe/App Store review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>T-002</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>THIS WEEKEND (17-20 Apr)</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Use-case content system</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>manifest + /stories index + cross-link strip + homepage dual-card — done 2026-04-18: src/lib/stories.ts (single source of truth, Story type, 4 helpers), src/components/stories/OtherCases.tsx (bilingual cross-link strip), src/app/stories/page.tsx (index with cautionary populated, success placeholder awaiting 11 May cohort), homepage example section refactored from single Suzi hook to manifest-driven dual-card grid with "See all cases →" link, Suzi + Samir pages thread OtherCases before footer, example block in en/fr/zh/ar/ur dictionaries refactored to label/heading/intro/seeAll/disclaimer. Adding a new case is now one append to stories.ts + one new /stories/&lt;slug&gt;/page.tsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>T-003</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
+  <autoFilter ref="A1:H4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -2918,7 +2918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Use-case content system</t>
+          <t>Fix /stories/* and /features/* redirecting to /auth/login</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>manifest + /stories index + cross-link strip + homepage dual-card — done 2026-04-18: src/lib/stories.ts (single source of truth, Story type, 4 helpers), src/components/stories/OtherCases.tsx (bilingual cross-link strip), src/app/stories/page.tsx (index with cautionary populated, success placeholder awaiting 11 May cohort), homepage example section refactored from single Suzi hook to manifest-driven dual-card grid with "See all cases →" link, Suzi + Samir pages thread OtherCases before footer, example block in en/fr/zh/ar/ur dictionaries refactored to label/heading/intro/seeAll/disclaimer. Adding a new case is now one append to stories.ts + one new /stories/&lt;slug&gt;/page.tsx.</t>
+          <t>done 2026-04-18: added "/stories" and "/features" to publicPaths in src/middleware.ts. Same isPublicPath startsWith match pattern as the /legal fix; single entry per parent covers all nested routes. Stories and features now reachable without auth as marketing/content surface.</t>
         </is>
       </c>
     </row>
@@ -3065,42 +3065,84 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
+          <t>THIS WEEKEND (17-20 Apr)</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Use-case content system</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>manifest + /stories index + cross-link strip + homepage dual-card — done 2026-04-18: src/lib/stories.ts (single source of truth, Story type, 4 helpers), src/components/stories/OtherCases.tsx (bilingual cross-link strip), src/app/stories/page.tsx (index with cautionary populated, success placeholder awaiting 11 May cohort), homepage example section refactored from single Suzi hook to manifest-driven dual-card grid with "See all cases →" link, Suzi + Samir pages thread OtherCases before footer, example block in en/fr/zh/ar/ur dictionaries refactored to label/heading/intro/seeAll/disclaimer. Adding a new case is now one append to stories.ts + one new /stories/&lt;slug&gt;/page.tsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>T-004</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H4"/>
+  <autoFilter ref="A1:H5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -756,7 +756,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Telegram one-time setup</t>
+          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
+          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
+          <t>Google Play Console developer account, USD 25 one-time</t>
         </is>
       </c>
     </row>
@@ -822,19 +822,19 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -844,19 +844,19 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Paste ANTHROPIC_API_KEY into .env.local + Vercel project env</t>
+          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -866,19 +866,19 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Paste BREVO_API_KEY into .env.local + Vercel project env</t>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -888,14 +888,14 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
+          <t>PDF generation leg</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -910,14 +910,14 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
+          <t>Brevo transactional email leg</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -932,19 +932,19 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -954,14 +954,14 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
+          <t>Capacitor 6 scaffold</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -976,14 +976,14 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1019,72 +1019,6 @@
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>Capacitor 6 scaffold</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
@@ -1101,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1222,19 +1156,15 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Telegram one-time setup</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>create bot via @BotFather, send token + chat_id</t>
-        </is>
-      </c>
+          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1264,12 +1194,12 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
+          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr"/>
@@ -1307,7 +1237,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
+          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr"/>
@@ -1345,7 +1275,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
+          <t>Google Play Console developer account, USD 25 one-time</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr"/>
@@ -1383,7 +1313,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr"/>
@@ -1396,17 +1326,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1416,15 +1346,19 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Paste ANTHROPIC_API_KEY into .env.local + Vercel project env</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr"/>
+          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>code shipped 2026-04-17: zod schema + FR/EN system prompts + Sonnet → Sonnet retry (no Haiku/Opus fallback) + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504, server-forced disclaimer injection via disclaimerFor(locale), route pulls scan v2 from inspections.risk_score.v2 and upserts dispute_letters row. BLOCKED: tsc verification — bash sandbox locked from prior session; needs Cowork session reset to run npx tsc --noEmit</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1434,17 +1368,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1454,15 +1388,19 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Paste BREVO_API_KEY into .env.local + Vercel project env</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr"/>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1472,7 +1410,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1482,7 +1420,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1492,15 +1430,19 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr"/>
+          <t>PDF generation leg</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1513,9 +1455,9 @@
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1530,17 +1472,17 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
+          <t>Brevo transactional email leg</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>code shipped 2026-04-17: zod schema + FR/EN system prompts + Sonnet → Sonnet retry (no Haiku/Opus fallback) + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504, server-forced disclaimer injection via disclaimerFor(locale), route pulls scan v2 from inspections.risk_score.v2 and upserts dispute_letters row. BLOCKED: tsc verification — bash sandbox locked from prior session; needs Cowork session reset to run npx tsc --noEmit</t>
+          <t>send scan-complete + dispute-ready emails with R2 PDF link</t>
         </is>
       </c>
     </row>
@@ -1572,15 +1514,19 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr"/>
+          <t>Capacitor 6 scaffold</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>iOS + Android native projects under app/ios and app/android</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1610,12 +1556,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr"/>
@@ -1648,19 +1594,15 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Capacitor 6 scaffold</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>iOS + Android native projects under app/ios and app/android</t>
-        </is>
-      </c>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1695,7 +1637,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr"/>
@@ -1718,7 +1660,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1728,12 +1670,12 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr"/>
@@ -1746,7 +1688,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1766,15 +1708,19 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr"/>
+          <t>App icon set</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1784,7 +1730,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1794,7 +1740,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1804,12 +1750,12 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
+          <t>Splash screens per density, status bar theming, safe-area insets</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr"/>
@@ -1822,7 +1768,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1832,7 +1778,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1842,12 +1788,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr"/>
@@ -1880,17 +1826,17 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>App icon set</t>
+          <t>Store listing copy drafted in FR + EN</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive</t>
+          <t>description, keywords, support URL, privacy URL</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1868,12 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Splash screens per density, status bar theming, safe-area insets</t>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr"/>
@@ -1950,7 +1896,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -1960,12 +1906,12 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr"/>
@@ -1988,7 +1934,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -1998,17 +1944,17 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Store listing copy drafted in FR + EN</t>
+          <t>Decide Apple IAP stance</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>description, keywords, support URL, privacy URL</t>
+          <t>physical service argument documented</t>
         </is>
       </c>
     </row>
@@ -2020,7 +1966,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -2040,12 +1986,12 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr"/>
@@ -2058,7 +2004,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2068,7 +2014,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2078,15 +2024,19 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr"/>
+          <t>Magic-link auth working inside app</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>email link opens app, session persists</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2096,7 +2046,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -2106,29 +2056,25 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>physical service argument documented</t>
-        </is>
-      </c>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2158,15 +2104,19 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr"/>
+          <t>T-103-core pipeline tests</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2196,19 +2146,15 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>email link opens app, session persists</t>
-        </is>
-      </c>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -2233,17 +2179,17 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr"/>
@@ -2266,7 +2212,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2276,17 +2222,17 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>T-103-core pipeline tests</t>
+          <t>Médiateur de la consommation signed</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
+          <t>MEDICYS OR SMCE OR AME Conso</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2254,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2318,12 +2264,12 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr"/>
@@ -2346,7 +2292,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2356,12 +2302,12 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr"/>
@@ -2399,14 +2345,10 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation signed</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>MEDICYS OR SMCE OR AME Conso</t>
-        </is>
-      </c>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -2436,15 +2378,19 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr"/>
+          <t>F&amp;F invite list</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>8 names, email, jurisdiction, case type</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -2474,12 +2420,12 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr"/>
@@ -2492,7 +2438,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2502,7 +2448,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2512,15 +2458,19 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr"/>
+          <t>Bug sweep on inspection UI</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>camera retries, upload resume, offline queue</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -2530,7 +2480,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2540,7 +2490,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2550,19 +2500,15 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
-        </is>
-      </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>8 names, email, jurisdiction, case type</t>
-        </is>
-      </c>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -2572,7 +2518,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -2592,12 +2538,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr"/>
@@ -2620,7 +2566,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2630,19 +2576,15 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Bug sweep on inspection UI</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>camera retries, upload resume, offline queue</t>
-        </is>
-      </c>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -2652,7 +2594,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -2667,20 +2609,20 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr"/>
+          <t>Full T-103 suite</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -2690,7 +2632,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2700,25 +2642,25 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr"/>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="inlineStr"/>
+          <t>14-day outcome survey cron</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Brevo trigger + Supabase write-back</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -2728,7 +2670,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -2738,25 +2680,25 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr"/>
+          <t>Additional UI locales</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -2787,127 +2729,13 @@
       <c r="F43" s="5" t="inlineStr"/>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Full T-103 suite</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>T-043</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr"/>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>14-day outcome survey cron</t>
-        </is>
-      </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>Brevo trigger + Supabase write-back</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>T-044</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr"/>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>Additional UI locales</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>T-045</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
           <t>App Store + Play production updates with post-launch fixes</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H46"/>
+  <autoFilter ref="A1:H43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2918,7 +2746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3107,42 +2935,252 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
+          <t>THIS WEEKEND (17-20 Apr)</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Telegram one-time setup</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>create bot via @BotFather, send token + chat_id — done 2026-04-18: bot created, token + chat_id set in .env.local and Vercel env (per Dr Mubashir)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>T-005</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>THIS WEEKEND (17-20 Apr)</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Paste ANTHROPIC_API_KEY into .env.local + Vercel project env</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>T-006</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>THIS WEEKEND (17-20 Apr)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Paste BREVO_API_KEY into .env.local + Vercel project env</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>T-007</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>T-008</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>T-009</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H5"/>
+  <autoFilter ref="A1:H10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -741,7 +741,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
+          <t>Delete three iCloud dedup files in scripts/ on Mac (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`). Fuse mount blocks Cowork rm</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
+          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
+          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
         </is>
       </c>
     </row>
@@ -822,19 +822,19 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
+          <t>Google Play Console developer account, USD 25 one-time</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -844,19 +844,19 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -866,19 +866,19 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -888,19 +888,19 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -910,19 +910,19 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Brevo transactional email leg</t>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -932,19 +932,19 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -954,14 +954,14 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Capacitor 6 scaffold</t>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -976,14 +976,14 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -998,27 +998,159 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>PDF generation leg</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Brevo transactional email leg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
@@ -1035,7 +1167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1346,17 +1478,17 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>code shipped 2026-04-17: zod schema + FR/EN system prompts + Sonnet → Sonnet retry (no Haiku/Opus fallback) + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504, server-forced disclaimer injection via disclaimerFor(locale), route pulls scan v2 from inspections.risk_score.v2 and upserts dispute_letters row. BLOCKED: tsc verification — bash sandbox locked from prior session; needs Cowork session reset to run npx tsc --noEmit</t>
+          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
         </is>
       </c>
     </row>
@@ -1371,9 +1503,9 @@
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1393,12 +1525,12 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>PDF generation leg</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
+          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
         </is>
       </c>
     </row>
@@ -1413,9 +1545,9 @@
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1435,12 +1567,12 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
+          <t>Brevo transactional email leg</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
+          <t>send scan-complete + dispute-ready emails with R2 PDF link — started 2026-04-18: model chosen = in-repo HTML templates under docs/email-templates/, Brevo as transport via API. Awaiting Dr Mubashir confirmation on template path vs dashboard-template-ID path before wiring.</t>
         </is>
       </c>
     </row>
@@ -1462,29 +1594,25 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Brevo transactional email leg</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>send scan-complete + dispute-ready emails with R2 PDF link</t>
-        </is>
-      </c>
+          <t>Delete three iCloud dedup files in scripts/ on Mac (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`). Fuse mount blocks Cowork rm</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1504,7 +1632,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1514,19 +1642,15 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Capacitor 6 scaffold</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>iOS + Android native projects under app/ios and app/android</t>
-        </is>
-      </c>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1546,7 +1670,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1556,12 +1680,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr"/>
@@ -1584,7 +1708,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1594,12 +1718,12 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr"/>
@@ -1622,7 +1746,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1632,12 +1756,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr"/>
@@ -1670,12 +1794,12 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr"/>
@@ -1688,7 +1812,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1698,7 +1822,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1708,19 +1832,15 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>App icon set</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive</t>
-        </is>
-      </c>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1730,7 +1850,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1740,7 +1860,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1750,12 +1870,12 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Splash screens per density, status bar theming, safe-area insets</t>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr"/>
@@ -1768,7 +1888,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1788,12 +1908,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr"/>
@@ -1806,7 +1926,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1826,19 +1946,15 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Store listing copy drafted in FR + EN</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>description, keywords, support URL, privacy URL</t>
-        </is>
-      </c>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1848,7 +1964,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1868,12 +1984,12 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr"/>
@@ -1886,7 +2002,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1906,12 +2022,12 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr"/>
@@ -1934,7 +2050,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -1949,12 +2065,12 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
+          <t>App icon set</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>physical service argument documented</t>
+          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive</t>
         </is>
       </c>
     </row>
@@ -1966,7 +2082,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1986,12 +2102,12 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+          <t>Splash screens per density, status bar theming, safe-area insets</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr"/>
@@ -2004,7 +2120,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2024,19 +2140,15 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>email link opens app, session persists</t>
-        </is>
-      </c>
+          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2046,7 +2158,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -2061,20 +2173,24 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr"/>
+          <t>Store listing copy drafted in FR + EN</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>description, keywords, support URL, privacy URL</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2084,7 +2200,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -2104,19 +2220,15 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>T-103-core pipeline tests</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
-        </is>
-      </c>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2126,7 +2238,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -2136,7 +2248,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2146,12 +2258,12 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr"/>
@@ -2164,7 +2276,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -2174,7 +2286,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2184,15 +2296,19 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr"/>
+          <t>Decide Apple IAP stance</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>physical service argument documented</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -2212,7 +2328,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2222,19 +2338,15 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation signed</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>MEDICYS OR SMCE OR AME Conso</t>
-        </is>
-      </c>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -2254,7 +2366,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2264,15 +2376,19 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr"/>
+          <t>Magic-link auth working inside app</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>email link opens app, session persists</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -2292,12 +2408,12 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2307,7 +2423,7 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr"/>
@@ -2330,7 +2446,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2340,15 +2456,19 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr"/>
+          <t>T-103-core pipeline tests</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -2368,7 +2488,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2378,19 +2498,15 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>8 names, email, jurisdiction, case type</t>
-        </is>
-      </c>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -2410,7 +2526,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2420,12 +2536,12 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr"/>
@@ -2438,7 +2554,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2448,7 +2564,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2458,17 +2574,17 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Bug sweep on inspection UI</t>
+          <t>Médiateur de la consommation signed</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>camera retries, upload resume, offline queue</t>
+          <t>MEDICYS OR SMCE OR AME Conso</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2596,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2490,7 +2606,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2500,12 +2616,12 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr"/>
@@ -2518,7 +2634,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -2538,12 +2654,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr"/>
@@ -2556,7 +2672,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -2576,12 +2692,12 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr"/>
@@ -2594,7 +2710,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>POST-LAUNCH (12-31 May)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -2604,23 +2720,27 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr"/>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Full T-103 suite</t>
+          <t>F&amp;F invite list</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+          <t>8 names, email, jurisdiction, case type</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2752,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>POST-LAUNCH (12-31 May)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2642,25 +2762,25 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr"/>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>14-day outcome survey cron</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>Brevo trigger + Supabase write-back</t>
-        </is>
-      </c>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -2670,7 +2790,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>POST-LAUNCH (12-31 May)</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -2685,18 +2805,22 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr"/>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Additional UI locales</t>
+          <t>Bug sweep on inspection UI</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
+          <t>camera retries, upload resume, offline queue</t>
         </is>
       </c>
     </row>
@@ -2708,34 +2832,262 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
+          <t>LAUNCH WEEK (8-11 May)</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>T-043</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>LAUNCH WEEK (8-11 May)</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>T-044</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>LAUNCH WEEK (8-11 May)</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>T-045</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
           <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>P2 Post-launch</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr"/>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Full T-103 suite</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>T-046</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>14-day outcome survey cron</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Brevo trigger + Supabase write-back</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>T-047</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>Additional UI locales</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>T-048</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>App Store + Play production updates with post-launch fixes</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H43"/>
+  <autoFilter ref="A1:H49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2746,7 +3098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3128,12 +3480,12 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
+          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
+          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3507,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3170,17 +3522,101 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
+          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>T-010</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Capacitor 7 scaffold</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>T-011</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
           <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H10"/>
+  <autoFilter ref="A1:H12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Brevo transactional email leg</t>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -1129,28 +1129,6 @@
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
@@ -1167,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1545,36 +1523,32 @@
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Brevo transactional email leg</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>send scan-complete + dispute-ready emails with R2 PDF link — started 2026-04-18: model chosen = in-repo HTML templates under docs/email-templates/, Brevo as transport via API. Awaiting Dr Mubashir confirmation on template path vs dashboard-template-ID path before wiring.</t>
-        </is>
-      </c>
+          <t>Delete three iCloud dedup files in scripts/ on Mac (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`). Fuse mount blocks Cowork rm</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1599,17 +1573,17 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Delete three iCloud dedup files in scripts/ on Mac (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`). Fuse mount blocks Cowork rm</t>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr"/>
@@ -1647,7 +1621,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr"/>
@@ -1685,7 +1659,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr"/>
@@ -1723,7 +1697,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr"/>
@@ -1761,7 +1735,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr"/>
@@ -1794,12 +1768,12 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr"/>
@@ -1837,7 +1811,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr"/>
@@ -1860,7 +1834,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1870,12 +1844,12 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr"/>
@@ -1908,12 +1882,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr"/>
@@ -1946,12 +1920,12 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr"/>
@@ -1974,7 +1948,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1989,7 +1963,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr"/>
@@ -2002,7 +1976,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -2012,7 +1986,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -2022,15 +1996,19 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr"/>
+          <t>App icon set</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2060,19 +2038,15 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>App icon set</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive</t>
-        </is>
-      </c>
+          <t>Splash screens per density, status bar theming, safe-area insets</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2102,12 +2076,12 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Splash screens per density, status bar theming, safe-area insets</t>
+          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr"/>
@@ -2145,10 +2119,14 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr"/>
+          <t>Store listing copy drafted in FR + EN</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>description, keywords, support URL, privacy URL</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2183,14 +2161,10 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Store listing copy drafted in FR + EN</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>description, keywords, support URL, privacy URL</t>
-        </is>
-      </c>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2210,7 +2184,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2220,12 +2194,12 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr"/>
@@ -2258,15 +2232,19 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr"/>
+          <t>Decide Apple IAP stance</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>physical service argument documented</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -2276,7 +2254,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -2286,7 +2264,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2296,19 +2274,15 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>physical service argument documented</t>
-        </is>
-      </c>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -2338,15 +2312,19 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr"/>
+          <t>Magic-link auth working inside app</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>email link opens app, session persists</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -2371,24 +2349,20 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>email link opens app, session persists</t>
-        </is>
-      </c>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -2413,20 +2387,24 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr"/>
+          <t>T-103-core pipeline tests</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2456,19 +2434,15 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>T-103-core pipeline tests</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
-        </is>
-      </c>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -2503,7 +2477,7 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr"/>
@@ -2526,7 +2500,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2536,15 +2510,19 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr"/>
+          <t>Médiateur de la consommation signed</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>MEDICYS OR SMCE OR AME Conso</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -2574,19 +2552,15 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation signed</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>MEDICYS OR SMCE OR AME Conso</t>
-        </is>
-      </c>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -2621,7 +2595,7 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr"/>
@@ -2654,12 +2628,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr"/>
@@ -2692,15 +2666,19 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr"/>
+          <t>F&amp;F invite list</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>8 names, email, jurisdiction, case type</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -2730,19 +2708,15 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>8 names, email, jurisdiction, case type</t>
-        </is>
-      </c>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -2752,7 +2726,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2762,7 +2736,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -2772,15 +2746,19 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="inlineStr"/>
+          <t>Bug sweep on inspection UI</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>camera retries, upload resume, offline queue</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -2810,19 +2788,15 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Bug sweep on inspection UI</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>camera retries, upload resume, offline queue</t>
-        </is>
-      </c>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -2842,7 +2816,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -2852,12 +2826,12 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr"/>
@@ -2890,12 +2864,12 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr"/>
@@ -2908,7 +2882,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -2918,25 +2892,25 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr"/>
+          <t>Full T-103 suite</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -2967,12 +2941,12 @@
       <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Full T-103 suite</t>
+          <t>14-day outcome survey cron</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+          <t>Brevo trigger + Supabase write-back</t>
         </is>
       </c>
     </row>
@@ -3005,12 +2979,12 @@
       <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>14-day outcome survey cron</t>
+          <t>Additional UI locales</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Brevo trigger + Supabase write-back</t>
+          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
         </is>
       </c>
     </row>
@@ -3043,51 +3017,13 @@
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Additional UI locales</t>
-        </is>
-      </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>T-048</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr"/>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
           <t>App Store + Play production updates with post-launch fixes</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H49"/>
+  <autoFilter ref="A1:H48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3098,7 +3034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3559,17 +3495,17 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Capacitor 7 scaffold</t>
+          <t>Brevo transactional email leg</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
+          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3527,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -3601,22 +3537,64 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Capacitor 7 scaffold</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>T-012</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H12"/>
+  <autoFilter ref="A1:H13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1107,28 +1107,6 @@
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
@@ -1145,7 +1123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1844,12 +1822,12 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr"/>
@@ -1882,12 +1860,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr"/>
@@ -1910,7 +1888,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1925,7 +1903,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr"/>
@@ -1938,7 +1916,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1948,7 +1926,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1958,12 +1936,12 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr"/>
@@ -1986,7 +1964,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -1996,19 +1974,15 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>App icon set</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive</t>
-        </is>
-      </c>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2028,7 +2002,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2038,15 +2012,19 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Splash screens per density, status bar theming, safe-area insets</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr"/>
+          <t>Decide Apple IAP stance</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>physical service argument documented</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2056,7 +2034,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -2076,12 +2054,12 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr"/>
@@ -2094,7 +2072,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2114,17 +2092,17 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Store listing copy drafted in FR + EN</t>
+          <t>Magic-link auth working inside app</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>description, keywords, support URL, privacy URL</t>
+          <t>email link opens app, session persists</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2114,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -2151,17 +2129,17 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr"/>
@@ -2174,7 +2152,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -2184,7 +2162,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2194,15 +2172,19 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr"/>
+          <t>T-103-core pipeline tests</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2212,7 +2194,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -2222,7 +2204,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2232,19 +2214,15 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>physical service argument documented</t>
-        </is>
-      </c>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -2279,7 +2257,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr"/>
@@ -2302,7 +2280,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2317,12 +2295,12 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
+          <t>Médiateur de la consommation signed</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>email link opens app, session persists</t>
+          <t>MEDICYS OR SMCE OR AME Conso</t>
         </is>
       </c>
     </row>
@@ -2344,12 +2322,12 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2359,7 +2337,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr"/>
@@ -2382,7 +2360,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2392,19 +2370,15 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>T-103-core pipeline tests</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
-        </is>
-      </c>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2424,7 +2398,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2434,12 +2408,12 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr"/>
@@ -2462,7 +2436,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2472,15 +2446,19 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr"/>
+          <t>F&amp;F invite list</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>8 names, email, jurisdiction, case type</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -2510,19 +2488,15 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation signed</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>MEDICYS OR SMCE OR AME Conso</t>
-        </is>
-      </c>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -2532,7 +2506,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2542,7 +2516,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2552,15 +2526,19 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr"/>
+          <t>Bug sweep on inspection UI</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>camera retries, upload resume, offline queue</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -2570,7 +2548,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2580,7 +2558,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2590,12 +2568,12 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr"/>
@@ -2608,7 +2586,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -2628,12 +2606,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr"/>
@@ -2646,7 +2624,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -2666,19 +2644,15 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>8 names, email, jurisdiction, case type</t>
-        </is>
-      </c>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -2688,7 +2662,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -2698,25 +2672,25 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr"/>
+          <t>Full T-103 suite</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -2726,7 +2700,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2741,22 +2715,18 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr"/>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Bug sweep on inspection UI</t>
+          <t>14-day outcome survey cron</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>camera retries, upload resume, offline queue</t>
+          <t>Brevo trigger + Supabase write-back</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2738,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -2783,20 +2753,20 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr"/>
+          <t>Additional UI locales</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -2816,214 +2786,24 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr"/>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+          <t>App Store + Play production updates with post-launch fixes</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr"/>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>T-043</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
-        </is>
-      </c>
-      <c r="H44" s="6" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>T-044</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr"/>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>Full T-103 suite</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>T-045</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>14-day outcome survey cron</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>Brevo trigger + Supabase write-back</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>T-046</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>Additional UI locales</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>T-047</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr"/>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>App Store + Play production updates with post-launch fixes</t>
-        </is>
-      </c>
-      <c r="H48" s="6" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H48"/>
+  <autoFilter ref="A1:H43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3034,7 +2814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3569,7 +3349,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -3579,22 +3359,442 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>T-013</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>T-014</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>MB-01</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>T-015</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>MB-03</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>T-016</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>MB-05</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>T-017</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>MB-08</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>T-018</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>MB-09</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>T-019</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>App icon set</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>T-020</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Splash screens per density, status bar theming, safe-area insets</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>T-021</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>T-022</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Store listing copy drafted in FR + EN</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>description, keywords, support URL, privacy URL — done 2026-04-18 (ahead of schedule): MB-07 shipped docs/store-listings/{ios-fr,ios-en,play-fr,play-en}.md. Professional services register throughout (no buzzwords, no guaranteed-outcome claims), character counts validated inline, Stripe reader-app classification explicitly argued in reviewer notes, data safety section filled for Play form. Awaits MH (nights) review + edit before submission. Commit 50db60f.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:H23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Regenerated 2026-04-18 from TASKS.md. Master = TASKS.md. Do not edit xlsx directly.</t>
+          <t>Regenerated 2026-04-19 from TASKS.md. Master = TASKS.md. Do not edit xlsx directly.</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -851,7 +851,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+          <t>Install scheduled-push v2</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
         </is>
       </c>
     </row>
@@ -954,19 +954,19 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+          <t>PDF generation leg</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1107,6 +1107,28 @@
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
@@ -1123,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1201,20 +1223,24 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr"/>
+          <t>Install scheduled-push v2</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>copy scripts/scheduled-tasks/tenu-daily-push.md into ~/Documents/Claude/Scheduled/tenu-daily-push/SKILL.md and drop BREVO_API_KEY into .secrets/brevo.env</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1249,7 +1275,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
+          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr"/>
@@ -1282,12 +1308,12 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
+          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr"/>
@@ -1325,7 +1351,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
+          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr"/>
@@ -1363,7 +1389,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
+          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr"/>
@@ -1401,7 +1427,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
+          <t>Google Play Console developer account, USD 25 one-time</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr"/>
@@ -1414,17 +1440,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1434,19 +1460,15 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
-        </is>
-      </c>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1459,9 +1481,9 @@
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1481,12 +1503,12 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
+          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
         </is>
       </c>
     </row>
@@ -1508,25 +1530,29 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Delete three iCloud dedup files in scripts/ on Mac (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`). Fuse mount blocks Cowork rm</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr"/>
+          <t>PDF generation leg</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1551,17 +1577,17 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+          <t>Delete three iCloud dedup files in scripts/ on Mac (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`). Fuse mount blocks Cowork rm</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr"/>
@@ -1599,7 +1625,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr"/>
@@ -1637,7 +1663,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr"/>
@@ -1675,7 +1701,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr"/>
@@ -1713,7 +1739,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr"/>
@@ -1746,12 +1772,12 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr"/>
@@ -1789,7 +1815,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr"/>
@@ -1812,7 +1838,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1827,7 +1853,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr"/>
@@ -1860,12 +1886,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr"/>
@@ -1888,7 +1914,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1903,7 +1929,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr"/>
@@ -1916,7 +1942,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1926,7 +1952,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1936,12 +1962,12 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr"/>
@@ -1964,7 +1990,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -1974,12 +2000,12 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr"/>
@@ -2012,19 +2038,15 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>physical service argument documented</t>
-        </is>
-      </c>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2034,7 +2056,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -2044,7 +2066,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2054,15 +2076,19 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr"/>
+          <t>Decide Apple IAP stance</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>physical service argument documented</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2092,19 +2118,15 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>email link opens app, session persists</t>
-        </is>
-      </c>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2129,20 +2151,24 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr"/>
+          <t>Magic-link auth working inside app</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>email link opens app, session persists</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2167,24 +2193,20 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>T-103-core pipeline tests</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
-        </is>
-      </c>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2214,15 +2236,19 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr"/>
+          <t>T-103-core pipeline tests</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -2257,7 +2283,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr"/>
@@ -2280,7 +2306,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2290,19 +2316,15 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation signed</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>MEDICYS OR SMCE OR AME Conso</t>
-        </is>
-      </c>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -2332,15 +2354,19 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr"/>
+          <t>Médiateur de la consommation signed</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>MEDICYS OR SMCE OR AME Conso</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -2375,7 +2401,7 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr"/>
@@ -2408,12 +2434,12 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr"/>
@@ -2446,19 +2472,15 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>8 names, email, jurisdiction, case type</t>
-        </is>
-      </c>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -2488,15 +2510,19 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr"/>
+          <t>F&amp;F invite list</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>8 names, email, jurisdiction, case type</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -2506,7 +2532,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2516,7 +2542,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2526,19 +2552,15 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Bug sweep on inspection UI</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>camera retries, upload resume, offline queue</t>
-        </is>
-      </c>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -2568,15 +2590,19 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
-        </is>
-      </c>
-      <c r="H37" s="6" t="inlineStr"/>
+          <t>Bug sweep on inspection UI</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>camera retries, upload resume, offline queue</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -2596,7 +2622,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2606,12 +2632,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr"/>
@@ -2644,12 +2670,12 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr"/>
@@ -2662,7 +2688,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>POST-LAUNCH (12-31 May)</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -2672,25 +2698,25 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr"/>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Full T-103 suite</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
-        </is>
-      </c>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -2721,12 +2747,12 @@
       <c r="F41" s="5" t="inlineStr"/>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>14-day outcome survey cron</t>
+          <t>Full T-103 suite</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Brevo trigger + Supabase write-back</t>
+          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
         </is>
       </c>
     </row>
@@ -2759,12 +2785,12 @@
       <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Additional UI locales</t>
+          <t>14-day outcome survey cron</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
+          <t>Brevo trigger + Supabase write-back</t>
         </is>
       </c>
     </row>
@@ -2797,13 +2823,51 @@
       <c r="F43" s="5" t="inlineStr"/>
       <c r="G43" s="6" t="inlineStr">
         <is>
+          <t>Additional UI locales</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>T-043</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
           <t>App Store + Play production updates with post-launch fixes</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H43"/>
+  <autoFilter ref="A1:H44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2814,7 +2878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2892,22 +2956,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Fix footer legal routes redirecting to /auth/login</t>
+          <t>Scheduled push v2</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>expose /legal, /auth/accept-terms, /api/consents as public paths in middleware — done 2026-04-18: middleware allow-list extended, verified on tenu.world production in incognito, all six legal pages render without auth. Commit via PR fix/public-legal-routes merged to main. Pre-contractual disclosure (art. L221-5 Code de la conso) now reachable as required for Stripe/App Store review.</t>
+          <t>replace Gmail create_draft with Brevo direct send — done 2026-04-19: new SKILL.md at scripts/scheduled-tasks/tenu-daily-push.md, brevo.env.example alongside. Telegram path unchanged. MH installs + adds BREVO_API_KEY — see MH line below.</t>
         </is>
       </c>
     </row>
@@ -2944,12 +3008,12 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Fix /stories/* and /features/* redirecting to /auth/login</t>
+          <t>Fix footer legal routes redirecting to /auth/login</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-18: added "/stories" and "/features" to publicPaths in src/middleware.ts. Same isPublicPath startsWith match pattern as the /legal fix; single entry per parent covers all nested routes. Stories and features now reachable without auth as marketing/content surface.</t>
+          <t>expose /legal, /auth/accept-terms, /api/consents as public paths in middleware — done 2026-04-18: middleware allow-list extended, verified on tenu.world production in incognito, all six legal pages render without auth. Commit via PR fix/public-legal-routes merged to main. Pre-contractual disclosure (art. L221-5 Code de la conso) now reachable as required for Stripe/App Store review.</t>
         </is>
       </c>
     </row>
@@ -2976,7 +3040,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -2986,12 +3050,12 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Use-case content system</t>
+          <t>Fix /stories/* and /features/* redirecting to /auth/login</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>manifest + /stories index + cross-link strip + homepage dual-card — done 2026-04-18: src/lib/stories.ts (single source of truth, Story type, 4 helpers), src/components/stories/OtherCases.tsx (bilingual cross-link strip), src/app/stories/page.tsx (index with cautionary populated, success placeholder awaiting 11 May cohort), homepage example section refactored from single Suzi hook to manifest-driven dual-card grid with "See all cases →" link, Suzi + Samir pages thread OtherCases before footer, example block in en/fr/zh/ar/ur dictionaries refactored to label/heading/intro/seeAll/disclaimer. Adding a new case is now one append to stories.ts + one new /stories/&lt;slug&gt;/page.tsx.</t>
+          <t>done 2026-04-18: added "/stories" and "/features" to publicPaths in src/middleware.ts. Same isPublicPath startsWith match pattern as the /legal fix; single entry per parent covers all nested routes. Stories and features now reachable without auth as marketing/content surface.</t>
         </is>
       </c>
     </row>
@@ -3013,27 +3077,27 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Telegram one-time setup</t>
+          <t>Use-case content system</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>create bot via @BotFather, send token + chat_id — done 2026-04-18: bot created, token + chat_id set in .env.local and Vercel env (per Dr Mubashir)</t>
+          <t>manifest + /stories index + cross-link strip + homepage dual-card — done 2026-04-18: src/lib/stories.ts (single source of truth, Story type, 4 helpers), src/components/stories/OtherCases.tsx (bilingual cross-link strip), src/app/stories/page.tsx (index with cautionary populated, success placeholder awaiting 11 May cohort), homepage example section refactored from single Suzi hook to manifest-driven dual-card grid with "See all cases →" link, Suzi + Samir pages thread OtherCases before footer, example block in en/fr/zh/ar/ur dictionaries refactored to label/heading/intro/seeAll/disclaimer. Adding a new case is now one append to stories.ts + one new /stories/&lt;slug&gt;/page.tsx.</t>
         </is>
       </c>
     </row>
@@ -3070,12 +3134,12 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Paste ANTHROPIC_API_KEY into .env.local + Vercel project env</t>
+          <t>Telegram one-time setup</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
+          <t>create bot via @BotFather, send token + chat_id — done 2026-04-18: bot created, token + chat_id set in .env.local and Vercel env (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3176,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Paste BREVO_API_KEY into .env.local + Vercel project env</t>
+          <t>Paste ANTHROPIC_API_KEY into .env.local + Vercel project env</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -3129,7 +3193,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -3139,7 +3203,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -3149,17 +3213,17 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
+          <t>Paste BREVO_API_KEY into .env.local + Vercel project env</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
+          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -3191,17 +3255,17 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
+          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
+          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3302,12 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
+          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
+          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
         </is>
       </c>
     </row>
@@ -3275,17 +3339,17 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Brevo transactional email leg</t>
+          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
+          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
         </is>
       </c>
     </row>
@@ -3317,17 +3381,17 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Capacitor 7 scaffold</t>
+          <t>Brevo transactional email leg</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
+          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3428,12 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+          <t>Capacitor 7 scaffold</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
+          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3455,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -3401,17 +3465,17 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
+          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3497,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -3443,17 +3507,17 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>MB-01</t>
+          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
+          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -3490,12 +3554,12 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>MB-03</t>
+          <t>MB-01</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
+          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
         </is>
       </c>
     </row>
@@ -3532,12 +3596,12 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>MB-05</t>
+          <t>MB-03</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
+          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3638,12 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>MB-08</t>
+          <t>MB-05</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
+          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
         </is>
       </c>
     </row>
@@ -3616,12 +3680,12 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>MB-09</t>
+          <t>MB-08</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
+          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3697,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -3653,17 +3717,17 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>App icon set</t>
+          <t>MB-09</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
+          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3759,17 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Splash screens per density, status bar theming, safe-area insets</t>
+          <t>App icon set</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
+          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
         </is>
       </c>
     </row>
@@ -3737,17 +3801,17 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+          <t>Splash screens per density, status bar theming, safe-area insets</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
         </is>
       </c>
     </row>
@@ -3784,17 +3848,59 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
+          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>T-023</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
           <t>Store listing copy drafted in FR + EN</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>description, keywords, support URL, privacy URL — done 2026-04-18 (ahead of schedule): MB-07 shipped docs/store-listings/{ios-fr,ios-en,play-fr,play-en}.md. Professional services register throughout (no buzzwords, no guaranteed-outcome claims), character counts validated inline, Stripe reader-app classification explicitly argued in reviewer notes, data safety section filled for Play form. Awaits MH (nights) review + edit before submission. Commit 50db60f.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H23"/>
+  <autoFilter ref="A1:H24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -751,19 +751,19 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Delete three iCloud dedup files in scripts/ on Mac (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`). Fuse mount blocks Cowork rm</t>
+          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -773,12 +773,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
+          <t>Delete iCloud dedup files on Mac</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
+          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
+          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
+          <t>Google Play Console developer account, USD 25 one-time</t>
         </is>
       </c>
     </row>
@@ -861,19 +861,19 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Install scheduled-push v2</t>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -883,34 +883,34 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+          <t>Install scheduled-push v2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
         </is>
       </c>
     </row>
@@ -976,19 +976,19 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -998,19 +998,19 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1020,14 +1020,14 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
         </is>
       </c>
     </row>
@@ -1086,19 +1086,19 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>PDF generation leg</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1108,27 +1108,93 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
@@ -1145,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1478,17 +1544,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1498,17 +1564,17 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
+          <t>`client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json`, the same with " (1)" suffix, and `stripe_backup_code.txt`. All three are sitting in plaintext in a Documents folder (iCloud-syncable, Time-Machine-backupable). Move to `~/.secrets/` or 1Password, then `rm` from disk. **Do NOT git commit them anywhere.**</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1586,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1535,22 +1601,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
+          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
+          <t>`01-Legal-Checklist.md` (review + dedupe against SOT 05-Legal-Compliance content first), `etat-des-lieux.pdf`, `etat-des-lieux-meuble.pdf`, `modele-etat-des-lieux T2-T3.pdf` into SOT `docs/reference/etat-des-lieux/` (or wherever Dr Mubashir prefers). Delete from stale clone after move</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1628,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1582,15 +1648,19 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Delete three iCloud dedup files in scripts/ on Mac (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`). Fuse mount blocks Cowork rm</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr"/>
+          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>archive to `~/Archive/` or `rm -rf`. Sandbox cannot delete the parent folder.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1603,14 +1673,14 @@
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1620,15 +1690,19 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr"/>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1648,7 +1722,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1658,15 +1732,19 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr"/>
+          <t>PDF generation leg</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1691,20 +1769,24 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr"/>
+          <t>Delete iCloud dedup files on Mac</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1739,7 +1821,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr"/>
@@ -1777,7 +1859,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr"/>
@@ -1810,12 +1892,12 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr"/>
@@ -1848,12 +1930,12 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr"/>
@@ -1876,7 +1958,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1886,12 +1968,12 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr"/>
@@ -1914,7 +1996,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1924,12 +2006,12 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr"/>
@@ -1962,12 +2044,12 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr"/>
@@ -1980,7 +2062,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1995,20 +2077,20 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr"/>
+          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2018,7 +2100,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -2028,7 +2110,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2038,12 +2120,12 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr"/>
@@ -2056,7 +2138,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -2066,7 +2148,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2076,19 +2158,15 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>physical service argument documented</t>
-        </is>
-      </c>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2098,7 +2176,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2108,7 +2186,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2118,12 +2196,12 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr"/>
@@ -2136,7 +2214,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -2156,19 +2234,15 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>email link opens app, session persists</t>
-        </is>
-      </c>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2178,7 +2252,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -2188,22 +2262,22 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr"/>
@@ -2216,7 +2290,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -2226,7 +2300,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2236,17 +2310,17 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>T-103-core pipeline tests</t>
+          <t>Decide Apple IAP stance</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
+          <t>physical service argument documented</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2357,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr"/>
@@ -2316,15 +2390,19 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr"/>
+          <t>Magic-link auth working inside app</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>email link opens app, session persists</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -2344,29 +2422,25 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation signed</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>MEDICYS OR SMCE OR AME Conso</t>
-        </is>
-      </c>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -2386,7 +2460,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2396,15 +2470,19 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr"/>
+          <t>T-103-core pipeline tests</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2424,7 +2502,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2434,12 +2512,12 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr"/>
@@ -2462,7 +2540,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2472,12 +2550,12 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr"/>
@@ -2510,17 +2588,17 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
+          <t>Médiateur de la consommation signed</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>8 names, email, jurisdiction, case type</t>
+          <t>MEDICYS OR SMCE OR AME Conso</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2630,12 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr"/>
@@ -2570,7 +2648,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2580,7 +2658,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2590,19 +2668,15 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Bug sweep on inspection UI</t>
-        </is>
-      </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>camera retries, upload resume, offline queue</t>
-        </is>
-      </c>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -2612,7 +2686,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -2622,7 +2696,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2632,12 +2706,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr"/>
@@ -2650,7 +2724,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -2670,15 +2744,19 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr"/>
+          <t>F&amp;F invite list</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>8 names, email, jurisdiction, case type</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -2688,7 +2766,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -2708,12 +2786,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr"/>
@@ -2726,7 +2804,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>POST-LAUNCH (12-31 May)</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2741,18 +2819,22 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr"/>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Full T-103 suite</t>
+          <t>Bug sweep on inspection UI</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+          <t>camera retries, upload resume, offline queue</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2846,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>POST-LAUNCH (12-31 May)</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -2779,20 +2861,20 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr"/>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>14-day outcome survey cron</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>Brevo trigger + Supabase write-back</t>
-        </is>
-      </c>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -2802,7 +2884,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>POST-LAUNCH (12-31 May)</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -2812,25 +2894,25 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr"/>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Additional UI locales</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
-        </is>
-      </c>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -2840,34 +2922,186 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
+          <t>LAUNCH WEEK (8-11 May)</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>T-044</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
           <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>P2 Post-launch</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr"/>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Full T-103 suite</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>T-045</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>14-day outcome survey cron</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Brevo trigger + Supabase write-back</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>T-046</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Additional UI locales</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>T-047</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="6" t="inlineStr">
         <is>
           <t>App Store + Play production updates with post-launch fixes</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H44"/>
+  <autoFilter ref="A1:H48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2878,7 +3112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3235,7 +3469,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3255,17 +3489,17 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
+          <t>SOT consolidation</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
+          <t>fix CLAUDE.md project path, refresh CLAUDE-CONTEXT.md to current React/in-code stack, replace stale-clone CLAUDE.md + CLAUDE-CONTEXT.md with redirect stubs — done 2026-04-19: SOT CLAUDE.md now declares `/Users/mmh/Documents/Claude/Projects/Tenu.World/` as canonical at the top, project structure block rewritten to match real layout (no nested `app/` wrapper, lists ios/, android/, mobile/, resources/, supabase/, scripts/). SOT CLAUDE-CONTEXT.md fully refreshed: dropped Webflow/Make.com/Tally/Airtable/Asana/Placid references, added pricing matrix, in-code pipeline, build timeline through 11 May, brand SOT pointers. Stale clone at `/Users/mmh/Documents/Global Apex/Tenu/` now has redirect-only CLAUDE.md + CLAUDE-CONTEXT.md so any agent invoked from that path bounces immediately.</t>
         </is>
       </c>
     </row>
@@ -3297,17 +3531,17 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
+          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
+          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3578,12 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
+          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
+          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
         </is>
       </c>
     </row>
@@ -3381,17 +3615,17 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Brevo transactional email leg</t>
+          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
+          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
         </is>
       </c>
     </row>
@@ -3423,17 +3657,17 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Capacitor 7 scaffold</t>
+          <t>Brevo transactional email leg</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
+          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3704,12 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+          <t>Capacitor 7 scaffold</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
+          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3731,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -3507,17 +3741,17 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
+          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3773,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -3549,17 +3783,17 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>MB-01</t>
+          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
+          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -3596,12 +3830,12 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>MB-03</t>
+          <t>MB-01</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
+          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
         </is>
       </c>
     </row>
@@ -3638,12 +3872,12 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>MB-05</t>
+          <t>MB-03</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
+          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3914,12 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>MB-08</t>
+          <t>MB-05</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
+          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
         </is>
       </c>
     </row>
@@ -3722,12 +3956,12 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>MB-09</t>
+          <t>MB-08</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
+          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3973,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -3759,17 +3993,17 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>App icon set</t>
+          <t>MB-09</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
+          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
         </is>
       </c>
     </row>
@@ -3801,17 +4035,17 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Splash screens per density, status bar theming, safe-area insets</t>
+          <t>App icon set</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
+          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
         </is>
       </c>
     </row>
@@ -3843,17 +4077,17 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+          <t>Splash screens per density, status bar theming, safe-area insets</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
         </is>
       </c>
     </row>
@@ -3890,17 +4124,59 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
+          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>T-024</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
           <t>Store listing copy drafted in FR + EN</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>description, keywords, support URL, privacy URL — done 2026-04-18 (ahead of schedule): MB-07 shipped docs/store-listings/{ios-fr,ios-en,play-fr,play-en}.md. Professional services register throughout (no buzzwords, no guaranteed-outcome claims), character counts validated inline, Stripe reader-app classification explicitly argued in reviewer notes, data safety section filled for Play form. Awaits MH (nights) review + edit before submission. Commit 50db60f.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H24"/>
+  <autoFilter ref="A1:H25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1211,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3089,19 +3089,57 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="6" t="inlineStr">
         <is>
+          <t>i18n audit phase 2</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>T-048</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
           <t>App Store + Play production updates with post-launch fixes</t>
         </is>
       </c>
-      <c r="H48" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H48"/>
+  <autoFilter ref="A1:H49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Regenerated 2026-04-19 from TASKS.md. Master = TASKS.md. Do not edit xlsx directly.</t>
+          <t>Regenerated 2026-04-21 from TASKS.md. Master = TASKS.md. Do not edit xlsx directly.</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -883,41 +883,41 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Install scheduled-push v2</t>
+          <t>Google Workspace subscription on `tenu.world`</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -932,14 +932,14 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -954,14 +954,14 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -976,14 +976,14 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -998,14 +998,14 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -1020,14 +1020,14 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -1037,46 +1037,46 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>Install scheduled-push v2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -1086,14 +1086,14 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -1108,14 +1108,14 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+          <t>Rotate R2_ACCESS_KEY_ID + R2_SECRET_ACCESS_KEY</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -1130,19 +1130,19 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+          <t>Rotate STRIPE_WEBHOOK_SECRET</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -1152,19 +1152,19 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>Rotate SUPABASE_SERVICE_ROLE_KEY AND NEXT_PUBLIC_SUPABASE_ANON_KEY together</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -1174,29 +1174,403 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>Audit hidden env vars</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Post-rotation smoke test verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>PDF generation leg</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Decide Apple IAP stance</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1670,17 +2044,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1690,17 +2064,17 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>Google Workspace subscription on `tenu.world`</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
+          <t>create `ops@tenu.world` (owner) + `support@tenu.world` + `dpo@tenu.world` (aliases acceptable)</t>
         </is>
       </c>
     </row>
@@ -1712,7 +2086,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1722,7 +2096,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1732,19 +2106,15 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
-        </is>
-      </c>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1754,7 +2124,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1769,24 +2139,20 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Delete iCloud dedup files on Mac</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run.</t>
-        </is>
-      </c>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1796,7 +2162,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1816,12 +2182,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr"/>
@@ -1834,7 +2200,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1854,12 +2220,12 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr"/>
@@ -1872,7 +2238,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1892,12 +2258,12 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr"/>
@@ -1910,7 +2276,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1930,15 +2296,19 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr"/>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>expect no 403 org_internal, consent screen shows "Tenu" with `support@tenu.world`</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1948,7 +2318,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1968,15 +2338,19 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr"/>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>do not archive, the secret is burned</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1986,7 +2360,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2006,15 +2380,19 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr"/>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>revokes the leaked secret at source even if a copy is still cached somewhere</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2024,7 +2402,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -2044,15 +2422,19 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr"/>
+          <t>Before 11 May</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>publish OAuth consent screen Testing → Production (requires domain verified + privacy URL + terms URL live at tenu.world/legal/privacy + /legal/terms)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2062,7 +2444,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -2072,23 +2454,27 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr"/>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
+          <t>Rotate R2_ACCESS_KEY_ID + R2_SECRET_ACCESS_KEY</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
+          <t>Cloudflare → R2 → Manage API tokens → new token scoped to tenu-evidence bucket (Object Read/Write only). Paste both into Vercel env, tick Sensitive, redeploy. Smoke: hit /api/mobile/upload-intent and upload a test photo. Then revoke old token in Cloudflare. Existing presigned URLs signed with old key keep working until expiry</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2486,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -2110,7 +2496,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2120,15 +2506,19 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr"/>
+          <t>Rotate STRIPE_WEBHOOK_SECRET</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Stripe → Developers → Webhooks → endpoint → Roll secret with 24h grace. Paste new into Vercel STRIPE_WEBHOOK_SECRET, tick Sensitive, redeploy. Smoke: `stripe trigger checkout.session.completed` and confirm /api/webhooks/stripe returns 200 in Vercel function logs. Old secret expires automatically at end of grace</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2138,7 +2528,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -2148,7 +2538,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2158,15 +2548,19 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr"/>
+          <t>Rotate SUPABASE_SERVICE_ROLE_KEY AND NEXT_PUBLIC_SUPABASE_ANON_KEY together</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Supabase → Project Settings → API → JWT Keys → Generate new JWT secret (regenerates both keys, both are JWTs signed by the same secret). Update both values in Vercel in the same save, tick Sensitive on service_role (anon stays public but encrypt-at-rest regardless), redeploy. All pre-rotation sessions invalidated (pre-launch, so non-event). Smoke: incognito magic-link signup → /app-home load → photo upload row insert</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2176,7 +2570,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2196,15 +2590,19 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr"/>
+          <t>Audit hidden env vars</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>scroll full Vercel env var list below the fold, confirm ANTHROPIC_API_KEY + BREVO_API_KEY + TELEGRAM_BOT_TOKEN + any other secret either shows Need To Rotate (rotate it) or was created Sensitive from day one (leave alone). If any non-public secret is unflagged and NOT marked Sensitive, treat as exposed and rotate</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2214,7 +2612,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -2224,7 +2622,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -2234,15 +2632,19 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr"/>
+          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Google Cloud Console → APIs &amp; Services → Credentials → restrict to HTTP referrers `*.tenu.world` + `localhost:*` + enable only Maps JavaScript + Places API. Public by design, not flagged by Vercel, but unrestricted = scraping risk against Global Apex billing</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2252,7 +2654,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -2272,15 +2674,19 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr"/>
+          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>hardening pass, single biggest structural lesson from this incident. Anything that isn't a NEXT_PUBLIC_* or a non-secret identifier (R2_ACCOUNT_ID, R2_BUCKET_NAME) should be Sensitive</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2290,7 +2696,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -2300,7 +2706,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2310,17 +2716,17 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
+          <t>Post-rotation smoke test verification</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>physical service argument documented</t>
+          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green</t>
         </is>
       </c>
     </row>
@@ -2332,12 +2738,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2352,15 +2758,19 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr"/>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -2370,7 +2780,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -2390,17 +2800,17 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
+          <t>PDF generation leg</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>email link opens app, session persists</t>
+          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2822,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -2422,7 +2832,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2432,15 +2842,19 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr"/>
+          <t>Delete iCloud dedup files on Mac</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -2450,7 +2864,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -2460,7 +2874,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2470,19 +2884,15 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>T-103-core pipeline tests</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
-        </is>
-      </c>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2492,7 +2902,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -2502,7 +2912,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2512,12 +2922,12 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr"/>
@@ -2530,7 +2940,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -2540,7 +2950,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2550,12 +2960,12 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr"/>
@@ -2568,7 +2978,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -2588,19 +2998,15 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation signed</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>MEDICYS OR SMCE OR AME Conso</t>
-        </is>
-      </c>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -2610,7 +3016,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2630,12 +3036,12 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr"/>
@@ -2648,7 +3054,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2668,12 +3074,12 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr"/>
@@ -2686,7 +3092,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -2706,12 +3112,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr"/>
@@ -2724,7 +3130,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -2734,27 +3140,23 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr"/>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
+          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>8 names, email, jurisdiction, case type</t>
+          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
         </is>
       </c>
     </row>
@@ -2766,7 +3168,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -2776,7 +3178,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -2786,12 +3188,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr"/>
@@ -2804,7 +3206,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2824,19 +3226,15 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Bug sweep on inspection UI</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>camera retries, upload resume, offline queue</t>
-        </is>
-      </c>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -2846,7 +3244,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -2856,7 +3254,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -2866,12 +3264,12 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr"/>
@@ -2884,7 +3282,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -2894,7 +3292,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -2904,12 +3302,12 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr"/>
@@ -2922,7 +3320,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -2942,12 +3340,12 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr"/>
@@ -2960,7 +3358,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>POST-LAUNCH (12-31 May)</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -2970,23 +3368,27 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr"/>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Full T-103 suite</t>
+          <t>Decide Apple IAP stance</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+          <t>physical service argument documented</t>
         </is>
       </c>
     </row>
@@ -2998,7 +3400,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>POST-LAUNCH (12-31 May)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -3013,20 +3415,20 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr"/>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>14-day outcome survey cron</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>Brevo trigger + Supabase write-back</t>
-        </is>
-      </c>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -3036,7 +3438,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>POST-LAUNCH (12-31 May)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -3051,18 +3453,22 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr"/>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Additional UI locales</t>
+          <t>Magic-link auth working inside app</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
+          <t>email link opens app, session persists</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3480,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>POST-LAUNCH (12-31 May)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -3092,17 +3498,17 @@
           <t>P1 Important</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>i18n audit phase 2</t>
-        </is>
-      </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
-        </is>
-      </c>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -3112,34 +3518,696 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>T-103-core pipeline tests</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>T-049</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>T-050</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>T-051</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>Médiateur de la consommation signed</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>MEDICYS OR SMCE OR AME Conso</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>T-052</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>T-053</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>T-054</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>T-055</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>F&amp;F invite list</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>8 names, email, jurisdiction, case type</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>T-056</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>T-057</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>LAUNCH WEEK (8-11 May)</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>Bug sweep on inspection UI</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>camera retries, upload resume, offline queue</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>T-058</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>LAUNCH WEEK (8-11 May)</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>T-059</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>LAUNCH WEEK (8-11 May)</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>T-060</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>LAUNCH WEEK (8-11 May)</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>T-061</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
           <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>P2 Post-launch</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr"/>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Full T-103 suite</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>T-062</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr"/>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>14-day outcome survey cron</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Brevo trigger + Supabase write-back</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>T-063</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>Additional UI locales</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>T-064</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr"/>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>i18n audit phase 2</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>T-065</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="6" t="inlineStr">
         <is>
           <t>App Store + Play production updates with post-launch fixes</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr"/>
+      <c r="H66" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H49"/>
+  <autoFilter ref="A1:H66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -105,10 +105,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Regenerated 2026-04-21 from TASKS.md. Master = TASKS.md. Do not edit xlsx directly.</t>
+          <t>Regenerated 2026-05-03 from TASKS.md. Master = TASKS.md. Do not edit xlsx directly.</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
@@ -697,7 +697,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -712,14 +712,14 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
+          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -729,41 +729,41 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
+          <t>Install scheduled-push v2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
+          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -778,19 +778,19 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Delete iCloud dedup files on Mac</t>
+          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -800,19 +800,19 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -822,14 +822,14 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
+          <t>Update store-listing copy + welcome email + landing page to reflect web-first launch + native binaries follow</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -844,14 +844,14 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
+          <t>Personalise + send the FR avocat brief (review draft, fill recipient name + cabinet, send by email)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -866,14 +866,14 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
+          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -888,14 +888,14 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Google Workspace subscription on `tenu.world`</t>
+          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -910,14 +910,14 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -932,14 +932,14 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -954,14 +954,14 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
+          <t>Google Play Console developer account, USD 25 one-time</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -976,14 +976,14 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -998,14 +998,14 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
+          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -1020,14 +1020,14 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+          <t>Audit hidden env vars</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -1042,14 +1042,14 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -1059,24 +1059,24 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Install scheduled-push v2</t>
+          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -1086,19 +1086,19 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+          <t>Post-rotation smoke test verification</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Rotate R2_ACCESS_KEY_ID + R2_SECRET_ACCESS_KEY</t>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -1130,19 +1130,19 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Rotate STRIPE_WEBHOOK_SECRET</t>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -1152,41 +1152,41 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Rotate SUPABASE_SERVICE_ROLE_KEY AND NEXT_PUBLIC_SUPABASE_ANON_KEY together</t>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Audit hidden env vars</t>
+          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
+          <t>Native Build Bridge plan</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -1218,19 +1218,19 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
+          <t>Google Workspace subscription on `tenu.world`</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -1240,36 +1240,36 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Post-rotation smoke test verification</t>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -1284,14 +1284,14 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -1306,14 +1306,14 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -1350,19 +1350,19 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+          <t>Before 11 May</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -1372,14 +1372,14 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
+          <t>Decide Apple IAP stance</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -1416,19 +1416,19 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>Magic-link auth working inside app</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -1438,14 +1438,14 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
+          <t>Médiateur de la consommation signed</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -1460,14 +1460,14 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -1482,19 +1482,19 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -1504,19 +1504,19 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -1526,14 +1526,14 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -1548,19 +1548,19 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -1570,7 +1570,249 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
+          <t>PDF generation leg</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>T-103-core pipeline tests</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>F&amp;F invite list</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Bug sweep on inspection UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1648,37 +1890,37 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>DECISION 2026-05-03 — Launch path: Option B (web-only on 11 May)</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>Install scheduled-push v2</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>copy scripts/scheduled-tasks/tenu-daily-push.md into ~/Documents/Claude/Scheduled/tenu-daily-push/SKILL.md and drop BREVO_API_KEY into .secrets/brevo.env</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Update store-listing copy + welcome email + landing page to reflect web-first launch + native binaries follow</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>opened 2026-05-03.</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1932,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
+          <t>DECISION 2026-05-03 — Launch path: Option B (web-only on 11 May)</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -1700,7 +1942,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -1710,15 +1952,19 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr"/>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Native Build Bridge plan</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>write docs/12-Native-Build-Bridge-2026-05-12.md mapping the 11-25 May path: cap add ios + cap add android dependencies, Xcode + Android Studio prerequisites, TestFlight + Play internal track submission, screenshots backlog, App Store reviewer notes refresh — opened 2026-05-03.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1728,7 +1974,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
+          <t>DECISION 2026-05-03 — Launch path: Option B (web-only on 11 May)</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -1738,25 +1984,29 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr"/>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>keep their content verbatim, only re-section + re-date so the launch checklist stops bleeding red on items that were never blocking 11 May web-only — opened 2026-05-03.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -1766,7 +2016,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
+          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1786,15 +2036,19 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr"/>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Personalise + send the FR avocat brief (review draft, fill recipient name + cabinet, send by email)</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>depends on CC line above.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1804,7 +2058,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
+          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1824,15 +2078,19 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr"/>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>depends on CC line above.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1857,7 +2115,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -1865,12 +2123,16 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Install scheduled-push v2</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>copy scripts/scheduled-tasks/tenu-daily-push.md into ~/Documents/Claude/Scheduled/tenu-daily-push/SKILL.md and drop BREVO_API_KEY into .secrets/brevo.env</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1900,15 +2162,15 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr"/>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1938,19 +2200,15 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>`client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json`, the same with " (1)" suffix, and `stripe_backup_code.txt`. All three are sitting in plaintext in a Documents folder (iCloud-syncable, Time-Machine-backupable). Move to `~/.secrets/` or 1Password, then `rm` from disk. **Do NOT git commit them anywhere.**</t>
-        </is>
-      </c>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1970,29 +2228,25 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>`01-Legal-Checklist.md` (review + dedupe against SOT 05-Legal-Compliance content first), `etat-des-lieux.pdf`, `etat-des-lieux-meuble.pdf`, `modele-etat-des-lieux T2-T3.pdf` into SOT `docs/reference/etat-des-lieux/` (or wherever Dr Mubashir prefers). Delete from stale clone after move</t>
-        </is>
-      </c>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2005,9 +2259,9 @@
           <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -2017,22 +2271,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>archive to `~/Archive/` or `rm -rf`. Sandbox cannot delete the parent folder.</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>submitted 2026-05-03, documents sent to Apple, awaiting verification (per Dr Mubashir). Apple identity check typically 2-5 business days; D-U-N-S verification gates the review. Track unblocking of Xcode signing / TestFlight upload off this line.</t>
         </is>
       </c>
     </row>
@@ -2064,19 +2318,15 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Google Workspace subscription on `tenu.world`</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>create `ops@tenu.world` (owner) + `support@tenu.world` + `dpo@tenu.world` (aliases acceptable)</t>
-        </is>
-      </c>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Google Play Console developer account, USD 25 one-time</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -2106,15 +2356,15 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr"/>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -2144,15 +2394,19 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr"/>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>`client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json`, the same with " (1)" suffix, and `stripe_backup_code.txt`. All three are sitting in plaintext in a Documents folder (iCloud-syncable, Time-Machine-backupable). Move to `~/.secrets/` or 1Password, then `rm` from disk. **Do NOT git commit them anywhere.**</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2172,25 +2426,29 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr"/>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>`01-Legal-Checklist.md` (review + dedupe against SOT 05-Legal-Compliance content first), `etat-des-lieux.pdf`, `etat-des-lieux-meuble.pdf`, `modele-etat-des-lieux T2-T3.pdf` into SOT `docs/reference/etat-des-lieux/` (or wherever Dr Mubashir prefers). Delete from stale clone after move</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2215,20 +2473,24 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr"/>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>archive to `~/Archive/` or `rm -rf`. Sandbox cannot delete the parent folder.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -2258,15 +2520,19 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr"/>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Google Workspace subscription on `tenu.world`</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>create `ops@tenu.world` (owner) + `support@tenu.world` + `dpo@tenu.world` (aliases acceptable)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2296,19 +2562,15 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>expect no 403 org_internal, consent screen shows "Tenu" with `support@tenu.world`</t>
-        </is>
-      </c>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2338,19 +2600,15 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>do not archive, the secret is burned</t>
-        </is>
-      </c>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2380,19 +2638,15 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>revokes the leaked secret at source even if a copy is still cached somewhere</t>
-        </is>
-      </c>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2425,16 +2679,12 @@
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Before 11 May</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>publish OAuth consent screen Testing → Production (requires domain verified + privacy URL + terms URL live at tenu.world/legal/privacy + /legal/terms)</t>
-        </is>
-      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2464,19 +2714,15 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>Rotate R2_ACCESS_KEY_ID + R2_SECRET_ACCESS_KEY</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Cloudflare → R2 → Manage API tokens → new token scoped to tenu-evidence bucket (Object Read/Write only). Paste both into Vercel env, tick Sensitive, redeploy. Smoke: hit /api/mobile/upload-intent and upload a test photo. Then revoke old token in Cloudflare. Existing presigned URLs signed with old key keep working until expiry</t>
-        </is>
-      </c>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2506,17 +2752,17 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>Rotate STRIPE_WEBHOOK_SECRET</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>Stripe → Developers → Webhooks → endpoint → Roll secret with 24h grace. Paste new into Vercel STRIPE_WEBHOOK_SECRET, tick Sensitive, redeploy. Smoke: `stripe trigger checkout.session.completed` and confirm /api/webhooks/stripe returns 200 in Vercel function logs. Old secret expires automatically at end of grace</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>expect no 403 org_internal, consent screen shows "Tenu" with `support@tenu.world`</t>
         </is>
       </c>
     </row>
@@ -2548,17 +2794,17 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Rotate SUPABASE_SERVICE_ROLE_KEY AND NEXT_PUBLIC_SUPABASE_ANON_KEY together</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Supabase → Project Settings → API → JWT Keys → Generate new JWT secret (regenerates both keys, both are JWTs signed by the same secret). Update both values in Vercel in the same save, tick Sensitive on service_role (anon stays public but encrypt-at-rest regardless), redeploy. All pre-rotation sessions invalidated (pre-launch, so non-event). Smoke: incognito magic-link signup → /app-home load → photo upload row insert</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>do not archive, the secret is burned</t>
         </is>
       </c>
     </row>
@@ -2590,17 +2836,17 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>Audit hidden env vars</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>scroll full Vercel env var list below the fold, confirm ANTHROPIC_API_KEY + BREVO_API_KEY + TELEGRAM_BOT_TOKEN + any other secret either shows Need To Rotate (rotate it) or was created Sensitive from day one (leave alone). If any non-public secret is unflagged and NOT marked Sensitive, treat as exposed and rotate</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>revokes the leaked secret at source even if a copy is still cached somewhere</t>
         </is>
       </c>
     </row>
@@ -2632,17 +2878,17 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>Google Cloud Console → APIs &amp; Services → Credentials → restrict to HTTP referrers `*.tenu.world` + `localhost:*` + enable only Maps JavaScript + Places API. Public by design, not flagged by Vercel, but unrestricted = scraping risk against Global Apex billing</t>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Before 11 May</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>publish OAuth consent screen Testing → Production (requires domain verified + privacy URL + terms URL live at tenu.world/legal/privacy + /legal/terms)</t>
         </is>
       </c>
     </row>
@@ -2674,17 +2920,17 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>hardening pass, single biggest structural lesson from this incident. Anything that isn't a NEXT_PUBLIC_* or a non-secret identifier (R2_ACCOUNT_ID, R2_BUCKET_NAME) should be Sensitive</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Audit hidden env vars</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>scroll full Vercel env var list below the fold, confirm ANTHROPIC_API_KEY + BREVO_API_KEY + TELEGRAM_BOT_TOKEN + any other secret either shows Need To Rotate (rotate it) or was created Sensitive from day one (leave alone). If any non-public secret is unflagged and NOT marked Sensitive, treat as exposed and rotate</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2952,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2716,17 +2962,17 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>Post-rotation smoke test verification</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Google Cloud Console → APIs &amp; Services → Credentials → restrict to HTTP referrers `*.tenu.world` + `localhost:*` + enable only Maps JavaScript + Places API. Public by design, not flagged by Vercel, but unrestricted = scraping risk against Global Apex billing</t>
         </is>
       </c>
     </row>
@@ -2738,17 +2984,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2758,17 +3004,17 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>hardening pass, single biggest structural lesson from this incident. Anything that isn't a NEXT_PUBLIC_* or a non-secret identifier (R2_ACCOUNT_ID, R2_BUCKET_NAME) should be Sensitive</t>
         </is>
       </c>
     </row>
@@ -2780,7 +3026,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -2800,17 +3046,17 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>PDF generation leg</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Post-rotation smoke test verification</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green</t>
         </is>
       </c>
     </row>
@@ -2825,34 +3071,34 @@
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>Delete iCloud dedup files on Mac</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run.</t>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
         </is>
       </c>
     </row>
@@ -2874,7 +3120,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2884,15 +3130,19 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr"/>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>PDF generation leg</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2922,15 +3172,15 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr"/>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -2960,15 +3210,15 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr"/>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -2998,15 +3248,15 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr"/>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3036,15 +3286,15 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr"/>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3074,15 +3324,15 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
-        </is>
-      </c>
-      <c r="H37" s="6" t="inlineStr"/>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3112,15 +3362,15 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="inlineStr"/>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3140,25 +3390,25 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
-        </is>
-      </c>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -3183,20 +3433,20 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr"/>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3226,15 +3476,15 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="inlineStr"/>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3254,7 +3504,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -3264,15 +3514,15 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr"/>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -3282,7 +3532,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -3292,7 +3542,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -3302,15 +3552,15 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="inlineStr"/>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3330,7 +3580,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -3340,15 +3590,15 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
-        </is>
-      </c>
-      <c r="H44" s="6" t="inlineStr"/>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3378,17 +3628,17 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>Decide Apple IAP stance</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>physical service argument documented</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>re-dated 2026-05-03: depends on CC web-only listing revision (line in DECISION 2026-05-03 section).</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3650,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -3410,7 +3660,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -3420,15 +3670,19 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr"/>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>Decide Apple IAP stance</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>physical service argument documented — re-dated 2026-05-03: needs to land before App Store reviewer notes lock.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -3458,19 +3712,15 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>Magic-link auth working inside app</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>email link opens app, session persists</t>
-        </is>
-      </c>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -3495,20 +3745,24 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
-        </is>
-      </c>
-      <c r="H48" s="6" t="inlineStr"/>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>Magic-link auth working inside app</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>email link opens app, session persists</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -3533,24 +3787,20 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>T-103-core pipeline tests</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
-        </is>
-      </c>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -3580,15 +3830,19 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr"/>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>T-103-core pipeline tests</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -3621,12 +3875,12 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="inlineStr"/>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -3646,7 +3900,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -3656,19 +3910,15 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>Médiateur de la consommation signed</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>MEDICYS OR SMCE OR AME Conso</t>
-        </is>
-      </c>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -3698,15 +3948,19 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="inlineStr"/>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Médiateur de la consommation signed</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>MEDICYS OR SMCE OR AME Conso</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -3739,12 +3993,12 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="inlineStr"/>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -3774,15 +4028,15 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr"/>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -3812,19 +4066,15 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>F&amp;F invite list</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>8 names, email, jurisdiction, case type</t>
-        </is>
-      </c>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -3854,15 +4104,19 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr"/>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>F&amp;F invite list</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>8 names, email, jurisdiction, case type</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -3872,7 +4126,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -3882,7 +4136,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -3892,19 +4146,15 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>Bug sweep on inspection UI</t>
-        </is>
-      </c>
-      <c r="H58" s="6" t="inlineStr">
-        <is>
-          <t>camera retries, upload resume, offline queue</t>
-        </is>
-      </c>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -3934,15 +4184,19 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="inlineStr"/>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Bug sweep on inspection UI</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>camera retries, upload resume, offline queue</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -3962,7 +4216,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -3972,15 +4226,15 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
-        </is>
-      </c>
-      <c r="H60" s="6" t="inlineStr"/>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -4010,15 +4264,15 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="inlineStr"/>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -4028,7 +4282,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>POST-LAUNCH (12-31 May)</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -4038,25 +4292,25 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr"/>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>Full T-103 suite</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
-        </is>
-      </c>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -4085,14 +4339,14 @@
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>14-day outcome survey cron</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>Brevo trigger + Supabase write-back</t>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Full T-103 suite</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
         </is>
       </c>
     </row>
@@ -4123,14 +4377,14 @@
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr"/>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>Additional UI locales</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>14-day outcome survey cron</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>Brevo trigger + Supabase write-back</t>
         </is>
       </c>
     </row>
@@ -4157,18 +4411,18 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P2 Post-launch</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr"/>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>i18n audit phase 2</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Additional UI locales</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
         </is>
       </c>
     </row>
@@ -4195,19 +4449,57 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>i18n audit phase 2</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>T-066</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
           <t>P2 Post-launch</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr"/>
-      <c r="G66" s="6" t="inlineStr">
+      <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>App Store + Play production updates with post-launch fixes</t>
         </is>
       </c>
-      <c r="H66" s="6" t="inlineStr"/>
+      <c r="H67" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H66"/>
+  <autoFilter ref="A1:H67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4218,7 +4510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4281,7 +4573,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
+          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
@@ -4296,22 +4588,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>Scheduled push v2</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>replace Gmail create_draft with Brevo direct send — done 2026-04-19: new SKILL.md at scripts/scheduled-tasks/tenu-daily-push.md, brevo.env.example alongside. Telegram path unchanged. MH installs + adds BREVO_API_KEY — see MH line below.</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Draft FR avocat fixed-fee review brief in French</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>`outreach/legal/letter-avocat-droit-immobilier-FR.md`. Scope: pre-contractual disclosure (art. L221-5), CGU, Privacy/RGPD, DPA, dispute-letter LRAR template, état-des-lieux verbiage. Budget €1,000-2,000 fixed-fee. Asks for sign-off date 2026-05-07. Includes one-page summary of Tenu, target user, jurisdiction. — done 2026-05-03: file written, recipient/cabinet bracketed, attachments list at end, notes for MH on cabinet leads + rétractation defence.</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4615,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
+          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -4343,17 +4635,17 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>Fix footer legal routes redirecting to /auth/login</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>expose /legal, /auth/accept-terms, /api/consents as public paths in middleware — done 2026-04-18: middleware allow-list extended, verified on tenu.world production in incognito, all six legal pages render without auth. Commit via PR fix/public-legal-routes merged to main. Pre-contractual disclosure (art. L221-5 Code de la conso) now reachable as required for Stripe/App Store review.</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Draft UK housing solicitor TDS/DPS brief in English</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>`outreach/legal/letter-uk-housing-solicitor-EN.md`. Scope: TDS/DPS/MyDeposits dispute-letter template review, UK Consumer Rights Act 2015 alignment, ICO/UK GDPR check on photo handling. Budget GBP 500-1,500 fixed-fee. Asks for sign-off date 2026-05-07. — done 2026-05-03: file written, recipient/firm bracketed, attachments list at end, notes for MH on solicitor sourcing + Legal Services Act 2007 reserved-activities check.</t>
         </is>
       </c>
     </row>
@@ -4380,22 +4672,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Fix /stories/* and /features/* redirecting to /auth/login</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: added "/stories" and "/features" to publicPaths in src/middleware.ts. Same isPublicPath startsWith match pattern as the /legal fix; single entry per parent covers all nested routes. Stories and features now reachable without auth as marketing/content surface.</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Scheduled push v2</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>replace Gmail create_draft with Brevo direct send — done 2026-04-19: new SKILL.md at scripts/scheduled-tasks/tenu-daily-push.md, brevo.env.example alongside. Telegram path unchanged. MH installs + adds BREVO_API_KEY — see MH line below.</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4714,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -4430,14 +4722,14 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Use-case content system</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>manifest + /stories index + cross-link strip + homepage dual-card — done 2026-04-18: src/lib/stories.ts (single source of truth, Story type, 4 helpers), src/components/stories/OtherCases.tsx (bilingual cross-link strip), src/app/stories/page.tsx (index with cautionary populated, success placeholder awaiting 11 May cohort), homepage example section refactored from single Suzi hook to manifest-driven dual-card grid with "See all cases →" link, Suzi + Samir pages thread OtherCases before footer, example block in en/fr/zh/ar/ur dictionaries refactored to label/heading/intro/seeAll/disclaimer. Adding a new case is now one append to stories.ts + one new /stories/&lt;slug&gt;/page.tsx.</t>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Fix footer legal routes redirecting to /auth/login</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>expose /legal, /auth/accept-terms, /api/consents as public paths in middleware — done 2026-04-18: middleware allow-list extended, verified on tenu.world production in incognito, all six legal pages render without auth. Commit via PR fix/public-legal-routes merged to main. Pre-contractual disclosure (art. L221-5 Code de la conso) now reachable as required for Stripe/App Store review.</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4751,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -4469,17 +4761,17 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Telegram one-time setup</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>create bot via @BotFather, send token + chat_id — done 2026-04-18: bot created, token + chat_id set in .env.local and Vercel env (per Dr Mubashir)</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Fix /stories/* and /features/* redirecting to /auth/login</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: added "/stories" and "/features" to publicPaths in src/middleware.ts. Same isPublicPath startsWith match pattern as the /legal fix; single entry per parent covers all nested routes. Stories and features now reachable without auth as marketing/content surface.</t>
         </is>
       </c>
     </row>
@@ -4501,27 +4793,27 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Paste ANTHROPIC_API_KEY into .env.local + Vercel project env</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Use-case content system</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>manifest + /stories index + cross-link strip + homepage dual-card — done 2026-04-18: src/lib/stories.ts (single source of truth, Story type, 4 helpers), src/components/stories/OtherCases.tsx (bilingual cross-link strip), src/app/stories/page.tsx (index with cautionary populated, success placeholder awaiting 11 May cohort), homepage example section refactored from single Suzi hook to manifest-driven dual-card grid with "See all cases →" link, Suzi + Samir pages thread OtherCases before footer, example block in en/fr/zh/ar/ur dictionaries refactored to label/heading/intro/seeAll/disclaimer. Adding a new case is now one append to stories.ts + one new /stories/&lt;slug&gt;/page.tsx.</t>
         </is>
       </c>
     </row>
@@ -4556,14 +4848,14 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Paste BREVO_API_KEY into .env.local + Vercel project env</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Telegram one-time setup</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>create bot via @BotFather, send token + chat_id — done 2026-04-18: bot created, token + chat_id set in .env.local and Vercel env (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4877,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -4595,17 +4887,17 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>SOT consolidation</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>fix CLAUDE.md project path, refresh CLAUDE-CONTEXT.md to current React/in-code stack, replace stale-clone CLAUDE.md + CLAUDE-CONTEXT.md with redirect stubs — done 2026-04-19: SOT CLAUDE.md now declares `/Users/mmh/Documents/Claude/Projects/Tenu.World/` as canonical at the top, project structure block rewritten to match real layout (no nested `app/` wrapper, lists ios/, android/, mobile/, resources/, supabase/, scripts/). SOT CLAUDE-CONTEXT.md fully refreshed: dropped Webflow/Make.com/Tally/Airtable/Asana/Placid references, added pricing matrix, in-code pipeline, build timeline through 11 May, brand SOT pointers. Stale clone at `/Users/mmh/Documents/Global Apex/Tenu/` now has redirect-only CLAUDE.md + CLAUDE-CONTEXT.md so any agent invoked from that path bounces immediately.</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Paste ANTHROPIC_API_KEY into .env.local + Vercel project env</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4909,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -4627,7 +4919,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -4637,17 +4929,17 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Paste BREVO_API_KEY into .env.local + Vercel project env</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4951,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -4679,17 +4971,17 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>SOT consolidation</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>fix CLAUDE.md project path, refresh CLAUDE-CONTEXT.md to current React/in-code stack, replace stale-clone CLAUDE.md + CLAUDE-CONTEXT.md with redirect stubs — done 2026-04-19: SOT CLAUDE.md now declares `/Users/mmh/Documents/Claude/Projects/Tenu.World/` as canonical at the top, project structure block rewritten to match real layout (no nested `app/` wrapper, lists ios/, android/, mobile/, resources/, supabase/, scripts/). SOT CLAUDE-CONTEXT.md fully refreshed: dropped Webflow/Make.com/Tally/Airtable/Asana/Placid references, added pricing matrix, in-code pipeline, build timeline through 11 May, brand SOT pointers. Stale clone at `/Users/mmh/Documents/Global Apex/Tenu/` now has redirect-only CLAUDE.md + CLAUDE-CONTEXT.md so any agent invoked from that path bounces immediately.</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4993,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4711,7 +5003,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -4721,17 +5013,17 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Rotate R2_ACCESS_KEY_ID + R2_SECRET_ACCESS_KEY</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Cloudflare → R2 → Manage API tokens → new token scoped to tenu-evidence bucket (Object Read/Write only). Paste both into Vercel env, tick Sensitive, redeploy. Smoke: hit /api/mobile/upload-intent and upload a test photo. Then revoke old token in Cloudflare. Existing presigned URLs signed with old key keep working until expiry — done 2026-05-03 (per Dr Mubashir, post-holiday). CC post-rotation E2E smoke owed (line below).</t>
         </is>
       </c>
     </row>
@@ -4743,7 +5035,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -4753,7 +5045,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -4763,17 +5055,17 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Brevo transactional email leg</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Rotate STRIPE_WEBHOOK_SECRET</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Stripe → Developers → Webhooks → endpoint → Roll secret with 24h grace. Paste new into Vercel STRIPE_WEBHOOK_SECRET, tick Sensitive, redeploy. Smoke: `stripe trigger checkout.session.completed` and confirm /api/webhooks/stripe returns 200 in Vercel function logs. Old secret expires automatically at end of grace — done 2026-05-03 (per Dr Mubashir).</t>
         </is>
       </c>
     </row>
@@ -4785,7 +5077,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -4795,7 +5087,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -4805,17 +5097,17 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Capacitor 7 scaffold</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Rotate SUPABASE_SERVICE_ROLE_KEY AND NEXT_PUBLIC_SUPABASE_ANON_KEY together</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Supabase → Project Settings → API → JWT Keys → Generate new JWT secret (regenerates both keys, both are JWTs signed by the same secret). Update both values in Vercel in the same save, tick Sensitive on service_role (anon stays public but encrypt-at-rest regardless), redeploy. All pre-rotation sessions invalidated (pre-launch, so non-event). Smoke: incognito magic-link signup → /app-home load → photo upload row insert — done 2026-05-03 (per Dr Mubashir).</t>
         </is>
       </c>
     </row>
@@ -4847,17 +5139,17 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
         </is>
       </c>
     </row>
@@ -4879,7 +5171,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -4892,14 +5184,14 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
         </is>
       </c>
     </row>
@@ -4931,17 +5223,17 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>MB-01</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
         </is>
       </c>
     </row>
@@ -4973,17 +5265,17 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>MB-03</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Brevo transactional email leg</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
         </is>
       </c>
     </row>
@@ -5005,27 +5297,27 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>MB-05</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Delete iCloud dedup files on Mac</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run. — done 2026-05-03: real damage was 2.7× larger than originally scoped. Total cleaned: 113 dedup files (109 src/app metadata route dedups across icon/apple-icon/opengraph-image/robots/sitemap × 21-22 each, 3 in scripts/, 1 in docs/paperclip-briefs/) + 121 empty paren-numbered directories under src/app/ + 4 space-numbered directories under src/app/auth/ (accept-terms 2, callback 2, callback 3, login 2 — verified to be older stale snapshots predating the i18n + signup-flow fixes, no imports, originals intact) + 2 i18n dictionary dedups (ar 2.json, zh 2.json) = grand total 240 entries. Verified: `find` returns 0 dedups repo-wide; `npm run build` exit 0 with all routes (icon, opengraph-image, robots.txt, sitemap.xml, manifest.webmanifest, /legal/*, /auth/*, /inspection/*, /features/*) compiled cleanly; Next.js convention parents (icon.tsx, apple-icon.tsx, opengraph-image.tsx, robots.ts, sitemap.ts) all present. Root cause documented: dual mirroring by iCloud (parens-N suffix) AND OneDrive (space-N suffix) on the old `~/Documents/Claude/Projects/Tenu.World/` path. Repo now lives at `~/Code/Tenu.World/` (no iCloud xattrs). Confirm OneDrive isn't mirroring `~/Code/` either to prevent recurrence.</t>
         </is>
       </c>
     </row>
@@ -5057,17 +5349,17 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>MB-08</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Capacitor 7 scaffold</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
         </is>
       </c>
     </row>
@@ -5099,17 +5391,17 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>MB-09</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5413,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -5131,7 +5423,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -5141,17 +5433,17 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>App icon set</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5455,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -5183,17 +5475,17 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>Splash screens per density, status bar theming, safe-area insets</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>MB-01</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5497,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -5225,17 +5517,17 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>MB-03</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
         </is>
       </c>
     </row>
@@ -5247,42 +5539,294 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>MB-05</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>T-025</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>MB-08</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>T-026</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>MB-09</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>T-027</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
           <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>App icon set</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>T-028</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Splash screens per density, status bar theming, safe-area insets</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>T-029</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>T-030</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>Store listing copy drafted in FR + EN</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>description, keywords, support URL, privacy URL — done 2026-04-18 (ahead of schedule): MB-07 shipped docs/store-listings/{ios-fr,ios-en,play-fr,play-en}.md. Professional services register throughout (no buzzwords, no guaranteed-outcome claims), character counts validated inline, Stripe reader-app classification explicitly argued in reviewer notes, data safety section filled for Play form. Awaits MH (nights) review + edit before submission. Commit 50db60f.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H25"/>
+  <autoFilter ref="A1:H31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -741,7 +741,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -751,46 +751,46 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
+          <t>Update store-listing copy + welcome email + landing page to reflect web-first launch + native binaries follow</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>Personalise + send the FR avocat brief (review draft, fill recipient name + cabinet, send by email)</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Update store-listing copy + welcome email + landing page to reflect web-first launch + native binaries follow</t>
+          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Personalise + send the FR avocat brief (review draft, fill recipient name + cabinet, send by email)</t>
+          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
+          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
+          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
+          <t>Google Play Console developer account, USD 25 one-time</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
+          <t>Audit hidden env vars</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
+          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
+          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Audit hidden env vars</t>
+          <t>Post-rotation smoke test verification</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Post-rotation smoke test verification</t>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
         </is>
       </c>
     </row>
@@ -1103,19 +1103,19 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -1130,19 +1130,19 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
+          <t>Native Build Bridge plan</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -1152,29 +1152,29 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
+          <t>Google Workspace subscription on `tenu.world`</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Native Build Bridge plan</t>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Google Workspace subscription on `tenu.world`</t>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
+          <t>Before 11 May</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
+          <t>Decide Apple IAP stance</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Before 11 May</t>
+          <t>Magic-link auth working inside app</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>Médiateur de la consommation signed</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -1416,14 +1416,14 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -1438,14 +1438,14 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation signed</t>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -1460,14 +1460,14 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+          <t>PDF generation leg</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
+          <t>T-103-core pipeline tests</t>
         </is>
       </c>
     </row>
@@ -1592,19 +1592,19 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+          <t>F&amp;F invite list</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -1614,19 +1614,19 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -1636,14 +1636,14 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>T-103-core pipeline tests</t>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
     </row>
@@ -1675,24 +1675,24 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -1724,14 +1724,14 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>Bug sweep on inspection UI</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -1741,76 +1741,10 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>Bug sweep on inspection UI</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
         </is>
@@ -1827,7 +1761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2394,17 +2328,17 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
+          <t>Google Workspace subscription on `tenu.world`</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>`client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json`, the same with " (1)" suffix, and `stripe_backup_code.txt`. All three are sitting in plaintext in a Documents folder (iCloud-syncable, Time-Machine-backupable). Move to `~/.secrets/` or 1Password, then `rm` from disk. **Do NOT git commit them anywhere.**</t>
+          <t>create `ops@tenu.world` (owner) + `support@tenu.world` + `dpo@tenu.world` (aliases acceptable)</t>
         </is>
       </c>
     </row>
@@ -2426,29 +2360,25 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>`01-Legal-Checklist.md` (review + dedupe against SOT 05-Legal-Compliance content first), `etat-des-lieux.pdf`, `etat-des-lieux-meuble.pdf`, `modele-etat-des-lieux T2-T3.pdf` into SOT `docs/reference/etat-des-lieux/` (or wherever Dr Mubashir prefers). Delete from stale clone after move</t>
-        </is>
-      </c>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2473,24 +2403,20 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>archive to `~/Archive/` or `rm -rf`. Sandbox cannot delete the parent folder.</t>
-        </is>
-      </c>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -2525,14 +2451,10 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Google Workspace subscription on `tenu.world`</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>create `ops@tenu.world` (owner) + `support@tenu.world` + `dpo@tenu.world` (aliases acceptable)</t>
-        </is>
-      </c>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2567,7 +2489,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
@@ -2605,7 +2527,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr"/>
@@ -2638,15 +2560,19 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr"/>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>expect no 403 org_internal, consent screen shows "Tenu" with `support@tenu.world`</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2676,15 +2602,19 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr"/>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>do not archive, the secret is burned</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2714,15 +2644,19 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr"/>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>revokes the leaked secret at source even if a copy is still cached somewhere</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2752,17 +2686,17 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+          <t>Before 11 May</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>expect no 403 org_internal, consent screen shows "Tenu" with `support@tenu.world`</t>
+          <t>publish OAuth consent screen Testing → Production (requires domain verified + privacy URL + terms URL live at tenu.world/legal/privacy + /legal/terms)</t>
         </is>
       </c>
     </row>
@@ -2794,17 +2728,17 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+          <t>Audit hidden env vars</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>do not archive, the secret is burned</t>
+          <t>scroll full Vercel env var list below the fold, confirm ANTHROPIC_API_KEY + BREVO_API_KEY + TELEGRAM_BOT_TOKEN + any other secret either shows Need To Rotate (rotate it) or was created Sensitive from day one (leave alone). If any non-public secret is unflagged and NOT marked Sensitive, treat as exposed and rotate</t>
         </is>
       </c>
     </row>
@@ -2836,17 +2770,17 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>revokes the leaked secret at source even if a copy is still cached somewhere</t>
+          <t>Google Cloud Console → APIs &amp; Services → Credentials → restrict to HTTP referrers `*.tenu.world` + `localhost:*` + enable only Maps JavaScript + Places API. Public by design, not flagged by Vercel, but unrestricted = scraping risk against Global Apex billing</t>
         </is>
       </c>
     </row>
@@ -2878,17 +2812,17 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Before 11 May</t>
+          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>publish OAuth consent screen Testing → Production (requires domain verified + privacy URL + terms URL live at tenu.world/legal/privacy + /legal/terms)</t>
+          <t>hardening pass, single biggest structural lesson from this incident. Anything that isn't a NEXT_PUBLIC_* or a non-secret identifier (R2_ACCOUNT_ID, R2_BUCKET_NAME) should be Sensitive</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2844,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2925,12 +2859,12 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Audit hidden env vars</t>
+          <t>Post-rotation smoke test verification</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>scroll full Vercel env var list below the fold, confirm ANTHROPIC_API_KEY + BREVO_API_KEY + TELEGRAM_BOT_TOKEN + any other secret either shows Need To Rotate (rotate it) or was created Sensitive from day one (leave alone). If any non-public secret is unflagged and NOT marked Sensitive, treat as exposed and rotate</t>
+          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green</t>
         </is>
       </c>
     </row>
@@ -2942,17 +2876,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2962,17 +2896,17 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Google Cloud Console → APIs &amp; Services → Credentials → restrict to HTTP referrers `*.tenu.world` + `localhost:*` + enable only Maps JavaScript + Places API. Public by design, not flagged by Vercel, but unrestricted = scraping risk against Global Apex billing</t>
+          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2918,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -2994,7 +2928,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3004,17 +2938,17 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
+          <t>PDF generation leg</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>hardening pass, single biggest structural lesson from this incident. Anything that isn't a NEXT_PUBLIC_* or a non-secret identifier (R2_ACCOUNT_ID, R2_BUCKET_NAME) should be Sensitive</t>
+          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
         </is>
       </c>
     </row>
@@ -3026,7 +2960,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -3036,7 +2970,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -3046,19 +2980,15 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>Post-rotation smoke test verification</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green</t>
-        </is>
-      </c>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3071,14 +3001,14 @@
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -3088,19 +3018,15 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
-        </is>
-      </c>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3120,7 +3046,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -3130,19 +3056,15 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
-        </is>
-      </c>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3172,12 +3094,12 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
@@ -3210,12 +3132,12 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
@@ -3248,12 +3170,12 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr"/>
@@ -3286,12 +3208,12 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr"/>
@@ -3314,25 +3236,25 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr"/>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr"/>
+          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3352,7 +3274,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -3362,12 +3284,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr"/>
@@ -3390,7 +3312,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -3400,12 +3322,12 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr"/>
@@ -3428,25 +3350,25 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr"/>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
-        </is>
-      </c>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3456,7 +3378,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -3476,12 +3398,12 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr"/>
@@ -3494,7 +3416,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -3504,7 +3426,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -3514,15 +3436,19 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr"/>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>re-dated 2026-05-03: depends on CC web-only listing revision (line in DECISION 2026-05-03 section).</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -3532,7 +3458,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -3552,15 +3478,19 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="inlineStr"/>
+          <t>Decide Apple IAP stance</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>physical service argument documented — re-dated 2026-05-03: needs to land before App Store reviewer notes lock.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3570,7 +3500,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -3590,12 +3520,12 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr"/>
@@ -3608,7 +3538,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -3618,7 +3548,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -3628,17 +3558,17 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
+          <t>Magic-link auth working inside app</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>re-dated 2026-05-03: depends on CC web-only listing revision (line in DECISION 2026-05-03 section).</t>
+          <t>email link opens app, session persists</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3580,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -3660,29 +3590,25 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>physical service argument documented — re-dated 2026-05-03: needs to land before App Store reviewer notes lock.</t>
-        </is>
-      </c>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -3712,15 +3638,19 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr"/>
+          <t>T-103-core pipeline tests</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -3750,19 +3680,15 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>email link opens app, session persists</t>
-        </is>
-      </c>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -3787,17 +3713,17 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr"/>
@@ -3820,7 +3746,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -3830,17 +3756,17 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>T-103-core pipeline tests</t>
+          <t>Médiateur de la consommation signed</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
+          <t>MEDICYS OR SMCE OR AME Conso</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3788,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -3872,12 +3798,12 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr"/>
@@ -3900,7 +3826,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -3910,12 +3836,12 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr"/>
@@ -3953,14 +3879,10 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation signed</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>MEDICYS OR SMCE OR AME Conso</t>
-        </is>
-      </c>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -3990,15 +3912,19 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="inlineStr"/>
+          <t>F&amp;F invite list</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>8 names, email, jurisdiction, case type</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -4028,12 +3954,12 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr"/>
@@ -4046,7 +3972,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -4056,7 +3982,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -4066,15 +3992,19 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr"/>
+          <t>Bug sweep on inspection UI</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>camera retries, upload resume, offline queue</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -4084,7 +4014,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -4094,7 +4024,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -4104,19 +4034,15 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>8 names, email, jurisdiction, case type</t>
-        </is>
-      </c>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -4126,7 +4052,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -4146,12 +4072,12 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr"/>
@@ -4174,7 +4100,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -4184,19 +4110,15 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Bug sweep on inspection UI</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>camera retries, upload resume, offline queue</t>
-        </is>
-      </c>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -4206,7 +4128,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -4221,20 +4143,20 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr"/>
+          <t>Full T-103 suite</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -4244,7 +4166,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -4254,25 +4176,25 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr"/>
+          <t>14-day outcome survey cron</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Brevo trigger + Supabase write-back</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -4282,7 +4204,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -4292,25 +4214,25 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="inlineStr"/>
+          <t>Additional UI locales</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -4335,18 +4257,18 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Full T-103 suite</t>
+          <t>i18n audit phase 2</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
         </is>
       </c>
     </row>
@@ -4379,127 +4301,13 @@
       <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>14-day outcome survey cron</t>
-        </is>
-      </c>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>Brevo trigger + Supabase write-back</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>T-064</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr"/>
-      <c r="G65" s="7" t="inlineStr">
-        <is>
-          <t>Additional UI locales</t>
-        </is>
-      </c>
-      <c r="H65" s="7" t="inlineStr">
-        <is>
-          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>T-065</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="inlineStr"/>
-      <c r="G66" s="7" t="inlineStr">
-        <is>
-          <t>i18n audit phase 2</t>
-        </is>
-      </c>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>T-066</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr"/>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
           <t>App Store + Play production updates with post-launch fixes</t>
         </is>
       </c>
-      <c r="H67" s="7" t="inlineStr"/>
+      <c r="H64" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H67"/>
+  <autoFilter ref="A1:H64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4510,7 +4318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5013,17 +4821,17 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Rotate R2_ACCESS_KEY_ID + R2_SECRET_ACCESS_KEY</t>
+          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Cloudflare → R2 → Manage API tokens → new token scoped to tenu-evidence bucket (Object Read/Write only). Paste both into Vercel env, tick Sensitive, redeploy. Smoke: hit /api/mobile/upload-intent and upload a test photo. Then revoke old token in Cloudflare. Existing presigned URLs signed with old key keep working until expiry — done 2026-05-03 (per Dr Mubashir, post-holiday). CC post-rotation E2E smoke owed (line below).</t>
+          <t>`client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json`, the same with " (1)" suffix, and `stripe_backup_code.txt`. All three are sitting in plaintext in a Documents folder (iCloud-syncable, Time-Machine-backupable). Move to `~/.secrets/` or 1Password, then `rm` from disk. **Do NOT git commit them anywhere.** — done 2026-05-03: stripe_backup_code.txt contents migrated to 1Password as Secure Note "Stripe 2FA backup codes — Global Apex NET" (per Dr Mubashir). Two client_secret JSON files deleted (burned credentials, no preservation needed — Cloud project shutdown will close the trust loop). All three files removed from disk via `rm -rf` on parent folder. Verify by inspection: `/Users/mmh/Documents/Global Apex/Tenu/` no longer exists.</t>
         </is>
       </c>
     </row>
@@ -5045,12 +4853,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -5060,12 +4868,12 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Rotate STRIPE_WEBHOOK_SECRET</t>
+          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Stripe → Developers → Webhooks → endpoint → Roll secret with 24h grace. Paste new into Vercel STRIPE_WEBHOOK_SECRET, tick Sensitive, redeploy. Smoke: `stripe trigger checkout.session.completed` and confirm /api/webhooks/stripe returns 200 in Vercel function logs. Old secret expires automatically at end of grace — done 2026-05-03 (per Dr Mubashir).</t>
+          <t>`01-Legal-Checklist.md` (review + dedupe against SOT 05-Legal-Compliance content first), `etat-des-lieux.pdf`, `etat-des-lieux-meuble.pdf`, `modele-etat-des-lieux T2-T3.pdf` into SOT `docs/reference/etat-des-lieux/` (or wherever Dr Mubashir prefers). Delete from stale clone after move — done 2026-05-03: audit found `01-Legal-Checklist.md` already byte-identical between stale and SOT (no migration needed); 3 PDFs in stale folder, two of which (`modele-etat-des-lieux.pdf` and `modele-etat-des-lieux T2-T3.pdf`) are byte-identical (sha 4b9fed2e0c14...) — only one carried over. Final SOT state: `docs/reference/etat-des-lieux/etat-des-lieux-meuble.pdf` (sha 6e1e3f5acd83...) + `docs/reference/etat-des-lieux/modele-etat-des-lieux T2-T3.pdf` (sha 4b9fed2e0c14...). Note: original task line referenced `etat-des-lieux.pdf` which never existed in stale clone — actual filenames discovered during audit.</t>
         </is>
       </c>
     </row>
@@ -5092,22 +4900,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Rotate SUPABASE_SERVICE_ROLE_KEY AND NEXT_PUBLIC_SUPABASE_ANON_KEY together</t>
+          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Supabase → Project Settings → API → JWT Keys → Generate new JWT secret (regenerates both keys, both are JWTs signed by the same secret). Update both values in Vercel in the same save, tick Sensitive on service_role (anon stays public but encrypt-at-rest regardless), redeploy. All pre-rotation sessions invalidated (pre-launch, so non-event). Smoke: incognito magic-link signup → /app-home load → photo upload row insert — done 2026-05-03 (per Dr Mubashir).</t>
+          <t>archive to `~/Archive/` or `rm -rf`. Sandbox cannot delete the parent folder. — done 2026-05-03 — decision: `rm -rf`, no archive. Audit grounds: (a) 533 MB of the 538 MB total was regenerable node_modules; (b) git remote pointed at the same `malikmubashir/tenu-world.git` with HEAD at `c3614ef` (the original April 3 scaffold commit, redundant with everything in main since); (c) all 10 doc files were either byte-identical to SOT or differed only in COI-scrubbed wording (HEC GEMM / MHF references that SOT correctly removed per role-separation policy in CLAUDE.md); (d) parent had `com.apple.macl` and `com.apple.provenance` xattrs only — NOT iCloud-synced, so no recurring sync source to sever; (e) Time Machine retains snapshots back to April 3 if recovery ever needed. Final stale-clone removal verified: parent path no longer exists. Container `/Users/mmh/Documents/Global Apex/` retained for other uses. Companion finding: the dedup chaos cleaned in the prior task was therefore NOT from active iCloud sync — likely a one-time merge incident from a multi-machine sync, not ongoing. Worth knowing for future repo-cleanup heuristics.</t>
         </is>
       </c>
     </row>
@@ -5119,7 +4927,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -5129,7 +4937,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -5144,12 +4952,12 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
+          <t>Rotate R2_ACCESS_KEY_ID + R2_SECRET_ACCESS_KEY</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
+          <t>Cloudflare → R2 → Manage API tokens → new token scoped to tenu-evidence bucket (Object Read/Write only). Paste both into Vercel env, tick Sensitive, redeploy. Smoke: hit /api/mobile/upload-intent and upload a test photo. Then revoke old token in Cloudflare. Existing presigned URLs signed with old key keep working until expiry — done 2026-05-03 (per Dr Mubashir, post-holiday). CC post-rotation E2E smoke owed (line below).</t>
         </is>
       </c>
     </row>
@@ -5161,7 +4969,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -5171,7 +4979,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -5181,17 +4989,17 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
+          <t>Rotate STRIPE_WEBHOOK_SECRET</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
+          <t>Stripe → Developers → Webhooks → endpoint → Roll secret with 24h grace. Paste new into Vercel STRIPE_WEBHOOK_SECRET, tick Sensitive, redeploy. Smoke: `stripe trigger checkout.session.completed` and confirm /api/webhooks/stripe returns 200 in Vercel function logs. Old secret expires automatically at end of grace — done 2026-05-03 (per Dr Mubashir).</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5011,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -5213,7 +5021,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -5223,17 +5031,17 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
+          <t>Rotate SUPABASE_SERVICE_ROLE_KEY AND NEXT_PUBLIC_SUPABASE_ANON_KEY together</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
+          <t>Supabase → Project Settings → API → JWT Keys → Generate new JWT secret (regenerates both keys, both are JWTs signed by the same secret). Update both values in Vercel in the same save, tick Sensitive on service_role (anon stays public but encrypt-at-rest regardless), redeploy. All pre-rotation sessions invalidated (pre-launch, so non-event). Smoke: incognito magic-link signup → /app-home load → photo upload row insert — done 2026-05-03 (per Dr Mubashir).</t>
         </is>
       </c>
     </row>
@@ -5265,17 +5073,17 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Brevo transactional email leg</t>
+          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
+          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
         </is>
       </c>
     </row>
@@ -5297,27 +5105,27 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Delete iCloud dedup files on Mac</t>
+          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run. — done 2026-05-03: real damage was 2.7× larger than originally scoped. Total cleaned: 113 dedup files (109 src/app metadata route dedups across icon/apple-icon/opengraph-image/robots/sitemap × 21-22 each, 3 in scripts/, 1 in docs/paperclip-briefs/) + 121 empty paren-numbered directories under src/app/ + 4 space-numbered directories under src/app/auth/ (accept-terms 2, callback 2, callback 3, login 2 — verified to be older stale snapshots predating the i18n + signup-flow fixes, no imports, originals intact) + 2 i18n dictionary dedups (ar 2.json, zh 2.json) = grand total 240 entries. Verified: `find` returns 0 dedups repo-wide; `npm run build` exit 0 with all routes (icon, opengraph-image, robots.txt, sitemap.xml, manifest.webmanifest, /legal/*, /auth/*, /inspection/*, /features/*) compiled cleanly; Next.js convention parents (icon.tsx, apple-icon.tsx, opengraph-image.tsx, robots.ts, sitemap.ts) all present. Root cause documented: dual mirroring by iCloud (parens-N suffix) AND OneDrive (space-N suffix) on the old `~/Documents/Claude/Projects/Tenu.World/` path. Repo now lives at `~/Code/Tenu.World/` (no iCloud xattrs). Confirm OneDrive isn't mirroring `~/Code/` either to prevent recurrence.</t>
+          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
         </is>
       </c>
     </row>
@@ -5349,17 +5157,17 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Capacitor 7 scaffold</t>
+          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
+          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
         </is>
       </c>
     </row>
@@ -5391,17 +5199,17 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+          <t>Brevo transactional email leg</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
+          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
         </is>
       </c>
     </row>
@@ -5428,22 +5236,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
+          <t>Delete iCloud dedup files on Mac</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
+          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run. — done 2026-05-03: real damage was 2.7× larger than originally scoped. Total cleaned: 113 dedup files (109 src/app metadata route dedups across icon/apple-icon/opengraph-image/robots/sitemap × 21-22 each, 3 in scripts/, 1 in docs/paperclip-briefs/) + 121 empty paren-numbered directories under src/app/ + 4 space-numbered directories under src/app/auth/ (accept-terms 2, callback 2, callback 3, login 2 — verified to be older stale snapshots predating the i18n + signup-flow fixes, no imports, originals intact) + 2 i18n dictionary dedups (ar 2.json, zh 2.json) = grand total 240 entries. Verified: `find` returns 0 dedups repo-wide; `npm run build` exit 0 with all routes (icon, opengraph-image, robots.txt, sitemap.xml, manifest.webmanifest, /legal/*, /auth/*, /inspection/*, /features/*) compiled cleanly; Next.js convention parents (icon.tsx, apple-icon.tsx, opengraph-image.tsx, robots.ts, sitemap.ts) all present. Root cause documented: dual mirroring by iCloud (parens-N suffix) AND OneDrive (space-N suffix) on the old `~/Documents/Claude/Projects/Tenu.World/` path. Repo now lives at `~/Code/Tenu.World/` (no iCloud xattrs). Confirm OneDrive isn't mirroring `~/Code/` either to prevent recurrence.</t>
         </is>
       </c>
     </row>
@@ -5475,17 +5283,17 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>MB-01</t>
+          <t>Capacitor 7 scaffold</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
+          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
         </is>
       </c>
     </row>
@@ -5517,17 +5325,17 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>MB-03</t>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
+          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5357,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -5559,17 +5367,17 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>MB-05</t>
+          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
+          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -5606,12 +5414,12 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>MB-08</t>
+          <t>MB-01</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
+          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
         </is>
       </c>
     </row>
@@ -5648,12 +5456,12 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>MB-09</t>
+          <t>MB-03</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
+          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5473,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -5685,17 +5493,17 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>App icon set</t>
+          <t>MB-05</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
+          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5515,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -5727,17 +5535,17 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Splash screens per density, status bar theming, safe-area insets</t>
+          <t>MB-08</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
+          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5557,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -5769,17 +5577,17 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+          <t>MB-09</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
         </is>
       </c>
     </row>
@@ -5811,22 +5619,148 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>App icon set</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>T-031</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>Splash screens per density, status bar theming, safe-area insets</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>T-032</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>T-033</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>Store listing copy drafted in FR + EN</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>description, keywords, support URL, privacy URL — done 2026-04-18 (ahead of schedule): MB-07 shipped docs/store-listings/{ios-fr,ios-en,play-fr,play-en}.md. Professional services register throughout (no buzzwords, no guaranteed-outcome claims), character counts validated inline, Stripe reader-app classification explicitly argued in reviewer notes, data safety section filled for Play form. Awaits MH (nights) review + edit before submission. Commit 50db60f.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H31"/>
+  <autoFilter ref="A1:H34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Regenerated 2026-05-03 from TASKS.md. Master = TASKS.md. Do not edit xlsx directly.</t>
+          <t>Regenerated 2026-05-06 from TASKS.md. Master = TASKS.md. Do not edit xlsx directly.</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -1027,7 +1027,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -1042,19 +1042,19 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+          <t>Native Build Bridge plan</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1064,19 +1064,19 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
+          <t>Google Workspace subscription on `tenu.world`</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -1086,29 +1086,29 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Native Build Bridge plan</t>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Google Workspace subscription on `tenu.world`</t>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+          <t>Before 11 May</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
+          <t>Decide Apple IAP stance</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
+          <t>Médiateur de la consommation signed</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Before 11 May</t>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -1306,14 +1306,14 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -1328,19 +1328,19 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -1350,14 +1350,14 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -1372,19 +1372,19 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation signed</t>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -1394,14 +1394,14 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+          <t>PDF generation leg</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+          <t>T-103-core pipeline tests</t>
         </is>
       </c>
     </row>
@@ -1482,14 +1482,14 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+          <t>F&amp;F invite list</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -1504,14 +1504,14 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -1526,14 +1526,14 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -1548,19 +1548,19 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -1570,14 +1570,14 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>T-103-core pipeline tests</t>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -1592,19 +1592,19 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -1614,14 +1614,14 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -1636,14 +1636,14 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -1658,41 +1658,41 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -1702,14 +1702,14 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -1724,29 +1724,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Bug sweep on inspection UI</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1908,7 +1886,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>DECISION 2026-05-03 — Launch path: Option B (web-only on 11 May)</t>
+          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -1918,12 +1896,12 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1933,12 +1911,12 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
+          <t>Personalise + send the FR avocat brief (review draft, fill recipient name + cabinet, send by email)</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>keep their content verbatim, only re-section + re-date so the launch checklist stops bleeding red on items that were never blocking 11 May web-only — opened 2026-05-03.</t>
+          <t>depends on CC line above.</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1953,7 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Personalise + send the FR avocat brief (review draft, fill recipient name + cabinet, send by email)</t>
+          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -1992,7 +1970,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -2007,22 +1985,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
+          <t>Install scheduled-push v2</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>depends on CC line above.</t>
+          <t>copy scripts/scheduled-tasks/tenu-daily-push.md into ~/Documents/Claude/Scheduled/tenu-daily-push/SKILL.md and drop BREVO_API_KEY into .secrets/brevo.env</t>
         </is>
       </c>
     </row>
@@ -2049,24 +2027,20 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Install scheduled-push v2</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>copy scripts/scheduled-tasks/tenu-daily-push.md into ~/Documents/Claude/Scheduled/tenu-daily-push/SKILL.md and drop BREVO_API_KEY into .secrets/brevo.env</t>
-        </is>
-      </c>
+          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2101,7 +2075,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
+          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
@@ -2139,7 +2113,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
+          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr"/>
@@ -2155,9 +2129,9 @@
           <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -2172,15 +2146,19 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr"/>
+          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>submitted 2026-05-03, documents sent to Apple, awaiting verification (per Dr Mubashir). Apple identity check typically 2-5 business days; D-U-N-S verification gates the review. Track unblocking of Xcode signing / TestFlight upload off this line.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2193,9 +2171,9 @@
           <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -2210,19 +2188,15 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>submitted 2026-05-03, documents sent to Apple, awaiting verification (per Dr Mubashir). Apple identity check typically 2-5 business days; D-U-N-S verification gates the review. Track unblocking of Xcode signing / TestFlight upload off this line.</t>
-        </is>
-      </c>
+          <t>Google Play Console developer account, USD 25 one-time</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2257,7 +2231,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr"/>
@@ -2290,15 +2264,19 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr"/>
+          <t>Google Workspace subscription on `tenu.world`</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>create `ops@tenu.world` (owner) + `support@tenu.world` + `dpo@tenu.world` (aliases acceptable)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -2333,14 +2311,10 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Google Workspace subscription on `tenu.world`</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>create `ops@tenu.world` (owner) + `support@tenu.world` + `dpo@tenu.world` (aliases acceptable)</t>
-        </is>
-      </c>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2375,7 +2349,7 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr"/>
@@ -2413,7 +2387,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr"/>
@@ -2451,7 +2425,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr"/>
@@ -2489,7 +2463,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
@@ -2522,15 +2496,19 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr"/>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>expect no 403 org_internal, consent screen shows "Tenu" with `support@tenu.world`</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2565,12 +2543,12 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>expect no 403 org_internal, consent screen shows "Tenu" with `support@tenu.world`</t>
+          <t>do not archive, the secret is burned</t>
         </is>
       </c>
     </row>
@@ -2607,12 +2585,12 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>do not archive, the secret is burned</t>
+          <t>revokes the leaked secret at source even if a copy is still cached somewhere</t>
         </is>
       </c>
     </row>
@@ -2644,17 +2622,17 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+          <t>Before 11 May</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>revokes the leaked secret at source even if a copy is still cached somewhere</t>
+          <t>publish OAuth consent screen Testing → Production (requires domain verified + privacy URL + terms URL live at tenu.world/legal/privacy + /legal/terms)</t>
         </is>
       </c>
     </row>
@@ -2686,17 +2664,17 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Before 11 May</t>
+          <t>Audit hidden env vars</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>publish OAuth consent screen Testing → Production (requires domain verified + privacy URL + terms URL live at tenu.world/legal/privacy + /legal/terms)</t>
+          <t>scroll full Vercel env var list below the fold, confirm ANTHROPIC_API_KEY + BREVO_API_KEY + TELEGRAM_BOT_TOKEN + any other secret either shows Need To Rotate (rotate it) or was created Sensitive from day one (leave alone). If any non-public secret is unflagged and NOT marked Sensitive, treat as exposed and rotate</t>
         </is>
       </c>
     </row>
@@ -2733,12 +2711,12 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Audit hidden env vars</t>
+          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>scroll full Vercel env var list below the fold, confirm ANTHROPIC_API_KEY + BREVO_API_KEY + TELEGRAM_BOT_TOKEN + any other secret either shows Need To Rotate (rotate it) or was created Sensitive from day one (leave alone). If any non-public secret is unflagged and NOT marked Sensitive, treat as exposed and rotate</t>
+          <t>Google Cloud Console → APIs &amp; Services → Credentials → restrict to HTTP referrers `*.tenu.world` + `localhost:*` + enable only Maps JavaScript + Places API. Public by design, not flagged by Vercel, but unrestricted = scraping risk against Global Apex billing</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2753,12 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
+          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Google Cloud Console → APIs &amp; Services → Credentials → restrict to HTTP referrers `*.tenu.world` + `localhost:*` + enable only Maps JavaScript + Places API. Public by design, not flagged by Vercel, but unrestricted = scraping risk against Global Apex billing</t>
+          <t>hardening pass, single biggest structural lesson from this incident. Anything that isn't a NEXT_PUBLIC_* or a non-secret identifier (R2_ACCOUNT_ID, R2_BUCKET_NAME) should be Sensitive</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2780,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -2817,12 +2795,12 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
+          <t>Post-rotation smoke test verification</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>hardening pass, single biggest structural lesson from this incident. Anything that isn't a NEXT_PUBLIC_* or a non-secret identifier (R2_ACCOUNT_ID, R2_BUCKET_NAME) should be Sensitive</t>
+          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2812,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2854,17 +2832,17 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Post-rotation smoke test verification</t>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green</t>
+          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
         </is>
       </c>
     </row>
@@ -2879,9 +2857,9 @@
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2896,17 +2874,17 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>PDF generation leg</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
+          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2906,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2938,19 +2916,15 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
-        </is>
-      </c>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -2985,7 +2959,7 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr"/>
@@ -3023,7 +2997,7 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr"/>
@@ -3056,12 +3030,12 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr"/>
@@ -3099,7 +3073,7 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
@@ -3132,12 +3106,12 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
@@ -3175,7 +3149,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr"/>
@@ -3198,25 +3172,25 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr"/>
+          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3241,20 +3215,20 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr"/>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
-        </is>
-      </c>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3284,12 +3258,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr"/>
@@ -3312,7 +3286,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -3322,12 +3296,12 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr"/>
@@ -3340,7 +3314,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -3350,7 +3324,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3360,12 +3334,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr"/>
@@ -3388,7 +3362,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -3398,15 +3372,19 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr"/>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>re-dated 2026-05-03: depends on CC web-only listing revision (line in DECISION 2026-05-03 section).</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3436,17 +3414,17 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
+          <t>Decide Apple IAP stance</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>re-dated 2026-05-03: depends on CC web-only listing revision (line in DECISION 2026-05-03 section).</t>
+          <t>physical service argument documented — re-dated 2026-05-03: needs to land before App Store reviewer notes lock.</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3436,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -3468,7 +3446,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -3478,19 +3456,15 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>physical service argument documented — re-dated 2026-05-03: needs to land before App Store reviewer notes lock.</t>
-        </is>
-      </c>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3520,15 +3494,19 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr"/>
+          <t>Magic-link auth working inside app</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>email link opens app, session persists</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3553,24 +3531,20 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>email link opens app, session persists</t>
-        </is>
-      </c>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -3595,20 +3569,24 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr"/>
+          <t>T-103-core pipeline tests</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -3638,19 +3616,15 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>T-103-core pipeline tests</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
-        </is>
-      </c>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -3680,12 +3654,12 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr"/>
@@ -3708,7 +3682,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -3718,15 +3692,19 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr"/>
+          <t>Médiateur de la consommation signed</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>MEDICYS OR SMCE OR AME Conso</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -3756,19 +3734,15 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation signed</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>MEDICYS OR SMCE OR AME Conso</t>
-        </is>
-      </c>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -3803,7 +3777,7 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr"/>
@@ -3836,12 +3810,12 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr"/>
@@ -3874,15 +3848,19 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr"/>
+          <t>F&amp;F invite list</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>8 names, email, jurisdiction, case type</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -3912,19 +3890,15 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>8 names, email, jurisdiction, case type</t>
-        </is>
-      </c>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -3934,7 +3908,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -3944,7 +3918,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -3954,12 +3928,12 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr"/>
@@ -3982,7 +3956,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -3992,19 +3966,15 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>Bug sweep on inspection UI</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>camera retries, upload resume, offline queue</t>
-        </is>
-      </c>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -4024,7 +3994,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -4034,12 +4004,12 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr"/>
@@ -4052,7 +4022,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -4062,25 +4032,25 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr"/>
+          <t>Full T-103 suite</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -4090,7 +4060,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -4100,25 +4070,25 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr"/>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr"/>
+          <t>14-day outcome survey cron</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>Brevo trigger + Supabase write-back</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -4149,12 +4119,12 @@
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>Full T-103 suite</t>
+          <t>Additional UI locales</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
         </is>
       </c>
     </row>
@@ -4181,18 +4151,18 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>14-day outcome survey cron</t>
+          <t>i18n audit phase 2</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Brevo trigger + Supabase write-back</t>
+          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
         </is>
       </c>
     </row>
@@ -4225,89 +4195,13 @@
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Additional UI locales</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>T-062</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr"/>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>i18n audit phase 2</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>T-063</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr"/>
-      <c r="G64" s="7" t="inlineStr">
-        <is>
           <t>App Store + Play production updates with post-launch fixes</t>
         </is>
       </c>
-      <c r="H64" s="7" t="inlineStr"/>
+      <c r="H62" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H64"/>
+  <autoFilter ref="A1:H62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4318,7 +4212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4381,7 +4275,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
+          <t>DECISION 2026-05-03 — Launch path: Option B (web-only on 11 May)</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
@@ -4396,22 +4290,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>Draft FR avocat fixed-fee review brief in French</t>
+          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>`outreach/legal/letter-avocat-droit-immobilier-FR.md`. Scope: pre-contractual disclosure (art. L221-5), CGU, Privacy/RGPD, DPA, dispute-letter LRAR template, état-des-lieux verbiage. Budget €1,000-2,000 fixed-fee. Asks for sign-off date 2026-05-07. Includes one-page summary of Tenu, target user, jurisdiction. — done 2026-05-03: file written, recipient/cabinet bracketed, attachments list at end, notes for MH on cabinet leads + rétractation defence.</t>
+          <t>keep their content verbatim, only re-section + re-date so the launch checklist stops bleeding red on items that were never blocking 11 May web-only — opened 2026-05-03. — done 2026-05-06: re-dating applied via runbook-2026-05-06 (TE-1..TE-7).</t>
         </is>
       </c>
     </row>
@@ -4448,12 +4342,12 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>Draft UK housing solicitor TDS/DPS brief in English</t>
+          <t>Draft FR avocat fixed-fee review brief in French</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>`outreach/legal/letter-uk-housing-solicitor-EN.md`. Scope: TDS/DPS/MyDeposits dispute-letter template review, UK Consumer Rights Act 2015 alignment, ICO/UK GDPR check on photo handling. Budget GBP 500-1,500 fixed-fee. Asks for sign-off date 2026-05-07. — done 2026-05-03: file written, recipient/firm bracketed, attachments list at end, notes for MH on solicitor sourcing + Legal Services Act 2007 reserved-activities check.</t>
+          <t>`outreach/legal/letter-avocat-droit-immobilier-FR.md`. Scope: pre-contractual disclosure (art. L221-5), CGU, Privacy/RGPD, DPA, dispute-letter LRAR template, état-des-lieux verbiage. Budget €1,000-2,000 fixed-fee. Asks for sign-off date 2026-05-07. Includes one-page summary of Tenu, target user, jurisdiction. — done 2026-05-03: file written, recipient/cabinet bracketed, attachments list at end, notes for MH on cabinet leads + rétractation defence.</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4359,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
+          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -4480,22 +4374,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Scheduled push v2</t>
+          <t>Draft UK housing solicitor TDS/DPS brief in English</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>replace Gmail create_draft with Brevo direct send — done 2026-04-19: new SKILL.md at scripts/scheduled-tasks/tenu-daily-push.md, brevo.env.example alongside. Telegram path unchanged. MH installs + adds BREVO_API_KEY — see MH line below.</t>
+          <t>`outreach/legal/letter-uk-housing-solicitor-EN.md`. Scope: TDS/DPS/MyDeposits dispute-letter template review, UK Consumer Rights Act 2015 alignment, ICO/UK GDPR check on photo handling. Budget GBP 500-1,500 fixed-fee. Asks for sign-off date 2026-05-07. — done 2026-05-03: file written, recipient/firm bracketed, attachments list at end, notes for MH on solicitor sourcing + Legal Services Act 2007 reserved-activities check.</t>
         </is>
       </c>
     </row>
@@ -4522,22 +4416,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Fix footer legal routes redirecting to /auth/login</t>
+          <t>Scheduled push v2</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>expose /legal, /auth/accept-terms, /api/consents as public paths in middleware — done 2026-04-18: middleware allow-list extended, verified on tenu.world production in incognito, all six legal pages render without auth. Commit via PR fix/public-legal-routes merged to main. Pre-contractual disclosure (art. L221-5 Code de la conso) now reachable as required for Stripe/App Store review.</t>
+          <t>replace Gmail create_draft with Brevo direct send — done 2026-04-19: new SKILL.md at scripts/scheduled-tasks/tenu-daily-push.md, brevo.env.example alongside. Telegram path unchanged. MH installs + adds BREVO_API_KEY — see MH line below.</t>
         </is>
       </c>
     </row>
@@ -4574,12 +4468,12 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Fix /stories/* and /features/* redirecting to /auth/login</t>
+          <t>Fix footer legal routes redirecting to /auth/login</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: added "/stories" and "/features" to publicPaths in src/middleware.ts. Same isPublicPath startsWith match pattern as the /legal fix; single entry per parent covers all nested routes. Stories and features now reachable without auth as marketing/content surface.</t>
+          <t>expose /legal, /auth/accept-terms, /api/consents as public paths in middleware — done 2026-04-18: middleware allow-list extended, verified on tenu.world production in incognito, all six legal pages render without auth. Commit via PR fix/public-legal-routes merged to main. Pre-contractual disclosure (art. L221-5 Code de la conso) now reachable as required for Stripe/App Store review.</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4500,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -4616,12 +4510,12 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Use-case content system</t>
+          <t>Fix /stories/* and /features/* redirecting to /auth/login</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>manifest + /stories index + cross-link strip + homepage dual-card — done 2026-04-18: src/lib/stories.ts (single source of truth, Story type, 4 helpers), src/components/stories/OtherCases.tsx (bilingual cross-link strip), src/app/stories/page.tsx (index with cautionary populated, success placeholder awaiting 11 May cohort), homepage example section refactored from single Suzi hook to manifest-driven dual-card grid with "See all cases →" link, Suzi + Samir pages thread OtherCases before footer, example block in en/fr/zh/ar/ur dictionaries refactored to label/heading/intro/seeAll/disclaimer. Adding a new case is now one append to stories.ts + one new /stories/&lt;slug&gt;/page.tsx.</t>
+          <t>done 2026-04-18: added "/stories" and "/features" to publicPaths in src/middleware.ts. Same isPublicPath startsWith match pattern as the /legal fix; single entry per parent covers all nested routes. Stories and features now reachable without auth as marketing/content surface.</t>
         </is>
       </c>
     </row>
@@ -4643,27 +4537,27 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Telegram one-time setup</t>
+          <t>Use-case content system</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>create bot via @BotFather, send token + chat_id — done 2026-04-18: bot created, token + chat_id set in .env.local and Vercel env (per Dr Mubashir)</t>
+          <t>manifest + /stories index + cross-link strip + homepage dual-card — done 2026-04-18: src/lib/stories.ts (single source of truth, Story type, 4 helpers), src/components/stories/OtherCases.tsx (bilingual cross-link strip), src/app/stories/page.tsx (index with cautionary populated, success placeholder awaiting 11 May cohort), homepage example section refactored from single Suzi hook to manifest-driven dual-card grid with "See all cases →" link, Suzi + Samir pages thread OtherCases before footer, example block in en/fr/zh/ar/ur dictionaries refactored to label/heading/intro/seeAll/disclaimer. Adding a new case is now one append to stories.ts + one new /stories/&lt;slug&gt;/page.tsx.</t>
         </is>
       </c>
     </row>
@@ -4700,12 +4594,12 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Paste ANTHROPIC_API_KEY into .env.local + Vercel project env</t>
+          <t>Telegram one-time setup</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
+          <t>create bot via @BotFather, send token + chat_id — done 2026-04-18: bot created, token + chat_id set in .env.local and Vercel env (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4636,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Paste BREVO_API_KEY into .env.local + Vercel project env</t>
+          <t>Paste ANTHROPIC_API_KEY into .env.local + Vercel project env</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -4769,7 +4663,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -4779,17 +4673,17 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>SOT consolidation</t>
+          <t>Paste BREVO_API_KEY into .env.local + Vercel project env</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>fix CLAUDE.md project path, refresh CLAUDE-CONTEXT.md to current React/in-code stack, replace stale-clone CLAUDE.md + CLAUDE-CONTEXT.md with redirect stubs — done 2026-04-19: SOT CLAUDE.md now declares `/Users/mmh/Documents/Claude/Projects/Tenu.World/` as canonical at the top, project structure block rewritten to match real layout (no nested `app/` wrapper, lists ios/, android/, mobile/, resources/, supabase/, scripts/). SOT CLAUDE-CONTEXT.md fully refreshed: dropped Webflow/Make.com/Tally/Airtable/Asana/Placid references, added pricing matrix, in-code pipeline, build timeline through 11 May, brand SOT pointers. Stale clone at `/Users/mmh/Documents/Global Apex/Tenu/` now has redirect-only CLAUDE.md + CLAUDE-CONTEXT.md so any agent invoked from that path bounces immediately.</t>
+          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4705,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -4821,17 +4715,17 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
+          <t>SOT consolidation</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>`client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json`, the same with " (1)" suffix, and `stripe_backup_code.txt`. All three are sitting in plaintext in a Documents folder (iCloud-syncable, Time-Machine-backupable). Move to `~/.secrets/` or 1Password, then `rm` from disk. **Do NOT git commit them anywhere.** — done 2026-05-03: stripe_backup_code.txt contents migrated to 1Password as Secure Note "Stripe 2FA backup codes — Global Apex NET" (per Dr Mubashir). Two client_secret JSON files deleted (burned credentials, no preservation needed — Cloud project shutdown will close the trust loop). All three files removed from disk via `rm -rf` on parent folder. Verify by inspection: `/Users/mmh/Documents/Global Apex/Tenu/` no longer exists.</t>
+          <t>fix CLAUDE.md project path, refresh CLAUDE-CONTEXT.md to current React/in-code stack, replace stale-clone CLAUDE.md + CLAUDE-CONTEXT.md with redirect stubs — done 2026-04-19: SOT CLAUDE.md now declares `/Users/mmh/Documents/Claude/Projects/Tenu.World/` as canonical at the top, project structure block rewritten to match real layout (no nested `app/` wrapper, lists ios/, android/, mobile/, resources/, supabase/, scripts/). SOT CLAUDE-CONTEXT.md fully refreshed: dropped Webflow/Make.com/Tally/Airtable/Asana/Placid references, added pricing matrix, in-code pipeline, build timeline through 11 May, brand SOT pointers. Stale clone at `/Users/mmh/Documents/Global Apex/Tenu/` now has redirect-only CLAUDE.md + CLAUDE-CONTEXT.md so any agent invoked from that path bounces immediately.</t>
         </is>
       </c>
     </row>
@@ -4853,27 +4747,27 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
+          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>`01-Legal-Checklist.md` (review + dedupe against SOT 05-Legal-Compliance content first), `etat-des-lieux.pdf`, `etat-des-lieux-meuble.pdf`, `modele-etat-des-lieux T2-T3.pdf` into SOT `docs/reference/etat-des-lieux/` (or wherever Dr Mubashir prefers). Delete from stale clone after move — done 2026-05-03: audit found `01-Legal-Checklist.md` already byte-identical between stale and SOT (no migration needed); 3 PDFs in stale folder, two of which (`modele-etat-des-lieux.pdf` and `modele-etat-des-lieux T2-T3.pdf`) are byte-identical (sha 4b9fed2e0c14...) — only one carried over. Final SOT state: `docs/reference/etat-des-lieux/etat-des-lieux-meuble.pdf` (sha 6e1e3f5acd83...) + `docs/reference/etat-des-lieux/modele-etat-des-lieux T2-T3.pdf` (sha 4b9fed2e0c14...). Note: original task line referenced `etat-des-lieux.pdf` which never existed in stale clone — actual filenames discovered during audit.</t>
+          <t>`client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json`, the same with " (1)" suffix, and `stripe_backup_code.txt`. All three are sitting in plaintext in a Documents folder (iCloud-syncable, Time-Machine-backupable). Move to `~/.secrets/` or 1Password, then `rm` from disk. **Do NOT git commit them anywhere.** — done 2026-05-03: stripe_backup_code.txt contents migrated to 1Password as Secure Note "Stripe 2FA backup codes — Global Apex NET" (per Dr Mubashir). Two client_secret JSON files deleted (burned credentials, no preservation needed — Cloud project shutdown will close the trust loop). All three files removed from disk via `rm -rf` on parent folder. Verify by inspection: `/Users/mmh/Documents/Global Apex/Tenu/` no longer exists.</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4789,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -4905,17 +4799,17 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
+          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>archive to `~/Archive/` or `rm -rf`. Sandbox cannot delete the parent folder. — done 2026-05-03 — decision: `rm -rf`, no archive. Audit grounds: (a) 533 MB of the 538 MB total was regenerable node_modules; (b) git remote pointed at the same `malikmubashir/tenu-world.git` with HEAD at `c3614ef` (the original April 3 scaffold commit, redundant with everything in main since); (c) all 10 doc files were either byte-identical to SOT or differed only in COI-scrubbed wording (HEC GEMM / MHF references that SOT correctly removed per role-separation policy in CLAUDE.md); (d) parent had `com.apple.macl` and `com.apple.provenance` xattrs only — NOT iCloud-synced, so no recurring sync source to sever; (e) Time Machine retains snapshots back to April 3 if recovery ever needed. Final stale-clone removal verified: parent path no longer exists. Container `/Users/mmh/Documents/Global Apex/` retained for other uses. Companion finding: the dedup chaos cleaned in the prior task was therefore NOT from active iCloud sync — likely a one-time merge incident from a multi-machine sync, not ongoing. Worth knowing for future repo-cleanup heuristics.</t>
+          <t>`01-Legal-Checklist.md` (review + dedupe against SOT 05-Legal-Compliance content first), `etat-des-lieux.pdf`, `etat-des-lieux-meuble.pdf`, `modele-etat-des-lieux T2-T3.pdf` into SOT `docs/reference/etat-des-lieux/` (or wherever Dr Mubashir prefers). Delete from stale clone after move — done 2026-05-03: audit found `01-Legal-Checklist.md` already byte-identical between stale and SOT (no migration needed); 3 PDFs in stale folder, two of which (`modele-etat-des-lieux.pdf` and `modele-etat-des-lieux T2-T3.pdf`) are byte-identical (sha 4b9fed2e0c14...) — only one carried over. Final SOT state: `docs/reference/etat-des-lieux/etat-des-lieux-meuble.pdf` (sha 6e1e3f5acd83...) + `docs/reference/etat-des-lieux/modele-etat-des-lieux T2-T3.pdf` (sha 4b9fed2e0c14...). Note: original task line referenced `etat-des-lieux.pdf` which never existed in stale clone — actual filenames discovered during audit.</t>
         </is>
       </c>
     </row>
@@ -4942,22 +4836,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Rotate R2_ACCESS_KEY_ID + R2_SECRET_ACCESS_KEY</t>
+          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Cloudflare → R2 → Manage API tokens → new token scoped to tenu-evidence bucket (Object Read/Write only). Paste both into Vercel env, tick Sensitive, redeploy. Smoke: hit /api/mobile/upload-intent and upload a test photo. Then revoke old token in Cloudflare. Existing presigned URLs signed with old key keep working until expiry — done 2026-05-03 (per Dr Mubashir, post-holiday). CC post-rotation E2E smoke owed (line below).</t>
+          <t>archive to `~/Archive/` or `rm -rf`. Sandbox cannot delete the parent folder. — done 2026-05-03 — decision: `rm -rf`, no archive. Audit grounds: (a) 533 MB of the 538 MB total was regenerable node_modules; (b) git remote pointed at the same `malikmubashir/tenu-world.git` with HEAD at `c3614ef` (the original April 3 scaffold commit, redundant with everything in main since); (c) all 10 doc files were either byte-identical to SOT or differed only in COI-scrubbed wording (HEC GEMM / MHF references that SOT correctly removed per role-separation policy in CLAUDE.md); (d) parent had `com.apple.macl` and `com.apple.provenance` xattrs only — NOT iCloud-synced, so no recurring sync source to sever; (e) Time Machine retains snapshots back to April 3 if recovery ever needed. Final stale-clone removal verified: parent path no longer exists. Container `/Users/mmh/Documents/Global Apex/` retained for other uses. Companion finding: the dedup chaos cleaned in the prior task was therefore NOT from active iCloud sync — likely a one-time merge incident from a multi-machine sync, not ongoing. Worth knowing for future repo-cleanup heuristics.</t>
         </is>
       </c>
     </row>
@@ -4994,12 +4888,12 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Rotate STRIPE_WEBHOOK_SECRET</t>
+          <t>Rotate R2_ACCESS_KEY_ID + R2_SECRET_ACCESS_KEY</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Stripe → Developers → Webhooks → endpoint → Roll secret with 24h grace. Paste new into Vercel STRIPE_WEBHOOK_SECRET, tick Sensitive, redeploy. Smoke: `stripe trigger checkout.session.completed` and confirm /api/webhooks/stripe returns 200 in Vercel function logs. Old secret expires automatically at end of grace — done 2026-05-03 (per Dr Mubashir).</t>
+          <t>Cloudflare → R2 → Manage API tokens → new token scoped to tenu-evidence bucket (Object Read/Write only). Paste both into Vercel env, tick Sensitive, redeploy. Smoke: hit /api/mobile/upload-intent and upload a test photo. Then revoke old token in Cloudflare. Existing presigned URLs signed with old key keep working until expiry — done 2026-05-03 (per Dr Mubashir, post-holiday). CC post-rotation E2E smoke owed (line below).</t>
         </is>
       </c>
     </row>
@@ -5036,12 +4930,12 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Rotate SUPABASE_SERVICE_ROLE_KEY AND NEXT_PUBLIC_SUPABASE_ANON_KEY together</t>
+          <t>Rotate STRIPE_WEBHOOK_SECRET</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Supabase → Project Settings → API → JWT Keys → Generate new JWT secret (regenerates both keys, both are JWTs signed by the same secret). Update both values in Vercel in the same save, tick Sensitive on service_role (anon stays public but encrypt-at-rest regardless), redeploy. All pre-rotation sessions invalidated (pre-launch, so non-event). Smoke: incognito magic-link signup → /app-home load → photo upload row insert — done 2026-05-03 (per Dr Mubashir).</t>
+          <t>Stripe → Developers → Webhooks → endpoint → Roll secret with 24h grace. Paste new into Vercel STRIPE_WEBHOOK_SECRET, tick Sensitive, redeploy. Smoke: `stripe trigger checkout.session.completed` and confirm /api/webhooks/stripe returns 200 in Vercel function logs. Old secret expires automatically at end of grace — done 2026-05-03 (per Dr Mubashir).</t>
         </is>
       </c>
     </row>
@@ -5053,7 +4947,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -5063,7 +4957,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -5078,12 +4972,12 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
+          <t>Rotate SUPABASE_SERVICE_ROLE_KEY AND NEXT_PUBLIC_SUPABASE_ANON_KEY together</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
+          <t>Supabase → Project Settings → API → JWT Keys → Generate new JWT secret (regenerates both keys, both are JWTs signed by the same secret). Update both values in Vercel in the same save, tick Sensitive on service_role (anon stays public but encrypt-at-rest regardless), redeploy. All pre-rotation sessions invalidated (pre-launch, so non-event). Smoke: incognito magic-link signup → /app-home load → photo upload row insert — done 2026-05-03 (per Dr Mubashir).</t>
         </is>
       </c>
     </row>
@@ -5115,17 +5009,17 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
+          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
+          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5056,12 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
+          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
+          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
         </is>
       </c>
     </row>
@@ -5199,17 +5093,17 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Brevo transactional email leg</t>
+          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
+          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
         </is>
       </c>
     </row>
@@ -5231,27 +5125,27 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Delete iCloud dedup files on Mac</t>
+          <t>Brevo transactional email leg</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run. — done 2026-05-03: real damage was 2.7× larger than originally scoped. Total cleaned: 113 dedup files (109 src/app metadata route dedups across icon/apple-icon/opengraph-image/robots/sitemap × 21-22 each, 3 in scripts/, 1 in docs/paperclip-briefs/) + 121 empty paren-numbered directories under src/app/ + 4 space-numbered directories under src/app/auth/ (accept-terms 2, callback 2, callback 3, login 2 — verified to be older stale snapshots predating the i18n + signup-flow fixes, no imports, originals intact) + 2 i18n dictionary dedups (ar 2.json, zh 2.json) = grand total 240 entries. Verified: `find` returns 0 dedups repo-wide; `npm run build` exit 0 with all routes (icon, opengraph-image, robots.txt, sitemap.xml, manifest.webmanifest, /legal/*, /auth/*, /inspection/*, /features/*) compiled cleanly; Next.js convention parents (icon.tsx, apple-icon.tsx, opengraph-image.tsx, robots.ts, sitemap.ts) all present. Root cause documented: dual mirroring by iCloud (parens-N suffix) AND OneDrive (space-N suffix) on the old `~/Documents/Claude/Projects/Tenu.World/` path. Repo now lives at `~/Code/Tenu.World/` (no iCloud xattrs). Confirm OneDrive isn't mirroring `~/Code/` either to prevent recurrence.</t>
+          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
         </is>
       </c>
     </row>
@@ -5273,27 +5167,27 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Capacitor 7 scaffold</t>
+          <t>Delete iCloud dedup files on Mac</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
+          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run. — done 2026-05-03: real damage was 2.7× larger than originally scoped. Total cleaned: 113 dedup files (109 src/app metadata route dedups across icon/apple-icon/opengraph-image/robots/sitemap × 21-22 each, 3 in scripts/, 1 in docs/paperclip-briefs/) + 121 empty paren-numbered directories under src/app/ + 4 space-numbered directories under src/app/auth/ (accept-terms 2, callback 2, callback 3, login 2 — verified to be older stale snapshots predating the i18n + signup-flow fixes, no imports, originals intact) + 2 i18n dictionary dedups (ar 2.json, zh 2.json) = grand total 240 entries. Verified: `find` returns 0 dedups repo-wide; `npm run build` exit 0 with all routes (icon, opengraph-image, robots.txt, sitemap.xml, manifest.webmanifest, /legal/*, /auth/*, /inspection/*, /features/*) compiled cleanly; Next.js convention parents (icon.tsx, apple-icon.tsx, opengraph-image.tsx, robots.ts, sitemap.ts) all present. Root cause documented: dual mirroring by iCloud (parens-N suffix) AND OneDrive (space-N suffix) on the old `~/Documents/Claude/Projects/Tenu.World/` path. Repo now lives at `~/Code/Tenu.World/` (no iCloud xattrs). Confirm OneDrive isn't mirroring `~/Code/` either to prevent recurrence.</t>
         </is>
       </c>
     </row>
@@ -5330,12 +5224,12 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+          <t>Capacitor 7 scaffold</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
+          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
         </is>
       </c>
     </row>
@@ -5357,7 +5251,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -5367,17 +5261,17 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
+          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5293,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -5409,17 +5303,17 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>MB-01</t>
+          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
+          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -5456,12 +5350,12 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>MB-03</t>
+          <t>MB-01</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
+          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
         </is>
       </c>
     </row>
@@ -5498,12 +5392,12 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>MB-05</t>
+          <t>MB-03</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
+          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5434,12 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>MB-08</t>
+          <t>MB-05</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
+          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
         </is>
       </c>
     </row>
@@ -5582,12 +5476,12 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>MB-09</t>
+          <t>MB-08</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
+          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5493,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -5619,17 +5513,17 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>App icon set</t>
+          <t>MB-09</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
+          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
         </is>
       </c>
     </row>
@@ -5661,17 +5555,17 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>Splash screens per density, status bar theming, safe-area insets</t>
+          <t>App icon set</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
+          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
         </is>
       </c>
     </row>
@@ -5703,17 +5597,17 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+          <t>Splash screens per density, status bar theming, safe-area insets</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
         </is>
       </c>
     </row>
@@ -5750,17 +5644,185 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
+          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>T-034</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
           <t>Store listing copy drafted in FR + EN</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>description, keywords, support URL, privacy URL — done 2026-04-18 (ahead of schedule): MB-07 shipped docs/store-listings/{ios-fr,ios-en,play-fr,play-en}.md. Professional services register throughout (no buzzwords, no guaranteed-outcome claims), character counts validated inline, Stripe reader-app classification explicitly argued in reviewer notes, data safety section filled for Play form. Awaits MH (nights) review + edit before submission. Commit 50db60f.</t>
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>T-035</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>LAUNCH WEEK (8-11 May)</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Bug sweep on inspection UI</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>camera retries, upload resume, offline queue — done 2026-05-06: EX-6. camera.ts: retry up to 3× on NotReadableError (500ms/1s backoff). uploadQueue.ts: StoredIntent interface + storeIntent/loadIntent/clearIntent (4.5-min TTL cache against R2 presigned URL). db.ts: v3 migration adds intent_url/key/headers/fetched_at columns to upload_queue. syncEngine.ts: uploadPhoto reuses cached intent on retry; startSyncLoop adds Capacitor Network.addListener + window.addEventListener("online") for reactive drain on reconnect; returns stop() that cancels both. AuthGate.tsx: wires startSyncLoop on native session confirmation. Commits 2bf561b (camera+sync) + earlier intent-cache commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>T-036</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>LAUNCH WEEK (8-11 May)</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Native build bridge doc for iOS TestFlight + Android Play internal track</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-05-06: EX-7. docs/12-Native-Build-Bridge-2026-05-12.md: 12 sections, all commands copy-pasteable with pinned versions, expected/red-flag per step, failure modes table, timeline 2026-05-11 to 2026-06-30. Commit 55892bf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>T-037</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>LAUNCH WEEK (8-11 May)</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Strip App Store/Play Store badges from hero, add 25 May mobile note, create reviewer-notes.md</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-05-06: EX-8. page.tsx: replaced SVG badge block with single &lt;p&gt; {app.heading}. All 5 dictionaries: stripped appStore/playStore/comingSoon/subtext, heading → "Apps mobiles natives à partir du 25 mai". docs/store-listings/reviewer-notes.md: test account, permission table, Reader App IAP declaration, AI disclosure, data handling. Commit f5ca79f.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H34"/>
+  <autoFilter ref="A1:H38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -105,10 +105,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -768,7 +768,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Update store-listing copy + welcome email + landing page to reflect web-first launch + native binaries follow</t>
+          <t>Personalise + send the FR avocat brief (review draft, fill recipient name + cabinet, send by email)</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Personalise + send the FR avocat brief (review draft, fill recipient name + cabinet, send by email)</t>
+          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
+          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
+          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
+          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
+          <t>Google Play Console developer account, USD 25 one-time</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
+          <t>Audit hidden env vars</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Audit hidden env vars</t>
+          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
+          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -998,19 +998,19 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
+          <t>Post-rotation smoke test verification</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Post-rotation smoke test verification</t>
+          <t>Google Workspace subscription on `tenu.world`</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Native Build Bridge plan</t>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Google Workspace subscription on `tenu.world`</t>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
+          <t>Before 11 May</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Before 11 May</t>
+          <t>Decide Apple IAP stance</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>Médiateur de la consommation signed</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
         </is>
       </c>
     </row>
@@ -1262,14 +1262,14 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation signed</t>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -1284,14 +1284,14 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+          <t>PDF generation leg</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+          <t>T-103-core pipeline tests</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
+          <t>F&amp;F invite list</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -1460,14 +1460,14 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>T-103-core pipeline tests</t>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -1504,14 +1504,14 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -1526,14 +1526,14 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -1548,14 +1548,14 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
         </is>
       </c>
     </row>
@@ -1614,14 +1614,14 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -1636,14 +1636,14 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -1679,50 +1679,6 @@
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
         </is>
@@ -1739,7 +1695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1802,17 +1758,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>DECISION 2026-05-03 — Launch path: Option B (web-only on 11 May)</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -1825,14 +1781,14 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>Update store-listing copy + welcome email + landing page to reflect web-first launch + native binaries follow</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>opened 2026-05-03.</t>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Personalise + send the FR avocat brief (review draft, fill recipient name + cabinet, send by email)</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>depends on CC line above.</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1800,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>DECISION 2026-05-03 — Launch path: Option B (web-only on 11 May)</t>
+          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -1854,7 +1810,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -1864,17 +1820,17 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>Native Build Bridge plan</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>write docs/12-Native-Build-Bridge-2026-05-12.md mapping the 11-25 May path: cap add ios + cap add android dependencies, Xcode + Android Studio prerequisites, TestFlight + Play internal track submission, screenshots backlog, App Store reviewer notes refresh — opened 2026-05-03.</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>depends on CC line above.</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1842,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -1901,22 +1857,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>Personalise + send the FR avocat brief (review draft, fill recipient name + cabinet, send by email)</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>depends on CC line above.</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Install scheduled-push v2</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>copy scripts/scheduled-tasks/tenu-daily-push.md into ~/Documents/Claude/Scheduled/tenu-daily-push/SKILL.md and drop BREVO_API_KEY into .secrets/brevo.env</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1884,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1951,16 +1907,12 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>depends on CC line above.</t>
-        </is>
-      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1985,24 +1937,20 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Install scheduled-push v2</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>copy scripts/scheduled-tasks/tenu-daily-push.md into ~/Documents/Claude/Scheduled/tenu-daily-push/SKILL.md and drop BREVO_API_KEY into .secrets/brevo.env</t>
-        </is>
-      </c>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2035,12 +1983,12 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2053,9 +2001,9 @@
           <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -2070,15 +2018,19 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr"/>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>submitted 2026-05-03, documents sent to Apple, awaiting verification (per Dr Mubashir). Apple identity check typically 2-5 business days; D-U-N-S verification gates the review. Track unblocking of Xcode signing / TestFlight upload off this line.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2111,12 +2063,12 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Google Play Console developer account, USD 25 one-time</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2129,9 +2081,9 @@
           <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -2146,19 +2098,15 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>submitted 2026-05-03, documents sent to Apple, awaiting verification (per Dr Mubashir). Apple identity check typically 2-5 business days; D-U-N-S verification gates the review. Track unblocking of Xcode signing / TestFlight upload off this line.</t>
-        </is>
-      </c>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2188,15 +2136,19 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr"/>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Google Workspace subscription on `tenu.world`</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>create `ops@tenu.world` (owner) + `support@tenu.world` + `dpo@tenu.world` (aliases acceptable)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2226,15 +2178,15 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr"/>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -2267,16 +2219,12 @@
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Google Workspace subscription on `tenu.world`</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>create `ops@tenu.world` (owner) + `support@tenu.world` + `dpo@tenu.world` (aliases acceptable)</t>
-        </is>
-      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -2309,12 +2257,12 @@
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2347,12 +2295,12 @@
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2385,12 +2333,12 @@
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -2420,15 +2368,19 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr"/>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>expect no 403 org_internal, consent screen shows "Tenu" with `support@tenu.world`</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2458,15 +2410,19 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr"/>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>do not archive, the secret is burned</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2499,14 +2455,14 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>expect no 403 org_internal, consent screen shows "Tenu" with `support@tenu.world`</t>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>revokes the leaked secret at source even if a copy is still cached somewhere</t>
         </is>
       </c>
     </row>
@@ -2538,17 +2494,17 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>do not archive, the secret is burned</t>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Before 11 May</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>publish OAuth consent screen Testing → Production (requires domain verified + privacy URL + terms URL live at tenu.world/legal/privacy + /legal/terms)</t>
         </is>
       </c>
     </row>
@@ -2580,17 +2536,17 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>revokes the leaked secret at source even if a copy is still cached somewhere</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Audit hidden env vars</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>scroll full Vercel env var list below the fold, confirm ANTHROPIC_API_KEY + BREVO_API_KEY + TELEGRAM_BOT_TOKEN + any other secret either shows Need To Rotate (rotate it) or was created Sensitive from day one (leave alone). If any non-public secret is unflagged and NOT marked Sensitive, treat as exposed and rotate</t>
         </is>
       </c>
     </row>
@@ -2622,17 +2578,17 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>Before 11 May</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>publish OAuth consent screen Testing → Production (requires domain verified + privacy URL + terms URL live at tenu.world/legal/privacy + /legal/terms)</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Google Cloud Console → APIs &amp; Services → Credentials → restrict to HTTP referrers `*.tenu.world` + `localhost:*` + enable only Maps JavaScript + Places API. Public by design, not flagged by Vercel, but unrestricted = scraping risk against Global Apex billing</t>
         </is>
       </c>
     </row>
@@ -2667,14 +2623,14 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Audit hidden env vars</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>scroll full Vercel env var list below the fold, confirm ANTHROPIC_API_KEY + BREVO_API_KEY + TELEGRAM_BOT_TOKEN + any other secret either shows Need To Rotate (rotate it) or was created Sensitive from day one (leave alone). If any non-public secret is unflagged and NOT marked Sensitive, treat as exposed and rotate</t>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>hardening pass, single biggest structural lesson from this incident. Anything that isn't a NEXT_PUBLIC_* or a non-secret identifier (R2_ACCOUNT_ID, R2_BUCKET_NAME) should be Sensitive</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2652,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2709,14 +2665,14 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>Google Cloud Console → APIs &amp; Services → Credentials → restrict to HTTP referrers `*.tenu.world` + `localhost:*` + enable only Maps JavaScript + Places API. Public by design, not flagged by Vercel, but unrestricted = scraping risk against Global Apex billing</t>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Post-rotation smoke test verification</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green</t>
         </is>
       </c>
     </row>
@@ -2728,17 +2684,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2748,17 +2704,17 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>hardening pass, single biggest structural lesson from this incident. Anything that isn't a NEXT_PUBLIC_* or a non-secret identifier (R2_ACCOUNT_ID, R2_BUCKET_NAME) should be Sensitive</t>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2726,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -2790,17 +2746,17 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>Post-rotation smoke test verification</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>PDF generation leg</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
         </is>
       </c>
     </row>
@@ -2815,14 +2771,14 @@
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2832,19 +2788,15 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
-        </is>
-      </c>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2864,7 +2816,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2874,19 +2826,15 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>PDF generation leg</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
-        </is>
-      </c>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -2919,12 +2867,12 @@
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -2954,15 +2902,15 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr"/>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -2992,15 +2940,15 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr"/>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3030,15 +2978,15 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr"/>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3068,15 +3016,15 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr"/>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3096,25 +3044,25 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr"/>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3134,7 +3082,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -3144,15 +3092,15 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr"/>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3177,20 +3125,20 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
-        </is>
-      </c>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3210,7 +3158,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -3220,15 +3168,15 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr"/>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3238,7 +3186,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -3258,15 +3206,15 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr"/>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3276,7 +3224,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -3299,12 +3247,16 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr"/>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>re-dated 2026-05-03: depends on CC web-only listing revision (line in DECISION 2026-05-03 section).</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -3324,7 +3276,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3334,15 +3286,19 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr"/>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Decide Apple IAP stance</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>physical service argument documented — re-dated 2026-05-03: needs to land before App Store reviewer notes lock.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3352,7 +3308,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -3362,7 +3318,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -3372,19 +3328,15 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>re-dated 2026-05-03: depends on CC web-only listing revision (line in DECISION 2026-05-03 section).</t>
-        </is>
-      </c>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3394,7 +3346,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -3404,7 +3356,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -3414,17 +3366,17 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>Decide Apple IAP stance</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>physical service argument documented — re-dated 2026-05-03: needs to land before App Store reviewer notes lock.</t>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>Magic-link auth working inside app</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>email link opens app, session persists</t>
         </is>
       </c>
     </row>
@@ -3451,20 +3403,20 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="inlineStr"/>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3494,17 +3446,17 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>Magic-link auth working inside app</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>email link opens app, session persists</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>T-103-core pipeline tests</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
         </is>
       </c>
     </row>
@@ -3531,20 +3483,20 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -3574,19 +3526,15 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>T-103-core pipeline tests</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
-        </is>
-      </c>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -3606,7 +3554,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -3616,15 +3564,19 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr"/>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Médiateur de la consommation signed</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>MEDICYS OR SMCE OR AME Conso</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -3644,7 +3596,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -3654,15 +3606,15 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="inlineStr"/>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -3692,19 +3644,15 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>Médiateur de la consommation signed</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>MEDICYS OR SMCE OR AME Conso</t>
-        </is>
-      </c>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -3734,15 +3682,15 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr"/>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -3772,15 +3720,19 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr"/>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>F&amp;F invite list</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>8 names, email, jurisdiction, case type</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -3813,12 +3765,12 @@
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr"/>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -3828,7 +3780,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -3838,7 +3790,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -3848,19 +3800,15 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>F&amp;F invite list</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>8 names, email, jurisdiction, case type</t>
-        </is>
-      </c>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -3870,7 +3818,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -3890,15 +3838,15 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="inlineStr"/>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -3918,7 +3866,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -3928,15 +3876,15 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr"/>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -3946,7 +3894,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -3956,25 +3904,25 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr"/>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Full T-103 suite</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -3984,7 +3932,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -3994,25 +3942,25 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr"/>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr"/>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>14-day outcome survey cron</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Brevo trigger + Supabase write-back</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -4041,14 +3989,14 @@
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr"/>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>Full T-103 suite</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>Additional UI locales</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
         </is>
       </c>
     </row>
@@ -4075,18 +4023,18 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr"/>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>14-day outcome survey cron</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>Brevo trigger + Supabase write-back</t>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>i18n audit phase 2</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
         </is>
       </c>
     </row>
@@ -4117,91 +4065,15 @@
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr"/>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>Additional UI locales</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>T-060</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr"/>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>i18n audit phase 2</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>T-061</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr"/>
-      <c r="G62" s="7" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>App Store + Play production updates with post-launch fixes</t>
         </is>
       </c>
-      <c r="H62" s="7" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H62"/>
+  <autoFilter ref="A1:H60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4212,7 +4084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4290,7 +4162,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -4298,14 +4170,14 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>keep their content verbatim, only re-section + re-date so the launch checklist stops bleeding red on items that were never blocking 11 May web-only — opened 2026-05-03. — done 2026-05-06: re-dating applied via runbook-2026-05-06 (TE-1..TE-7).</t>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Update store-listing copy + welcome email + landing page to reflect web-first launch + native binaries follow</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-05-06: EX-8. Hero badge block stripped, all 5 dictionaries reduced to single "25 mai" heading, docs/store-listings/reviewer-notes.md created. Commit f5ca79f.</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4189,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
+          <t>DECISION 2026-05-03 — Launch path: Option B (web-only on 11 May)</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -4337,17 +4209,17 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>Draft FR avocat fixed-fee review brief in French</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>`outreach/legal/letter-avocat-droit-immobilier-FR.md`. Scope: pre-contractual disclosure (art. L221-5), CGU, Privacy/RGPD, DPA, dispute-letter LRAR template, état-des-lieux verbiage. Budget €1,000-2,000 fixed-fee. Asks for sign-off date 2026-05-07. Includes one-page summary of Tenu, target user, jurisdiction. — done 2026-05-03: file written, recipient/cabinet bracketed, attachments list at end, notes for MH on cabinet leads + rétractation defence.</t>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Native Build Bridge plan</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>write docs/12-Native-Build-Bridge-2026-05-12.md mapping the 11-25 May path: cap add ios + cap add android dependencies, Xcode + Android Studio prerequisites, TestFlight + Play internal track submission, screenshots backlog, App Store reviewer notes refresh — done 2026-05-06: EX-7. 12-section doc, all commands copy-pasteable, failure modes table, timeline 2026-05-11 to 2026-06-30. Commit 55892bf.</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4231,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
+          <t>DECISION 2026-05-03 — Launch path: Option B (web-only on 11 May)</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -4374,22 +4246,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>Draft UK housing solicitor TDS/DPS brief in English</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>`outreach/legal/letter-uk-housing-solicitor-EN.md`. Scope: TDS/DPS/MyDeposits dispute-letter template review, UK Consumer Rights Act 2015 alignment, ICO/UK GDPR check on photo handling. Budget GBP 500-1,500 fixed-fee. Asks for sign-off date 2026-05-07. — done 2026-05-03: file written, recipient/firm bracketed, attachments list at end, notes for MH on solicitor sourcing + Legal Services Act 2007 reserved-activities check.</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>keep their content verbatim, only re-section + re-date so the launch checklist stops bleeding red on items that were never blocking 11 May web-only — opened 2026-05-03. — done 2026-05-06: re-dating applied via runbook-2026-05-06 (TE-1..TE-7).</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4273,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
+          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -4416,22 +4288,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Scheduled push v2</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>replace Gmail create_draft with Brevo direct send — done 2026-04-19: new SKILL.md at scripts/scheduled-tasks/tenu-daily-push.md, brevo.env.example alongside. Telegram path unchanged. MH installs + adds BREVO_API_KEY — see MH line below.</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Draft FR avocat fixed-fee review brief in French</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>`outreach/legal/letter-avocat-droit-immobilier-FR.md`. Scope: pre-contractual disclosure (art. L221-5), CGU, Privacy/RGPD, DPA, dispute-letter LRAR template, état-des-lieux verbiage. Budget €1,000-2,000 fixed-fee. Asks for sign-off date 2026-05-07. Includes one-page summary of Tenu, target user, jurisdiction. — done 2026-05-03: file written, recipient/cabinet bracketed, attachments list at end, notes for MH on cabinet leads + rétractation defence.</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4315,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
+          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -4463,17 +4335,17 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Fix footer legal routes redirecting to /auth/login</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>expose /legal, /auth/accept-terms, /api/consents as public paths in middleware — done 2026-04-18: middleware allow-list extended, verified on tenu.world production in incognito, all six legal pages render without auth. Commit via PR fix/public-legal-routes merged to main. Pre-contractual disclosure (art. L221-5 Code de la conso) now reachable as required for Stripe/App Store review.</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Draft UK housing solicitor TDS/DPS brief in English</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>`outreach/legal/letter-uk-housing-solicitor-EN.md`. Scope: TDS/DPS/MyDeposits dispute-letter template review, UK Consumer Rights Act 2015 alignment, ICO/UK GDPR check on photo handling. Budget GBP 500-1,500 fixed-fee. Asks for sign-off date 2026-05-07. — done 2026-05-03: file written, recipient/firm bracketed, attachments list at end, notes for MH on solicitor sourcing + Legal Services Act 2007 reserved-activities check.</t>
         </is>
       </c>
     </row>
@@ -4500,22 +4372,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Fix /stories/* and /features/* redirecting to /auth/login</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: added "/stories" and "/features" to publicPaths in src/middleware.ts. Same isPublicPath startsWith match pattern as the /legal fix; single entry per parent covers all nested routes. Stories and features now reachable without auth as marketing/content surface.</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Scheduled push v2</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>replace Gmail create_draft with Brevo direct send — done 2026-04-19: new SKILL.md at scripts/scheduled-tasks/tenu-daily-push.md, brevo.env.example alongside. Telegram path unchanged. MH installs + adds BREVO_API_KEY — see MH line below.</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4414,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -4550,14 +4422,14 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>Use-case content system</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>manifest + /stories index + cross-link strip + homepage dual-card — done 2026-04-18: src/lib/stories.ts (single source of truth, Story type, 4 helpers), src/components/stories/OtherCases.tsx (bilingual cross-link strip), src/app/stories/page.tsx (index with cautionary populated, success placeholder awaiting 11 May cohort), homepage example section refactored from single Suzi hook to manifest-driven dual-card grid with "See all cases →" link, Suzi + Samir pages thread OtherCases before footer, example block in en/fr/zh/ar/ur dictionaries refactored to label/heading/intro/seeAll/disclaimer. Adding a new case is now one append to stories.ts + one new /stories/&lt;slug&gt;/page.tsx.</t>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Fix footer legal routes redirecting to /auth/login</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>expose /legal, /auth/accept-terms, /api/consents as public paths in middleware — done 2026-04-18: middleware allow-list extended, verified on tenu.world production in incognito, all six legal pages render without auth. Commit via PR fix/public-legal-routes merged to main. Pre-contractual disclosure (art. L221-5 Code de la conso) now reachable as required for Stripe/App Store review.</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4451,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -4589,17 +4461,17 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>Telegram one-time setup</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>create bot via @BotFather, send token + chat_id — done 2026-04-18: bot created, token + chat_id set in .env.local and Vercel env (per Dr Mubashir)</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Fix /stories/* and /features/* redirecting to /auth/login</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: added "/stories" and "/features" to publicPaths in src/middleware.ts. Same isPublicPath startsWith match pattern as the /legal fix; single entry per parent covers all nested routes. Stories and features now reachable without auth as marketing/content surface.</t>
         </is>
       </c>
     </row>
@@ -4621,27 +4493,27 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>Paste ANTHROPIC_API_KEY into .env.local + Vercel project env</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Use-case content system</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>manifest + /stories index + cross-link strip + homepage dual-card — done 2026-04-18: src/lib/stories.ts (single source of truth, Story type, 4 helpers), src/components/stories/OtherCases.tsx (bilingual cross-link strip), src/app/stories/page.tsx (index with cautionary populated, success placeholder awaiting 11 May cohort), homepage example section refactored from single Suzi hook to manifest-driven dual-card grid with "See all cases →" link, Suzi + Samir pages thread OtherCases before footer, example block in en/fr/zh/ar/ur dictionaries refactored to label/heading/intro/seeAll/disclaimer. Adding a new case is now one append to stories.ts + one new /stories/&lt;slug&gt;/page.tsx.</t>
         </is>
       </c>
     </row>
@@ -4676,14 +4548,14 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>Paste BREVO_API_KEY into .env.local + Vercel project env</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Telegram one-time setup</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>create bot via @BotFather, send token + chat_id — done 2026-04-18: bot created, token + chat_id set in .env.local and Vercel env (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4577,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -4715,17 +4587,17 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>SOT consolidation</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>fix CLAUDE.md project path, refresh CLAUDE-CONTEXT.md to current React/in-code stack, replace stale-clone CLAUDE.md + CLAUDE-CONTEXT.md with redirect stubs — done 2026-04-19: SOT CLAUDE.md now declares `/Users/mmh/Documents/Claude/Projects/Tenu.World/` as canonical at the top, project structure block rewritten to match real layout (no nested `app/` wrapper, lists ios/, android/, mobile/, resources/, supabase/, scripts/). SOT CLAUDE-CONTEXT.md fully refreshed: dropped Webflow/Make.com/Tally/Airtable/Asana/Placid references, added pricing matrix, in-code pipeline, build timeline through 11 May, brand SOT pointers. Stale clone at `/Users/mmh/Documents/Global Apex/Tenu/` now has redirect-only CLAUDE.md + CLAUDE-CONTEXT.md so any agent invoked from that path bounces immediately.</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Paste ANTHROPIC_API_KEY into .env.local + Vercel project env</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -4757,17 +4629,17 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>`client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json`, the same with " (1)" suffix, and `stripe_backup_code.txt`. All three are sitting in plaintext in a Documents folder (iCloud-syncable, Time-Machine-backupable). Move to `~/.secrets/` or 1Password, then `rm` from disk. **Do NOT git commit them anywhere.** — done 2026-05-03: stripe_backup_code.txt contents migrated to 1Password as Secure Note "Stripe 2FA backup codes — Global Apex NET" (per Dr Mubashir). Two client_secret JSON files deleted (burned credentials, no preservation needed — Cloud project shutdown will close the trust loop). All three files removed from disk via `rm -rf` on parent folder. Verify by inspection: `/Users/mmh/Documents/Global Apex/Tenu/` no longer exists.</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Paste BREVO_API_KEY into .env.local + Vercel project env</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -4794,22 +4666,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>`01-Legal-Checklist.md` (review + dedupe against SOT 05-Legal-Compliance content first), `etat-des-lieux.pdf`, `etat-des-lieux-meuble.pdf`, `modele-etat-des-lieux T2-T3.pdf` into SOT `docs/reference/etat-des-lieux/` (or wherever Dr Mubashir prefers). Delete from stale clone after move — done 2026-05-03: audit found `01-Legal-Checklist.md` already byte-identical between stale and SOT (no migration needed); 3 PDFs in stale folder, two of which (`modele-etat-des-lieux.pdf` and `modele-etat-des-lieux T2-T3.pdf`) are byte-identical (sha 4b9fed2e0c14...) — only one carried over. Final SOT state: `docs/reference/etat-des-lieux/etat-des-lieux-meuble.pdf` (sha 6e1e3f5acd83...) + `docs/reference/etat-des-lieux/modele-etat-des-lieux T2-T3.pdf` (sha 4b9fed2e0c14...). Note: original task line referenced `etat-des-lieux.pdf` which never existed in stale clone — actual filenames discovered during audit.</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>SOT consolidation</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>fix CLAUDE.md project path, refresh CLAUDE-CONTEXT.md to current React/in-code stack, replace stale-clone CLAUDE.md + CLAUDE-CONTEXT.md with redirect stubs — done 2026-04-19: SOT CLAUDE.md now declares `/Users/mmh/Documents/Claude/Projects/Tenu.World/` as canonical at the top, project structure block rewritten to match real layout (no nested `app/` wrapper, lists ios/, android/, mobile/, resources/, supabase/, scripts/). SOT CLAUDE-CONTEXT.md fully refreshed: dropped Webflow/Make.com/Tally/Airtable/Asana/Placid references, added pricing matrix, in-code pipeline, build timeline through 11 May, brand SOT pointers. Stale clone at `/Users/mmh/Documents/Global Apex/Tenu/` now has redirect-only CLAUDE.md + CLAUDE-CONTEXT.md so any agent invoked from that path bounces immediately.</t>
         </is>
       </c>
     </row>
@@ -4836,22 +4708,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>archive to `~/Archive/` or `rm -rf`. Sandbox cannot delete the parent folder. — done 2026-05-03 — decision: `rm -rf`, no archive. Audit grounds: (a) 533 MB of the 538 MB total was regenerable node_modules; (b) git remote pointed at the same `malikmubashir/tenu-world.git` with HEAD at `c3614ef` (the original April 3 scaffold commit, redundant with everything in main since); (c) all 10 doc files were either byte-identical to SOT or differed only in COI-scrubbed wording (HEC GEMM / MHF references that SOT correctly removed per role-separation policy in CLAUDE.md); (d) parent had `com.apple.macl` and `com.apple.provenance` xattrs only — NOT iCloud-synced, so no recurring sync source to sever; (e) Time Machine retains snapshots back to April 3 if recovery ever needed. Final stale-clone removal verified: parent path no longer exists. Container `/Users/mmh/Documents/Global Apex/` retained for other uses. Companion finding: the dedup chaos cleaned in the prior task was therefore NOT from active iCloud sync — likely a one-time merge incident from a multi-machine sync, not ongoing. Worth knowing for future repo-cleanup heuristics.</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>`client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json`, the same with " (1)" suffix, and `stripe_backup_code.txt`. All three are sitting in plaintext in a Documents folder (iCloud-syncable, Time-Machine-backupable). Move to `~/.secrets/` or 1Password, then `rm` from disk. **Do NOT git commit them anywhere.** — done 2026-05-03: stripe_backup_code.txt contents migrated to 1Password as Secure Note "Stripe 2FA backup codes — Global Apex NET" (per Dr Mubashir). Two client_secret JSON files deleted (burned credentials, no preservation needed — Cloud project shutdown will close the trust loop). All three files removed from disk via `rm -rf` on parent folder. Verify by inspection: `/Users/mmh/Documents/Global Apex/Tenu/` no longer exists.</t>
         </is>
       </c>
     </row>
@@ -4873,12 +4745,12 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -4886,14 +4758,14 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Rotate R2_ACCESS_KEY_ID + R2_SECRET_ACCESS_KEY</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Cloudflare → R2 → Manage API tokens → new token scoped to tenu-evidence bucket (Object Read/Write only). Paste both into Vercel env, tick Sensitive, redeploy. Smoke: hit /api/mobile/upload-intent and upload a test photo. Then revoke old token in Cloudflare. Existing presigned URLs signed with old key keep working until expiry — done 2026-05-03 (per Dr Mubashir, post-holiday). CC post-rotation E2E smoke owed (line below).</t>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>`01-Legal-Checklist.md` (review + dedupe against SOT 05-Legal-Compliance content first), `etat-des-lieux.pdf`, `etat-des-lieux-meuble.pdf`, `modele-etat-des-lieux T2-T3.pdf` into SOT `docs/reference/etat-des-lieux/` (or wherever Dr Mubashir prefers). Delete from stale clone after move — done 2026-05-03: audit found `01-Legal-Checklist.md` already byte-identical between stale and SOT (no migration needed); 3 PDFs in stale folder, two of which (`modele-etat-des-lieux.pdf` and `modele-etat-des-lieux T2-T3.pdf`) are byte-identical (sha 4b9fed2e0c14...) — only one carried over. Final SOT state: `docs/reference/etat-des-lieux/etat-des-lieux-meuble.pdf` (sha 6e1e3f5acd83...) + `docs/reference/etat-des-lieux/modele-etat-des-lieux T2-T3.pdf` (sha 4b9fed2e0c14...). Note: original task line referenced `etat-des-lieux.pdf` which never existed in stale clone — actual filenames discovered during audit.</t>
         </is>
       </c>
     </row>
@@ -4920,22 +4792,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>Rotate STRIPE_WEBHOOK_SECRET</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Stripe → Developers → Webhooks → endpoint → Roll secret with 24h grace. Paste new into Vercel STRIPE_WEBHOOK_SECRET, tick Sensitive, redeploy. Smoke: `stripe trigger checkout.session.completed` and confirm /api/webhooks/stripe returns 200 in Vercel function logs. Old secret expires automatically at end of grace — done 2026-05-03 (per Dr Mubashir).</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>archive to `~/Archive/` or `rm -rf`. Sandbox cannot delete the parent folder. — done 2026-05-03 — decision: `rm -rf`, no archive. Audit grounds: (a) 533 MB of the 538 MB total was regenerable node_modules; (b) git remote pointed at the same `malikmubashir/tenu-world.git` with HEAD at `c3614ef` (the original April 3 scaffold commit, redundant with everything in main since); (c) all 10 doc files were either byte-identical to SOT or differed only in COI-scrubbed wording (HEC GEMM / MHF references that SOT correctly removed per role-separation policy in CLAUDE.md); (d) parent had `com.apple.macl` and `com.apple.provenance` xattrs only — NOT iCloud-synced, so no recurring sync source to sever; (e) Time Machine retains snapshots back to April 3 if recovery ever needed. Final stale-clone removal verified: parent path no longer exists. Container `/Users/mmh/Documents/Global Apex/` retained for other uses. Companion finding: the dedup chaos cleaned in the prior task was therefore NOT from active iCloud sync — likely a one-time merge incident from a multi-machine sync, not ongoing. Worth knowing for future repo-cleanup heuristics.</t>
         </is>
       </c>
     </row>
@@ -4970,14 +4842,14 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Rotate SUPABASE_SERVICE_ROLE_KEY AND NEXT_PUBLIC_SUPABASE_ANON_KEY together</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Supabase → Project Settings → API → JWT Keys → Generate new JWT secret (regenerates both keys, both are JWTs signed by the same secret). Update both values in Vercel in the same save, tick Sensitive on service_role (anon stays public but encrypt-at-rest regardless), redeploy. All pre-rotation sessions invalidated (pre-launch, so non-event). Smoke: incognito magic-link signup → /app-home load → photo upload row insert — done 2026-05-03 (per Dr Mubashir).</t>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Rotate R2_ACCESS_KEY_ID + R2_SECRET_ACCESS_KEY</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Cloudflare → R2 → Manage API tokens → new token scoped to tenu-evidence bucket (Object Read/Write only). Paste both into Vercel env, tick Sensitive, redeploy. Smoke: hit /api/mobile/upload-intent and upload a test photo. Then revoke old token in Cloudflare. Existing presigned URLs signed with old key keep working until expiry — done 2026-05-03 (per Dr Mubashir, post-holiday). CC post-rotation E2E smoke owed (line below).</t>
         </is>
       </c>
     </row>
@@ -4989,7 +4861,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -4999,7 +4871,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -5012,14 +4884,14 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Rotate STRIPE_WEBHOOK_SECRET</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Stripe → Developers → Webhooks → endpoint → Roll secret with 24h grace. Paste new into Vercel STRIPE_WEBHOOK_SECRET, tick Sensitive, redeploy. Smoke: `stripe trigger checkout.session.completed` and confirm /api/webhooks/stripe returns 200 in Vercel function logs. Old secret expires automatically at end of grace — done 2026-05-03 (per Dr Mubashir).</t>
         </is>
       </c>
     </row>
@@ -5031,7 +4903,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5041,7 +4913,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -5051,17 +4923,17 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Rotate SUPABASE_SERVICE_ROLE_KEY AND NEXT_PUBLIC_SUPABASE_ANON_KEY together</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Supabase → Project Settings → API → JWT Keys → Generate new JWT secret (regenerates both keys, both are JWTs signed by the same secret). Update both values in Vercel in the same save, tick Sensitive on service_role (anon stays public but encrypt-at-rest regardless), redeploy. All pre-rotation sessions invalidated (pre-launch, so non-event). Smoke: incognito magic-link signup → /app-home load → photo upload row insert — done 2026-05-03 (per Dr Mubashir).</t>
         </is>
       </c>
     </row>
@@ -5093,17 +4965,17 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
         </is>
       </c>
     </row>
@@ -5135,17 +5007,17 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>Brevo transactional email leg</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
         </is>
       </c>
     </row>
@@ -5167,27 +5039,27 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Delete iCloud dedup files on Mac</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run. — done 2026-05-03: real damage was 2.7× larger than originally scoped. Total cleaned: 113 dedup files (109 src/app metadata route dedups across icon/apple-icon/opengraph-image/robots/sitemap × 21-22 each, 3 in scripts/, 1 in docs/paperclip-briefs/) + 121 empty paren-numbered directories under src/app/ + 4 space-numbered directories under src/app/auth/ (accept-terms 2, callback 2, callback 3, login 2 — verified to be older stale snapshots predating the i18n + signup-flow fixes, no imports, originals intact) + 2 i18n dictionary dedups (ar 2.json, zh 2.json) = grand total 240 entries. Verified: `find` returns 0 dedups repo-wide; `npm run build` exit 0 with all routes (icon, opengraph-image, robots.txt, sitemap.xml, manifest.webmanifest, /legal/*, /auth/*, /inspection/*, /features/*) compiled cleanly; Next.js convention parents (icon.tsx, apple-icon.tsx, opengraph-image.tsx, robots.ts, sitemap.ts) all present. Root cause documented: dual mirroring by iCloud (parens-N suffix) AND OneDrive (space-N suffix) on the old `~/Documents/Claude/Projects/Tenu.World/` path. Repo now lives at `~/Code/Tenu.World/` (no iCloud xattrs). Confirm OneDrive isn't mirroring `~/Code/` either to prevent recurrence.</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
         </is>
       </c>
     </row>
@@ -5219,17 +5091,17 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>Capacitor 7 scaffold</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Brevo transactional email leg</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
         </is>
       </c>
     </row>
@@ -5251,27 +5123,27 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Delete iCloud dedup files on Mac</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run. — done 2026-05-03: real damage was 2.7× larger than originally scoped. Total cleaned: 113 dedup files (109 src/app metadata route dedups across icon/apple-icon/opengraph-image/robots/sitemap × 21-22 each, 3 in scripts/, 1 in docs/paperclip-briefs/) + 121 empty paren-numbered directories under src/app/ + 4 space-numbered directories under src/app/auth/ (accept-terms 2, callback 2, callback 3, login 2 — verified to be older stale snapshots predating the i18n + signup-flow fixes, no imports, originals intact) + 2 i18n dictionary dedups (ar 2.json, zh 2.json) = grand total 240 entries. Verified: `find` returns 0 dedups repo-wide; `npm run build` exit 0 with all routes (icon, opengraph-image, robots.txt, sitemap.xml, manifest.webmanifest, /legal/*, /auth/*, /inspection/*, /features/*) compiled cleanly; Next.js convention parents (icon.tsx, apple-icon.tsx, opengraph-image.tsx, robots.ts, sitemap.ts) all present. Root cause documented: dual mirroring by iCloud (parens-N suffix) AND OneDrive (space-N suffix) on the old `~/Documents/Claude/Projects/Tenu.World/` path. Repo now lives at `~/Code/Tenu.World/` (no iCloud xattrs). Confirm OneDrive isn't mirroring `~/Code/` either to prevent recurrence.</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5165,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -5303,17 +5175,17 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Capacitor 7 scaffold</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
         </is>
       </c>
     </row>
@@ -5345,17 +5217,17 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>MB-01</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5249,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -5387,17 +5259,17 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>MB-03</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -5432,14 +5304,14 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>MB-05</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>MB-01</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
         </is>
       </c>
     </row>
@@ -5474,14 +5346,14 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>MB-08</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>MB-03</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
         </is>
       </c>
     </row>
@@ -5516,14 +5388,14 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>MB-09</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>MB-05</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
         </is>
       </c>
     </row>
@@ -5535,7 +5407,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -5555,17 +5427,17 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>App icon set</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>MB-08</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5449,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -5597,17 +5469,17 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>Splash screens per density, status bar theming, safe-area insets</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>MB-09</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
         </is>
       </c>
     </row>
@@ -5639,17 +5511,17 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>App icon set</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
         </is>
       </c>
     </row>
@@ -5681,17 +5553,17 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>Store listing copy drafted in FR + EN</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>description, keywords, support URL, privacy URL — done 2026-04-18 (ahead of schedule): MB-07 shipped docs/store-listings/{ios-fr,ios-en,play-fr,play-en}.md. Professional services register throughout (no buzzwords, no guaranteed-outcome claims), character counts validated inline, Stripe reader-app classification explicitly argued in reviewer notes, data safety section filled for Play form. Awaits MH (nights) review + edit before submission. Commit 50db60f.</t>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Splash screens per density, status bar theming, safe-area insets</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5575,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -5723,17 +5595,17 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>Bug sweep on inspection UI</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>camera retries, upload resume, offline queue — done 2026-05-06: EX-6. camera.ts: retry up to 3× on NotReadableError (500ms/1s backoff). uploadQueue.ts: StoredIntent interface + storeIntent/loadIntent/clearIntent (4.5-min TTL cache against R2 presigned URL). db.ts: v3 migration adds intent_url/key/headers/fetched_at columns to upload_queue. syncEngine.ts: uploadPhoto reuses cached intent on retry; startSyncLoop adds Capacitor Network.addListener + window.addEventListener("online") for reactive drain on reconnect; returns stop() that cancels both. AuthGate.tsx: wires startSyncLoop on native session confirmation. Commits 2bf561b (camera+sync) + earlier intent-cache commit.</t>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5617,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -5765,17 +5637,17 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>Native build bridge doc for iOS TestFlight + Android Play internal track</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-05-06: EX-7. docs/12-Native-Build-Bridge-2026-05-12.md: 12 sections, all commands copy-pasteable with pinned versions, expected/red-flag per step, failure modes table, timeline 2026-05-11 to 2026-06-30. Commit 55892bf.</t>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>Store listing copy drafted in FR + EN</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>description, keywords, support URL, privacy URL — done 2026-04-18 (ahead of schedule): MB-07 shipped docs/store-listings/{ios-fr,ios-en,play-fr,play-en}.md. Professional services register throughout (no buzzwords, no guaranteed-outcome claims), character counts validated inline, Stripe reader-app classification explicitly argued in reviewer notes, data safety section filled for Play form. Awaits MH (nights) review + edit before submission. Commit 50db60f.</t>
         </is>
       </c>
     </row>
@@ -5807,22 +5679,106 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>Bug sweep on inspection UI</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>camera retries, upload resume, offline queue — done 2026-05-06: EX-6. camera.ts: retry up to 3× on NotReadableError (500ms/1s backoff). uploadQueue.ts: StoredIntent interface + storeIntent/loadIntent/clearIntent (4.5-min TTL cache against R2 presigned URL). db.ts: v3 migration adds intent_url/key/headers/fetched_at columns to upload_queue. syncEngine.ts: uploadPhoto reuses cached intent on retry; startSyncLoop adds Capacitor Network.addListener + window.addEventListener("online") for reactive drain on reconnect; returns stop() that cancels both. AuthGate.tsx: wires startSyncLoop on native session confirmation. Commits 2bf561b (camera+sync) + earlier intent-cache commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>T-038</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>LAUNCH WEEK (8-11 May)</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>Native build bridge doc for iOS TestFlight + Android Play internal track</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-05-06: EX-7. docs/12-Native-Build-Bridge-2026-05-12.md: 12 sections, all commands copy-pasteable with pinned versions, expected/red-flag per step, failure modes table, timeline 2026-05-11 to 2026-06-30. Commit 55892bf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>T-039</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>LAUNCH WEEK (8-11 May)</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>Strip App Store/Play Store badges from hero, add 25 May mobile note, create reviewer-notes.md</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>done 2026-05-06: EX-8. page.tsx: replaced SVG badge block with single &lt;p&gt; {app.heading}. All 5 dictionaries: stripped appStore/playStore/comingSoon/subtext, heading → "Apps mobiles natives à partir du 25 mai". docs/store-listings/reviewer-notes.md: test account, permission table, Reader App IAP declaration, AI disclosure, data handling. Commit f5ca79f.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H38"/>
+  <autoFilter ref="A1:H40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Regenerated 2026-05-03 from TASKS.md. Master = TASKS.md. Do not edit xlsx directly.</t>
+          <t>Regenerated 2026-05-07 from TASKS.md. Master = TASKS.md. Do not edit xlsx directly.</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -719,29 +719,29 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Install scheduled-push v2</t>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>Update store-listing copy + welcome email + landing page to reflect web-first launch + native binaries follow</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Update store-listing copy + welcome email + landing page to reflect web-first launch + native binaries follow</t>
+          <t>Personalise + send the FR avocat brief (review draft, fill recipient name + cabinet, send by email)</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Personalise + send the FR avocat brief (review draft, fill recipient name + cabinet, send by email)</t>
+          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
+          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
+          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
+          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
+          <t>Google Play Console developer account, USD 25 one-time</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
+          <t>Audit hidden env vars</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Audit hidden env vars</t>
+          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
+          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
+          <t>Post-rotation smoke test verification</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Post-rotation smoke test verification</t>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
+          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
+          <t>Install scheduled-push v2</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
+          <t>T-103-core pipeline tests</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -1570,19 +1570,19 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>T-103-core pipeline tests</t>
+          <t>F&amp;F invite list</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
     </row>
@@ -1648,24 +1648,24 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
         </is>
       </c>
     </row>
@@ -1692,17 +1692,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+          <t>Recover Brevo account access</t>
         </is>
       </c>
     </row>
@@ -1747,6 +1747,204 @@
       <c r="D71" s="5" t="inlineStr">
         <is>
           <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2037,9 +2235,9 @@
           <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -2054,7 +2252,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -2064,7 +2262,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>copy scripts/scheduled-tasks/tenu-daily-push.md into ~/Documents/Claude/Scheduled/tenu-daily-push/SKILL.md and drop BREVO_API_KEY into .secrets/brevo.env</t>
+          <t>copy scripts/scheduled-tasks/tenu-daily-push.md into ~/Documents/Claude/Scheduled/tenu-daily-push/SKILL.md and drop BREVO_API_KEY into .secrets/brevo.env — re-dated 2026-05-03. CC fixed all 6 hardcoded paths in SKILL.md from `/Users/mmh/Documents/Claude/Projects/Tenu.World/` to `/Users/mmh/Code/Tenu.World/` (root cause of today's 09:04 diagnostic log). Bumped to v2.1. brevo.env.example header path also corrected. SKILL.md installed at ~/Documents/Claude/Scheduled/tenu-daily-push/SKILL.md. .secrets/brevo.env file created but currently holds CC's placeholder text (51 bytes, "xkeysib-PASTE_THE_REAL_KEY_VALUE_HERE"). MH must pull real BREVO_API_KEY from Vercel env panel and overwrite. After overwrite, remove the [&gt;] marker and close [x].</t>
         </is>
       </c>
     </row>
@@ -2091,20 +2289,24 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr"/>
+          <t>Recover Brevo account access</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>can't log in to dashboard as of 2026-05-03. Try password reset at app.brevo.com/account/login → mubashirr@gmail.com. If 2FA is the blocker, contact Brevo support (help.brevo.com) for identity-verified MFA reset. Search Downloads folder for any "brevo" or "recovery" file from original signup. Needed before F&amp;F cohort outcome data starts coming in mid-May (template tuning + bounce monitoring)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2139,7 +2341,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
+          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr"/>
@@ -2177,7 +2379,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
+          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
@@ -2193,9 +2395,9 @@
           <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -2210,19 +2412,15 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>submitted 2026-05-03, documents sent to Apple, awaiting verification (per Dr Mubashir). Apple identity check typically 2-5 business days; D-U-N-S verification gates the review. Track unblocking of Xcode signing / TestFlight upload off this line.</t>
-        </is>
-      </c>
+          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2235,9 +2433,9 @@
           <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -2252,15 +2450,19 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr"/>
+          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>submitted 2026-05-03, documents sent to Apple, awaiting verification (per Dr Mubashir). Apple identity check typically 2-5 business days; D-U-N-S verification gates the review. Track unblocking of Xcode signing / TestFlight upload off this line.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -2295,7 +2497,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
+          <t>Google Play Console developer account, USD 25 one-time</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
@@ -2328,19 +2530,15 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Google Workspace subscription on `tenu.world`</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>create `ops@tenu.world` (owner) + `support@tenu.world` + `dpo@tenu.world` (aliases acceptable)</t>
-        </is>
-      </c>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2375,10 +2573,14 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr"/>
+          <t>Google Workspace subscription on `tenu.world`</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>create `ops@tenu.world` (owner) + `support@tenu.world` + `dpo@tenu.world` (aliases acceptable)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2413,7 +2615,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr"/>
@@ -2451,7 +2653,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr"/>
@@ -2489,7 +2691,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
@@ -2527,7 +2729,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr"/>
@@ -2560,19 +2762,15 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>expect no 403 org_internal, consent screen shows "Tenu" with `support@tenu.world`</t>
-        </is>
-      </c>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2607,12 +2805,12 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>do not archive, the secret is burned</t>
+          <t>expect no 403 org_internal, consent screen shows "Tenu" with `support@tenu.world`</t>
         </is>
       </c>
     </row>
@@ -2649,12 +2847,12 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>revokes the leaked secret at source even if a copy is still cached somewhere</t>
+          <t>do not archive, the secret is burned</t>
         </is>
       </c>
     </row>
@@ -2686,17 +2884,17 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Before 11 May</t>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>publish OAuth consent screen Testing → Production (requires domain verified + privacy URL + terms URL live at tenu.world/legal/privacy + /legal/terms)</t>
+          <t>revokes the leaked secret at source even if a copy is still cached somewhere</t>
         </is>
       </c>
     </row>
@@ -2728,17 +2926,17 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Audit hidden env vars</t>
+          <t>Before 11 May</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>scroll full Vercel env var list below the fold, confirm ANTHROPIC_API_KEY + BREVO_API_KEY + TELEGRAM_BOT_TOKEN + any other secret either shows Need To Rotate (rotate it) or was created Sensitive from day one (leave alone). If any non-public secret is unflagged and NOT marked Sensitive, treat as exposed and rotate</t>
+          <t>publish OAuth consent screen Testing → Production (requires domain verified + privacy URL + terms URL live at tenu.world/legal/privacy + /legal/terms)</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2973,12 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
+          <t>Audit hidden env vars</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Google Cloud Console → APIs &amp; Services → Credentials → restrict to HTTP referrers `*.tenu.world` + `localhost:*` + enable only Maps JavaScript + Places API. Public by design, not flagged by Vercel, but unrestricted = scraping risk against Global Apex billing</t>
+          <t>scroll full Vercel env var list below the fold, confirm ANTHROPIC_API_KEY + BREVO_API_KEY + TELEGRAM_BOT_TOKEN + any other secret either shows Need To Rotate (rotate it) or was created Sensitive from day one (leave alone). If any non-public secret is unflagged and NOT marked Sensitive, treat as exposed and rotate</t>
         </is>
       </c>
     </row>
@@ -2817,12 +3015,12 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
+          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>hardening pass, single biggest structural lesson from this incident. Anything that isn't a NEXT_PUBLIC_* or a non-secret identifier (R2_ACCOUNT_ID, R2_BUCKET_NAME) should be Sensitive</t>
+          <t>Google Cloud Console → APIs &amp; Services → Credentials → restrict to HTTP referrers `*.tenu.world` + `localhost:*` + enable only Maps JavaScript + Places API. Public by design, not flagged by Vercel, but unrestricted = scraping risk against Global Apex billing</t>
         </is>
       </c>
     </row>
@@ -2844,7 +3042,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2859,12 +3057,12 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Post-rotation smoke test verification</t>
+          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green</t>
+          <t>hardening pass, single biggest structural lesson from this incident. Anything that isn't a NEXT_PUBLIC_* or a non-secret identifier (R2_ACCOUNT_ID, R2_BUCKET_NAME) should be Sensitive</t>
         </is>
       </c>
     </row>
@@ -2876,12 +3074,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2896,17 +3094,17 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>Post-rotation smoke test verification</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
+          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green</t>
         </is>
       </c>
     </row>
@@ -2921,9 +3119,9 @@
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2938,17 +3136,17 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
+          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
         </is>
       </c>
     </row>
@@ -4306,8 +4504,110 @@
       </c>
       <c r="H64" s="7" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>T-064</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr"/>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Add scans.pdf_url + scans.pdf_sha256 columns; migrate from risk_score.pdfUrl jsonb.</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>T-065</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>Extract /api/pdf/build dedicated route with runtime='nodejs' + maxDuration=60; trigger async from /api/ai/scan.</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>T-066</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Switch R2 PDF URLs to signed URLs with renewable TTL (default 30 days).</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H64"/>
+  <autoFilter ref="A1:H67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4318,7 +4618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5199,17 +5499,17 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Brevo transactional email leg</t>
+          <t>PDF generation leg</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
+          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2 — done 2026-04-19: shipped via MB-16 (commit d77d85b, 2026-04-19); architectural deltas captured as 3 new p:1 hardening lines below.</t>
         </is>
       </c>
     </row>
@@ -5231,27 +5531,27 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Delete iCloud dedup files on Mac</t>
+          <t>Brevo transactional email leg</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run. — done 2026-05-03: real damage was 2.7× larger than originally scoped. Total cleaned: 113 dedup files (109 src/app metadata route dedups across icon/apple-icon/opengraph-image/robots/sitemap × 21-22 each, 3 in scripts/, 1 in docs/paperclip-briefs/) + 121 empty paren-numbered directories under src/app/ + 4 space-numbered directories under src/app/auth/ (accept-terms 2, callback 2, callback 3, login 2 — verified to be older stale snapshots predating the i18n + signup-flow fixes, no imports, originals intact) + 2 i18n dictionary dedups (ar 2.json, zh 2.json) = grand total 240 entries. Verified: `find` returns 0 dedups repo-wide; `npm run build` exit 0 with all routes (icon, opengraph-image, robots.txt, sitemap.xml, manifest.webmanifest, /legal/*, /auth/*, /inspection/*, /features/*) compiled cleanly; Next.js convention parents (icon.tsx, apple-icon.tsx, opengraph-image.tsx, robots.ts, sitemap.ts) all present. Root cause documented: dual mirroring by iCloud (parens-N suffix) AND OneDrive (space-N suffix) on the old `~/Documents/Claude/Projects/Tenu.World/` path. Repo now lives at `~/Code/Tenu.World/` (no iCloud xattrs). Confirm OneDrive isn't mirroring `~/Code/` either to prevent recurrence.</t>
+          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
         </is>
       </c>
     </row>
@@ -5273,27 +5573,27 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Capacitor 7 scaffold</t>
+          <t>Delete iCloud dedup files on Mac</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
+          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run. — done 2026-05-03: real damage was 2.7× larger than originally scoped. Total cleaned: 113 dedup files (109 src/app metadata route dedups across icon/apple-icon/opengraph-image/robots/sitemap × 21-22 each, 3 in scripts/, 1 in docs/paperclip-briefs/) + 121 empty paren-numbered directories under src/app/ + 4 space-numbered directories under src/app/auth/ (accept-terms 2, callback 2, callback 3, login 2 — verified to be older stale snapshots predating the i18n + signup-flow fixes, no imports, originals intact) + 2 i18n dictionary dedups (ar 2.json, zh 2.json) = grand total 240 entries. Verified: `find` returns 0 dedups repo-wide; `npm run build` exit 0 with all routes (icon, opengraph-image, robots.txt, sitemap.xml, manifest.webmanifest, /legal/*, /auth/*, /inspection/*, /features/*) compiled cleanly; Next.js convention parents (icon.tsx, apple-icon.tsx, opengraph-image.tsx, robots.ts, sitemap.ts) all present. Root cause documented: dual mirroring by iCloud (parens-N suffix) AND OneDrive (space-N suffix) on the old `~/Documents/Claude/Projects/Tenu.World/` path. Repo now lives at `~/Code/Tenu.World/` (no iCloud xattrs). Confirm OneDrive isn't mirroring `~/Code/` either to prevent recurrence.</t>
         </is>
       </c>
     </row>
@@ -5330,12 +5630,12 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+          <t>Capacitor 7 scaffold</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
+          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
         </is>
       </c>
     </row>
@@ -5357,7 +5657,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -5367,17 +5667,17 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
+          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5699,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -5409,17 +5709,17 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>MB-01</t>
+          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
+          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -5456,12 +5756,12 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>MB-03</t>
+          <t>MB-01</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
+          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
         </is>
       </c>
     </row>
@@ -5498,12 +5798,12 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>MB-05</t>
+          <t>MB-03</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
+          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5840,12 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>MB-08</t>
+          <t>MB-05</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
+          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
         </is>
       </c>
     </row>
@@ -5582,12 +5882,12 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>MB-09</t>
+          <t>MB-08</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
+          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5899,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -5619,17 +5919,17 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>App icon set</t>
+          <t>MB-09</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
+          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
         </is>
       </c>
     </row>
@@ -5661,17 +5961,17 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>Splash screens per density, status bar theming, safe-area insets</t>
+          <t>App icon set</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
+          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
         </is>
       </c>
     </row>
@@ -5703,17 +6003,17 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+          <t>Splash screens per density, status bar theming, safe-area insets</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
         </is>
       </c>
     </row>
@@ -5750,17 +6050,59 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
+          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>T-034</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
           <t>Store listing copy drafted in FR + EN</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>description, keywords, support URL, privacy URL — done 2026-04-18 (ahead of schedule): MB-07 shipped docs/store-listings/{ios-fr,ios-en,play-fr,play-en}.md. Professional services register throughout (no buzzwords, no guaranteed-outcome claims), character counts validated inline, Stripe reader-app classification explicitly argued in reviewer notes, data safety section filled for Play form. Awaits MH (nights) review + edit before submission. Commit 50db60f.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H34"/>
+  <autoFilter ref="A1:H35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -719,29 +719,29 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>Install scheduled-push v2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Update store-listing copy + welcome email + landing page to reflect web-first launch + native binaries follow</t>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Personalise + send the FR avocat brief (review draft, fill recipient name + cabinet, send by email)</t>
+          <t>Update store-listing copy + welcome email + landing page to reflect web-first launch + native binaries follow</t>
         </is>
       </c>
     </row>
@@ -1093,22 +1093,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Install scheduled-push v2</t>
+          <t>Native Build Bridge plan</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Native Build Bridge plan</t>
+          <t>Google Workspace subscription on `tenu.world`</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Google Workspace subscription on `tenu.world`</t>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
+          <t>Before 11 May</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Before 11 May</t>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>Decide Apple IAP stance</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
+          <t>Magic-link auth working inside app</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
         </is>
       </c>
     </row>
@@ -1372,14 +1372,14 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation signed</t>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -1394,14 +1394,14 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+          <t>PDF generation leg</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
+          <t>T-103-core pipeline tests</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -1548,19 +1548,19 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>T-103-core pipeline tests</t>
+          <t>F&amp;F invite list</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
+          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
     </row>
@@ -1626,24 +1626,24 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -1653,24 +1653,24 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -1680,14 +1680,14 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+          <t>Suivi avocat·e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Recover Brevo account access</t>
+          <t>Médiateur de la consommation</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2168,17 +2168,17 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Personalise + send the FR avocat brief (review draft, fill recipient name + cabinet, send by email)</t>
+          <t>Suivi avocat·e</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>depends on CC line above.</t>
+          <t>relance polie si pas de réponse à J+2 — opened 2026-05-07. Critical path pour décision launch-vs-slip 11 May ; bloque CGU §11 médiateur, mentions légales §médiation, et la levée des bannières DRAFT.</t>
         </is>
       </c>
     </row>
@@ -2235,9 +2235,9 @@
           <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>copy scripts/scheduled-tasks/tenu-daily-push.md into ~/Documents/Claude/Scheduled/tenu-daily-push/SKILL.md and drop BREVO_API_KEY into .secrets/brevo.env — re-dated 2026-05-03. CC fixed all 6 hardcoded paths in SKILL.md from `/Users/mmh/Documents/Claude/Projects/Tenu.World/` to `/Users/mmh/Code/Tenu.World/` (root cause of today's 09:04 diagnostic log). Bumped to v2.1. brevo.env.example header path also corrected. SKILL.md installed at ~/Documents/Claude/Scheduled/tenu-daily-push/SKILL.md. .secrets/brevo.env file created but currently holds CC's placeholder text (51 bytes, "xkeysib-PASTE_THE_REAL_KEY_VALUE_HERE"). MH must pull real BREVO_API_KEY from Vercel env panel and overwrite. After overwrite, remove the [&gt;] marker and close [x].</t>
+          <t>copy scripts/scheduled-tasks/tenu-daily-push.md into ~/Documents/Claude/Scheduled/tenu-daily-push/SKILL.md and drop BREVO_API_KEY into .secrets/brevo.env</t>
         </is>
       </c>
     </row>
@@ -2289,24 +2289,20 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Recover Brevo account access</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>can't log in to dashboard as of 2026-05-03. Try password reset at app.brevo.com/account/login → mubashirr@gmail.com. If 2FA is the blocker, contact Brevo support (help.brevo.com) for identity-verified MFA reset. Search Downloads folder for any "brevo" or "recovery" file from original signup. Needed before F&amp;F cohort outcome data starts coming in mid-May (template tuning + bounce monitoring)</t>
-        </is>
-      </c>
+          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2341,7 +2337,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
+          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr"/>
@@ -2379,7 +2375,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
+          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
@@ -2395,9 +2391,9 @@
           <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -2412,15 +2408,19 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr"/>
+          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>submitted 2026-05-03, documents sent to Apple, awaiting verification (per Dr Mubashir). Apple identity check typically 2-5 business days; D-U-N-S verification gates the review. Track unblocking of Xcode signing / TestFlight upload off this line.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2433,9 +2433,9 @@
           <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -2450,19 +2450,15 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>submitted 2026-05-03, documents sent to Apple, awaiting verification (per Dr Mubashir). Apple identity check typically 2-5 business days; D-U-N-S verification gates the review. Track unblocking of Xcode signing / TestFlight upload off this line.</t>
-        </is>
-      </c>
+          <t>Google Play Console developer account, USD 25 one-time</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -2497,7 +2493,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
@@ -2530,15 +2526,19 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr"/>
+          <t>Google Workspace subscription on `tenu.world`</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>create `ops@tenu.world` (owner) + `support@tenu.world` + `dpo@tenu.world` (aliases acceptable)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2573,14 +2573,10 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Google Workspace subscription on `tenu.world`</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>create `ops@tenu.world` (owner) + `support@tenu.world` + `dpo@tenu.world` (aliases acceptable)</t>
-        </is>
-      </c>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2615,7 +2611,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr"/>
@@ -2653,7 +2649,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr"/>
@@ -2691,7 +2687,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
@@ -2729,7 +2725,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr"/>
@@ -2762,15 +2758,19 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr"/>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>expect no 403 org_internal, consent screen shows "Tenu" with `support@tenu.world`</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>expect no 403 org_internal, consent screen shows "Tenu" with `support@tenu.world`</t>
+          <t>do not archive, the secret is burned</t>
         </is>
       </c>
     </row>
@@ -2847,12 +2847,12 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>do not archive, the secret is burned</t>
+          <t>revokes the leaked secret at source even if a copy is still cached somewhere</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+          <t>Before 11 May</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>revokes the leaked secret at source even if a copy is still cached somewhere</t>
+          <t>publish OAuth consent screen Testing → Production (requires domain verified + privacy URL + terms URL live at tenu.world/legal/privacy + /legal/terms)</t>
         </is>
       </c>
     </row>
@@ -2926,17 +2926,17 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Before 11 May</t>
+          <t>Audit hidden env vars</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>publish OAuth consent screen Testing → Production (requires domain verified + privacy URL + terms URL live at tenu.world/legal/privacy + /legal/terms)</t>
+          <t>scroll full Vercel env var list below the fold, confirm ANTHROPIC_API_KEY + BREVO_API_KEY + TELEGRAM_BOT_TOKEN + any other secret either shows Need To Rotate (rotate it) or was created Sensitive from day one (leave alone). If any non-public secret is unflagged and NOT marked Sensitive, treat as exposed and rotate</t>
         </is>
       </c>
     </row>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Audit hidden env vars</t>
+          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>scroll full Vercel env var list below the fold, confirm ANTHROPIC_API_KEY + BREVO_API_KEY + TELEGRAM_BOT_TOKEN + any other secret either shows Need To Rotate (rotate it) or was created Sensitive from day one (leave alone). If any non-public secret is unflagged and NOT marked Sensitive, treat as exposed and rotate</t>
+          <t>Google Cloud Console → APIs &amp; Services → Credentials → restrict to HTTP referrers `*.tenu.world` + `localhost:*` + enable only Maps JavaScript + Places API. Public by design, not flagged by Vercel, but unrestricted = scraping risk against Global Apex billing</t>
         </is>
       </c>
     </row>
@@ -3015,12 +3015,12 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
+          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Google Cloud Console → APIs &amp; Services → Credentials → restrict to HTTP referrers `*.tenu.world` + `localhost:*` + enable only Maps JavaScript + Places API. Public by design, not flagged by Vercel, but unrestricted = scraping risk against Global Apex billing</t>
+          <t>hardening pass, single biggest structural lesson from this incident. Anything that isn't a NEXT_PUBLIC_* or a non-secret identifier (R2_ACCOUNT_ID, R2_BUCKET_NAME) should be Sensitive</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
+          <t>Post-rotation smoke test verification</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>hardening pass, single biggest structural lesson from this incident. Anything that isn't a NEXT_PUBLIC_* or a non-secret identifier (R2_ACCOUNT_ID, R2_BUCKET_NAME) should be Sensitive</t>
+          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -3094,17 +3094,17 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Post-rotation smoke test verification</t>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green</t>
+          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
         </is>
       </c>
     </row>
@@ -3119,9 +3119,9 @@
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -3136,17 +3136,17 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>PDF generation leg</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
+          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2</t>
         </is>
       </c>
     </row>
@@ -3937,9 +3937,9 @@
           <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -3954,17 +3954,17 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation signed</t>
+          <t>Médiateur de la consommation</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>MEDICYS OR SMCE OR AME Conso</t>
+          <t>comparer MEDICYS vs CM2C (frais d'adhésion, délai de saisine, périmètre B2C numérique), choisir, signer, publier le nom dans CGU §11 + remboursement §6 + mentions légales §médiation — opened 2026-05-07: shortlist réduite à MEDICYS + CM2C, à arbitrer cette semaine. Obligation L612-1 Code de la conso pour activité B2C en ligne, blocage de la mise en service tant que le médiateur n'est pas adhéré.</t>
         </is>
       </c>
     </row>
@@ -4504,110 +4504,8 @@
       </c>
       <c r="H64" s="7" t="inlineStr"/>
     </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>T-064</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr"/>
-      <c r="G65" s="7" t="inlineStr">
-        <is>
-          <t>Add scans.pdf_url + scans.pdf_sha256 columns; migrate from risk_score.pdfUrl jsonb.</t>
-        </is>
-      </c>
-      <c r="H65" s="7" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>T-065</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="inlineStr"/>
-      <c r="G66" s="7" t="inlineStr">
-        <is>
-          <t>Extract /api/pdf/build dedicated route with runtime='nodejs' + maxDuration=60; trigger async from /api/ai/scan.</t>
-        </is>
-      </c>
-      <c r="H66" s="7" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>T-066</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr"/>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>Switch R2 PDF URLs to signed URLs with renewable TTL (default 30 days).</t>
-        </is>
-      </c>
-      <c r="H67" s="7" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H67"/>
+  <autoFilter ref="A1:H64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4765,7 +4663,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
+          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -4775,27 +4673,27 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Scheduled push v2</t>
+          <t>Personalise + send the FR avocat brief (review draft, fill recipient name + cabinet, send by email)</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>replace Gmail create_draft with Brevo direct send — done 2026-04-19: new SKILL.md at scripts/scheduled-tasks/tenu-daily-push.md, brevo.env.example alongside. Telegram path unchanged. MH installs + adds BREVO_API_KEY — see MH line below.</t>
+          <t>done 2026-05-07: lettre `outreach/legal/letter-avocat-droit-immobilier-FR.docx` + dossier 9 pièces `outreach/legal/Tenu-Dossier-Revue-Avocat-FR.zip` envoyés à l'avocat·e. Réponse en attente. Suivi : nouvelle ligne MH ci-dessous.</t>
         </is>
       </c>
     </row>
@@ -4822,22 +4720,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Fix footer legal routes redirecting to /auth/login</t>
+          <t>Scheduled push v2</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>expose /legal, /auth/accept-terms, /api/consents as public paths in middleware — done 2026-04-18: middleware allow-list extended, verified on tenu.world production in incognito, all six legal pages render without auth. Commit via PR fix/public-legal-routes merged to main. Pre-contractual disclosure (art. L221-5 Code de la conso) now reachable as required for Stripe/App Store review.</t>
+          <t>replace Gmail create_draft with Brevo direct send — done 2026-04-19: new SKILL.md at scripts/scheduled-tasks/tenu-daily-push.md, brevo.env.example alongside. Telegram path unchanged. MH installs + adds BREVO_API_KEY — see MH line below.</t>
         </is>
       </c>
     </row>
@@ -4874,12 +4772,12 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Fix /stories/* and /features/* redirecting to /auth/login</t>
+          <t>Fix footer legal routes redirecting to /auth/login</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: added "/stories" and "/features" to publicPaths in src/middleware.ts. Same isPublicPath startsWith match pattern as the /legal fix; single entry per parent covers all nested routes. Stories and features now reachable without auth as marketing/content surface.</t>
+          <t>expose /legal, /auth/accept-terms, /api/consents as public paths in middleware — done 2026-04-18: middleware allow-list extended, verified on tenu.world production in incognito, all six legal pages render without auth. Commit via PR fix/public-legal-routes merged to main. Pre-contractual disclosure (art. L221-5 Code de la conso) now reachable as required for Stripe/App Store review.</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4804,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -4916,12 +4814,12 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Use-case content system</t>
+          <t>Fix /stories/* and /features/* redirecting to /auth/login</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>manifest + /stories index + cross-link strip + homepage dual-card — done 2026-04-18: src/lib/stories.ts (single source of truth, Story type, 4 helpers), src/components/stories/OtherCases.tsx (bilingual cross-link strip), src/app/stories/page.tsx (index with cautionary populated, success placeholder awaiting 11 May cohort), homepage example section refactored from single Suzi hook to manifest-driven dual-card grid with "See all cases →" link, Suzi + Samir pages thread OtherCases before footer, example block in en/fr/zh/ar/ur dictionaries refactored to label/heading/intro/seeAll/disclaimer. Adding a new case is now one append to stories.ts + one new /stories/&lt;slug&gt;/page.tsx.</t>
+          <t>done 2026-04-18: added "/stories" and "/features" to publicPaths in src/middleware.ts. Same isPublicPath startsWith match pattern as the /legal fix; single entry per parent covers all nested routes. Stories and features now reachable without auth as marketing/content surface.</t>
         </is>
       </c>
     </row>
@@ -4943,27 +4841,27 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Telegram one-time setup</t>
+          <t>Use-case content system</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>create bot via @BotFather, send token + chat_id — done 2026-04-18: bot created, token + chat_id set in .env.local and Vercel env (per Dr Mubashir)</t>
+          <t>manifest + /stories index + cross-link strip + homepage dual-card — done 2026-04-18: src/lib/stories.ts (single source of truth, Story type, 4 helpers), src/components/stories/OtherCases.tsx (bilingual cross-link strip), src/app/stories/page.tsx (index with cautionary populated, success placeholder awaiting 11 May cohort), homepage example section refactored from single Suzi hook to manifest-driven dual-card grid with "See all cases →" link, Suzi + Samir pages thread OtherCases before footer, example block in en/fr/zh/ar/ur dictionaries refactored to label/heading/intro/seeAll/disclaimer. Adding a new case is now one append to stories.ts + one new /stories/&lt;slug&gt;/page.tsx.</t>
         </is>
       </c>
     </row>
@@ -5000,12 +4898,12 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Paste ANTHROPIC_API_KEY into .env.local + Vercel project env</t>
+          <t>Telegram one-time setup</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
+          <t>create bot via @BotFather, send token + chat_id — done 2026-04-18: bot created, token + chat_id set in .env.local and Vercel env (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -5042,7 +4940,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Paste BREVO_API_KEY into .env.local + Vercel project env</t>
+          <t>Paste ANTHROPIC_API_KEY into .env.local + Vercel project env</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -5069,7 +4967,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -5079,17 +4977,17 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>SOT consolidation</t>
+          <t>Paste BREVO_API_KEY into .env.local + Vercel project env</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>fix CLAUDE.md project path, refresh CLAUDE-CONTEXT.md to current React/in-code stack, replace stale-clone CLAUDE.md + CLAUDE-CONTEXT.md with redirect stubs — done 2026-04-19: SOT CLAUDE.md now declares `/Users/mmh/Documents/Claude/Projects/Tenu.World/` as canonical at the top, project structure block rewritten to match real layout (no nested `app/` wrapper, lists ios/, android/, mobile/, resources/, supabase/, scripts/). SOT CLAUDE-CONTEXT.md fully refreshed: dropped Webflow/Make.com/Tally/Airtable/Asana/Placid references, added pricing matrix, in-code pipeline, build timeline through 11 May, brand SOT pointers. Stale clone at `/Users/mmh/Documents/Global Apex/Tenu/` now has redirect-only CLAUDE.md + CLAUDE-CONTEXT.md so any agent invoked from that path bounces immediately.</t>
+          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5009,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -5121,17 +5019,17 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
+          <t>SOT consolidation</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>`client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json`, the same with " (1)" suffix, and `stripe_backup_code.txt`. All three are sitting in plaintext in a Documents folder (iCloud-syncable, Time-Machine-backupable). Move to `~/.secrets/` or 1Password, then `rm` from disk. **Do NOT git commit them anywhere.** — done 2026-05-03: stripe_backup_code.txt contents migrated to 1Password as Secure Note "Stripe 2FA backup codes — Global Apex NET" (per Dr Mubashir). Two client_secret JSON files deleted (burned credentials, no preservation needed — Cloud project shutdown will close the trust loop). All three files removed from disk via `rm -rf` on parent folder. Verify by inspection: `/Users/mmh/Documents/Global Apex/Tenu/` no longer exists.</t>
+          <t>fix CLAUDE.md project path, refresh CLAUDE-CONTEXT.md to current React/in-code stack, replace stale-clone CLAUDE.md + CLAUDE-CONTEXT.md with redirect stubs — done 2026-04-19: SOT CLAUDE.md now declares `/Users/mmh/Documents/Claude/Projects/Tenu.World/` as canonical at the top, project structure block rewritten to match real layout (no nested `app/` wrapper, lists ios/, android/, mobile/, resources/, supabase/, scripts/). SOT CLAUDE-CONTEXT.md fully refreshed: dropped Webflow/Make.com/Tally/Airtable/Asana/Placid references, added pricing matrix, in-code pipeline, build timeline through 11 May, brand SOT pointers. Stale clone at `/Users/mmh/Documents/Global Apex/Tenu/` now has redirect-only CLAUDE.md + CLAUDE-CONTEXT.md so any agent invoked from that path bounces immediately.</t>
         </is>
       </c>
     </row>
@@ -5153,27 +5051,27 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
+          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>`01-Legal-Checklist.md` (review + dedupe against SOT 05-Legal-Compliance content first), `etat-des-lieux.pdf`, `etat-des-lieux-meuble.pdf`, `modele-etat-des-lieux T2-T3.pdf` into SOT `docs/reference/etat-des-lieux/` (or wherever Dr Mubashir prefers). Delete from stale clone after move — done 2026-05-03: audit found `01-Legal-Checklist.md` already byte-identical between stale and SOT (no migration needed); 3 PDFs in stale folder, two of which (`modele-etat-des-lieux.pdf` and `modele-etat-des-lieux T2-T3.pdf`) are byte-identical (sha 4b9fed2e0c14...) — only one carried over. Final SOT state: `docs/reference/etat-des-lieux/etat-des-lieux-meuble.pdf` (sha 6e1e3f5acd83...) + `docs/reference/etat-des-lieux/modele-etat-des-lieux T2-T3.pdf` (sha 4b9fed2e0c14...). Note: original task line referenced `etat-des-lieux.pdf` which never existed in stale clone — actual filenames discovered during audit.</t>
+          <t>`client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json`, the same with " (1)" suffix, and `stripe_backup_code.txt`. All three are sitting in plaintext in a Documents folder (iCloud-syncable, Time-Machine-backupable). Move to `~/.secrets/` or 1Password, then `rm` from disk. **Do NOT git commit them anywhere.** — done 2026-05-03: stripe_backup_code.txt contents migrated to 1Password as Secure Note "Stripe 2FA backup codes — Global Apex NET" (per Dr Mubashir). Two client_secret JSON files deleted (burned credentials, no preservation needed — Cloud project shutdown will close the trust loop). All three files removed from disk via `rm -rf` on parent folder. Verify by inspection: `/Users/mmh/Documents/Global Apex/Tenu/` no longer exists.</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5093,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -5205,17 +5103,17 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
+          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>archive to `~/Archive/` or `rm -rf`. Sandbox cannot delete the parent folder. — done 2026-05-03 — decision: `rm -rf`, no archive. Audit grounds: (a) 533 MB of the 538 MB total was regenerable node_modules; (b) git remote pointed at the same `malikmubashir/tenu-world.git` with HEAD at `c3614ef` (the original April 3 scaffold commit, redundant with everything in main since); (c) all 10 doc files were either byte-identical to SOT or differed only in COI-scrubbed wording (HEC GEMM / MHF references that SOT correctly removed per role-separation policy in CLAUDE.md); (d) parent had `com.apple.macl` and `com.apple.provenance` xattrs only — NOT iCloud-synced, so no recurring sync source to sever; (e) Time Machine retains snapshots back to April 3 if recovery ever needed. Final stale-clone removal verified: parent path no longer exists. Container `/Users/mmh/Documents/Global Apex/` retained for other uses. Companion finding: the dedup chaos cleaned in the prior task was therefore NOT from active iCloud sync — likely a one-time merge incident from a multi-machine sync, not ongoing. Worth knowing for future repo-cleanup heuristics.</t>
+          <t>`01-Legal-Checklist.md` (review + dedupe against SOT 05-Legal-Compliance content first), `etat-des-lieux.pdf`, `etat-des-lieux-meuble.pdf`, `modele-etat-des-lieux T2-T3.pdf` into SOT `docs/reference/etat-des-lieux/` (or wherever Dr Mubashir prefers). Delete from stale clone after move — done 2026-05-03: audit found `01-Legal-Checklist.md` already byte-identical between stale and SOT (no migration needed); 3 PDFs in stale folder, two of which (`modele-etat-des-lieux.pdf` and `modele-etat-des-lieux T2-T3.pdf`) are byte-identical (sha 4b9fed2e0c14...) — only one carried over. Final SOT state: `docs/reference/etat-des-lieux/etat-des-lieux-meuble.pdf` (sha 6e1e3f5acd83...) + `docs/reference/etat-des-lieux/modele-etat-des-lieux T2-T3.pdf` (sha 4b9fed2e0c14...). Note: original task line referenced `etat-des-lieux.pdf` which never existed in stale clone — actual filenames discovered during audit.</t>
         </is>
       </c>
     </row>
@@ -5242,22 +5140,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Rotate R2_ACCESS_KEY_ID + R2_SECRET_ACCESS_KEY</t>
+          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Cloudflare → R2 → Manage API tokens → new token scoped to tenu-evidence bucket (Object Read/Write only). Paste both into Vercel env, tick Sensitive, redeploy. Smoke: hit /api/mobile/upload-intent and upload a test photo. Then revoke old token in Cloudflare. Existing presigned URLs signed with old key keep working until expiry — done 2026-05-03 (per Dr Mubashir, post-holiday). CC post-rotation E2E smoke owed (line below).</t>
+          <t>archive to `~/Archive/` or `rm -rf`. Sandbox cannot delete the parent folder. — done 2026-05-03 — decision: `rm -rf`, no archive. Audit grounds: (a) 533 MB of the 538 MB total was regenerable node_modules; (b) git remote pointed at the same `malikmubashir/tenu-world.git` with HEAD at `c3614ef` (the original April 3 scaffold commit, redundant with everything in main since); (c) all 10 doc files were either byte-identical to SOT or differed only in COI-scrubbed wording (HEC GEMM / MHF references that SOT correctly removed per role-separation policy in CLAUDE.md); (d) parent had `com.apple.macl` and `com.apple.provenance` xattrs only — NOT iCloud-synced, so no recurring sync source to sever; (e) Time Machine retains snapshots back to April 3 if recovery ever needed. Final stale-clone removal verified: parent path no longer exists. Container `/Users/mmh/Documents/Global Apex/` retained for other uses. Companion finding: the dedup chaos cleaned in the prior task was therefore NOT from active iCloud sync — likely a one-time merge incident from a multi-machine sync, not ongoing. Worth knowing for future repo-cleanup heuristics.</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5192,12 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Rotate STRIPE_WEBHOOK_SECRET</t>
+          <t>Rotate R2_ACCESS_KEY_ID + R2_SECRET_ACCESS_KEY</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Stripe → Developers → Webhooks → endpoint → Roll secret with 24h grace. Paste new into Vercel STRIPE_WEBHOOK_SECRET, tick Sensitive, redeploy. Smoke: `stripe trigger checkout.session.completed` and confirm /api/webhooks/stripe returns 200 in Vercel function logs. Old secret expires automatically at end of grace — done 2026-05-03 (per Dr Mubashir).</t>
+          <t>Cloudflare → R2 → Manage API tokens → new token scoped to tenu-evidence bucket (Object Read/Write only). Paste both into Vercel env, tick Sensitive, redeploy. Smoke: hit /api/mobile/upload-intent and upload a test photo. Then revoke old token in Cloudflare. Existing presigned URLs signed with old key keep working until expiry — done 2026-05-03 (per Dr Mubashir, post-holiday). CC post-rotation E2E smoke owed (line below).</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5234,12 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Rotate SUPABASE_SERVICE_ROLE_KEY AND NEXT_PUBLIC_SUPABASE_ANON_KEY together</t>
+          <t>Rotate STRIPE_WEBHOOK_SECRET</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Supabase → Project Settings → API → JWT Keys → Generate new JWT secret (regenerates both keys, both are JWTs signed by the same secret). Update both values in Vercel in the same save, tick Sensitive on service_role (anon stays public but encrypt-at-rest regardless), redeploy. All pre-rotation sessions invalidated (pre-launch, so non-event). Smoke: incognito magic-link signup → /app-home load → photo upload row insert — done 2026-05-03 (per Dr Mubashir).</t>
+          <t>Stripe → Developers → Webhooks → endpoint → Roll secret with 24h grace. Paste new into Vercel STRIPE_WEBHOOK_SECRET, tick Sensitive, redeploy. Smoke: `stripe trigger checkout.session.completed` and confirm /api/webhooks/stripe returns 200 in Vercel function logs. Old secret expires automatically at end of grace — done 2026-05-03 (per Dr Mubashir).</t>
         </is>
       </c>
     </row>
@@ -5353,7 +5251,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -5363,7 +5261,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -5378,12 +5276,12 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
+          <t>Rotate SUPABASE_SERVICE_ROLE_KEY AND NEXT_PUBLIC_SUPABASE_ANON_KEY together</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
+          <t>Supabase → Project Settings → API → JWT Keys → Generate new JWT secret (regenerates both keys, both are JWTs signed by the same secret). Update both values in Vercel in the same save, tick Sensitive on service_role (anon stays public but encrypt-at-rest regardless), redeploy. All pre-rotation sessions invalidated (pre-launch, so non-event). Smoke: incognito magic-link signup → /app-home load → photo upload row insert — done 2026-05-03 (per Dr Mubashir).</t>
         </is>
       </c>
     </row>
@@ -5415,17 +5313,17 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
+          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
+          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
         </is>
       </c>
     </row>
@@ -5462,12 +5360,12 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
+          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
+          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
         </is>
       </c>
     </row>
@@ -5499,17 +5397,17 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
+          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2 — done 2026-04-19: shipped via MB-16 (commit d77d85b, 2026-04-19); architectural deltas captured as 3 new p:1 hardening lines below.</t>
+          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
         </is>
       </c>
     </row>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Regenerated 2026-05-03 from TASKS.md. Master = TASKS.md. Do not edit xlsx directly.</t>
+          <t>Regenerated 2026-05-08 from TASKS.md. Master = TASKS.md. Do not edit xlsx directly.</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
     </row>
@@ -1648,24 +1648,24 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -1702,14 +1702,14 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+          <t>Bug sweep on inspection UI</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -1724,19 +1724,19 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Bug sweep on inspection UI</t>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -1746,7 +1746,183 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3312,7 +3488,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -3322,12 +3498,12 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron for EUR/GBP feeding calculatePrice</t>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr"/>
@@ -3340,7 +3516,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -3350,7 +3526,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3360,12 +3536,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr"/>
@@ -3388,7 +3564,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -3398,15 +3574,19 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr"/>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>re-dated 2026-05-03: depends on CC web-only listing revision (line in DECISION 2026-05-03 section).</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3436,17 +3616,17 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
+          <t>Decide Apple IAP stance</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>re-dated 2026-05-03: depends on CC web-only listing revision (line in DECISION 2026-05-03 section).</t>
+          <t>physical service argument documented — re-dated 2026-05-03: needs to land before App Store reviewer notes lock.</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3638,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -3468,7 +3648,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -3478,19 +3658,15 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>physical service argument documented — re-dated 2026-05-03: needs to land before App Store reviewer notes lock.</t>
-        </is>
-      </c>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3520,15 +3696,19 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr"/>
+          <t>Magic-link auth working inside app</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>email link opens app, session persists</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3553,24 +3733,20 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>email link opens app, session persists</t>
-        </is>
-      </c>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -3595,20 +3771,24 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr"/>
+          <t>T-103-core pipeline tests</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -3638,19 +3818,15 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>T-103-core pipeline tests</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
-        </is>
-      </c>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -3685,7 +3861,7 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr"/>
@@ -3708,7 +3884,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -3718,15 +3894,19 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr"/>
+          <t>Médiateur de la consommation signed</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>MEDICYS OR SMCE OR AME Conso</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -3756,19 +3936,15 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation signed</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>MEDICYS OR SMCE OR AME Conso</t>
-        </is>
-      </c>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -3803,7 +3979,7 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr"/>
@@ -3836,12 +4012,12 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr"/>
@@ -3874,15 +4050,19 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr"/>
+          <t>F&amp;F invite list</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>8 names, email, jurisdiction, case type</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -3912,19 +4092,15 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>8 names, email, jurisdiction, case type</t>
-        </is>
-      </c>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -3934,7 +4110,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -3944,7 +4120,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -3954,15 +4130,19 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr"/>
+          <t>Bug sweep on inspection UI</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>camera retries, upload resume, offline queue</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -3992,19 +4172,15 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>Bug sweep on inspection UI</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>camera retries, upload resume, offline queue</t>
-        </is>
-      </c>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -4024,7 +4200,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -4034,12 +4210,12 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr"/>
@@ -4072,12 +4248,12 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr"/>
@@ -4090,7 +4266,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -4100,25 +4276,25 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr"/>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr"/>
+          <t>Full T-103 suite</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -4149,12 +4325,12 @@
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>Full T-103 suite</t>
+          <t>14-day outcome survey cron</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+          <t>Brevo trigger + Supabase write-back</t>
         </is>
       </c>
     </row>
@@ -4187,12 +4363,12 @@
       <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>14-day outcome survey cron</t>
+          <t>Additional UI locales</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Brevo trigger + Supabase write-back</t>
+          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
         </is>
       </c>
     </row>
@@ -4219,18 +4395,18 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Additional UI locales</t>
+          <t>i18n audit phase 2</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
+          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
         </is>
       </c>
     </row>
@@ -4257,57 +4433,19 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P2 Post-launch</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>i18n audit phase 2</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>T-063</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr"/>
-      <c r="G64" s="7" t="inlineStr">
-        <is>
           <t>App Store + Play production updates with post-launch fixes</t>
         </is>
       </c>
-      <c r="H64" s="7" t="inlineStr"/>
+      <c r="H63" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H64"/>
+  <autoFilter ref="A1:H63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4318,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5357,29 +5495,17 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
-        </is>
-      </c>
+          <t>ECB daily refresh cron, KILLED 2026-05-08. No FX surface: pricing jurisdiction-pinned via TIER_PRICE_CENTS + CURRENCY[jurisdiction] in src/lib/payments/stripe.ts</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -5399,7 +5525,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -5409,17 +5535,17 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>MB-01</t>
+          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
+          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -5456,12 +5582,12 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>MB-03</t>
+          <t>MB-01</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
+          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
         </is>
       </c>
     </row>
@@ -5498,12 +5624,12 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>MB-05</t>
+          <t>MB-03</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
+          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5666,12 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>MB-08</t>
+          <t>MB-05</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
+          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
         </is>
       </c>
     </row>
@@ -5582,12 +5708,12 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>MB-09</t>
+          <t>MB-08</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
+          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5725,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -5619,17 +5745,17 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>App icon set</t>
+          <t>MB-09</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
+          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
         </is>
       </c>
     </row>
@@ -5661,17 +5787,17 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>Splash screens per density, status bar theming, safe-area insets</t>
+          <t>App icon set</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
+          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
         </is>
       </c>
     </row>
@@ -5703,17 +5829,17 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+          <t>Splash screens per density, status bar theming, safe-area insets</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
         </is>
       </c>
     </row>
@@ -5750,17 +5876,59 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
+          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>T-034</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
           <t>Store listing copy drafted in FR + EN</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>description, keywords, support URL, privacy URL — done 2026-04-18 (ahead of schedule): MB-07 shipped docs/store-listings/{ios-fr,ios-en,play-fr,play-en}.md. Professional services register throughout (no buzzwords, no guaranteed-outcome claims), character counts validated inline, Stripe reader-app classification explicitly argued in reviewer notes, data safety section filled for Play form. Awaits MH (nights) review + edit before submission. Commit 50db60f.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H34"/>
+  <autoFilter ref="A1:H35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Post-rotation smoke test verification</t>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
+          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1064,29 +1064,29 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
+          <t>Install scheduled-push v2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Install scheduled-push v2</t>
+          <t>Native Build Bridge plan</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Native Build Bridge plan</t>
+          <t>Google Workspace subscription on `tenu.world`</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Google Workspace subscription on `tenu.world`</t>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
+          <t>Before 11 May</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Before 11 May</t>
+          <t>Decide Apple IAP stance</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>Magic-link auth working inside app</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -1350,14 +1350,14 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
         </is>
       </c>
     </row>
@@ -1460,14 +1460,14 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+          <t>F&amp;F invite list</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -1482,19 +1482,19 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -1504,41 +1504,41 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>T-103-core pipeline tests</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -1548,14 +1548,14 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -1565,46 +1565,46 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>Recover Brevo account access</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+          <t>Suivi avocat·e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -1614,41 +1614,41 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+          <t>Médiateur de la consommation</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Recover Brevo account access</t>
+          <t>Bug sweep on inspection UI</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -1658,14 +1658,14 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Suivi avocat·e</t>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -1680,19 +1680,19 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation</t>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Bug sweep on inspection UI</t>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -1724,14 +1724,14 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
         </is>
       </c>
     </row>
@@ -1768,14 +1768,14 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -1790,14 +1790,14 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -1812,14 +1812,14 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -1834,14 +1834,14 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -1856,73 +1856,51 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+          <t>Wire e2e env</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+          <t>Lawyer formal sign-off letter (FR avocat + UK solicitor)</t>
         </is>
       </c>
     </row>
@@ -3052,12 +3030,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -3072,17 +3050,17 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Post-rotation smoke test verification</t>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green</t>
+          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
         </is>
       </c>
     </row>
@@ -3097,14 +3075,14 @@
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3114,19 +3092,15 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
-        </is>
-      </c>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3161,7 +3135,7 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr"/>
@@ -3199,7 +3173,7 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr"/>
@@ -3232,12 +3206,12 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr"/>
@@ -3275,7 +3249,7 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
@@ -3308,12 +3282,12 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
@@ -3351,7 +3325,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr"/>
@@ -3374,25 +3348,25 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr"/>
+          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3412,25 +3386,25 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr"/>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
-        </is>
-      </c>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3440,7 +3414,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -3460,12 +3434,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr"/>
@@ -3478,7 +3452,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -3503,10 +3477,14 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr"/>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>re-dated 2026-05-03: depends on CC web-only listing revision (line in DECISION 2026-05-03 section).</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -3526,7 +3504,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3536,15 +3514,19 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr"/>
+          <t>Decide Apple IAP stance</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>physical service argument documented — re-dated 2026-05-03: needs to land before App Store reviewer notes lock.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3554,7 +3536,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -3564,7 +3546,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -3574,19 +3556,15 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>re-dated 2026-05-03: depends on CC web-only listing revision (line in DECISION 2026-05-03 section).</t>
-        </is>
-      </c>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3596,7 +3574,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -3606,7 +3584,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -3621,12 +3599,12 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
+          <t>Magic-link auth working inside app</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>physical service argument documented — re-dated 2026-05-03: needs to land before App Store reviewer notes lock.</t>
+          <t>email link opens app, session persists</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3631,17 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr"/>
@@ -3696,19 +3674,15 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>email link opens app, session persists</t>
-        </is>
-      </c>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3733,17 +3707,17 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr"/>
@@ -3759,14 +3733,14 @@
           <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -3776,17 +3750,17 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>T-103-core pipeline tests</t>
+          <t>Médiateur de la consommation</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>unit + integration for critical path only, skip full 48-item P0 coverage</t>
+          <t>comparer MEDICYS vs CM2C (frais d'adhésion, délai de saisine, périmètre B2C numérique), choisir, signer, publier le nom dans CGU §11 + remboursement §6 + mentions légales §médiation — opened 2026-05-07: shortlist réduite à MEDICYS + CM2C, à arbitrer cette semaine. Obligation L612-1 Code de la conso pour activité B2C en ligne, blocage de la mise en service tant que le médiateur n'est pas adhéré.</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3782,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -3818,12 +3792,12 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr"/>
@@ -3846,7 +3820,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -3856,12 +3830,12 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr"/>
@@ -3877,9 +3851,9 @@
           <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -3894,19 +3868,15 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>comparer MEDICYS vs CM2C (frais d'adhésion, délai de saisine, périmètre B2C numérique), choisir, signer, publier le nom dans CGU §11 + remboursement §6 + mentions légales §médiation — opened 2026-05-07: shortlist réduite à MEDICYS + CM2C, à arbitrer cette semaine. Obligation L612-1 Code de la conso pour activité B2C en ligne, blocage de la mise en service tant que le médiateur n'est pas adhéré.</t>
-        </is>
-      </c>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -3936,15 +3906,19 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr"/>
+          <t>F&amp;F invite list</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>8 names, email, jurisdiction, case type</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -3974,12 +3948,12 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr"/>
@@ -3992,7 +3966,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -4002,7 +3976,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -4012,15 +3986,19 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr"/>
+          <t>Bug sweep on inspection UI</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>camera retries, upload resume, offline queue</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -4030,7 +4008,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -4040,7 +4018,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -4050,19 +4028,15 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>8 names, email, jurisdiction, case type</t>
-        </is>
-      </c>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -4072,7 +4046,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -4092,12 +4066,12 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr"/>
@@ -4120,7 +4094,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -4130,19 +4104,15 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>Bug sweep on inspection UI</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>camera retries, upload resume, offline queue</t>
-        </is>
-      </c>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -4152,7 +4122,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -4167,20 +4137,20 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr"/>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr"/>
+          <t>Full T-103 suite</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -4190,7 +4160,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -4200,25 +4170,25 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr"/>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr"/>
+          <t>14-day outcome survey cron</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>Brevo trigger + Supabase write-back</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -4228,7 +4198,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -4238,25 +4208,25 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr"/>
+          <t>Additional UI locales</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -4281,18 +4251,18 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr"/>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Full T-103 suite</t>
+          <t>i18n audit phase 2</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
         </is>
       </c>
     </row>
@@ -4325,14 +4295,10 @@
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>14-day outcome survey cron</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>Brevo trigger + Supabase write-back</t>
-        </is>
-      </c>
+          <t>App Store + Play production updates with post-launch fixes</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -4357,20 +4323,16 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>Additional UI locales</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
-        </is>
-      </c>
+          <t>Add scans.pdf_url + scans.pdf_sha256 columns; migrate from risk_score.pdfUrl jsonb.</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -4401,14 +4363,10 @@
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>i18n audit phase 2</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
-        </is>
-      </c>
+          <t>Extract /api/pdf/build dedicated route with runtime='nodejs' + maxDuration=60; trigger async from /api/ai/scan.</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -4433,13 +4391,13 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>App Store + Play production updates with post-launch fixes</t>
+          <t>Switch R2 PDF URLs to signed URLs with renewable TTL (default 30 days).</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr"/>
@@ -4470,13 +4428,21 @@
           <t>P1 Important</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr"/>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Add scans.pdf_url + scans.pdf_sha256 columns; migrate from risk_score.pdfUrl jsonb.</t>
-        </is>
-      </c>
-      <c r="H64" s="7" t="inlineStr"/>
+          <t>Wire e2e env</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>create .env.test.local with Supabase service-role key + Stripe test keys so npm run test:e2e actually executes</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -4504,13 +4470,21 @@
           <t>P1 Important</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr"/>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>Extract /api/pdf/build dedicated route with runtime='nodejs' + maxDuration=60; trigger async from /api/ai/scan.</t>
-        </is>
-      </c>
-      <c r="H65" s="7" t="inlineStr"/>
+          <t>Lawyer formal sign-off letter (FR avocat + UK solicitor)</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>agreed in principle 2026-05-08; formal letter required before paid signups open beyond F&amp;F cohort</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -4535,16 +4509,24 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="inlineStr"/>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>Switch R2 PDF URLs to signed URLs with renewable TTL (default 30 days).</t>
-        </is>
-      </c>
-      <c r="H66" s="7" t="inlineStr"/>
+          <t>Consider promoting /inspection/new DPA gate from client-side useEffect to middleware for defence-in-depth</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>currently a router.replace() in useEffect (f9aea8a), not server-enforced</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H66"/>
@@ -4558,7 +4540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5335,7 +5317,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -5355,17 +5337,17 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
+          <t>Post-rotation smoke test verification</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
+          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green — done 2026-05-08: Playwright spec + fixture + playwright.config.ts landed via 6ce9b29 (e2e/post-rotation-smoke.spec.ts). Full execution requires .env.test.local with Supabase service role + Stripe test keys; env wiring deferred to v0.1 (see p:1 follow-up line in POST-LAUNCH).</t>
         </is>
       </c>
     </row>
@@ -5397,17 +5379,17 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
+          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
+          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
         </is>
       </c>
     </row>
@@ -5444,12 +5426,12 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
+          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
+          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
         </is>
       </c>
     </row>
@@ -5481,17 +5463,17 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
+          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2 — done 2026-04-19: shipped via MB-16 (commit d77d85b, 2026-04-19); architectural deltas captured as 3 new p:1 hardening lines below.</t>
+          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
         </is>
       </c>
     </row>
@@ -5523,17 +5505,17 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Brevo transactional email leg</t>
+          <t>PDF generation leg</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
+          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2 — done 2026-04-19: shipped via MB-16 (commit d77d85b, 2026-04-19); architectural deltas captured as 3 new p:1 hardening lines below.</t>
         </is>
       </c>
     </row>
@@ -5555,27 +5537,27 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Delete iCloud dedup files on Mac</t>
+          <t>Brevo transactional email leg</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run. — done 2026-05-03: real damage was 2.7× larger than originally scoped. Total cleaned: 113 dedup files (109 src/app metadata route dedups across icon/apple-icon/opengraph-image/robots/sitemap × 21-22 each, 3 in scripts/, 1 in docs/paperclip-briefs/) + 121 empty paren-numbered directories under src/app/ + 4 space-numbered directories under src/app/auth/ (accept-terms 2, callback 2, callback 3, login 2 — verified to be older stale snapshots predating the i18n + signup-flow fixes, no imports, originals intact) + 2 i18n dictionary dedups (ar 2.json, zh 2.json) = grand total 240 entries. Verified: `find` returns 0 dedups repo-wide; `npm run build` exit 0 with all routes (icon, opengraph-image, robots.txt, sitemap.xml, manifest.webmanifest, /legal/*, /auth/*, /inspection/*, /features/*) compiled cleanly; Next.js convention parents (icon.tsx, apple-icon.tsx, opengraph-image.tsx, robots.ts, sitemap.ts) all present. Root cause documented: dual mirroring by iCloud (parens-N suffix) AND OneDrive (space-N suffix) on the old `~/Documents/Claude/Projects/Tenu.World/` path. Repo now lives at `~/Code/Tenu.World/` (no iCloud xattrs). Confirm OneDrive isn't mirroring `~/Code/` either to prevent recurrence.</t>
+          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
         </is>
       </c>
     </row>
@@ -5597,27 +5579,27 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Capacitor 7 scaffold</t>
+          <t>Delete iCloud dedup files on Mac</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
+          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run. — done 2026-05-03: real damage was 2.7× larger than originally scoped. Total cleaned: 113 dedup files (109 src/app metadata route dedups across icon/apple-icon/opengraph-image/robots/sitemap × 21-22 each, 3 in scripts/, 1 in docs/paperclip-briefs/) + 121 empty paren-numbered directories under src/app/ + 4 space-numbered directories under src/app/auth/ (accept-terms 2, callback 2, callback 3, login 2 — verified to be older stale snapshots predating the i18n + signup-flow fixes, no imports, originals intact) + 2 i18n dictionary dedups (ar 2.json, zh 2.json) = grand total 240 entries. Verified: `find` returns 0 dedups repo-wide; `npm run build` exit 0 with all routes (icon, opengraph-image, robots.txt, sitemap.xml, manifest.webmanifest, /legal/*, /auth/*, /inspection/*, /features/*) compiled cleanly; Next.js convention parents (icon.tsx, apple-icon.tsx, opengraph-image.tsx, robots.ts, sitemap.ts) all present. Root cause documented: dual mirroring by iCloud (parens-N suffix) AND OneDrive (space-N suffix) on the old `~/Documents/Claude/Projects/Tenu.World/` path. Repo now lives at `~/Code/Tenu.World/` (no iCloud xattrs). Confirm OneDrive isn't mirroring `~/Code/` either to prevent recurrence.</t>
         </is>
       </c>
     </row>
@@ -5654,12 +5636,12 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+          <t>Capacitor 7 scaffold</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
+          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
         </is>
       </c>
     </row>
@@ -5684,14 +5666,26 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron, KILLED 2026-05-08. No FX surface: pricing jurisdiction-pinned via TIER_PRICE_CENTS + CURRENCY[jurisdiction] in src/lib/payments/stripe.ts</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr"/>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -5711,7 +5705,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -5721,17 +5715,17 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
+          <t>done 2026-05-08: gate landed via f9aea8a (useEffect client-side redirect on /inspection/new), version pinning via supabase/migrations/005_profile_consent_cache.sql, touchpoints via /auth/accept-terms + /api/checkout waiver + CNIL banner. Merged into main via b54db18.</t>
         </is>
       </c>
     </row>
@@ -5756,26 +5750,14 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>MB-01</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
-        </is>
-      </c>
+          <t>ECB daily refresh cron, KILLED 2026-05-08. No FX surface: pricing jurisdiction-pinned via TIER_PRICE_CENTS + CURRENCY[jurisdiction] in src/lib/payments/stripe.ts</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -5795,7 +5777,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -5805,17 +5787,17 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>MB-03</t>
+          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
+          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5834,12 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>MB-05</t>
+          <t>MB-01</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
+          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
         </is>
       </c>
     </row>
@@ -5894,12 +5876,12 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>MB-08</t>
+          <t>MB-03</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
+          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
         </is>
       </c>
     </row>
@@ -5936,12 +5918,12 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>MB-09</t>
+          <t>MB-05</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
+          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
         </is>
       </c>
     </row>
@@ -5953,7 +5935,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -5973,17 +5955,17 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>App icon set</t>
+          <t>MB-08</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
+          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5977,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -6015,17 +5997,17 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Splash screens per density, status bar theming, safe-area insets</t>
+          <t>MB-09</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
+          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
         </is>
       </c>
     </row>
@@ -6057,17 +6039,17 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+          <t>App icon set</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
         </is>
       </c>
     </row>
@@ -6099,22 +6081,148 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Splash screens per density, status bar theming, safe-area insets</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>T-037</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>T-038</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>Store listing copy drafted in FR + EN</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>description, keywords, support URL, privacy URL — done 2026-04-18 (ahead of schedule): MB-07 shipped docs/store-listings/{ios-fr,ios-en,play-fr,play-en}.md. Professional services register throughout (no buzzwords, no guaranteed-outcome claims), character counts validated inline, Stripe reader-app classification explicitly argued in reviewer notes, data safety section filled for Play form. Awaits MH (nights) review + edit before submission. Commit 50db60f.</t>
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>T-039</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>T-103-core pipeline tests</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>unit + integration for critical path only, skip full 48-item P0 coverage — done 2026-05-08: 4 vitest files shipped via f1cb161 (src/tests/{ai-dispute,ai-scan,webhooks-stripe,pricing-calculate}.test.ts), 10 tests all passing. Vitest run: 4 files / 10 tests, exit 0.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H37"/>
+  <autoFilter ref="A1:H40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -697,12 +697,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -712,14 +712,14 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>Update store-listing copy + welcome email + landing page to reflect web-first launch + native binaries follow</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Update store-listing copy + welcome email + landing page to reflect web-first launch + native binaries follow</t>
+          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
+          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
+          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
+          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
+          <t>Google Play Console developer account, USD 25 one-time</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
+          <t>Audit hidden env vars</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Audit hidden env vars</t>
+          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
+          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
+          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -1042,29 +1042,29 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
+          <t>Install scheduled-push v2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Install scheduled-push v2</t>
+          <t>Native Build Bridge plan</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Native Build Bridge plan</t>
+          <t>Google Workspace subscription on `tenu.world`</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Google Workspace subscription on `tenu.world`</t>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
+          <t>Before 11 May</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Before 11 May</t>
+          <t>Decide Apple IAP stance</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
+          <t>Magic-link auth working inside app</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
         </is>
       </c>
     </row>
@@ -1306,14 +1306,14 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
+          <t>F&amp;F invite list</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
     </row>
@@ -1494,24 +1494,24 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
         </is>
       </c>
     </row>
@@ -1538,24 +1538,24 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+          <t>Recover Brevo account access</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Recover Brevo account access</t>
+          <t>Suivi avocat·e</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Suivi avocat·e</t>
+          <t>Médiateur de la consommation</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -1614,14 +1614,14 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation</t>
+          <t>Bug sweep on inspection UI</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -1636,19 +1636,19 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Bug sweep on inspection UI</t>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -1658,14 +1658,14 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
         </is>
       </c>
     </row>
@@ -1746,14 +1746,14 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
         </is>
       </c>
     </row>
@@ -1790,14 +1790,14 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
         </is>
       </c>
     </row>
@@ -1834,29 +1834,29 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+          <t>Wire e2e env</t>
         </is>
       </c>
     </row>
@@ -1877,28 +1877,6 @@
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>Wire e2e env</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>Lawyer formal sign-off letter (FR avocat + UK solicitor)</t>
         </is>
@@ -1915,7 +1893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2389,9 +2367,9 @@
           <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -2406,19 +2384,15 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>submitted 2026-05-03, documents sent to Apple, awaiting verification (per Dr Mubashir). Apple identity check typically 2-5 business days; D-U-N-S verification gates the review. Track unblocking of Xcode signing / TestFlight upload off this line.</t>
-        </is>
-      </c>
+          <t>Google Play Console developer account, USD 25 one-time</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -2453,7 +2427,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
@@ -2486,15 +2460,19 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr"/>
+          <t>Google Workspace subscription on `tenu.world`</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>create `ops@tenu.world` (owner) + `support@tenu.world` + `dpo@tenu.world` (aliases acceptable)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2529,14 +2507,10 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Google Workspace subscription on `tenu.world`</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>create `ops@tenu.world` (owner) + `support@tenu.world` + `dpo@tenu.world` (aliases acceptable)</t>
-        </is>
-      </c>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2571,7 +2545,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr"/>
@@ -2609,7 +2583,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr"/>
@@ -2647,7 +2621,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
@@ -2685,7 +2659,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr"/>
@@ -2718,15 +2692,19 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr"/>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>expect no 403 org_internal, consent screen shows "Tenu" with `support@tenu.world`</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2761,12 +2739,12 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>expect no 403 org_internal, consent screen shows "Tenu" with `support@tenu.world`</t>
+          <t>do not archive, the secret is burned</t>
         </is>
       </c>
     </row>
@@ -2803,12 +2781,12 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>do not archive, the secret is burned</t>
+          <t>revokes the leaked secret at source even if a copy is still cached somewhere</t>
         </is>
       </c>
     </row>
@@ -2840,17 +2818,17 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+          <t>Before 11 May</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>revokes the leaked secret at source even if a copy is still cached somewhere</t>
+          <t>publish OAuth consent screen Testing → Production (requires domain verified + privacy URL + terms URL live at tenu.world/legal/privacy + /legal/terms)</t>
         </is>
       </c>
     </row>
@@ -2882,17 +2860,17 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Before 11 May</t>
+          <t>Audit hidden env vars</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>publish OAuth consent screen Testing → Production (requires domain verified + privacy URL + terms URL live at tenu.world/legal/privacy + /legal/terms)</t>
+          <t>scroll full Vercel env var list below the fold, confirm ANTHROPIC_API_KEY + BREVO_API_KEY + TELEGRAM_BOT_TOKEN + any other secret either shows Need To Rotate (rotate it) or was created Sensitive from day one (leave alone). If any non-public secret is unflagged and NOT marked Sensitive, treat as exposed and rotate</t>
         </is>
       </c>
     </row>
@@ -2929,12 +2907,12 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Audit hidden env vars</t>
+          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>scroll full Vercel env var list below the fold, confirm ANTHROPIC_API_KEY + BREVO_API_KEY + TELEGRAM_BOT_TOKEN + any other secret either shows Need To Rotate (rotate it) or was created Sensitive from day one (leave alone). If any non-public secret is unflagged and NOT marked Sensitive, treat as exposed and rotate</t>
+          <t>Google Cloud Console → APIs &amp; Services → Credentials → restrict to HTTP referrers `*.tenu.world` + `localhost:*` + enable only Maps JavaScript + Places API. Public by design, not flagged by Vercel, but unrestricted = scraping risk against Global Apex billing</t>
         </is>
       </c>
     </row>
@@ -2971,12 +2949,12 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
+          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Google Cloud Console → APIs &amp; Services → Credentials → restrict to HTTP referrers `*.tenu.world` + `localhost:*` + enable only Maps JavaScript + Places API. Public by design, not flagged by Vercel, but unrestricted = scraping risk against Global Apex billing</t>
+          <t>hardening pass, single biggest structural lesson from this incident. Anything that isn't a NEXT_PUBLIC_* or a non-secret identifier (R2_ACCOUNT_ID, R2_BUCKET_NAME) should be Sensitive</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2966,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -3008,17 +2986,17 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>hardening pass, single biggest structural lesson from this incident. Anything that isn't a NEXT_PUBLIC_* or a non-secret identifier (R2_ACCOUNT_ID, R2_BUCKET_NAME) should be Sensitive</t>
+          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
         </is>
       </c>
     </row>
@@ -3033,14 +3011,14 @@
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -3050,19 +3028,15 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
-        </is>
-      </c>
+          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3097,7 +3071,7 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr"/>
@@ -3135,7 +3109,7 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr"/>
@@ -3168,12 +3142,12 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr"/>
@@ -3211,7 +3185,7 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr"/>
@@ -3244,12 +3218,12 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
@@ -3287,7 +3261,7 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
@@ -3310,25 +3284,25 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr"/>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr"/>
+          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3348,25 +3322,25 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr"/>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
-        </is>
-      </c>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3376,7 +3350,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -3386,7 +3360,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -3396,12 +3370,12 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr"/>
@@ -3424,7 +3398,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -3434,15 +3408,19 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr"/>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>re-dated 2026-05-03: depends on CC web-only listing revision (line in DECISION 2026-05-03 section).</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3472,17 +3450,17 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
+          <t>Decide Apple IAP stance</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>re-dated 2026-05-03: depends on CC web-only listing revision (line in DECISION 2026-05-03 section).</t>
+          <t>physical service argument documented — re-dated 2026-05-03: needs to land before App Store reviewer notes lock.</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3472,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -3504,7 +3482,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3514,19 +3492,15 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>physical service argument documented — re-dated 2026-05-03: needs to land before App Store reviewer notes lock.</t>
-        </is>
-      </c>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3556,15 +3530,19 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr"/>
+          <t>Magic-link auth working inside app</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>email link opens app, session persists</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3589,24 +3567,20 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>email link opens app, session persists</t>
-        </is>
-      </c>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -3631,17 +3605,17 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr"/>
@@ -3679,7 +3653,7 @@
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr"/>
@@ -3695,14 +3669,14 @@
           <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -3712,15 +3686,19 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr"/>
+          <t>Médiateur de la consommation</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>comparer MEDICYS vs CM2C (frais d'adhésion, délai de saisine, périmètre B2C numérique), choisir, signer, publier le nom dans CGU §11 + remboursement §6 + mentions légales §médiation — opened 2026-05-07: shortlist réduite à MEDICYS + CM2C, à arbitrer cette semaine. Obligation L612-1 Code de la conso pour activité B2C en ligne, blocage de la mise en service tant que le médiateur n'est pas adhéré.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -3733,9 +3711,9 @@
           <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -3750,19 +3728,15 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>comparer MEDICYS vs CM2C (frais d'adhésion, délai de saisine, périmètre B2C numérique), choisir, signer, publier le nom dans CGU §11 + remboursement §6 + mentions légales §médiation — opened 2026-05-07: shortlist réduite à MEDICYS + CM2C, à arbitrer cette semaine. Obligation L612-1 Code de la conso pour activité B2C en ligne, blocage de la mise en service tant que le médiateur n'est pas adhéré.</t>
-        </is>
-      </c>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -3797,7 +3771,7 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr"/>
@@ -3830,12 +3804,12 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr"/>
@@ -3868,15 +3842,19 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr"/>
+          <t>F&amp;F invite list</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>8 names, email, jurisdiction, case type</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -3906,19 +3884,15 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>8 names, email, jurisdiction, case type</t>
-        </is>
-      </c>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -3928,7 +3902,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -3938,7 +3912,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -3948,15 +3922,19 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr"/>
+          <t>Bug sweep on inspection UI</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>camera retries, upload resume, offline queue</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -3986,19 +3964,15 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>Bug sweep on inspection UI</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr">
-        <is>
-          <t>camera retries, upload resume, offline queue</t>
-        </is>
-      </c>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -4018,7 +3992,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -4028,12 +4002,12 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr"/>
@@ -4066,12 +4040,12 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr"/>
@@ -4084,7 +4058,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -4094,25 +4068,25 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr"/>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr"/>
+          <t>Full T-103 suite</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -4143,12 +4117,12 @@
       <c r="F56" s="5" t="inlineStr"/>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>Full T-103 suite</t>
+          <t>14-day outcome survey cron</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+          <t>Brevo trigger + Supabase write-back</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4155,12 @@
       <c r="F57" s="5" t="inlineStr"/>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>14-day outcome survey cron</t>
+          <t>Additional UI locales</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>Brevo trigger + Supabase write-back</t>
+          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
         </is>
       </c>
     </row>
@@ -4213,18 +4187,18 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>Additional UI locales</t>
+          <t>i18n audit phase 2</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
+          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
         </is>
       </c>
     </row>
@@ -4251,20 +4225,16 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P2 Post-launch</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr"/>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>i18n audit phase 2</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
-        </is>
-      </c>
+          <t>App Store + Play production updates with post-launch fixes</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -4289,13 +4259,13 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>App Store + Play production updates with post-launch fixes</t>
+          <t>Add scans.pdf_url + scans.pdf_sha256 columns; migrate from risk_score.pdfUrl jsonb.</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr"/>
@@ -4329,7 +4299,7 @@
       <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>Add scans.pdf_url + scans.pdf_sha256 columns; migrate from risk_score.pdfUrl jsonb.</t>
+          <t>Extract /api/pdf/build dedicated route with runtime='nodejs' + maxDuration=60; trigger async from /api/ai/scan.</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr"/>
@@ -4363,7 +4333,7 @@
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Extract /api/pdf/build dedicated route with runtime='nodejs' + maxDuration=60; trigger async from /api/ai/scan.</t>
+          <t>Switch R2 PDF URLs to signed URLs with renewable TTL (default 30 days).</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr"/>
@@ -4394,13 +4364,21 @@
           <t>P1 Important</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr"/>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Switch R2 PDF URLs to signed URLs with renewable TTL (default 30 days).</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr"/>
+          <t>Wire e2e env</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>create .env.test.local with Supabase service-role key + Stripe test keys so npm run test:e2e actually executes</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -4435,12 +4413,12 @@
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Wire e2e env</t>
+          <t>Lawyer formal sign-off letter (FR avocat + UK solicitor)</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>create .env.test.local with Supabase service-role key + Stripe test keys so npm run test:e2e actually executes</t>
+          <t>agreed in principle 2026-05-08; formal letter required before paid signups open beyond F&amp;F cohort</t>
         </is>
       </c>
     </row>
@@ -4467,69 +4445,27 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P2 Post-launch</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>Lawyer formal sign-off letter (FR avocat + UK solicitor)</t>
+          <t>Consider promoting /inspection/new DPA gate from client-side useEffect to middleware for defence-in-depth</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>agreed in principle 2026-05-08; formal letter required before paid signups open beyond F&amp;F cohort</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>T-065</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G66" s="7" t="inlineStr">
-        <is>
-          <t>Consider promoting /inspection/new DPA gate from client-side useEffect to middleware for defence-in-depth</t>
-        </is>
-      </c>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
           <t>currently a router.replace() in useEffect (f9aea8a), not server-enforced</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H66"/>
+  <autoFilter ref="A1:H65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4540,7 +4476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4964,12 +4900,12 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Paste ANTHROPIC_API_KEY into .env.local + Vercel project env</t>
+          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
+          <t>submitted 2026-05-03, documents sent to Apple, awaiting verification (per Dr Mubashir). Apple identity check typically 2-5 business days; D-U-N-S verification gates the review. Track unblocking of Xcode signing / TestFlight upload off this line.</t>
         </is>
       </c>
     </row>
@@ -5006,7 +4942,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Paste BREVO_API_KEY into .env.local + Vercel project env</t>
+          <t>Paste ANTHROPIC_API_KEY into .env.local + Vercel project env</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -5033,7 +4969,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -5043,17 +4979,17 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>SOT consolidation</t>
+          <t>Paste BREVO_API_KEY into .env.local + Vercel project env</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>fix CLAUDE.md project path, refresh CLAUDE-CONTEXT.md to current React/in-code stack, replace stale-clone CLAUDE.md + CLAUDE-CONTEXT.md with redirect stubs — done 2026-04-19: SOT CLAUDE.md now declares `/Users/mmh/Documents/Claude/Projects/Tenu.World/` as canonical at the top, project structure block rewritten to match real layout (no nested `app/` wrapper, lists ios/, android/, mobile/, resources/, supabase/, scripts/). SOT CLAUDE-CONTEXT.md fully refreshed: dropped Webflow/Make.com/Tally/Airtable/Asana/Placid references, added pricing matrix, in-code pipeline, build timeline through 11 May, brand SOT pointers. Stale clone at `/Users/mmh/Documents/Global Apex/Tenu/` now has redirect-only CLAUDE.md + CLAUDE-CONTEXT.md so any agent invoked from that path bounces immediately.</t>
+          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5011,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -5085,17 +5021,17 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
+          <t>SOT consolidation</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>`client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json`, the same with " (1)" suffix, and `stripe_backup_code.txt`. All three are sitting in plaintext in a Documents folder (iCloud-syncable, Time-Machine-backupable). Move to `~/.secrets/` or 1Password, then `rm` from disk. **Do NOT git commit them anywhere.** — done 2026-05-03: stripe_backup_code.txt contents migrated to 1Password as Secure Note "Stripe 2FA backup codes — Global Apex NET" (per Dr Mubashir). Two client_secret JSON files deleted (burned credentials, no preservation needed — Cloud project shutdown will close the trust loop). All three files removed from disk via `rm -rf` on parent folder. Verify by inspection: `/Users/mmh/Documents/Global Apex/Tenu/` no longer exists.</t>
+          <t>fix CLAUDE.md project path, refresh CLAUDE-CONTEXT.md to current React/in-code stack, replace stale-clone CLAUDE.md + CLAUDE-CONTEXT.md with redirect stubs — done 2026-04-19: SOT CLAUDE.md now declares `/Users/mmh/Documents/Claude/Projects/Tenu.World/` as canonical at the top, project structure block rewritten to match real layout (no nested `app/` wrapper, lists ios/, android/, mobile/, resources/, supabase/, scripts/). SOT CLAUDE-CONTEXT.md fully refreshed: dropped Webflow/Make.com/Tally/Airtable/Asana/Placid references, added pricing matrix, in-code pipeline, build timeline through 11 May, brand SOT pointers. Stale clone at `/Users/mmh/Documents/Global Apex/Tenu/` now has redirect-only CLAUDE.md + CLAUDE-CONTEXT.md so any agent invoked from that path bounces immediately.</t>
         </is>
       </c>
     </row>
@@ -5117,27 +5053,27 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
+          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>`01-Legal-Checklist.md` (review + dedupe against SOT 05-Legal-Compliance content first), `etat-des-lieux.pdf`, `etat-des-lieux-meuble.pdf`, `modele-etat-des-lieux T2-T3.pdf` into SOT `docs/reference/etat-des-lieux/` (or wherever Dr Mubashir prefers). Delete from stale clone after move — done 2026-05-03: audit found `01-Legal-Checklist.md` already byte-identical between stale and SOT (no migration needed); 3 PDFs in stale folder, two of which (`modele-etat-des-lieux.pdf` and `modele-etat-des-lieux T2-T3.pdf`) are byte-identical (sha 4b9fed2e0c14...) — only one carried over. Final SOT state: `docs/reference/etat-des-lieux/etat-des-lieux-meuble.pdf` (sha 6e1e3f5acd83...) + `docs/reference/etat-des-lieux/modele-etat-des-lieux T2-T3.pdf` (sha 4b9fed2e0c14...). Note: original task line referenced `etat-des-lieux.pdf` which never existed in stale clone — actual filenames discovered during audit.</t>
+          <t>`client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json`, the same with " (1)" suffix, and `stripe_backup_code.txt`. All three are sitting in plaintext in a Documents folder (iCloud-syncable, Time-Machine-backupable). Move to `~/.secrets/` or 1Password, then `rm` from disk. **Do NOT git commit them anywhere.** — done 2026-05-03: stripe_backup_code.txt contents migrated to 1Password as Secure Note "Stripe 2FA backup codes — Global Apex NET" (per Dr Mubashir). Two client_secret JSON files deleted (burned credentials, no preservation needed — Cloud project shutdown will close the trust loop). All three files removed from disk via `rm -rf` on parent folder. Verify by inspection: `/Users/mmh/Documents/Global Apex/Tenu/` no longer exists.</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5095,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -5169,17 +5105,17 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
+          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>archive to `~/Archive/` or `rm -rf`. Sandbox cannot delete the parent folder. — done 2026-05-03 — decision: `rm -rf`, no archive. Audit grounds: (a) 533 MB of the 538 MB total was regenerable node_modules; (b) git remote pointed at the same `malikmubashir/tenu-world.git` with HEAD at `c3614ef` (the original April 3 scaffold commit, redundant with everything in main since); (c) all 10 doc files were either byte-identical to SOT or differed only in COI-scrubbed wording (HEC GEMM / MHF references that SOT correctly removed per role-separation policy in CLAUDE.md); (d) parent had `com.apple.macl` and `com.apple.provenance` xattrs only — NOT iCloud-synced, so no recurring sync source to sever; (e) Time Machine retains snapshots back to April 3 if recovery ever needed. Final stale-clone removal verified: parent path no longer exists. Container `/Users/mmh/Documents/Global Apex/` retained for other uses. Companion finding: the dedup chaos cleaned in the prior task was therefore NOT from active iCloud sync — likely a one-time merge incident from a multi-machine sync, not ongoing. Worth knowing for future repo-cleanup heuristics.</t>
+          <t>`01-Legal-Checklist.md` (review + dedupe against SOT 05-Legal-Compliance content first), `etat-des-lieux.pdf`, `etat-des-lieux-meuble.pdf`, `modele-etat-des-lieux T2-T3.pdf` into SOT `docs/reference/etat-des-lieux/` (or wherever Dr Mubashir prefers). Delete from stale clone after move — done 2026-05-03: audit found `01-Legal-Checklist.md` already byte-identical between stale and SOT (no migration needed); 3 PDFs in stale folder, two of which (`modele-etat-des-lieux.pdf` and `modele-etat-des-lieux T2-T3.pdf`) are byte-identical (sha 4b9fed2e0c14...) — only one carried over. Final SOT state: `docs/reference/etat-des-lieux/etat-des-lieux-meuble.pdf` (sha 6e1e3f5acd83...) + `docs/reference/etat-des-lieux/modele-etat-des-lieux T2-T3.pdf` (sha 4b9fed2e0c14...). Note: original task line referenced `etat-des-lieux.pdf` which never existed in stale clone — actual filenames discovered during audit.</t>
         </is>
       </c>
     </row>
@@ -5206,22 +5142,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Rotate R2_ACCESS_KEY_ID + R2_SECRET_ACCESS_KEY</t>
+          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Cloudflare → R2 → Manage API tokens → new token scoped to tenu-evidence bucket (Object Read/Write only). Paste both into Vercel env, tick Sensitive, redeploy. Smoke: hit /api/mobile/upload-intent and upload a test photo. Then revoke old token in Cloudflare. Existing presigned URLs signed with old key keep working until expiry — done 2026-05-03 (per Dr Mubashir, post-holiday). CC post-rotation E2E smoke owed (line below).</t>
+          <t>archive to `~/Archive/` or `rm -rf`. Sandbox cannot delete the parent folder. — done 2026-05-03 — decision: `rm -rf`, no archive. Audit grounds: (a) 533 MB of the 538 MB total was regenerable node_modules; (b) git remote pointed at the same `malikmubashir/tenu-world.git` with HEAD at `c3614ef` (the original April 3 scaffold commit, redundant with everything in main since); (c) all 10 doc files were either byte-identical to SOT or differed only in COI-scrubbed wording (HEC GEMM / MHF references that SOT correctly removed per role-separation policy in CLAUDE.md); (d) parent had `com.apple.macl` and `com.apple.provenance` xattrs only — NOT iCloud-synced, so no recurring sync source to sever; (e) Time Machine retains snapshots back to April 3 if recovery ever needed. Final stale-clone removal verified: parent path no longer exists. Container `/Users/mmh/Documents/Global Apex/` retained for other uses. Companion finding: the dedup chaos cleaned in the prior task was therefore NOT from active iCloud sync — likely a one-time merge incident from a multi-machine sync, not ongoing. Worth knowing for future repo-cleanup heuristics.</t>
         </is>
       </c>
     </row>
@@ -5258,12 +5194,12 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Rotate STRIPE_WEBHOOK_SECRET</t>
+          <t>Rotate R2_ACCESS_KEY_ID + R2_SECRET_ACCESS_KEY</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Stripe → Developers → Webhooks → endpoint → Roll secret with 24h grace. Paste new into Vercel STRIPE_WEBHOOK_SECRET, tick Sensitive, redeploy. Smoke: `stripe trigger checkout.session.completed` and confirm /api/webhooks/stripe returns 200 in Vercel function logs. Old secret expires automatically at end of grace — done 2026-05-03 (per Dr Mubashir).</t>
+          <t>Cloudflare → R2 → Manage API tokens → new token scoped to tenu-evidence bucket (Object Read/Write only). Paste both into Vercel env, tick Sensitive, redeploy. Smoke: hit /api/mobile/upload-intent and upload a test photo. Then revoke old token in Cloudflare. Existing presigned URLs signed with old key keep working until expiry — done 2026-05-03 (per Dr Mubashir, post-holiday). CC post-rotation E2E smoke owed (line below).</t>
         </is>
       </c>
     </row>
@@ -5300,12 +5236,12 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Rotate SUPABASE_SERVICE_ROLE_KEY AND NEXT_PUBLIC_SUPABASE_ANON_KEY together</t>
+          <t>Rotate STRIPE_WEBHOOK_SECRET</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Supabase → Project Settings → API → JWT Keys → Generate new JWT secret (regenerates both keys, both are JWTs signed by the same secret). Update both values in Vercel in the same save, tick Sensitive on service_role (anon stays public but encrypt-at-rest regardless), redeploy. All pre-rotation sessions invalidated (pre-launch, so non-event). Smoke: incognito magic-link signup → /app-home load → photo upload row insert — done 2026-05-03 (per Dr Mubashir).</t>
+          <t>Stripe → Developers → Webhooks → endpoint → Roll secret with 24h grace. Paste new into Vercel STRIPE_WEBHOOK_SECRET, tick Sensitive, redeploy. Smoke: `stripe trigger checkout.session.completed` and confirm /api/webhooks/stripe returns 200 in Vercel function logs. Old secret expires automatically at end of grace — done 2026-05-03 (per Dr Mubashir).</t>
         </is>
       </c>
     </row>
@@ -5327,7 +5263,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -5337,17 +5273,17 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Post-rotation smoke test verification</t>
+          <t>Rotate SUPABASE_SERVICE_ROLE_KEY AND NEXT_PUBLIC_SUPABASE_ANON_KEY together</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green — done 2026-05-08: Playwright spec + fixture + playwright.config.ts landed via 6ce9b29 (e2e/post-rotation-smoke.spec.ts). Full execution requires .env.test.local with Supabase service role + Stripe test keys; env wiring deferred to v0.1 (see p:1 follow-up line in POST-LAUNCH).</t>
+          <t>Supabase → Project Settings → API → JWT Keys → Generate new JWT secret (regenerates both keys, both are JWTs signed by the same secret). Update both values in Vercel in the same save, tick Sensitive on service_role (anon stays public but encrypt-at-rest regardless), redeploy. All pre-rotation sessions invalidated (pre-launch, so non-event). Smoke: incognito magic-link signup → /app-home load → photo upload row insert — done 2026-05-03 (per Dr Mubashir).</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5295,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5379,17 +5315,17 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
+          <t>Post-rotation smoke test verification</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
+          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green — done 2026-05-08: Playwright spec + fixture + playwright.config.ts landed via 6ce9b29 (e2e/post-rotation-smoke.spec.ts). Full execution requires .env.test.local with Supabase service role + Stripe test keys; env wiring deferred to v0.1 (see p:1 follow-up line in POST-LAUNCH).</t>
         </is>
       </c>
     </row>
@@ -5421,17 +5357,17 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
+          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
+          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
         </is>
       </c>
     </row>
@@ -5468,12 +5404,12 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
+          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
+          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
         </is>
       </c>
     </row>
@@ -5505,17 +5441,17 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>PDF generation leg</t>
+          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2 — done 2026-04-19: shipped via MB-16 (commit d77d85b, 2026-04-19); architectural deltas captured as 3 new p:1 hardening lines below.</t>
+          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
         </is>
       </c>
     </row>
@@ -5547,17 +5483,17 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Brevo transactional email leg</t>
+          <t>PDF generation leg</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
+          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2 — done 2026-04-19: shipped via MB-16 (commit d77d85b, 2026-04-19); architectural deltas captured as 3 new p:1 hardening lines below.</t>
         </is>
       </c>
     </row>
@@ -5579,27 +5515,27 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Delete iCloud dedup files on Mac</t>
+          <t>Brevo transactional email leg</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run. — done 2026-05-03: real damage was 2.7× larger than originally scoped. Total cleaned: 113 dedup files (109 src/app metadata route dedups across icon/apple-icon/opengraph-image/robots/sitemap × 21-22 each, 3 in scripts/, 1 in docs/paperclip-briefs/) + 121 empty paren-numbered directories under src/app/ + 4 space-numbered directories under src/app/auth/ (accept-terms 2, callback 2, callback 3, login 2 — verified to be older stale snapshots predating the i18n + signup-flow fixes, no imports, originals intact) + 2 i18n dictionary dedups (ar 2.json, zh 2.json) = grand total 240 entries. Verified: `find` returns 0 dedups repo-wide; `npm run build` exit 0 with all routes (icon, opengraph-image, robots.txt, sitemap.xml, manifest.webmanifest, /legal/*, /auth/*, /inspection/*, /features/*) compiled cleanly; Next.js convention parents (icon.tsx, apple-icon.tsx, opengraph-image.tsx, robots.ts, sitemap.ts) all present. Root cause documented: dual mirroring by iCloud (parens-N suffix) AND OneDrive (space-N suffix) on the old `~/Documents/Claude/Projects/Tenu.World/` path. Repo now lives at `~/Code/Tenu.World/` (no iCloud xattrs). Confirm OneDrive isn't mirroring `~/Code/` either to prevent recurrence.</t>
+          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
         </is>
       </c>
     </row>
@@ -5621,27 +5557,27 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Capacitor 7 scaffold</t>
+          <t>Delete iCloud dedup files on Mac</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
+          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run. — done 2026-05-03: real damage was 2.7× larger than originally scoped. Total cleaned: 113 dedup files (109 src/app metadata route dedups across icon/apple-icon/opengraph-image/robots/sitemap × 21-22 each, 3 in scripts/, 1 in docs/paperclip-briefs/) + 121 empty paren-numbered directories under src/app/ + 4 space-numbered directories under src/app/auth/ (accept-terms 2, callback 2, callback 3, login 2 — verified to be older stale snapshots predating the i18n + signup-flow fixes, no imports, originals intact) + 2 i18n dictionary dedups (ar 2.json, zh 2.json) = grand total 240 entries. Verified: `find` returns 0 dedups repo-wide; `npm run build` exit 0 with all routes (icon, opengraph-image, robots.txt, sitemap.xml, manifest.webmanifest, /legal/*, /auth/*, /inspection/*, /features/*) compiled cleanly; Next.js convention parents (icon.tsx, apple-icon.tsx, opengraph-image.tsx, robots.ts, sitemap.ts) all present. Root cause documented: dual mirroring by iCloud (parens-N suffix) AND OneDrive (space-N suffix) on the old `~/Documents/Claude/Projects/Tenu.World/` path. Repo now lives at `~/Code/Tenu.World/` (no iCloud xattrs). Confirm OneDrive isn't mirroring `~/Code/` either to prevent recurrence.</t>
         </is>
       </c>
     </row>
@@ -5678,12 +5614,12 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+          <t>Capacitor 7 scaffold</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
+          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
         </is>
       </c>
     </row>
@@ -5715,17 +5651,17 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>done 2026-05-08: gate landed via f9aea8a (useEffect client-side redirect on /inspection/new), version pinning via supabase/migrations/005_profile_consent_cache.sql, touchpoints via /auth/accept-terms + /api/checkout waiver + CNIL banner. Merged into main via b54db18.</t>
+          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
         </is>
       </c>
     </row>
@@ -5750,14 +5686,26 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron, KILLED 2026-05-08. No FX surface: pricing jurisdiction-pinned via TIER_PRICE_CENTS + CURRENCY[jurisdiction] in src/lib/payments/stripe.ts</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr"/>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>done 2026-05-08: gate landed via f9aea8a (useEffect client-side redirect on /inspection/new), version pinning via supabase/migrations/005_profile_consent_cache.sql, touchpoints via /auth/accept-terms + /api/checkout waiver + CNIL banner. Merged into main via b54db18.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -5777,29 +5725,17 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
-        </is>
-      </c>
+          <t>ECB daily refresh cron, KILLED 2026-05-08. No FX surface: pricing jurisdiction-pinned via TIER_PRICE_CENTS + CURRENCY[jurisdiction] in src/lib/payments/stripe.ts</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -5819,7 +5755,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -5829,17 +5765,17 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>MB-01</t>
+          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
+          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -5876,12 +5812,12 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>MB-03</t>
+          <t>MB-01</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
+          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
         </is>
       </c>
     </row>
@@ -5918,12 +5854,12 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>MB-05</t>
+          <t>MB-03</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
+          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5896,12 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>MB-08</t>
+          <t>MB-05</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
+          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
         </is>
       </c>
     </row>
@@ -6002,12 +5938,12 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>MB-09</t>
+          <t>MB-08</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
+          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
         </is>
       </c>
     </row>
@@ -6019,7 +5955,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -6039,17 +5975,17 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>App icon set</t>
+          <t>MB-09</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
+          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
         </is>
       </c>
     </row>
@@ -6081,17 +6017,17 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>Splash screens per density, status bar theming, safe-area insets</t>
+          <t>App icon set</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
+          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
         </is>
       </c>
     </row>
@@ -6123,17 +6059,17 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+          <t>Splash screens per density, status bar theming, safe-area insets</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
         </is>
       </c>
     </row>
@@ -6170,12 +6106,12 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>Store listing copy drafted in FR + EN</t>
+          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>description, keywords, support URL, privacy URL — done 2026-04-18 (ahead of schedule): MB-07 shipped docs/store-listings/{ios-fr,ios-en,play-fr,play-en}.md. Professional services register throughout (no buzzwords, no guaranteed-outcome claims), character counts validated inline, Stripe reader-app classification explicitly argued in reviewer notes, data safety section filled for Play form. Awaits MH (nights) review + edit before submission. Commit 50db60f.</t>
+          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
         </is>
       </c>
     </row>
@@ -6187,42 +6123,84 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>Store listing copy drafted in FR + EN</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>description, keywords, support URL, privacy URL — done 2026-04-18 (ahead of schedule): MB-07 shipped docs/store-listings/{ios-fr,ios-en,play-fr,play-en}.md. Professional services register throughout (no buzzwords, no guaranteed-outcome claims), character counts validated inline, Stripe reader-app classification explicitly argued in reviewer notes, data safety section filled for Play form. Awaits MH (nights) review + edit before submission. Commit 50db60f.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>T-040</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
           <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>T-103-core pipeline tests</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>unit + integration for critical path only, skip full 48-item P0 coverage — done 2026-05-08: 4 vitest files shipped via f1cb161 (src/tests/{ai-dispute,ai-scan,webhooks-stripe,pricing-calculate}.test.ts), 10 tests all passing. Vitest run: 4 files / 10 tests, exit 0.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H40"/>
+  <autoFilter ref="A1:H41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -105,10 +105,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -697,12 +697,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Update store-listing copy + welcome email + landing page to reflect web-first launch + native binaries follow</t>
+          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
+          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
+          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
+          <t>Google Play Console developer account, USD 25 one-time</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
+          <t>Audit hidden env vars</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
+          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Audit hidden env vars</t>
+          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
         </is>
       </c>
     </row>
@@ -900,17 +900,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
+          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
         </is>
       </c>
     </row>
@@ -927,24 +927,24 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
+          <t>Install scheduled-push v2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -954,19 +954,19 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+          <t>Google Workspace subscription on `tenu.world`</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -976,19 +976,19 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -998,36 +998,36 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Install scheduled-push v2</t>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Native Build Bridge plan</t>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Google Workspace subscription on `tenu.world`</t>
+          <t>Before 11 May</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+          <t>Decide Apple IAP stance</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
         </is>
       </c>
     </row>
@@ -1152,14 +1152,14 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -1174,14 +1174,14 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -1218,14 +1218,14 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Before 11 May</t>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -1240,19 +1240,19 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -1262,14 +1262,14 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -1284,14 +1284,14 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+          <t>F&amp;F invite list</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -1306,14 +1306,14 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -1328,36 +1328,36 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -1367,19 +1367,19 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+          <t>Recover Brevo account access</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -1394,14 +1394,14 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+          <t>Suivi avocat·e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -1416,14 +1416,14 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
+          <t>Médiateur de la consommation</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -1438,14 +1438,14 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
+          <t>Create Stripe coupon LAUNCH25</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -1460,14 +1460,14 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -1482,36 +1482,36 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>Run `npm run build:mobile` on Mac to produce non-empty out/ static export</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -1521,19 +1521,19 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+          <t>Fix static export</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -1543,19 +1543,19 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Recover Brevo account access</t>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -1570,36 +1570,36 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Suivi avocat·e</t>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation</t>
+          <t>Bug sweep</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -1609,19 +1609,19 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Bug sweep on inspection UI</t>
+          <t>Wire e2e env</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -1631,252 +1631,10 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>Wire e2e env</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>Lawyer formal sign-off letter (FR avocat + UK solicitor)</t>
         </is>
@@ -1893,7 +1651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1959,9 +1717,9 @@
           <t>DECISION 2026-05-03 — Launch path: Option B (web-only on 11 May)</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -1971,7 +1729,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -1979,14 +1737,14 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>Update store-listing copy + welcome email + landing page to reflect web-first launch + native binaries follow</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>opened 2026-05-03.</t>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>keep their content verbatim, only re-section + re-date so the launch checklist stops bleeding red on items that were never blocking 11 May web-only — opened 2026-05-03.</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1756,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>DECISION 2026-05-03 — Launch path: Option B (web-only on 11 May)</t>
+          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -2008,7 +1766,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -2018,17 +1776,17 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>Native Build Bridge plan</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>write docs/12-Native-Build-Bridge-2026-05-12.md mapping the 11-25 May path: cap add ios + cap add android dependencies, Xcode + Android Studio prerequisites, TestFlight + Play internal track submission, screenshots backlog, App Store reviewer notes refresh — opened 2026-05-03.</t>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Suivi avocat·e</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>relance polie si pas de réponse à J+2 — opened 2026-05-07. Critical path pour décision launch-vs-slip 11 May ; bloque CGU §11 médiateur, mentions légales §médiation, et la levée des bannières DRAFT.</t>
         </is>
       </c>
     </row>
@@ -2040,7 +1798,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>DECISION 2026-05-03 — Launch path: Option B (web-only on 11 May)</t>
+          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -2050,12 +1808,12 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -2063,14 +1821,14 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>Move native-build MH lines (build:mobile, cap add, cap sync, Xcode, Android Studio) into the Native Build Bridge section dated 18-25 May</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>keep their content verbatim, only re-section + re-date so the launch checklist stops bleeding red on items that were never blocking 11 May web-only — opened 2026-05-03.</t>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>depends on CC line above.</t>
         </is>
       </c>
     </row>
@@ -2082,12 +1840,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -2097,22 +1855,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Suivi avocat·e</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>relance polie si pas de réponse à J+2 — opened 2026-05-07. Critical path pour décision launch-vs-slip 11 May ; bloque CGU §11 médiateur, mentions légales §médiation, et la levée des bannières DRAFT.</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Install scheduled-push v2</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>copy scripts/scheduled-tasks/tenu-daily-push.md into ~/Documents/Claude/Scheduled/tenu-daily-push/SKILL.md and drop BREVO_API_KEY into .secrets/brevo.env — re-dated 2026-05-03. CC fixed all 6 hardcoded paths in SKILL.md from `/Users/mmh/Documents/Claude/Projects/Tenu.World/` to `/Users/mmh/Code/Tenu.World/` (root cause of today's 09:04 diagnostic log). Bumped to v2.1. brevo.env.example header path also corrected. SKILL.md installed at ~/Documents/Claude/Scheduled/tenu-daily-push/SKILL.md. .secrets/brevo.env file created but currently holds CC's placeholder text (51 bytes, "xkeysib-PASTE_THE_REAL_KEY_VALUE_HERE"). MH must pull real BREVO_API_KEY from Vercel env panel and overwrite. After overwrite, remove the [&gt;] marker and close [x].</t>
         </is>
       </c>
     </row>
@@ -2124,7 +1882,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -2139,22 +1897,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Personalise + send the UK solicitor brief (review draft, fill recipient name + firm, send by email)</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>depends on CC line above.</t>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Recover Brevo account access</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>can't log in to dashboard as of 2026-05-03. Try password reset at app.brevo.com/account/login → mubashirr@gmail.com. If 2FA is the blocker, contact Brevo support (help.brevo.com) for identity-verified MFA reset. Search Downloads folder for any "brevo" or "recovery" file from original signup. Needed before F&amp;F cohort outcome data starts coming in mid-May (template tuning + bounce monitoring)</t>
         </is>
       </c>
     </row>
@@ -2169,9 +1927,9 @@
           <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -2181,7 +1939,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -2189,16 +1947,12 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Install scheduled-push v2</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>copy scripts/scheduled-tasks/tenu-daily-push.md into ~/Documents/Claude/Scheduled/tenu-daily-push/SKILL.md and drop BREVO_API_KEY into .secrets/brevo.env — re-dated 2026-05-03. CC fixed all 6 hardcoded paths in SKILL.md from `/Users/mmh/Documents/Claude/Projects/Tenu.World/` to `/Users/mmh/Code/Tenu.World/` (root cause of today's 09:04 diagnostic log). Bumped to v2.1. brevo.env.example header path also corrected. SKILL.md installed at ~/Documents/Claude/Scheduled/tenu-daily-push/SKILL.md. .secrets/brevo.env file created but currently holds CC's placeholder text (51 bytes, "xkeysib-PASTE_THE_REAL_KEY_VALUE_HERE"). MH must pull real BREVO_API_KEY from Vercel env panel and overwrite. After overwrite, remove the [&gt;] marker and close [x].</t>
-        </is>
-      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2223,24 +1977,20 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>Recover Brevo account access</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>can't log in to dashboard as of 2026-05-03. Try password reset at app.brevo.com/account/login → mubashirr@gmail.com. If 2FA is the blocker, contact Brevo support (help.brevo.com) for identity-verified MFA reset. Search Downloads folder for any "brevo" or "recovery" file from original signup. Needed before F&amp;F cohort outcome data starts coming in mid-May (template tuning + bounce monitoring)</t>
-        </is>
-      </c>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2273,12 +2023,12 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>Check D-U-N-S number for Global Apex NET SAS at dnb.com/duns-number-lookup</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2311,12 +2061,12 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>Email UK housing-law solicitor for fixed-fee TDS/DPS template review, GBP 500-1500 budget</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Google Play Console developer account, USD 25 one-time</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2349,12 +2099,12 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>Email French avocat droit immobilier for fixed-fee legal v1.0 review</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2384,15 +2134,19 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Google Play Console developer account, USD 25 one-time</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr"/>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Google Workspace subscription on `tenu.world`</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>create `ops@tenu.world` (owner) + `support@tenu.world` + `dpo@tenu.world` (aliases acceptable)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -2422,15 +2176,15 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Confirm SAS legal name + siège exactly match Apple + Play enrolment forms</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr"/>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -2463,16 +2217,12 @@
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Google Workspace subscription on `tenu.world`</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>create `ops@tenu.world` (owner) + `support@tenu.world` + `dpo@tenu.world` (aliases acceptable)</t>
-        </is>
-      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2505,12 +2255,12 @@
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Create new Cloud project `tenu-production` signed in as `ops@tenu.world` at console.cloud.google.com</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2543,12 +2293,12 @@
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Verify `tenu.world` domain ownership via Search Console TXT record</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -2581,12 +2331,12 @@
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>OAuth consent screen → User Type: External → App name "Tenu" → support email `support@tenu.world` → developer contact `dpo@tenu.world` → scopes: email, profile, openid only</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2616,15 +2366,19 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Create OAuth 2.0 Client ID (Web application) → authorized redirect URI = Supabase callback (`https://&lt;project-ref&gt;.supabase.co/auth/v1/callback`) → save client_id + client_secret into 1Password, NOT to disk</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr"/>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>expect no 403 org_internal, consent screen shows "Tenu" with `support@tenu.world`</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2654,15 +2408,19 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Paste new client_id + client_secret into Supabase dashboard → Authentication → Providers → Google → Save</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr"/>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>do not archive, the secret is burned</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2695,14 +2453,14 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>Smoke-test Google login end-to-end on tenu.world production + localhost</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>expect no 403 org_internal, consent screen shows "Tenu" with `support@tenu.world`</t>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>revokes the leaked secret at source even if a copy is still cached somewhere</t>
         </is>
       </c>
     </row>
@@ -2734,17 +2492,17 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Delete `05-Legal-Compliance/client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json` AND the ` (1).json` duplicate from disk. `rm` only</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>do not archive, the secret is burned</t>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Before 11 May</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>publish OAuth consent screen Testing → Production (requires domain verified + privacy URL + terms URL live at tenu.world/legal/privacy + /legal/terms)</t>
         </is>
       </c>
     </row>
@@ -2776,17 +2534,17 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>Shut down old `gen-lang-client-0896170717` Cloud project (Cloud Console → Settings → Shut down)</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>revokes the leaked secret at source even if a copy is still cached somewhere</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Audit hidden env vars</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>scroll full Vercel env var list below the fold, confirm ANTHROPIC_API_KEY + BREVO_API_KEY + TELEGRAM_BOT_TOKEN + any other secret either shows Need To Rotate (rotate it) or was created Sensitive from day one (leave alone). If any non-public secret is unflagged and NOT marked Sensitive, treat as exposed and rotate</t>
         </is>
       </c>
     </row>
@@ -2818,17 +2576,17 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Before 11 May</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>publish OAuth consent screen Testing → Production (requires domain verified + privacy URL + terms URL live at tenu.world/legal/privacy + /legal/terms)</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Google Cloud Console → APIs &amp; Services → Credentials → restrict to HTTP referrers `*.tenu.world` + `localhost:*` + enable only Maps JavaScript + Places API. Public by design, not flagged by Vercel, but unrestricted = scraping risk against Global Apex billing</t>
         </is>
       </c>
     </row>
@@ -2863,14 +2621,14 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>Audit hidden env vars</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>scroll full Vercel env var list below the fold, confirm ANTHROPIC_API_KEY + BREVO_API_KEY + TELEGRAM_BOT_TOKEN + any other secret either shows Need To Rotate (rotate it) or was created Sensitive from day one (leave alone). If any non-public secret is unflagged and NOT marked Sensitive, treat as exposed and rotate</t>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>hardening pass, single biggest structural lesson from this incident. Anything that isn't a NEXT_PUBLIC_* or a non-secret identifier (R2_ACCOUNT_ID, R2_BUCKET_NAME) should be Sensitive</t>
         </is>
       </c>
     </row>
@@ -2882,12 +2640,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2902,17 +2660,17 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>Lock down NEXT_PUBLIC_GOOGLE_MAPS_API_KEY at source</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>Google Cloud Console → APIs &amp; Services → Credentials → restrict to HTTP referrers `*.tenu.world` + `localhost:*` + enable only Maps JavaScript + Places API. Public by design, not flagged by Vercel, but unrestricted = scraping risk against Global Apex billing</t>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Run `npm run build:mobile` on Mac to produce non-empty out/ static export</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKER: CC fix required first (add `export const dynamic = 'force-static'` to mobile routes; see docs/12 §2). Once CC fix lands, MH re-runs build:mobile and verifies out/ is non-empty.</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2682,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -2944,19 +2702,15 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>Tick Sensitive on every remaining non-public secret in Vercel env var list</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>hardening pass, single biggest structural lesson from this incident. Anything that isn't a NEXT_PUBLIC_* or a non-secret identifier (R2_ACCOUNT_ID, R2_BUCKET_NAME) should be Sensitive</t>
-        </is>
-      </c>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2969,14 +2723,14 @@
           <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2986,19 +2740,15 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>partially wired 2026-04-18: Stripe webhook → Supabase chain live (src/app/api/webhooks/stripe/route.ts, commit ce748ec, admin client bypasses RLS). Photos up through R2, scan via /api/ai/scan (Haiku) and dispute via /api/ai/dispute (Sonnet). MISSING: @react-pdf/renderer PDF generation step (only present in features/scan marketing page, not pipeline), Brevo transactional email leg (zero references in src/). Split into two new tasks below.</t>
-        </is>
-      </c>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -3018,25 +2768,25 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>Run `npm run build:mobile` on Mac to produce out/ static export</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr"/>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3066,15 +2816,15 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr"/>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3084,7 +2834,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -3094,25 +2844,29 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr"/>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>rescheduled 2026-05-08: web-only launch 11 May. Screenshots require simulator with seeded data. Planned W/C 18 May per docs/12 §8.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3122,7 +2876,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -3142,15 +2896,19 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr"/>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>re-dated 2026-05-03: depends on CC web-only listing revision (line in DECISION 2026-05-03 section).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3160,7 +2918,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -3180,15 +2938,19 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr"/>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Decide Apple IAP stance</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>physical service argument documented — re-dated 2026-05-03: needs to land before App Store reviewer notes lock.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3198,7 +2960,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -3208,25 +2970,29 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr"/>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>deferred 2026-05-08: native app concern. Web-only F&amp;F launch uses browser Stripe Checkout directly. Needed before App Store/Play submission.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3236,7 +3002,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -3246,25 +3012,29 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr"/>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Magic-link auth working inside app</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>email link opens app, session persists — deferred 2026-05-08: native app concern. Web-only magic link works in browser. Needed before App Store/Play submission.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3274,7 +3044,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -3292,17 +3062,17 @@
           <t>P1 Important</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
-        </is>
-      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3312,12 +3082,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -3332,15 +3102,19 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr"/>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Médiateur de la consommation</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>comparer MEDICYS vs CM2C (frais d'adhésion, délai de saisine, périmètre B2C numérique), choisir, signer, publier le nom dans CGU §11 + remboursement §6 + mentions légales §médiation — opened 2026-05-07: shortlist réduite à MEDICYS + CM2C, à arbitrer cette semaine. Obligation L612-1 Code de la conso pour activité B2C en ligne, blocage de la mise en service tant que le médiateur n'est pas adhéré.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3350,7 +3124,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -3360,7 +3134,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -3370,15 +3144,15 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr"/>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3388,7 +3162,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -3408,19 +3182,15 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>re-dated 2026-05-03: depends on CC web-only listing revision (line in DECISION 2026-05-03 section).</t>
-        </is>
-      </c>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3430,7 +3200,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -3453,16 +3223,12 @@
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>Decide Apple IAP stance</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>physical service argument documented — re-dated 2026-05-03: needs to land before App Store reviewer notes lock.</t>
-        </is>
-      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -3482,7 +3248,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3492,15 +3258,19 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr"/>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>F&amp;F invite list</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>8 names, email, jurisdiction, case type</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3520,7 +3290,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -3533,16 +3303,12 @@
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>Magic-link auth working inside app</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>email link opens app, session persists</t>
-        </is>
-      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3552,7 +3318,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -3562,25 +3328,29 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr"/>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>Create Stripe coupon LAUNCH25</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>100% off, duration=once, 8 redemption limit, code=LAUNCH25. Stripe Dashboard → Coupons → + Create. Must exist before F&amp;F invites go out. Templates at docs/launch/ff-invite-en.md + ff-invite-fr.md reference this code.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -3590,7 +3360,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -3600,7 +3370,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -3610,15 +3380,19 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>Signed iOS production binary uploaded to App Store Connect</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="inlineStr"/>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>use docs/launch/ff-invite-en.md or ff-invite-fr.md templates. Confirm LAUNCH25 coupon exists in Stripe first.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3628,7 +3402,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -3638,7 +3412,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -3648,15 +3422,15 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>Signed Android app bundle uploaded to Play Console production track</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr"/>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3666,37 +3440,37 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>Médiateur de la consommation</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>comparer MEDICYS vs CM2C (frais d'adhésion, délai de saisine, périmètre B2C numérique), choisir, signer, publier le nom dans CGU §11 + remboursement §6 + mentions légales §médiation — opened 2026-05-07: shortlist réduite à MEDICYS + CM2C, à arbitrer cette semaine. Obligation L612-1 Code de la conso pour activité B2C en ligne, blocage de la mise en service tant que le médiateur n'est pas adhéré.</t>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Fix static export</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>add `export const dynamic = 'force-static'` to all mobile routes so out/ is non-empty for Capacitor — opened 2026-05-08. Blocker for MH build:mobile. Routes: src/app/(mobile)/intro/, src/app/app-home/. Root cause: root layout uses cookies()/headers(); fix scoped to mobile routes only.</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3482,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -3718,25 +3492,29 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr"/>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Bug sweep</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>camera upload retry + offline queue hardening — deferred from launch week; acceptable for F&amp;F web, required before native App Store submission.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -3746,7 +3524,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -3756,25 +3534,25 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr"/>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Full T-103 suite</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -3784,7 +3562,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -3794,25 +3572,25 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="inlineStr"/>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>14-day outcome survey cron</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Brevo trigger + Supabase write-back</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -3822,7 +3600,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -3832,27 +3610,23 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>F&amp;F invite list</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>8 names, email, jurisdiction, case type</t>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Additional UI locales</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3638,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -3874,25 +3648,25 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr"/>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>i18n audit phase 2</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -3902,7 +3676,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -3917,24 +3691,16 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>Bug sweep on inspection UI</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>camera retries, upload resume, offline queue</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>App Store + Play production updates with post-launch fixes</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -3944,7 +3710,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -3959,20 +3725,16 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr"/>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>Add scans.pdf_url + scans.pdf_sha256 columns; migrate from risk_score.pdfUrl jsonb.</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -3982,7 +3744,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -3992,25 +3754,21 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr"/>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>Extract /api/pdf/build dedicated route with runtime='nodejs' + maxDuration=60; trigger async from /api/ai/scan.</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -4020,7 +3778,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -4030,25 +3788,21 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="inlineStr"/>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Switch R2 PDF URLs to signed URLs with renewable TTL (default 30 days).</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -4073,18 +3827,22 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr"/>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>Full T-103 suite</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Wire e2e env</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>create .env.test.local with Supabase service-role key + Stripe test keys so npm run test:e2e actually executes</t>
         </is>
       </c>
     </row>
@@ -4111,18 +3869,22 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr"/>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>14-day outcome survey cron</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>Brevo trigger + Supabase write-back</t>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Lawyer formal sign-off letter (FR avocat + UK solicitor)</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>agreed in principle 2026-05-08; formal letter required before paid signups open beyond F&amp;F cohort</t>
         </is>
       </c>
     </row>
@@ -4152,320 +3914,24 @@
           <t>P2 Post-launch</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr"/>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>Additional UI locales</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>T-057</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr"/>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>i18n audit phase 2</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>T-058</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr"/>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>App Store + Play production updates with post-launch fixes</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>T-059</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr"/>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>Add scans.pdf_url + scans.pdf_sha256 columns; migrate from risk_score.pdfUrl jsonb.</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>T-060</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr"/>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>Extract /api/pdf/build dedicated route with runtime='nodejs' + maxDuration=60; trigger async from /api/ai/scan.</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>T-061</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr"/>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>Switch R2 PDF URLs to signed URLs with renewable TTL (default 30 days).</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>T-062</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>Wire e2e env</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>create .env.test.local with Supabase service-role key + Stripe test keys so npm run test:e2e actually executes</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>T-063</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr">
-        <is>
-          <t>Lawyer formal sign-off letter (FR avocat + UK solicitor)</t>
-        </is>
-      </c>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>agreed in principle 2026-05-08; formal letter required before paid signups open beyond F&amp;F cohort</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>T-064</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="G65" s="7" t="inlineStr">
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>Consider promoting /inspection/new DPA gate from client-side useEffect to middleware for defence-in-depth</t>
         </is>
       </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>currently a router.replace() in useEffect (f9aea8a), not server-enforced</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H65"/>
+  <autoFilter ref="A1:H57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4476,7 +3942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4539,7 +4005,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
+          <t>DECISION 2026-05-03 — Launch path: Option B (web-only on 11 May)</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
@@ -4559,17 +4025,17 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>Draft FR avocat fixed-fee review brief in French</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>`outreach/legal/letter-avocat-droit-immobilier-FR.md`. Scope: pre-contractual disclosure (art. L221-5), CGU, Privacy/RGPD, DPA, dispute-letter LRAR template, état-des-lieux verbiage. Budget €1,000-2,000 fixed-fee. Asks for sign-off date 2026-05-07. Includes one-page summary of Tenu, target user, jurisdiction. — done 2026-05-03: file written, recipient/cabinet bracketed, attachments list at end, notes for MH on cabinet leads + rétractation defence.</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Update store-listing copy + welcome email + landing page to reflect web-first launch + native binaries follow</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-05-08: homepage app section heading updated across all 5 locales (EN/FR/ZH/AR/UR) from "Available on iOS and Android" → "Coming to iOS/Android" equivalents; subtext updated to say "use tenu.world in browser today, no download needed"; Brevo welcome email confirmed no app-download references; store listing docs in docs/store-listings/ are App Store submission docs (not user-facing web), will be revised in native-app sprint W/C 18 May.</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4047,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
+          <t>DECISION 2026-05-03 — Launch path: Option B (web-only on 11 May)</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -4601,17 +4067,17 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>Draft UK housing solicitor TDS/DPS brief in English</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>`outreach/legal/letter-uk-housing-solicitor-EN.md`. Scope: TDS/DPS/MyDeposits dispute-letter template review, UK Consumer Rights Act 2015 alignment, ICO/UK GDPR check on photo handling. Budget GBP 500-1,500 fixed-fee. Asks for sign-off date 2026-05-07. — done 2026-05-03: file written, recipient/firm bracketed, attachments list at end, notes for MH on solicitor sourcing + Legal Services Act 2007 reserved-activities check.</t>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Native Build Bridge plan</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>write docs/12-Native-Build-Bridge-2026-05-12.md mapping the 11-25 May path: cap add ios + cap add android dependencies, Xcode + Android Studio prerequisites, TestFlight + Play internal track submission, screenshots backlog, App Store reviewer notes refresh — done 2026-05-08: docs/12-Native-Build-Bridge-2026-05-12.md written; iOS simulator BUILD SUCCEEDED; Android blocked on missing Java runtime (brew install openjdk@17 needed); brand icons + splash committed (3f7c76c).</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4099,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -4643,17 +4109,17 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>Personalise + send the FR avocat brief (review draft, fill recipient name + cabinet, send by email)</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-05-07: lettre `outreach/legal/letter-avocat-droit-immobilier-FR.docx` + dossier 9 pièces `outreach/legal/Tenu-Dossier-Revue-Avocat-FR.zip` envoyés à l'avocat·e. Réponse en attente. Suivi : nouvelle ligne MH ci-dessous.</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Draft FR avocat fixed-fee review brief in French</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>`outreach/legal/letter-avocat-droit-immobilier-FR.md`. Scope: pre-contractual disclosure (art. L221-5), CGU, Privacy/RGPD, DPA, dispute-letter LRAR template, état-des-lieux verbiage. Budget €1,000-2,000 fixed-fee. Asks for sign-off date 2026-05-07. Includes one-page summary of Tenu, target user, jurisdiction. — done 2026-05-03: file written, recipient/cabinet bracketed, attachments list at end, notes for MH on cabinet leads + rétractation defence.</t>
         </is>
       </c>
     </row>
@@ -4665,7 +4131,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
+          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -4680,22 +4146,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Scheduled push v2</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>replace Gmail create_draft with Brevo direct send — done 2026-04-19: new SKILL.md at scripts/scheduled-tasks/tenu-daily-push.md, brevo.env.example alongside. Telegram path unchanged. MH installs + adds BREVO_API_KEY — see MH line below.</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Draft UK housing solicitor TDS/DPS brief in English</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>`outreach/legal/letter-uk-housing-solicitor-EN.md`. Scope: TDS/DPS/MyDeposits dispute-letter template review, UK Consumer Rights Act 2015 alignment, ICO/UK GDPR check on photo handling. Budget GBP 500-1,500 fixed-fee. Asks for sign-off date 2026-05-07. — done 2026-05-03: file written, recipient/firm bracketed, attachments list at end, notes for MH on solicitor sourcing + Legal Services Act 2007 reserved-activities check.</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4173,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>THIS WEEKEND (17-20 Apr)</t>
+          <t>LEGAL — fixed-fee review briefs (CC drafts ready for MH to send, opened 2026-05-03)</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -4717,7 +4183,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -4727,17 +4193,17 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Fix footer legal routes redirecting to /auth/login</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>expose /legal, /auth/accept-terms, /api/consents as public paths in middleware — done 2026-04-18: middleware allow-list extended, verified on tenu.world production in incognito, all six legal pages render without auth. Commit via PR fix/public-legal-routes merged to main. Pre-contractual disclosure (art. L221-5 Code de la conso) now reachable as required for Stripe/App Store review.</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Personalise + send the FR avocat brief (review draft, fill recipient name + cabinet, send by email)</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-05-07: lettre `outreach/legal/letter-avocat-droit-immobilier-FR.docx` + dossier 9 pièces `outreach/legal/Tenu-Dossier-Revue-Avocat-FR.zip` envoyés à l'avocat·e. Réponse en attente. Suivi : nouvelle ligne MH ci-dessous.</t>
         </is>
       </c>
     </row>
@@ -4764,22 +4230,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Fix /stories/* and /features/* redirecting to /auth/login</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: added "/stories" and "/features" to publicPaths in src/middleware.ts. Same isPublicPath startsWith match pattern as the /legal fix; single entry per parent covers all nested routes. Stories and features now reachable without auth as marketing/content surface.</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Scheduled push v2</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>replace Gmail create_draft with Brevo direct send — done 2026-04-19: new SKILL.md at scripts/scheduled-tasks/tenu-daily-push.md, brevo.env.example alongside. Telegram path unchanged. MH installs + adds BREVO_API_KEY — see MH line below.</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4272,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -4814,14 +4280,14 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>Use-case content system</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>manifest + /stories index + cross-link strip + homepage dual-card — done 2026-04-18: src/lib/stories.ts (single source of truth, Story type, 4 helpers), src/components/stories/OtherCases.tsx (bilingual cross-link strip), src/app/stories/page.tsx (index with cautionary populated, success placeholder awaiting 11 May cohort), homepage example section refactored from single Suzi hook to manifest-driven dual-card grid with "See all cases →" link, Suzi + Samir pages thread OtherCases before footer, example block in en/fr/zh/ar/ur dictionaries refactored to label/heading/intro/seeAll/disclaimer. Adding a new case is now one append to stories.ts + one new /stories/&lt;slug&gt;/page.tsx.</t>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Fix footer legal routes redirecting to /auth/login</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>expose /legal, /auth/accept-terms, /api/consents as public paths in middleware — done 2026-04-18: middleware allow-list extended, verified on tenu.world production in incognito, all six legal pages render without auth. Commit via PR fix/public-legal-routes merged to main. Pre-contractual disclosure (art. L221-5 Code de la conso) now reachable as required for Stripe/App Store review.</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4309,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -4853,17 +4319,17 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>Telegram one-time setup</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>create bot via @BotFather, send token + chat_id — done 2026-04-18: bot created, token + chat_id set in .env.local and Vercel env (per Dr Mubashir)</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Fix /stories/* and /features/* redirecting to /auth/login</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: added "/stories" and "/features" to publicPaths in src/middleware.ts. Same isPublicPath startsWith match pattern as the /legal fix; single entry per parent covers all nested routes. Stories and features now reachable without auth as marketing/content surface.</t>
         </is>
       </c>
     </row>
@@ -4885,27 +4351,27 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>submitted 2026-05-03, documents sent to Apple, awaiting verification (per Dr Mubashir). Apple identity check typically 2-5 business days; D-U-N-S verification gates the review. Track unblocking of Xcode signing / TestFlight upload off this line.</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Use-case content system</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>manifest + /stories index + cross-link strip + homepage dual-card — done 2026-04-18: src/lib/stories.ts (single source of truth, Story type, 4 helpers), src/components/stories/OtherCases.tsx (bilingual cross-link strip), src/app/stories/page.tsx (index with cautionary populated, success placeholder awaiting 11 May cohort), homepage example section refactored from single Suzi hook to manifest-driven dual-card grid with "See all cases →" link, Suzi + Samir pages thread OtherCases before footer, example block in en/fr/zh/ar/ur dictionaries refactored to label/heading/intro/seeAll/disclaimer. Adding a new case is now one append to stories.ts + one new /stories/&lt;slug&gt;/page.tsx.</t>
         </is>
       </c>
     </row>
@@ -4940,14 +4406,14 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>Paste ANTHROPIC_API_KEY into .env.local + Vercel project env</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Telegram one-time setup</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>create bot via @BotFather, send token + chat_id — done 2026-04-18: bot created, token + chat_id set in .env.local and Vercel env (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -4982,14 +4448,14 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Paste BREVO_API_KEY into .env.local + Vercel project env</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Apple Developer Program enrollment for Global Apex NET SAS, EUR 99/year</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>submitted 2026-05-03, documents sent to Apple, awaiting verification (per Dr Mubashir). Apple identity check typically 2-5 business days; D-U-N-S verification gates the review. Track unblocking of Xcode signing / TestFlight upload off this line.</t>
         </is>
       </c>
     </row>
@@ -5011,7 +4477,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -5021,17 +4487,17 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>SOT consolidation</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>fix CLAUDE.md project path, refresh CLAUDE-CONTEXT.md to current React/in-code stack, replace stale-clone CLAUDE.md + CLAUDE-CONTEXT.md with redirect stubs — done 2026-04-19: SOT CLAUDE.md now declares `/Users/mmh/Documents/Claude/Projects/Tenu.World/` as canonical at the top, project structure block rewritten to match real layout (no nested `app/` wrapper, lists ios/, android/, mobile/, resources/, supabase/, scripts/). SOT CLAUDE-CONTEXT.md fully refreshed: dropped Webflow/Make.com/Tally/Airtable/Asana/Placid references, added pricing matrix, in-code pipeline, build timeline through 11 May, brand SOT pointers. Stale clone at `/Users/mmh/Documents/Global Apex/Tenu/` now has redirect-only CLAUDE.md + CLAUDE-CONTEXT.md so any agent invoked from that path bounces immediately.</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Paste ANTHROPIC_API_KEY into .env.local + Vercel project env</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -5063,17 +4529,17 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>`client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json`, the same with " (1)" suffix, and `stripe_backup_code.txt`. All three are sitting in plaintext in a Documents folder (iCloud-syncable, Time-Machine-backupable). Move to `~/.secrets/` or 1Password, then `rm` from disk. **Do NOT git commit them anywhere.** — done 2026-05-03: stripe_backup_code.txt contents migrated to 1Password as Secure Note "Stripe 2FA backup codes — Global Apex NET" (per Dr Mubashir). Two client_secret JSON files deleted (burned credentials, no preservation needed — Cloud project shutdown will close the trust loop). All three files removed from disk via `rm -rf` on parent folder. Verify by inspection: `/Users/mmh/Documents/Global Apex/Tenu/` no longer exists.</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Paste BREVO_API_KEY into .env.local + Vercel project env</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: key set in .env.local and Vercel project env (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -5100,22 +4566,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>`01-Legal-Checklist.md` (review + dedupe against SOT 05-Legal-Compliance content first), `etat-des-lieux.pdf`, `etat-des-lieux-meuble.pdf`, `modele-etat-des-lieux T2-T3.pdf` into SOT `docs/reference/etat-des-lieux/` (or wherever Dr Mubashir prefers). Delete from stale clone after move — done 2026-05-03: audit found `01-Legal-Checklist.md` already byte-identical between stale and SOT (no migration needed); 3 PDFs in stale folder, two of which (`modele-etat-des-lieux.pdf` and `modele-etat-des-lieux T2-T3.pdf`) are byte-identical (sha 4b9fed2e0c14...) — only one carried over. Final SOT state: `docs/reference/etat-des-lieux/etat-des-lieux-meuble.pdf` (sha 6e1e3f5acd83...) + `docs/reference/etat-des-lieux/modele-etat-des-lieux T2-T3.pdf` (sha 4b9fed2e0c14...). Note: original task line referenced `etat-des-lieux.pdf` which never existed in stale clone — actual filenames discovered during audit.</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>SOT consolidation</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>fix CLAUDE.md project path, refresh CLAUDE-CONTEXT.md to current React/in-code stack, replace stale-clone CLAUDE.md + CLAUDE-CONTEXT.md with redirect stubs — done 2026-04-19: SOT CLAUDE.md now declares `/Users/mmh/Documents/Claude/Projects/Tenu.World/` as canonical at the top, project structure block rewritten to match real layout (no nested `app/` wrapper, lists ios/, android/, mobile/, resources/, supabase/, scripts/). SOT CLAUDE-CONTEXT.md fully refreshed: dropped Webflow/Make.com/Tally/Airtable/Asana/Placid references, added pricing matrix, in-code pipeline, build timeline through 11 May, brand SOT pointers. Stale clone at `/Users/mmh/Documents/Global Apex/Tenu/` now has redirect-only CLAUDE.md + CLAUDE-CONTEXT.md so any agent invoked from that path bounces immediately.</t>
         </is>
       </c>
     </row>
@@ -5142,22 +4608,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>archive to `~/Archive/` or `rm -rf`. Sandbox cannot delete the parent folder. — done 2026-05-03 — decision: `rm -rf`, no archive. Audit grounds: (a) 533 MB of the 538 MB total was regenerable node_modules; (b) git remote pointed at the same `malikmubashir/tenu-world.git` with HEAD at `c3614ef` (the original April 3 scaffold commit, redundant with everything in main since); (c) all 10 doc files were either byte-identical to SOT or differed only in COI-scrubbed wording (HEC GEMM / MHF references that SOT correctly removed per role-separation policy in CLAUDE.md); (d) parent had `com.apple.macl` and `com.apple.provenance` xattrs only — NOT iCloud-synced, so no recurring sync source to sever; (e) Time Machine retains snapshots back to April 3 if recovery ever needed. Final stale-clone removal verified: parent path no longer exists. Container `/Users/mmh/Documents/Global Apex/` retained for other uses. Companion finding: the dedup chaos cleaned in the prior task was therefore NOT from active iCloud sync — likely a one-time merge incident from a multi-machine sync, not ongoing. Worth knowing for future repo-cleanup heuristics.</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Move leaked secrets out of `/Users/mmh/Documents/Global Apex/Tenu/05-Legal-Compliance/`</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>`client_secret_1016793771503-bnq65154rootrva2e81kh1jicoks7hss.apps.googleusercontent.com.json`, the same with " (1)" suffix, and `stripe_backup_code.txt`. All three are sitting in plaintext in a Documents folder (iCloud-syncable, Time-Machine-backupable). Move to `~/.secrets/` or 1Password, then `rm` from disk. **Do NOT git commit them anywhere.** — done 2026-05-03: stripe_backup_code.txt contents migrated to 1Password as Secure Note "Stripe 2FA backup codes — Global Apex NET" (per Dr Mubashir). Two client_secret JSON files deleted (burned credentials, no preservation needed — Cloud project shutdown will close the trust loop). All three files removed from disk via `rm -rf` on parent folder. Verify by inspection: `/Users/mmh/Documents/Global Apex/Tenu/` no longer exists.</t>
         </is>
       </c>
     </row>
@@ -5179,12 +4645,12 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -5192,14 +4658,14 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>Rotate R2_ACCESS_KEY_ID + R2_SECRET_ACCESS_KEY</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Cloudflare → R2 → Manage API tokens → new token scoped to tenu-evidence bucket (Object Read/Write only). Paste both into Vercel env, tick Sensitive, redeploy. Smoke: hit /api/mobile/upload-intent and upload a test photo. Then revoke old token in Cloudflare. Existing presigned URLs signed with old key keep working until expiry — done 2026-05-03 (per Dr Mubashir, post-holiday). CC post-rotation E2E smoke owed (line below).</t>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Migrate stragglers from stale-clone `05-Legal-Compliance/` into SOT</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>`01-Legal-Checklist.md` (review + dedupe against SOT 05-Legal-Compliance content first), `etat-des-lieux.pdf`, `etat-des-lieux-meuble.pdf`, `modele-etat-des-lieux T2-T3.pdf` into SOT `docs/reference/etat-des-lieux/` (or wherever Dr Mubashir prefers). Delete from stale clone after move — done 2026-05-03: audit found `01-Legal-Checklist.md` already byte-identical between stale and SOT (no migration needed); 3 PDFs in stale folder, two of which (`modele-etat-des-lieux.pdf` and `modele-etat-des-lieux T2-T3.pdf`) are byte-identical (sha 4b9fed2e0c14...) — only one carried over. Final SOT state: `docs/reference/etat-des-lieux/etat-des-lieux-meuble.pdf` (sha 6e1e3f5acd83...) + `docs/reference/etat-des-lieux/modele-etat-des-lieux T2-T3.pdf` (sha 4b9fed2e0c14...). Note: original task line referenced `etat-des-lieux.pdf` which never existed in stale clone — actual filenames discovered during audit.</t>
         </is>
       </c>
     </row>
@@ -5226,22 +4692,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Rotate STRIPE_WEBHOOK_SECRET</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Stripe → Developers → Webhooks → endpoint → Roll secret with 24h grace. Paste new into Vercel STRIPE_WEBHOOK_SECRET, tick Sensitive, redeploy. Smoke: `stripe trigger checkout.session.completed` and confirm /api/webhooks/stripe returns 200 in Vercel function logs. Old secret expires automatically at end of grace — done 2026-05-03 (per Dr Mubashir).</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Decide fate of `/Users/mmh/Documents/Global Apex/Tenu/` once secrets + legal stragglers are out</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>archive to `~/Archive/` or `rm -rf`. Sandbox cannot delete the parent folder. — done 2026-05-03 — decision: `rm -rf`, no archive. Audit grounds: (a) 533 MB of the 538 MB total was regenerable node_modules; (b) git remote pointed at the same `malikmubashir/tenu-world.git` with HEAD at `c3614ef` (the original April 3 scaffold commit, redundant with everything in main since); (c) all 10 doc files were either byte-identical to SOT or differed only in COI-scrubbed wording (HEC GEMM / MHF references that SOT correctly removed per role-separation policy in CLAUDE.md); (d) parent had `com.apple.macl` and `com.apple.provenance` xattrs only — NOT iCloud-synced, so no recurring sync source to sever; (e) Time Machine retains snapshots back to April 3 if recovery ever needed. Final stale-clone removal verified: parent path no longer exists. Container `/Users/mmh/Documents/Global Apex/` retained for other uses. Companion finding: the dedup chaos cleaned in the prior task was therefore NOT from active iCloud sync — likely a one-time merge incident from a multi-machine sync, not ongoing. Worth knowing for future repo-cleanup heuristics.</t>
         </is>
       </c>
     </row>
@@ -5276,14 +4742,14 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Rotate SUPABASE_SERVICE_ROLE_KEY AND NEXT_PUBLIC_SUPABASE_ANON_KEY together</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Supabase → Project Settings → API → JWT Keys → Generate new JWT secret (regenerates both keys, both are JWTs signed by the same secret). Update both values in Vercel in the same save, tick Sensitive on service_role (anon stays public but encrypt-at-rest regardless), redeploy. All pre-rotation sessions invalidated (pre-launch, so non-event). Smoke: incognito magic-link signup → /app-home load → photo upload row insert — done 2026-05-03 (per Dr Mubashir).</t>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Rotate R2_ACCESS_KEY_ID + R2_SECRET_ACCESS_KEY</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Cloudflare → R2 → Manage API tokens → new token scoped to tenu-evidence bucket (Object Read/Write only). Paste both into Vercel env, tick Sensitive, redeploy. Smoke: hit /api/mobile/upload-intent and upload a test photo. Then revoke old token in Cloudflare. Existing presigned URLs signed with old key keep working until expiry — done 2026-05-03 (per Dr Mubashir, post-holiday). CC post-rotation E2E smoke owed (line below).</t>
         </is>
       </c>
     </row>
@@ -5305,7 +4771,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -5315,17 +4781,17 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>Post-rotation smoke test verification</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green — done 2026-05-08: Playwright spec + fixture + playwright.config.ts landed via 6ce9b29 (e2e/post-rotation-smoke.spec.ts). Full execution requires .env.test.local with Supabase service role + Stripe test keys; env wiring deferred to v0.1 (see p:1 follow-up line in POST-LAUNCH).</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Rotate STRIPE_WEBHOOK_SECRET</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Stripe → Developers → Webhooks → endpoint → Roll secret with 24h grace. Paste new into Vercel STRIPE_WEBHOOK_SECRET, tick Sensitive, redeploy. Smoke: `stripe trigger checkout.session.completed` and confirm /api/webhooks/stripe returns 200 in Vercel function logs. Old secret expires automatically at end of grace — done 2026-05-03 (per Dr Mubashir).</t>
         </is>
       </c>
     </row>
@@ -5337,7 +4803,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -5347,7 +4813,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -5360,14 +4826,14 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Rotate SUPABASE_SERVICE_ROLE_KEY AND NEXT_PUBLIC_SUPABASE_ANON_KEY together</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Supabase → Project Settings → API → JWT Keys → Generate new JWT secret (regenerates both keys, both are JWTs signed by the same secret). Update both values in Vercel in the same save, tick Sensitive on service_role (anon stays public but encrypt-at-rest regardless), redeploy. All pre-rotation sessions invalidated (pre-launch, so non-event). Smoke: incognito magic-link signup → /app-home load → photo upload row insert — done 2026-05-03 (per Dr Mubashir).</t>
         </is>
       </c>
     </row>
@@ -5379,7 +4845,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>THIS WEEKEND (17-20 Apr)</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -5399,17 +4865,17 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Post-rotation smoke test verification</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>run full E2E after Dr Mubashir signals all rotations done: incognito signup → magic link → /app-home → /api/mobile/upload-intent presigned URL → test photo upload → /api/ai/scan trigger → Stripe test webhook fired via CLI → confirm /api/webhooks/stripe 200 → Supabase RLS read-as-user sanity check. Report pass/fail per leg in this line. Zero auth errors in Vercel function logs = green — done 2026-05-08: Playwright spec + fixture + playwright.config.ts landed via 6ce9b29 (e2e/post-rotation-smoke.spec.ts). Full execution requires .env.test.local with Supabase service role + Stripe test keys; env wiring deferred to v0.1 (see p:1 follow-up line in POST-LAUNCH).</t>
         </is>
       </c>
     </row>
@@ -5441,17 +4907,17 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Implement /api/risk-scan Haiku handler per prompt-spec-scan-v2.md, JSON validation, cost cap</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-17: French system prompt, grille injection, zod validation, Haiku→Haiku→Sonnet retry, €0.12 cost cap per scan, v2 payload persisted to inspections.risk_score jsonb, ScanError codes surfaced as 400/402/422/502 on the route</t>
         </is>
       </c>
     </row>
@@ -5483,17 +4949,17 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>PDF generation leg</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2 — done 2026-04-19: shipped via MB-16 (commit d77d85b, 2026-04-19); architectural deltas captured as 3 new p:1 hardening lines below.</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Implement /api/dispute-letter Sonnet handler per prompt-spec-dispute-v2.md, FR LRAR + UK TDS/DPS branches</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: code shipped 2026-04-17 (zod schema + FR/EN system prompts + Sonnet → Sonnet retry + items-sum validation ±1 EUR + €0.50 cost cap + DisputeError 9 codes → HTTP 400/402/404/409/502/504 + server-forced disclaimer injection + /api/ai/dispute reads v2 scan from inspections.risk_score.v2 and upserts dispute_letters). Typecheck verified 2026-04-18: `npx tsc --noEmit` exit 0 on fresh sandbox after index.lock clear.</t>
         </is>
       </c>
     </row>
@@ -5525,17 +4991,17 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>Brevo transactional email leg</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Implement /api/upload Cloudflare R2 EU + presigned URL flow</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: shipped as two-phase flow at /api/mobile/upload-intent (presigned PUT URL) + /api/mobile/upload-commit (object verification + DB row), backed by src/lib/storage/r2-upload.ts and src/app/api/photos/route.ts. Commits 0a0192b + 22d028f. Path differs from original /api/upload title — same goal, mobile-scoped route.</t>
         </is>
       </c>
     </row>
@@ -5557,27 +5023,27 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>Delete iCloud dedup files on Mac</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run. — done 2026-05-03: real damage was 2.7× larger than originally scoped. Total cleaned: 113 dedup files (109 src/app metadata route dedups across icon/apple-icon/opengraph-image/robots/sitemap × 21-22 each, 3 in scripts/, 1 in docs/paperclip-briefs/) + 121 empty paren-numbered directories under src/app/ + 4 space-numbered directories under src/app/auth/ (accept-terms 2, callback 2, callback 3, login 2 — verified to be older stale snapshots predating the i18n + signup-flow fixes, no imports, originals intact) + 2 i18n dictionary dedups (ar 2.json, zh 2.json) = grand total 240 entries. Verified: `find` returns 0 dedups repo-wide; `npm run build` exit 0 with all routes (icon, opengraph-image, robots.txt, sitemap.xml, manifest.webmanifest, /legal/*, /auth/*, /inspection/*, /features/*) compiled cleanly; Next.js convention parents (icon.tsx, apple-icon.tsx, opengraph-image.tsx, robots.ts, sitemap.ts) all present. Root cause documented: dual mirroring by iCloud (parens-N suffix) AND OneDrive (space-N suffix) on the old `~/Documents/Claude/Projects/Tenu.World/` path. Repo now lives at `~/Code/Tenu.World/` (no iCloud xattrs). Confirm OneDrive isn't mirroring `~/Code/` either to prevent recurrence.</t>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>End-to-end pipeline wiring Stripe webhook → Supabase → R2 → Haiku → @react-pdf/renderer → R2 → Brevo</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-05-08: full chain confirmed wired. Stripe webhook → Supabase: src/app/api/webhooks/stripe/route.ts (ce748ec). R2: /api/mobile/upload-intent + /api/mobile/upload-commit. Haiku: /api/ai/scan calls renderAndUploadScanPdf (src/lib/pdf/render-and-upload.tsx, d77d85b) + notifyScanComplete (src/lib/email/notify.ts), both best-effort try/catch post-scan. Prior "MISSING" note was stale — PDF + Brevo legs both shipped 2026-04-18/19 as sub-tasks below.</t>
         </is>
       </c>
     </row>
@@ -5609,17 +5075,17 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Capacitor 7 scaffold</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>PDF generation leg</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>@react-pdf/renderer report builder invoked by webhook/post-scan, output to R2 — done 2026-04-19: shipped via MB-16 (commit d77d85b, 2026-04-19); architectural deltas captured as 3 new p:1 hardening lines below.</t>
         </is>
       </c>
     </row>
@@ -5651,17 +5117,17 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Brevo transactional email leg</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>send scan-complete + dispute-ready emails with R2 PDF link — done 2026-04-18: in-repo template model (HTML-as-TS-string), Brevo as REST transport. Shipped src/lib/email/brevo.ts (fetch wrapper, no SDK dep), src/lib/email/notify.ts (high-level notifyScanComplete + notifyDisputeReady pulling email/locale/display_name from profiles via admin client), src/lib/email/templates/{scan-complete,dispute-ready}.ts (FR/EN stacked, Identity v1 palette, matches brevo-welcome.html register). Wired into /api/ai/scan post-update and /api/ai/dispute post-persist, both best-effort (try/catch + console.warn, never block caller). Typecheck exit 0. Link currently points to /inspection/{id}/report — dispute-ready template will grow a "Download PDF" button fed by R2 presigned URL once the @react-pdf/renderer leg lands; helper signature is already stable.</t>
         </is>
       </c>
     </row>
@@ -5683,27 +5149,27 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-05-08: gate landed via f9aea8a (useEffect client-side redirect on /inspection/new), version pinning via supabase/migrations/005_profile_consent_cache.sql, touchpoints via /auth/accept-terms + /api/checkout waiver + CNIL banner. Merged into main via b54db18.</t>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Delete iCloud dedup files on Mac</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>fuse mount blocks Cowork `rm`. Three in `scripts/` (`check-agent-runs 2.sql`, `governance-sync 2.py`, `queue-agent-tasks-2026-04-17 2.sql`) PLUS ~40 more under `src/app/` matching the ` (N).{tsx,ts}` pattern: `icon (1..8).tsx`, `apple-icon (1..7).tsx`, `opengraph-image (1..8).tsx`, `robots (1..7).ts`, `sitemap (1..8).ts`. Verify Next.js still routes correctly after deletion (these names are likely ignored but the parenthesised form is suspicious — confirm `npm run build` exit 0). One-liner from repo root: `find src/app scripts -type f -name "* [0-9]*" -print -delete` after a quick `find` dry-run. — done 2026-05-03: real damage was 2.7× larger than originally scoped. Total cleaned: 113 dedup files (109 src/app metadata route dedups across icon/apple-icon/opengraph-image/robots/sitemap × 21-22 each, 3 in scripts/, 1 in docs/paperclip-briefs/) + 121 empty paren-numbered directories under src/app/ + 4 space-numbered directories under src/app/auth/ (accept-terms 2, callback 2, callback 3, login 2 — verified to be older stale snapshots predating the i18n + signup-flow fixes, no imports, originals intact) + 2 i18n dictionary dedups (ar 2.json, zh 2.json) = grand total 240 entries. Verified: `find` returns 0 dedups repo-wide; `npm run build` exit 0 with all routes (icon, opengraph-image, robots.txt, sitemap.xml, manifest.webmanifest, /legal/*, /auth/*, /inspection/*, /features/*) compiled cleanly; Next.js convention parents (icon.tsx, apple-icon.tsx, opengraph-image.tsx, robots.ts, sitemap.ts) all present. Root cause documented: dual mirroring by iCloud (parens-N suffix) AND OneDrive (space-N suffix) on the old `~/Documents/Claude/Projects/Tenu.World/` path. Repo now lives at `~/Code/Tenu.World/` (no iCloud xattrs). Confirm OneDrive isn't mirroring `~/Code/` either to prevent recurrence.</t>
         </is>
       </c>
     </row>
@@ -5728,14 +5194,26 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>ECB daily refresh cron, KILLED 2026-05-08. No FX surface: pricing jurisdiction-pinned via TIER_PRICE_CENTS + CURRENCY[jurisdiction] in src/lib/payments/stripe.ts</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>Capacitor 7 scaffold</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>TS code-side complete: capacitor.config.ts, MobileGate, Shell, intro/onboarding carousel, preferences wrapper, deep-link handler, mobile/upload-intent + upload-commit — done 2026-04-18: intro flow at src/app/(mobile)/intro/{layout,page}.tsx (3-screen swipe carousel, Apple HIG dots/haptics/skip, Portal mark on screen 1), MobileGate mounted in src/app/layout.tsx (native first-launch routes to /intro/, returning users to /app-home/), preferences.ts with Capacitor Preferences + localStorage fallback, brand colours aligned to Identity v1 (#F4F1EA paper / #0B1F3A ink — drift from #F5F1E8/#0F3B2E corrected in capacitor.config.ts and Shell.tsx), resources/{icon,icon-foreground,icon-background,splash,splash-dark}.svg authored for @capacitor/assets. Native iOS + Android project add still required on Mac — see MH lines below.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -5765,17 +5243,17 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-05-08: ios/ Capacitor project already present on main with all Info.plist snippet keys merged. Pods installed. BUILD SUCCEEDED on iphonesimulator arm64+x86_64.</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5275,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -5807,17 +5285,17 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>MB-01</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-05-08: android/ Capacitor project present on main, AndroidManifest merged, network_security_config.xml in place. Android APK blocked on missing Java runtime — MH must `brew install openjdk@17` (see docs/12 §1).</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5317,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -5849,17 +5327,17 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>MB-03</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-05-08: CC ran ./node_modules/.bin/capacitor-assets generate; all Android density buckets + iOS AppIcon + Splash imageset committed (3f7c76c, 70 files).</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5359,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -5891,17 +5369,17 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>MB-05</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-05-08: cap sync verified clean. xattr fix on ios/App/build documented in docs/12 if needed.</t>
         </is>
       </c>
     </row>
@@ -5933,17 +5411,17 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>MB-08</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
         </is>
       </c>
     </row>
@@ -5975,17 +5453,17 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>MB-09</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-05-08: gate landed via f9aea8a (useEffect client-side redirect on /inspection/new), version pinning via supabase/migrations/005_profile_consent_cache.sql, touchpoints via /auth/accept-terms + /api/checkout waiver + CNIL banner. Merged into main via b54db18.</t>
         </is>
       </c>
     </row>
@@ -5997,7 +5475,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -6010,26 +5488,14 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>App icon set</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
-        </is>
-      </c>
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>ECB daily refresh cron, KILLED 2026-05-08. No FX surface: pricing jurisdiction-pinned via TIER_PRICE_CENTS + CURRENCY[jurisdiction] in src/lib/payments/stripe.ts</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -6039,7 +5505,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -6049,7 +5515,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -6059,17 +5525,17 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>Splash screens per density, status bar theming, safe-area insets</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -6081,7 +5547,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -6101,17 +5567,17 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>MB-01</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
         </is>
       </c>
     </row>
@@ -6123,7 +5589,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -6143,17 +5609,17 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>Store listing copy drafted in FR + EN</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>description, keywords, support URL, privacy URL — done 2026-04-18 (ahead of schedule): MB-07 shipped docs/store-listings/{ios-fr,ios-en,play-fr,play-en}.md. Professional services register throughout (no buzzwords, no guaranteed-outcome claims), character counts validated inline, Stripe reader-app classification explicitly argued in reviewer notes, data safety section filled for Play form. Awaits MH (nights) review + edit before submission. Commit 50db60f.</t>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>MB-03</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Info.plist + AndroidManifest snippets with bilingual usage descriptions — done 2026-04-18: ITSAppUsesNonExemptEncryption=false + LSApplicationQueriesSchemes added to ios-Info.plist.snippet.xml; android-AndroidManifest.xml.snippet renamed to android-manifest.snippet.xml to match TASKS.md references; POST_NOTIFICATIONS permission added; standalone mobile/network_security_config.xml created for drop-in to res/xml/. Commit 5ef8c71.</t>
         </is>
       </c>
     </row>
@@ -6165,42 +5631,336 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>MB-05</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>iOS Privacy Manifest (Apple May 2024 mandate) — done 2026-04-18: mobile/PrivacyInfo.xcprivacy authored per Apple spec. Declared collected types (email, photos, userID, product interaction — all linked, none tracking), accessed APIs (UserDefaults CA92.1, FileTimestamp C617.1, DiskSpace E174.1, SystemBootTime 35F9.1), NSPrivacyTracking=false. Commit a4b21b4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>T-041</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>MB-08</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Mac-side mobile build handover doc — done 2026-04-18: docs/10-Mobile-Build-Handover-2026-04-19.md. Steps 0–10 with expected output + red-flag per step, covers repo sync, npm install, build:mobile verify, cap add ios + Info.plist merge, Privacy Manifest drop, cap add android + manifest + network security config, icon generation (capacitor-assets OR manual copy), cap sync, Xcode signing + capabilities, keystore + SHA-256 capture, TestFlight + Play internal upload. Explicit callout on root-layout dynamic-APIs blocker with two recovery paths. Commit c24f3d6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>T-042</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>MB-09</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>session closeout + tracker mirror refresh — done 2026-04-18: this entry. Tracker xlsx + dashboard regenerated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>T-043</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>App icon set</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>1024, 512, 180, 120, 87, 60, 40, 29 iOS + Play adaptive — done 2026-04-18 (ahead of schedule): MB-02 shipped scripts/generate-icons.mjs (sharp-based ladder generator, npm run icons:generate) and committed the full PNG set at resources/icons-generated/{ios,android}/ — 13 iOS sizes (20@1x through 1024 marketing) + 5 Android mipmap densities (mdpi→xxxhdpi, launcher + launcher_round + adaptive foreground + adaptive background) + 512 Play Store. MH can choose capacitor-assets OR direct copy at cap-add time. Commit 93e6592.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>T-044</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Splash screens per density, status bar theming, safe-area insets</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: already shipped via commit f21f5a8 (MobileGate + Shell + resources/{splash,splash-dark}.svg sources + capacitor.config.ts SplashScreen plugin config at #F4F1EA/#0B1F3A, StatusBar overlaysWebView=false). capacitor-assets generate on the Mac (documented in the handover doc) produces the density ladder from the SVG sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>T-045</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Deep-linking scheme tenu:// + Universal Links config pointing at tenu.world</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-04-18: MB-04 shipped src/app/.well-known/apple-app-site-association/route.ts (applinks details for /auth/callback, /app-home, /inspection, /report, /dispute with force-static) and assetlinks.json/route.ts (android_app target world.tenu.app, SHA-256 placeholder with TODO for MH post-keystore), middleware allow-listed /.well-known. tenu:// scheme already present in capacitor.config.ts + Info.plist + AndroidManifest snippets. TEAMID still a TODO (unblocks once Apple Developer enrolment completes). Commit 88cc97e.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>T-046</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>OOO BRIDGE (27-30 Apr)</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Store listing copy drafted in FR + EN</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>description, keywords, support URL, privacy URL — done 2026-04-18 (ahead of schedule): MB-07 shipped docs/store-listings/{ios-fr,ios-en,play-fr,play-en}.md. Professional services register throughout (no buzzwords, no guaranteed-outcome claims), character counts validated inline, Stripe reader-app classification explicitly argued in reviewer notes, data safety section filled for Play form. Awaits MH (nights) review + edit before submission. Commit 50db60f.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>T-047</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
           <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G48" s="6" t="inlineStr">
         <is>
           <t>T-103-core pipeline tests</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="H48" s="6" t="inlineStr">
         <is>
           <t>unit + integration for critical path only, skip full 48-item P0 coverage — done 2026-05-08: 4 vitest files shipped via f1cb161 (src/tests/{ai-dispute,ai-scan,webhooks-stripe,pricing-calculate}.test.ts), 10 tests all passing. Vitest run: 4 files / 10 tests, exit 0.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H41"/>
+  <autoFilter ref="A1:H48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6211,7 +5971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6266,8 +6026,176 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>T-001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Dropped</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Signed iOS production binary uploaded to App Store Connect</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>deferred 2026-05-08: web-only launch 11 May per DECISION 2026-05-03. TestFlight submission moved to W/C 18 May (docs/12 §6). MH owns Xcode Archive + upload; Apple Developer enrolment verification still pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>T-002</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Dropped</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Signed Android app bundle uploaded to Play Console production track</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>deferred 2026-05-08: web-only launch 11 May. Play internal track submission moved to W/C 21 May (docs/12 §7). Android APK blocked on missing Java runtime (MH: brew install openjdk@17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>T-003</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>LAUNCH WEEK (8-11 May)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Dropped</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Bug sweep on inspection UI</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>camera retries, upload resume, offline queue — dropped for web-only F&amp;F launch 2026-05-08: CameraCapture.tsx is capture-only (no upload logic). R2 upload is single-attempt; user can manually retry. Acceptable risk for 8-person cohort. Re-open as p:1 for native-app sprint (docs/12 scope).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>T-004</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>LAUNCH WEEK (8-11 May)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Dropped</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>F&amp;F install test on 2 real devices each (iPhone + Android)</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>deferred 2026-05-08: web-only launch. Native device testing in docs/12 §5, W/C 14 May, MH-owned.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
+  <autoFilter ref="A1:H5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1511,22 +1511,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Fix static export</t>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
     </row>
@@ -1560,24 +1560,24 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+          <t>Bug sweep</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Bug sweep</t>
+          <t>Wire e2e env</t>
         </is>
       </c>
     </row>
@@ -1613,28 +1613,6 @@
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Wire e2e env</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>Lawyer formal sign-off letter (FR avocat + UK solicitor)</t>
         </is>
@@ -1651,7 +1629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3460,17 +3438,17 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Fix static export</t>
+          <t>Bug sweep</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>add `export const dynamic = 'force-static'` to all mobile routes so out/ is non-empty for Capacitor — opened 2026-05-08. Blocker for MH build:mobile. Routes: src/app/(mobile)/intro/, src/app/app-home/. Root cause: root layout uses cookies()/headers(); fix scoped to mobile routes only.</t>
+          <t>camera upload retry + offline queue hardening — deferred from launch week; acceptable for F&amp;F web, required before native App Store submission.</t>
         </is>
       </c>
     </row>
@@ -3497,22 +3475,18 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Bug sweep</t>
+          <t>Full T-103 suite</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>camera upload retry + offline queue hardening — deferred from launch week; acceptable for F&amp;F web, required before native App Store submission.</t>
+          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3519,12 @@
       <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Full T-103 suite</t>
+          <t>14-day outcome survey cron</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+          <t>Brevo trigger + Supabase write-back</t>
         </is>
       </c>
     </row>
@@ -3583,12 +3557,12 @@
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>14-day outcome survey cron</t>
+          <t>Additional UI locales</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Brevo trigger + Supabase write-back</t>
+          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
         </is>
       </c>
     </row>
@@ -3615,18 +3589,18 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr"/>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>Additional UI locales</t>
+          <t>i18n audit phase 2</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
+          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
         </is>
       </c>
     </row>
@@ -3653,20 +3627,16 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P2 Post-launch</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>i18n audit phase 2</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
-        </is>
-      </c>
+          <t>App Store + Play production updates with post-launch fixes</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -3691,13 +3661,13 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr"/>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>App Store + Play production updates with post-launch fixes</t>
+          <t>Add scans.pdf_url + scans.pdf_sha256 columns; migrate from risk_score.pdfUrl jsonb.</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr"/>
@@ -3731,7 +3701,7 @@
       <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Add scans.pdf_url + scans.pdf_sha256 columns; migrate from risk_score.pdfUrl jsonb.</t>
+          <t>Extract /api/pdf/build dedicated route with runtime='nodejs' + maxDuration=60; trigger async from /api/ai/scan.</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr"/>
@@ -3765,7 +3735,7 @@
       <c r="F53" s="5" t="inlineStr"/>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Extract /api/pdf/build dedicated route with runtime='nodejs' + maxDuration=60; trigger async from /api/ai/scan.</t>
+          <t>Switch R2 PDF URLs to signed URLs with renewable TTL (default 30 days).</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr"/>
@@ -3796,13 +3766,21 @@
           <t>P1 Important</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr"/>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Switch R2 PDF URLs to signed URLs with renewable TTL (default 30 days).</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="inlineStr"/>
+          <t>Wire e2e env</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>create .env.test.local with Supabase service-role key + Stripe test keys so npm run test:e2e actually executes</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -3837,12 +3815,12 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Wire e2e env</t>
+          <t>Lawyer formal sign-off letter (FR avocat + UK solicitor)</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>create .env.test.local with Supabase service-role key + Stripe test keys so npm run test:e2e actually executes</t>
+          <t>agreed in principle 2026-05-08; formal letter required before paid signups open beyond F&amp;F cohort</t>
         </is>
       </c>
     </row>
@@ -3869,69 +3847,27 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P2 Post-launch</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Lawyer formal sign-off letter (FR avocat + UK solicitor)</t>
+          <t>Consider promoting /inspection/new DPA gate from client-side useEffect to middleware for defence-in-depth</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>agreed in principle 2026-05-08; formal letter required before paid signups open beyond F&amp;F cohort</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>T-056</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>Consider promoting /inspection/new DPA gate from client-side useEffect to middleware for defence-in-depth</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
           <t>currently a router.replace() in useEffect (f9aea8a), not server-enforced</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H57"/>
+  <autoFilter ref="A1:H56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3942,7 +3878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5959,8 +5895,50 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>T-048</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>POST-LAUNCH (12-31 May)</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Fix static export</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>root cause was top-level `import { cookies, headers }` in layout.tsx and page.tsx marking all pages as dynamic — done 2026-05-08: changed to `await import("next/headers")` inside existing IS_MOBILE_EXPORT guards in both src/app/layout.tsx and src/app/page.tsx. Dynamic [id] routes already had generateStaticParams(_placeholder). `tsc --noEmit` clean. MH can now run `npm run build:mobile` and get a populated out/.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H48"/>
+  <autoFilter ref="A1:H49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Tenu-Reste-a-Faire.xlsx
+++ b/Tenu-Reste-a-Faire.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropped" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$H$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Done'!$A$1:$H$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dropped'!$A$1:$H$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -1482,14 +1482,14 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Run `npm run build:mobile` on Mac to produce non-empty out/ static export</t>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
     </row>
@@ -1538,24 +1538,24 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
+          <t>Bug sweep</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Bug sweep</t>
+          <t>Wire e2e env</t>
         </is>
       </c>
     </row>
@@ -1591,28 +1591,6 @@
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>Wire e2e env</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Lawyer formal sign-off letter (FR avocat + UK solicitor)</t>
         </is>
@@ -1629,7 +1607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2638,17 +2616,17 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Run `npm run build:mobile` on Mac to produce non-empty out/ static export</t>
+          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>BLOCKER: CC fix required first (add `export const dynamic = 'force-static'` to mobile routes; see docs/12 §2). Once CC fix lands, MH re-runs build:mobile and verifies out/ is non-empty.</t>
+          <t>simulator confirmed running 2026-05-08. Next: set Team ID + signing, run on physical device.</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2663,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Open Xcode (`npx cap open ios`), set Team ID + Bundle world.tenu.app + capabilities (Camera, Push, Associated Domains for tenu.world), run on simulator + physical iPhone</t>
+          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr"/>
@@ -2708,25 +2686,25 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
+          <t>P1 Important</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Open Android Studio (`npx cap open android`), set release keystore SHA-256 in mobile/.well-known/assetlinks.json placeholder, run on emulator + physical device</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr"/>
+          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2746,25 +2724,25 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr"/>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Android ↔ iOS native-chrome parity audit (splash, status bar, safe-area, fonts, haptics, hardware back, keyboard)</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>DEFERRED until MH completes `npx cap add ios`/`add android` + `cap sync` and both simulators boot a real `out/` bundle. Audit brief drafted 2026-04-19 (Dr Mubashir provided checkpoints a–l + parity checks 1–9). Cannot execute on empty native shells. Re-open this line once cap-add work lands.</t>
-        </is>
-      </c>
+          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -2774,7 +2752,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>WEEK 1 (20-24 Apr) — pipeline + native scaffold</t>
+          <t>OOO BRIDGE (27-30 Apr)</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -2784,25 +2762,29 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Sign DPAs with Supabase, Cloudflare, Stripe, Vercel, Brevo, Anthropic</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr"/>
+          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>rescheduled 2026-05-08: web-only launch 11 May. Screenshots require simulator with seeded data. Planned W/C 18 May per docs/12 §8.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -2822,27 +2804,27 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>6 iOS screenshots at 6.9 inch + 4 Play screenshots at 16:9</t>
+          <t>Review store listing copy in Notion/file, approve or edit</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>rescheduled 2026-05-08: web-only launch 11 May. Screenshots require simulator with seeded data. Planned W/C 18 May per docs/12 §8.</t>
+          <t>re-dated 2026-05-03: depends on CC web-only listing revision (line in DECISION 2026-05-03 section).</t>
         </is>
       </c>
     </row>
@@ -2874,17 +2856,17 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Review store listing copy in Notion/file, approve or edit</t>
+          <t>Decide Apple IAP stance</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>re-dated 2026-05-03: depends on CC web-only listing revision (line in DECISION 2026-05-03 section).</t>
+          <t>physical service argument documented — re-dated 2026-05-03: needs to land before App Store reviewer notes lock.</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2878,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>OOO BRIDGE (27-30 Apr)</t>
+          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -2906,27 +2888,27 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Decide Apple IAP stance</t>
+          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>physical service argument documented — re-dated 2026-05-03: needs to land before App Store reviewer notes lock.</t>
+          <t>deferred 2026-05-08: native app concern. Web-only F&amp;F launch uses browser Stripe Checkout directly. Needed before App Store/Play submission.</t>
         </is>
       </c>
     </row>
@@ -2963,12 +2945,12 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Stripe Checkout in-app web view with return-URL deep link back to app</t>
+          <t>Magic-link auth working inside app</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>deferred 2026-05-08: native app concern. Web-only F&amp;F launch uses browser Stripe Checkout directly. Needed before App Store/Play submission.</t>
+          <t>email link opens app, session persists — deferred 2026-05-08: native app concern. Web-only magic link works in browser. Needed before App Store/Play submission.</t>
         </is>
       </c>
     </row>
@@ -3000,19 +2982,15 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Magic-link auth working inside app</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>email link opens app, session persists — deferred 2026-05-08: native app concern. Web-only magic link works in browser. Needed before App Store/Play submission.</t>
-        </is>
-      </c>
+          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3025,32 +3003,36 @@
           <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P0 Blocker</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Push notifications APNs + FCM for risk-scan complete + letter ready</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr"/>
+          <t>Médiateur de la consommation</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>comparer MEDICYS vs CM2C (frais d'adhésion, délai de saisine, périmètre B2C numérique), choisir, signer, publier le nom dans CGU §11 + remboursement §6 + mentions légales §médiation — opened 2026-05-07: shortlist réduite à MEDICYS + CM2C, à arbitrer cette semaine. Obligation L612-1 Code de la conso pour activité B2C en ligne, blocage de la mise en service tant que le médiateur n'est pas adhéré.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3063,9 +3045,9 @@
           <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -3080,19 +3062,15 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Médiateur de la consommation</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>comparer MEDICYS vs CM2C (frais d'adhésion, délai de saisine, périmètre B2C numérique), choisir, signer, publier le nom dans CGU §11 + remboursement §6 + mentions légales §médiation — opened 2026-05-07: shortlist réduite à MEDICYS + CM2C, à arbitrer cette semaine. Obligation L612-1 Code de la conso pour activité B2C en ligne, blocage de la mise en service tant que le médiateur n'est pas adhéré.</t>
-        </is>
-      </c>
+          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3127,7 +3105,7 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>French avocat sign-off on legal v1.0, strip DRAFT banners</t>
+          <t>UK solicitor sign-off on TDS/DPS template</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr"/>
@@ -3160,12 +3138,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>UK solicitor sign-off on TDS/DPS template</t>
+          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr"/>
@@ -3198,15 +3176,19 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>dpo@tenu.world mailbox live with auto-acknowledge</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr"/>
+          <t>F&amp;F invite list</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>8 names, email, jurisdiction, case type</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -3236,19 +3218,15 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>F&amp;F invite list</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>8 names, email, jurisdiction, case type</t>
-        </is>
-      </c>
+          <t>512x512 production logo finalised, favicon set, OG image</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3258,7 +3236,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>WEEK 2 (4-7 May + 8 May bank holiday) — submit + pray</t>
+          <t>LAUNCH WEEK (8-11 May)</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -3278,15 +3256,19 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>512x512 production logo finalised, favicon set, OG image</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="inlineStr"/>
+          <t>Create Stripe coupon LAUNCH25</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>100% off, duration=once, 8 redemption limit, code=LAUNCH25. Stripe Dashboard → Coupons → + Create. Must exist before F&amp;F invites go out. Templates at docs/launch/ff-invite-en.md + ff-invite-fr.md reference this code.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3321,12 +3303,12 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Create Stripe coupon LAUNCH25</t>
+          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>100% off, duration=once, 8 redemption limit, code=LAUNCH25. Stripe Dashboard → Coupons → + Create. Must exist before F&amp;F invites go out. Templates at docs/launch/ff-invite-en.md + ff-invite-fr.md reference this code.</t>
+          <t>use docs/launch/ff-invite-en.md or ff-invite-fr.md templates. Confirm LAUNCH25 coupon exists in Stripe first.</t>
         </is>
       </c>
     </row>
@@ -3358,19 +3340,15 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Invite F&amp;F list on 11 May 09:00 Paris</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>use docs/launch/ff-invite-en.md or ff-invite-fr.md templates. Confirm LAUNCH25 coupon exists in Stripe first.</t>
-        </is>
-      </c>
+          <t>Monitor first 24h, triage, log issues, not fix</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3380,7 +3358,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>LAUNCH WEEK (8-11 May)</t>
+          <t>POST-LAUNCH (12-31 May)</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -3390,25 +3368,29 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>P0 Blocker</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Monitor first 24h, triage, log issues, not fix</t>
-        </is>
-      </c>
-      <c r="H44" s="6" t="inlineStr"/>
+          <t>Bug sweep</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>camera upload retry + offline queue hardening — deferred from launch week; acceptable for F&amp;F web, required before native App Store submission.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3433,22 +3415,18 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
+          <t>P2 Post-launch</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Bug sweep</t>
+          <t>Full T-103 suite</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>camera upload retry + offline queue hardening — deferred from launch week; acceptable for F&amp;F web, required before native App Store submission.</t>
+          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3459,12 @@
       <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Full T-103 suite</t>
+          <t>14-day outcome survey cron</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>24 unit + 10 E2E + 5 canaries + 20 evals + OWASP ZAP baseline</t>
+          <t>Brevo trigger + Supabase write-back</t>
         </is>
       </c>
     </row>
@@ -3519,12 +3497,12 @@
       <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>14-day outcome survey cron</t>
+          <t>Additional UI locales</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Brevo trigger + Supabase write-back</t>
+          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
         </is>
       </c>
     </row>
@@ -3551,18 +3529,18 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Additional UI locales</t>
+          <t>i18n audit phase 2</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>ar, zh, hi, ur, ja, es, it, uk, pt, ko staged rollout</t>
+          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
         </is>
       </c>
     </row>
@@ -3589,20 +3567,16 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P2 Post-launch</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr"/>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>i18n audit phase 2</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>inspection/new/page.tsx (715 lines, FR-hardcoded client component): extract all string literals into a `COPY: Record&lt;Locale, InspectionCopy&gt;` dict; room labels (Chambre, Séjour…), step labels, field labels, error messages</t>
-        </is>
-      </c>
+          <t>App Store + Play production updates with post-launch fixes</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -3627,13 +3601,13 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>P2 Post-launch</t>
+          <t>P1 Important</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>App Store + Play production updates with post-launch fixes</t>
+          <t>Add scans.pdf_url + scans.pdf_sha256 columns; migrate from risk_score.pdfUrl jsonb.</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr"/>
@@ -3667,7 +3641,7 @@
       <c r="F51" s="5" t="inlineStr"/>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Add scans.pdf_url + scans.pdf_sha256 columns; migrate from risk_score.pdfUrl jsonb.</t>
+          <t>Extract /api/pdf/build dedicated route with runtime='nodejs' + maxDuration=60; trigger async from /api/ai/scan.</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr"/>
@@ -3701,7 +3675,7 @@
       <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Extract /api/pdf/build dedicated route with runtime='nodejs' + maxDuration=60; trigger async from /api/ai/scan.</t>
+          <t>Switch R2 PDF URLs to signed URLs with renewable TTL (default 30 days).</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr"/>
@@ -3732,13 +3706,21 @@
           <t>P1 Important</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Switch R2 PDF URLs to signed URLs with renewable TTL (default 30 days).</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="inlineStr"/>
+          <t>Wire e2e env</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>create .env.test.local with Supabase service-role key + Stripe test keys so npm run test:e2e actually executes</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -3773,12 +3755,12 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Wire e2e env</t>
+          <t>Lawyer formal sign-off letter (FR avocat + UK solicitor)</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>create .env.test.local with Supabase service-role key + Stripe test keys so npm run test:e2e actually executes</t>
+          <t>agreed in principle 2026-05-08; formal letter required before paid signups open beyond F&amp;F cohort</t>
         </is>
       </c>
     </row>
@@ -3805,69 +3787,27 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>P1 Important</t>
+          <t>P2 Post-launch</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Lawyer formal sign-off letter (FR avocat + UK solicitor)</t>
+          <t>Consider promoting /inspection/new DPA gate from client-side useEffect to middleware for defence-in-depth</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>agreed in principle 2026-05-08; formal letter required before paid signups open beyond F&amp;F cohort</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>T-055</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>POST-LAUNCH (12-31 May)</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>P2 Post-launch</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>Consider promoting /inspection/new DPA gate from client-side useEffect to middleware for defence-in-depth</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
           <t>currently a router.replace() in useEffect (f9aea8a), not server-enforced</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H56"/>
+  <autoFilter ref="A1:H55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3878,7 +3818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5184,12 +5124,12 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
+          <t>Run `npm run build:mobile` on Mac to produce non-empty out/ static export</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>done 2026-05-08: ios/ Capacitor project already present on main with all Info.plist snippet keys merged. Pods installed. BUILD SUCCEEDED on iphonesimulator arm64+x86_64.</t>
+          <t>done 2026-05-08: 15 pages exported, out/ fully populated after CC dynamic-import fix. cap sync clean. App running in iOS simulator.</t>
         </is>
       </c>
     </row>
@@ -5226,12 +5166,12 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
+          <t>Run `npx cap add ios` on Mac, then merge mobile/ios-Info.plist.snippet.xml entries into ios/App/App/Info.plist</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>done 2026-05-08: android/ Capacitor project present on main, AndroidManifest merged, network_security_config.xml in place. Android APK blocked on missing Java runtime — MH must `brew install openjdk@17` (see docs/12 §1).</t>
+          <t>done 2026-05-08: ios/ Capacitor project already present on main with all Info.plist snippet keys merged. Pods installed. BUILD SUCCEEDED on iphonesimulator arm64+x86_64.</t>
         </is>
       </c>
     </row>
@@ -5263,17 +5203,17 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
+          <t>Run `npx cap add android` on Mac, then merge mobile/android-manifest.snippet.xml + drop network_security_config.xml under res/xml/</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>done 2026-05-08: CC ran ./node_modules/.bin/capacitor-assets generate; all Android density buckets + iOS AppIcon + Splash imageset committed (3f7c76c, 70 files).</t>
+          <t>done 2026-05-08: android/ Capacitor project present on main, AndroidManifest merged, network_security_config.xml in place. Android APK blocked on missing Java runtime — MH must `brew install openjdk@17` (see docs/12 §1).</t>
         </is>
       </c>
     </row>
@@ -5310,12 +5250,12 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
+          <t>Run `npx capacitor-assets generate --iconBackgroundColor "#0B1F3A" --iconBackgroundColorDark "#0B1F3A" --splashBackgroundColor "#F4F1EA" --splashBackgroundColorDark "#0B1F3A"` after cap add</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>done 2026-05-08: cap sync verified clean. xattr fix on ios/App/build documented in docs/12 if needed.</t>
+          <t>done 2026-05-08: CC ran ./node_modules/.bin/capacitor-assets generate; all Android density buckets + iOS AppIcon + Splash imageset committed (3f7c76c, 70 files).</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5277,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -5347,17 +5287,17 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Capacitor Camera plugin wired, replace HTML file input</t>
+          <t>Run `npx cap sync` to wire build:mobile output into native projects</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
+          <t>done 2026-05-08: cap sync verified clean. xattr fix on ios/App/build documented in docs/12 if needed.</t>
         </is>
       </c>
     </row>
@@ -5389,17 +5329,17 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+          <t>Capacitor Camera plugin wired, replace HTML file input</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>done 2026-05-08: gate landed via f9aea8a (useEffect client-side redirect on /inspection/new), version pinning via supabase/migrations/005_profile_consent_cache.sql, touchpoints via /auth/accept-terms + /api/checkout waiver + CNIL banner. Merged into main via b54db18.</t>
+          <t>done 2026-04-18: MB-06 reworked src/lib/mobile/camera.ts to match brief spec (resultType=Uri, quality=75, width=1600, correctOrientation=true), added CameraPermissionError typed class, null-on-cancel semantics, CameraButton updated to handle null cleanly without error haptic. tsc exit 0. Commit e3714ea.</t>
         </is>
       </c>
     </row>
@@ -5424,14 +5364,26 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="5" t="inlineStr"/>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>P0 Blocker</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>ECB daily refresh cron, KILLED 2026-05-08. No FX surface: pricing jurisdiction-pinned via TIER_PRICE_CENTS + CURRENCY[jurisdiction] in src/lib/payments/stripe.ts</t>
-        </is>
-      </c>
-      <c r="H37" s="6" t="inlineStr"/>
+          <t>consents table + 4 consent UX touchpoints + timestamp + version pin</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>done 2026-05-08: gate landed via f9aea8a (useEffect client-side redirect on /inspection/new), version pinning via supabase/migrations/005_profile_consent_cache.sql, touchpoints via /auth/accept-terms + /api/checkout waiver + CNIL banner. Merged into main via b54db18.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -5451,29 +5403,17 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>P0 Blocker</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr"/>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
-        </is>
-      </c>
+          <t>ECB daily refresh cron, KILLED 2026-05-08. No FX surface: pricing jurisdiction-pinned via TIER_PRICE_CENTS + CURRENCY[jurisdiction] in src/lib/payments/stripe.ts</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -5493,7 +5433,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -5503,17 +5443,17 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>MB-01</t>
+          <t>Stripe webhook endpoint created in live mode, paste signing secret</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>verify npm run build:mobile produces clean out/ — done 2026-04-18: exit 0, out/ present, no @anthropic-ai/sdk or SUPABASE_SERVICE_ROLE_KEY in client chunks. Known structural issue documented in handover doc: app router pages drop from export because root layout uses async cookies()/headers() — only /404 ships. Two recovery paths offered to MH. Commit cddebcb.</t>
+          <t>done 2026-04-18: webhook endpoint configured in Stripe live mode, signing secret pasted to .env.local + Vercel (per Dr Mubashir)</t>
         </is>
       </c>
     </row>
@@ -5550,12 +5490,12 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>MB-03</t>
+          <t>MB-01</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Info.plist + AndroidManifest snippets with bilingual usage descrip